--- a/models/Leviathan_PE_HOLDCO_Model_IC_VLetalis_Faxon.xlsx
+++ b/models/Leviathan_PE_HOLDCO_Model_IC_VLetalis_Faxon.xlsx
@@ -161,7 +161,7 @@
             <rFont val="Arial"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">Munitions shortage 5: direct bomb-body / warhead-case supplier (BLU-136/B, LPWC IDIQ). FMS 3: indirect pull-through via allied munitions buys. Scores are informational for Faxon (overlay is netted out in F:I).</t>
+          <t xml:space="preserve">Munitions shortage 5: direct bomb-body / warhead-case supplier (BLU-136/B, MOP, NGP, LPWC IDIQ). FMS 4: TLAM export customers (Japan, Australia, Netherlands, UK) plus allied munitions buys. Scores are informational for Faxon (overlay is netted out in F:I).</t>
         </r>
       </text>
     </comment>
@@ -206,7 +206,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1223" uniqueCount="657">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1258" uniqueCount="680">
   <si>
     <t xml:space="preserve">LEVIATHAN FUND — CORE PE VEHICLE</t>
   </si>
@@ -220,7 +220,7 @@
     <t xml:space="preserve">PURPOSE</t>
   </si>
   <si>
-    <t xml:space="preserve">Leviathan's core PE holdco is an $840M vehicle across THREE sub-funds: IQT-mirror deep-tech ($250M), Weapons ($390M), and Consumer/Value ($200M). All three sleeves are modeled bottom-up from individual holdings — IQT-mirror (nine In-Q-Tel names), Weapons (ten physical-layer holdings, incl. The Ellwood Group and Superior &amp; Grand Valley for missile-procurement metal forging, and Faxon Machining for warhead-case machining), Consumer/Value (nine DTC/spending-cycle names) — each across four scenarios, 5/7/10-yr holds, gross-to-net waterfall, and PME, and roll up to a blended holdco return on the Holdco Summary tab. Start there for the top-down view; the sleeve tabs hold the detail.</t>
+    <t xml:space="preserve">Leviathan's core PE holdco is an $840M vehicle across THREE sub-funds: IQT-mirror deep-tech ($250M), Weapons ($390M), and Consumer/Value ($200M). All three sleeves are modeled bottom-up from individual holdings — IQT-mirror (nine In-Q-Tel names), Weapons (ten physical-layer holdings, incl. The Ellwood Group and Superior &amp; Grand Valley for missile-procurement metal forging, and Faxon Machining for NGP / MOP / TLAM / BLU-136 warhead-case and missile machining), Consumer/Value (nine DTC/spending-cycle names) — each across four scenarios, 5/7/10-yr holds, gross-to-net waterfall, and PME, and roll up to a blended holdco return on the Holdco Summary tab. Start there for the top-down view; the sleeve tabs hold the detail.</t>
   </si>
   <si>
     <t xml:space="preserve">Scope: Leviathan runs four vehicles (~$1.5B AUM total); this workbook models only the core PE holdco vehicle ($840M) and its equity targets — not the other three vehicles.</t>
@@ -254,7 +254,7 @@
     <t xml:space="preserve">• Scenario Summary — dashboard across all vehicles, all four cases, and the Expected column.</t>
   </si>
   <si>
-    <t xml:space="preserve">• Faxon Build — bottom-up model for the $9M / ~9.8% Faxon Machining stake ($92M post): supercycle, missile-ramp, penetrator (NGP/MOP) and FMS drivers -&gt; revenue, EBITDA, exit value -&gt; implied CAGR feeding Weapons Sleeve row 21.</t>
+    <t xml:space="preserve">• Faxon Build — program-level model for the $9M / ~9.8% Faxon Machining stake ($92M post): BLU-136/B, GBU-57 MOP, NGP GBU-76/B (with production-award step), Tomahawk (TLAM), penetrator IDIQ and FMS lines tied to supercycle drivers -&gt; revenue, EBITDA, exit value -&gt; implied CAGR feeding Weapons Sleeve row 21.</t>
   </si>
   <si>
     <t xml:space="preserve">RETURN &amp; SHOCK MECHANICS</t>
@@ -1568,7 +1568,7 @@
     <t xml:space="preserve">Faxon Machining</t>
   </si>
   <si>
-    <t xml:space="preserve">PRIVATE — wholly owned sub of Consolidated Boring Inc. (CBI); ~9.8% minority; warhead-case machining (BLU-136/B, LPWC IDIQ); BLU-136 order period ends 30-Sep-26</t>
+    <t xml:space="preserve">PRIVATE — CBI sub; ~9.8% minority; warhead-case &amp; missile machining: BLU-136/B, GBU-57 MOP, NGP GBU-76/B, TLAM, LPWC IDIQ; BLU-136 order period ends 30-Sep-26</t>
   </si>
   <si>
     <t xml:space="preserve">Post-money $92M (user input); contract-derived prob-wtd EV — see Faxon Build</t>
@@ -1586,10 +1586,10 @@
     <t xml:space="preserve">10-YEAR HOLD — GROSS PROCEEDS</t>
   </si>
   <si>
-    <t xml:space="preserve">FAXON MACHINING — BOTTOM-UP STAKE BUILD ($9M @ $92M POST)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weapons-sleeve holding #10. Revenue is driven by the defense supercycle (munitions procurement), the missile production ramp, hard-target penetrator programs (NGP / MOP) and FMS demand. Blue = input; green = link; black = formula. USD $M. Implied 7-yr equity CAGR feeds Weapons Sleeve row 21.</t>
+    <t xml:space="preserve">FAXON MACHINING — PROGRAM-LEVEL STAKE BUILD ($9M @ $92M POST)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weapons-sleeve holding #10. Revenue is built by program — BLU-136/B, GBU-57 MOP, NGP GBU-76/B, Tomahawk (TLAM), penetrator IDIQ, FMS — each tied to a defense-supercycle driver. NGP carries an explicit production-award step. Blue = input; green = link; black = formula. USD $M. 7-yr implied equity CAGR feeds Weapons Sleeve row 21.</t>
   </si>
   <si>
     <t xml:space="preserve">DEAL TERMS &amp; ENTRY</t>
@@ -1628,7 +1628,7 @@
     <t xml:space="preserve">FY26E revenue ($M)</t>
   </si>
   <si>
-    <t xml:space="preserve">Sum of segment build below (contract-derived; aggregator figure of ~$21M judged stale vs $473M BLU-136/B award).</t>
+    <t xml:space="preserve">Sum of program build below (contract-derived; aggregator figure of ~$21M judged stale vs $473M BLU-136/B award).</t>
   </si>
   <si>
     <t xml:space="preserve">FY26E EBITDA margin</t>
@@ -1652,7 +1652,7 @@
     <t xml:space="preserve">FCF conversion (% of EBITDA retained as cash)</t>
   </si>
   <si>
-    <t xml:space="preserve">After tax and growth capex (flowform / deep-hole capacity); retained on balance sheet, no dividends.</t>
+    <t xml:space="preserve">After tax and growth capex (large-case machining / deep-hole capacity for MOP &amp; NGP); retained on balance sheet, no dividends.</t>
   </si>
   <si>
     <t xml:space="preserve">Margin ramp period (yrs)</t>
@@ -1661,7 +1661,7 @@
     <t xml:space="preserve">EBITDA margin moves linearly from FY26E to scenario exit margin over this many years.</t>
   </si>
   <si>
-    <t xml:space="preserve">SUPERCYCLE DRIVERS — ANNUAL END-MARKET GROWTH BY SCENARIO (blue = lever)</t>
+    <t xml:space="preserve">SUPERCYCLE DRIVERS — ANNUAL PROGRAM / END-MARKET GROWTH BY SCENARIO (blue = lever)</t>
   </si>
   <si>
     <t xml:space="preserve">Basis / evidence</t>
@@ -1670,37 +1670,49 @@
     <t xml:space="preserve">1  US munitions procurement (bomb bodies / area-attack)</t>
   </si>
   <si>
-    <t xml:space="preserve">Stockpile replenishment after 2025-26 Iran strikes; USAF buying more bunker busters (Defense News, 13-Feb-26); multiyear munitions buys.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2  Missile production ramp (Tomahawk / SM-6 / PAC-3 / PrSM)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RTX $22.9B 7-yr Tomahawk multiyear to 1,000+/yr (Manufacturing Dive / Armada, Aug-26); tier-2 deep-hole &amp; flowform content.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3  Hard-target penetrators (NGP GBU-76/B, MOP, BLU-137)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NGP full-scale static tests FY26; GBU-76/B production sources-sought 1-Jun-26; $149M LPWC IDIQ (4 awardees incl. Faxon). Small base -&gt; high growth.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4  FMS / allied export demand</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Record FMS (FY24 $117.9B per CRS IF11437, as cited on Defense Supercycle tab); Israel / NATO / Indo-Pacific replenishment.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5  Commercial &amp; other defense industrial</t>
+    <t xml:space="preserve">Stockpile replenishment after 2025-26 Iran strikes; multiyear munitions buys.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2  TLAM production ramp (Tomahawk MYP)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RTX $22.9B 7-yr Tomahawk multiyear to 1,000+/yr (Manufacturing Dive / Armada, Aug-26): ~4x from low-hundreds/yr =&gt; ~20%+/yr over 7 yrs.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3  Other missile production (SM-6 / PAC-3 / PrSM)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Multiyear missile procurement; tier-2 deep-hole &amp; flowform content.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4  GBU-57 MOP replenishment</t>
+  </si>
+  <si>
+    <t xml:space="preserve">USAF buying more bunker busters after Iran nuclear strikes (Defense News, 13-Feb-26); MOP bridges to NGP.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5  NGP GBU-76/B development / LRIP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ARA system design agent (Sep-25, 24-mo); full-scale static tests FY26; GBU-76/B production sources-sought 1-Jun-26. Production step modeled separately below.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6  FMS / allied export demand</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Record FMS (FY24 $117.9B per CRS IF11437); TLAM export buyers (Japan, Australia, Netherlands, UK); Israel / NATO replenishment.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7  Commercial &amp; other defense industrial</t>
   </si>
   <si>
     <t xml:space="preserve">GD / L3Harris / Northrop / Lockheed machining work, vehicle and firearm components.</t>
   </si>
   <si>
-    <t xml:space="preserve">REVENUE SEGMENTS — FY26E BASE &amp; SEGMENT CAGR = DRIVER GROWTH + SHARE GAIN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Segment</t>
+    <t xml:space="preserve">PROGRAM REVENUE — FY26E BASE &amp; PROGRAM CAGR = DRIVER GROWTH + SHARE GAIN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Program / segment</t>
   </si>
   <si>
     <t xml:space="preserve">FY26E rev ($M)</t>
@@ -1733,6 +1745,9 @@
     <t xml:space="preserve">CAGR Shock</t>
   </si>
   <si>
+    <t xml:space="preserve">% FY26E</t>
+  </si>
+  <si>
     <t xml:space="preserve">Basis</t>
   </si>
   <si>
@@ -1742,16 +1757,34 @@
     <t xml:space="preserve">$473M BLU-136/B bomb bodies &amp; containers (Local12); order period ends 30-Sep-26 -&gt; Bear = partial loss on recompete.</t>
   </si>
   <si>
-    <t xml:space="preserve">Large penetrator warhead cases (LPWC IDIQ -&gt; NGP / MOP)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 of 4 awardees on $149M LPWC IDIQ; share gain = winning GBU-76/B case work.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Missile structures / deep-hole &amp; flowform parts (tier-2)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Precision machining for primes; sister co. American Flowform (ex-ATI) adds flowform capability.</t>
+    <t xml:space="preserve">GBU-57 MOP penetrator case machining</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MOP exposure per user (IC, 9/2026). Low-volume / high-value Eglin-steel cases; replenishment buy.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NGP GBU-76/B prototype &amp; dev cases</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NGP exposure per user (IC, 9/2026). Sub-scale / full-scale prototype cases; production phase in NGP step below.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tomahawk (TLAM) components</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TLAM exposure per user (IC, 9/2026); part scope to confirm in diligence (not in public contract data). Tracks Tomahawk ramp.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Other penetrators — LPWC IDIQ (BLU-137 / BLU-109)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 of 4 awardees on $149M large penetrator warhead case IDIQ (Defence Blog, 2026).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Other missile structures / flowform (tier-2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Precision machining for primes; sister co. American Flowform (ex-ATI).</t>
   </si>
   <si>
     <t xml:space="preserve">FMS / allied export pull-through</t>
@@ -1766,7 +1799,31 @@
     <t xml:space="preserve">Legacy contract machining (since 1978).</t>
   </si>
   <si>
-    <t xml:space="preserve">TOTAL FY26E revenue / blended Y1 growth</t>
+    <t xml:space="preserve">TOTAL FY26E revenue / revenue-weighted program CAGR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Memo: NGP + MOP + TLAM share of FY26E revenue</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NGP GBU-76/B PRODUCTION STEP — ADDED ON TOP OF PROGRAM CAGR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">First production year for Faxon (t, years from FY26)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Base: production award FY28, deliveries FY29 after FY26-27 test program. Bear 99 = no Faxon production share.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Faxon full-rate NGP revenue ($M/yr)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Case machining content at full rate; B-21 carriage implies larger quantities than MOP. Shock = wartime surge.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ramp to full rate (yrs)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linear ramp from first production year.</t>
   </si>
   <si>
     <t xml:space="preserve">EXIT ASSUMPTIONS BY SCENARIO</t>
@@ -1775,13 +1832,13 @@
     <t xml:space="preserve">Exit EBITDA margin</t>
   </si>
   <si>
-    <t xml:space="preserve">Operating leverage on volume; Bear = under-absorbed capacity after BLU-136 step-down.</t>
+    <t xml:space="preserve">Operating leverage on volume; MOP/NGP large-case work carries premium pricing. Bear = under-absorbed capacity after BLU-136 step-down.</t>
   </si>
   <si>
     <t xml:space="preserve">Exit EV / EBITDA</t>
   </si>
   <si>
-    <t xml:space="preserve">Base ~ entry multiple; Bull/Shock = scarcity premium (few qualified large-case sources) to a prime / strategic; Bear = generic job-shop.</t>
+    <t xml:space="preserve">Base ~ entry multiple; Bull/Shock = scarcity premium (sole-/few-source MOP, NGP &amp; TLAM content) to a prime / strategic; Bear = generic job-shop.</t>
   </si>
   <si>
     <t xml:space="preserve">PROJECTIONS — YEAR 0 (FY26E) TO YEAR 10, BY SCENARIO</t>
@@ -1826,7 +1883,13 @@
     <t xml:space="preserve">BASE</t>
   </si>
   <si>
-    <t xml:space="preserve">Revenue ($M)</t>
+    <t xml:space="preserve">Program revenue ex-NGP production ($M)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NGP production revenue ($M)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total revenue ($M)</t>
   </si>
   <si>
     <t xml:space="preserve">EBITDA margin</t>
@@ -1868,6 +1931,12 @@
     <t xml:space="preserve">Implied equity CAGR — 10-yr</t>
   </si>
   <si>
+    <t xml:space="preserve">Year-7 revenue ($M)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Year-7 NGP production share of revenue</t>
+  </si>
+  <si>
     <t xml:space="preserve">STAKE RETURNS — $9M CHECK (from Weapons Sleeve, incl. dilution retention 0.92 / 0.88 / 0.82)</t>
   </si>
   <si>
@@ -1910,10 +1979,10 @@
     <t xml:space="preserve">Stake &lt; $10M (user constraint)</t>
   </si>
   <si>
-    <t xml:space="preserve">Segment revenue ties to FY26E revenue</t>
-  </si>
-  <si>
-    <t xml:space="preserve">• Swing factor #1: BLU-136/B follow-on after 30-Sep-26 (53% of FY26E revenue). Swing factor #2: share of NGP GBU-76/B case work under the LPWC IDIQ.</t>
+    <t xml:space="preserve">Program shares sum to 100%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• Swing factors: (1) BLU-136/B follow-on after 30-Sep-26; (2) NGP production-share award timing and size; (3) TLAM content per missile as Tomahawk ramps to 1,000+/yr.</t>
   </si>
   <si>
     <t xml:space="preserve">• Munitions/FMS overlay on the Weapons Sleeve is netted out of Faxon F:I, so the supercycle is counted once — here, in the driver table.</t>
@@ -3233,6 +3302,10 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="165" fontId="14" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="176" fontId="17" fillId="4" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -3270,10 +3343,6 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="176" fontId="14" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="14" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -5901,20 +5970,20 @@
         <v>453</v>
       </c>
       <c r="F21" s="123" t="n">
-        <f aca="false">'Faxon Build'!C$74-$R21*$Q$5</f>
-        <v>0.137363999133814</v>
+        <f aca="false">'Faxon Build'!C$97-$R21*$Q$5</f>
+        <v>0.146702814424438</v>
       </c>
       <c r="G21" s="123" t="n">
-        <f aca="false">'Faxon Build'!D$74-$R21*$Q$6</f>
-        <v>0.302558904469404</v>
+        <f aca="false">'Faxon Build'!D$97-$R21*$Q$6</f>
+        <v>0.294194842742812</v>
       </c>
       <c r="H21" s="123" t="n">
-        <f aca="false">'Faxon Build'!E$74-$R21*$Q$7</f>
-        <v>-0.0952573011585949</v>
+        <f aca="false">'Faxon Build'!E$97-$R21*$Q$7</f>
+        <v>-0.094799895310316</v>
       </c>
       <c r="I21" s="123" t="n">
-        <f aca="false">'Faxon Build'!F$74-$R21*$Q$8</f>
-        <v>0.286377300892187</v>
+        <f aca="false">'Faxon Build'!F$97-$R21*$Q$8</f>
+        <v>0.30205132917649</v>
       </c>
       <c r="J21" s="75" t="s">
         <v>454</v>
@@ -5927,27 +5996,27 @@
         <v>5</v>
       </c>
       <c r="Q21" s="115" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R21" s="116" t="n">
         <f aca="false">AVERAGE(P21:Q21)</f>
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="S21" s="117" t="n">
         <f aca="false">F21+$R21*$Q$5</f>
-        <v>0.157363999133814</v>
+        <v>0.169202814424438</v>
       </c>
       <c r="T21" s="117" t="n">
         <f aca="false">G21+$R21*$Q$6</f>
-        <v>0.334558904469404</v>
+        <v>0.330194842742812</v>
       </c>
       <c r="U21" s="117" t="n">
         <f aca="false">H21+$R21*$Q$7</f>
-        <v>-0.0792573011585949</v>
+        <v>-0.076799895310316</v>
       </c>
       <c r="V21" s="117" t="n">
         <f aca="false">I21+$R21*$Q$8</f>
-        <v>0.310377300892187</v>
+        <v>0.32905132917649</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6582,51 +6651,51 @@
       </c>
       <c r="C35" s="95" t="n">
         <f aca="false">B35*(1+S21)^5*'Weapons Sleeve'!$B$6</f>
-        <v>17.1941290634076</v>
+        <v>18.0917091503932</v>
       </c>
       <c r="D35" s="68" t="n">
         <f aca="false">C35/B35</f>
-        <v>1.91045878482307</v>
+        <v>2.01018990559924</v>
       </c>
       <c r="E35" s="46" t="n">
         <f aca="false">(C35/B35)^(1/5)-1</f>
-        <v>0.138223465090436</v>
+        <v>0.149866489560477</v>
       </c>
       <c r="F35" s="95" t="n">
         <f aca="false">B35*(1+T21)^5*'Weapons Sleeve'!$B$6</f>
-        <v>35.0525060947374</v>
+        <v>34.4831264997212</v>
       </c>
       <c r="G35" s="68" t="n">
         <f aca="false">F35/B35</f>
-        <v>3.89472289941527</v>
+        <v>3.83145849996902</v>
       </c>
       <c r="H35" s="46" t="n">
         <f aca="false">(F35/B35)^(1/5)-1</f>
-        <v>0.312487913698128</v>
+        <v>0.308196025006215</v>
       </c>
       <c r="I35" s="95" t="n">
         <f aca="false">B35*(1+U21)^5*'Weapons Sleeve'!$B$6</f>
-        <v>5.47925806429684</v>
+        <v>5.55276842801235</v>
       </c>
       <c r="J35" s="68" t="n">
         <f aca="false">I35/B35</f>
-        <v>0.608806451588538</v>
+        <v>0.61697426977915</v>
       </c>
       <c r="K35" s="46" t="n">
         <f aca="false">(I35/B35)^(1/5)-1</f>
-        <v>-0.0944845822780659</v>
+        <v>-0.0920678171101024</v>
       </c>
       <c r="L35" s="96" t="n">
         <f aca="false">B35*(1+V21)^5*'Weapons Sleeve'!$B$6</f>
-        <v>31.9898455814136</v>
+        <v>34.3351625174457</v>
       </c>
       <c r="M35" s="69" t="n">
         <f aca="false">L35/B35</f>
-        <v>3.55442728682374</v>
+        <v>3.81501805749396</v>
       </c>
       <c r="N35" s="71" t="n">
         <f aca="false">(L35/B35)^(1/5)-1</f>
-        <v>0.288706226488483</v>
+        <v>0.3070714229149</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6639,51 +6708,51 @@
       </c>
       <c r="C36" s="97" t="n">
         <f aca="false">SUM(C26:C35)</f>
-        <v>936.082583763805</v>
+        <v>936.98016385079</v>
       </c>
       <c r="D36" s="98" t="n">
         <f aca="false">C36/B36</f>
-        <v>2.40021175324052</v>
+        <v>2.40251324064305</v>
       </c>
       <c r="E36" s="99" t="n">
         <f aca="false">(C36/B36)^(1/5)-1</f>
-        <v>0.191378920249819</v>
+        <v>0.191607307808727</v>
       </c>
       <c r="F36" s="97" t="n">
         <f aca="false">SUM(F26:F35)</f>
-        <v>1556.63064100488</v>
+        <v>1556.06126140986</v>
       </c>
       <c r="G36" s="98" t="n">
         <f aca="false">F36/B36</f>
-        <v>3.99136061796123</v>
+        <v>3.9899006702817</v>
       </c>
       <c r="H36" s="99" t="n">
         <f aca="false">(F36/B36)^(1/5)-1</f>
-        <v>0.318937431053323</v>
+        <v>0.31884092955315</v>
       </c>
       <c r="I36" s="97" t="n">
         <f aca="false">SUM(I26:I35)</f>
-        <v>438.346146296154</v>
+        <v>438.419656659869</v>
       </c>
       <c r="J36" s="98" t="n">
         <f aca="false">I36/B36</f>
-        <v>1.12396447768245</v>
+        <v>1.12415296579454</v>
       </c>
       <c r="K36" s="99" t="n">
         <f aca="false">(I36/B36)^(1/5)-1</f>
-        <v>0.0236477051644459</v>
+        <v>0.0236820358725416</v>
       </c>
       <c r="L36" s="100" t="n">
         <f aca="false">SUM(L26:L35)</f>
-        <v>1556.63824127303</v>
+        <v>1558.98355820907</v>
       </c>
       <c r="M36" s="101" t="n">
         <f aca="false">L36/B36</f>
-        <v>3.99138010582829</v>
+        <v>3.9973937389976</v>
       </c>
       <c r="N36" s="102" t="n">
         <f aca="false">(L36/B36)^(1/5)-1</f>
-        <v>0.318938718996437</v>
+        <v>0.319335916840433</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7313,51 +7382,51 @@
       </c>
       <c r="C50" s="95" t="n">
         <f aca="false">B50*(1+S21)^7*'Weapons Sleeve'!$B$7</f>
-        <v>22.0300237504834</v>
+        <v>23.6566991160678</v>
       </c>
       <c r="D50" s="68" t="n">
         <f aca="false">C50/B50</f>
-        <v>2.44778041672038</v>
+        <v>2.62852212400753</v>
       </c>
       <c r="E50" s="46" t="n">
         <f aca="false">(C50/B50)^(1/7)-1</f>
-        <v>0.136420141178412</v>
+        <v>0.148044719231665</v>
       </c>
       <c r="F50" s="95" t="n">
         <f aca="false">B50*(1+T21)^7*'Weapons Sleeve'!$B$7</f>
-        <v>59.7158217457192</v>
+        <v>58.3622463674085</v>
       </c>
       <c r="G50" s="68" t="n">
         <f aca="false">F50/B50</f>
-        <v>6.63509130507991</v>
+        <v>6.48469404082317</v>
       </c>
       <c r="H50" s="46" t="n">
         <f aca="false">(F50/B50)^(1/7)-1</f>
-        <v>0.310408497035577</v>
+        <v>0.30612340812046</v>
       </c>
       <c r="I50" s="95" t="n">
         <f aca="false">B50*(1+U21)^7*'Weapons Sleeve'!$B$7</f>
-        <v>4.44317243177915</v>
+        <v>4.52684992594265</v>
       </c>
       <c r="J50" s="68" t="n">
         <f aca="false">I50/B50</f>
-        <v>0.493685825753239</v>
+        <v>0.502983325104739</v>
       </c>
       <c r="K50" s="46" t="n">
         <f aca="false">(I50/B50)^(1/7)-1</f>
-        <v>-0.0959192193731242</v>
+        <v>-0.0935062831636656</v>
       </c>
       <c r="L50" s="96" t="n">
         <f aca="false">B50*(1+V21)^7*'Weapons Sleeve'!$B$7</f>
-        <v>52.541166580511</v>
+        <v>58.0119495215529</v>
       </c>
       <c r="M50" s="69" t="n">
         <f aca="false">L50/B50</f>
-        <v>5.83790739783455</v>
+        <v>6.44577216906144</v>
       </c>
       <c r="N50" s="71" t="n">
         <f aca="false">(L50/B50)^(1/7)-1</f>
-        <v>0.286664487915104</v>
+        <v>0.305000587772279</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7370,51 +7439,51 @@
       </c>
       <c r="C51" s="97" t="n">
         <f aca="false">SUM(C41:C50)</f>
-        <v>1336.32523759324</v>
+        <v>1337.95191295883</v>
       </c>
       <c r="D51" s="98" t="n">
         <f aca="false">C51/B51</f>
-        <v>3.4264749681878</v>
+        <v>3.43064593066365</v>
       </c>
       <c r="E51" s="99" t="n">
         <f aca="false">(C51/B51)^(1/7)-1</f>
-        <v>0.192358342854872</v>
+        <v>0.192565581630973</v>
       </c>
       <c r="F51" s="97" t="n">
         <f aca="false">SUM(F41:F50)</f>
-        <v>2757.09590712155</v>
+        <v>2755.74233174324</v>
       </c>
       <c r="G51" s="98" t="n">
         <f aca="false">F51/B51</f>
-        <v>7.06947668492704</v>
+        <v>7.06600597882881</v>
       </c>
       <c r="H51" s="99" t="n">
         <f aca="false">(F51/B51)^(1/7)-1</f>
-        <v>0.322333614426532</v>
+        <v>0.322240853523934</v>
       </c>
       <c r="I51" s="97" t="n">
         <f aca="false">SUM(I41:I50)</f>
-        <v>457.170363684206</v>
+        <v>457.254041178369</v>
       </c>
       <c r="J51" s="98" t="n">
         <f aca="false">I51/B51</f>
-        <v>1.17223170175437</v>
+        <v>1.17244625943172</v>
       </c>
       <c r="K51" s="99" t="n">
         <f aca="false">(I51/B51)^(1/7)-1</f>
-        <v>0.0229609748393165</v>
+        <v>0.0229877207603559</v>
       </c>
       <c r="L51" s="100" t="n">
         <f aca="false">SUM(L41:L50)</f>
-        <v>2753.13480508018</v>
+        <v>2758.60558802122</v>
       </c>
       <c r="M51" s="101" t="n">
         <f aca="false">L51/B51</f>
-        <v>7.05932001302611</v>
+        <v>7.07334766159288</v>
       </c>
       <c r="N51" s="102" t="n">
         <f aca="false">(L51/B51)^(1/7)-1</f>
-        <v>0.322062048850876</v>
+        <v>0.322437027249076</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8044,51 +8113,51 @@
       </c>
       <c r="C65" s="95" t="n">
         <f aca="false">B65*(1+S21)^10*'Weapons Sleeve'!$B$8</f>
-        <v>31.824094318982</v>
+        <v>35.2334266416698</v>
       </c>
       <c r="D65" s="68" t="n">
         <f aca="false">C65/B65</f>
-        <v>3.53601047988689</v>
+        <v>3.91482518240776</v>
       </c>
       <c r="E65" s="46" t="n">
         <f aca="false">(C65/B65)^(1/10)-1</f>
-        <v>0.13462240283425</v>
+        <v>0.146228591606159</v>
       </c>
       <c r="F65" s="95" t="n">
         <f aca="false">B65*(1+T21)^10*'Weapons Sleeve'!$B$8</f>
-        <v>132.261619209163</v>
+        <v>127.999702113597</v>
       </c>
       <c r="G65" s="68" t="n">
         <f aca="false">F65/B65</f>
-        <v>14.6957354676847</v>
+        <v>14.222189123733</v>
       </c>
       <c r="H65" s="46" t="n">
         <f aca="false">(F65/B65)^(1/10)-1</f>
-        <v>0.308335521103284</v>
+        <v>0.304057210903513</v>
       </c>
       <c r="I65" s="95" t="n">
         <f aca="false">B65*(1+U21)^10*'Weapons Sleeve'!$B$8</f>
-        <v>3.23176072868525</v>
+        <v>3.31905777625593</v>
       </c>
       <c r="J65" s="68" t="n">
         <f aca="false">I65/B65</f>
-        <v>0.359084525409473</v>
+        <v>0.36878419736177</v>
       </c>
       <c r="K65" s="46" t="n">
         <f aca="false">(I65/B65)^(1/10)-1</f>
-        <v>-0.0973494128611304</v>
+        <v>-0.0949402937504618</v>
       </c>
       <c r="L65" s="96" t="n">
         <f aca="false">B65*(1+V21)^10*'Weapons Sleeve'!$B$8</f>
-        <v>110.158997671787</v>
+        <v>126.903588503139</v>
       </c>
       <c r="M65" s="69" t="n">
         <f aca="false">L65/B65</f>
-        <v>12.2398886301986</v>
+        <v>14.100398722571</v>
       </c>
       <c r="N65" s="71" t="n">
         <f aca="false">(L65/B65)^(1/10)-1</f>
-        <v>0.284629073368863</v>
+        <v>0.302936166779741</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8101,51 +8170,51 @@
       </c>
       <c r="C66" s="97" t="n">
         <f aca="false">SUM(C56:C65)</f>
-        <v>2310.85548875078</v>
+        <v>2314.26482107347</v>
       </c>
       <c r="D66" s="98" t="n">
         <f aca="false">C66/B66</f>
-        <v>5.92527048397637</v>
+        <v>5.93401236172685</v>
       </c>
       <c r="E66" s="99" t="n">
         <f aca="false">(C66/B66)^(1/10)-1</f>
-        <v>0.194732885630137</v>
+        <v>0.194909034234977</v>
       </c>
       <c r="F66" s="97" t="n">
         <f aca="false">SUM(F56:F65)</f>
-        <v>6665.18653960977</v>
+        <v>6660.9246225142</v>
       </c>
       <c r="G66" s="98" t="n">
         <f aca="false">F66/B66</f>
-        <v>17.0902218964353</v>
+        <v>17.0792939038826</v>
       </c>
       <c r="H66" s="99" t="n">
         <f aca="false">(F66/B66)^(1/10)-1</f>
-        <v>0.328234541590603</v>
+        <v>0.328149585903458</v>
       </c>
       <c r="I66" s="97" t="n">
         <f aca="false">SUM(I56:I65)</f>
-        <v>487.957228143275</v>
+        <v>488.044525190846</v>
       </c>
       <c r="J66" s="98" t="n">
         <f aca="false">I66/B66</f>
-        <v>1.25117237985455</v>
+        <v>1.25139621843807</v>
       </c>
       <c r="K66" s="99" t="n">
         <f aca="false">(I66/B66)^(1/10)-1</f>
-        <v>0.0226610488950949</v>
+        <v>0.0226793431427603</v>
       </c>
       <c r="L66" s="100" t="n">
         <f aca="false">SUM(L56:L65)</f>
-        <v>6641.65954753269</v>
+        <v>6658.40413836404</v>
       </c>
       <c r="M66" s="101" t="n">
         <f aca="false">L66/B66</f>
-        <v>17.0298962757248</v>
+        <v>17.0728311240104</v>
       </c>
       <c r="N66" s="102" t="n">
         <f aca="false">(L66/B66)^(1/10)-1</f>
-        <v>0.32776495065176</v>
+        <v>0.3280993203573</v>
       </c>
     </row>
   </sheetData>
@@ -8166,10 +8235,10 @@
     <tabColor rgb="FF7A3B2E"/>
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:M95"/>
+  <dimension ref="A1:M121"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="46"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="48"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="2" style="0" width="12"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="60"/>
   </cols>
@@ -8179,7 +8248,7 @@
         <v>459</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="2" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="124" t="s">
         <v>460</v>
       </c>
@@ -8324,7 +8393,7 @@
         <v>472</v>
       </c>
       <c r="B10" s="132" t="n">
-        <f aca="false">B32</f>
+        <f aca="false">B37</f>
         <v>60</v>
       </c>
       <c r="C10" s="129" t="s">
@@ -8524,16 +8593,16 @@
         <v>488</v>
       </c>
       <c r="B20" s="133" t="n">
-        <v>0.12</v>
+        <v>0.2</v>
       </c>
       <c r="C20" s="133" t="n">
-        <v>0.2</v>
+        <v>0.28</v>
       </c>
       <c r="D20" s="133" t="n">
-        <v>0.03</v>
+        <v>0.06</v>
       </c>
       <c r="E20" s="133" t="n">
-        <v>0.22</v>
+        <v>0.3</v>
       </c>
       <c r="F20" s="129" t="s">
         <v>489</v>
@@ -8551,16 +8620,16 @@
         <v>490</v>
       </c>
       <c r="B21" s="133" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="C21" s="133" t="n">
         <v>0.2</v>
       </c>
-      <c r="C21" s="133" t="n">
-        <v>0.35</v>
-      </c>
       <c r="D21" s="133" t="n">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="E21" s="133" t="n">
-        <v>0.3</v>
+        <v>0.22</v>
       </c>
       <c r="F21" s="129" t="s">
         <v>491</v>
@@ -8578,16 +8647,16 @@
         <v>492</v>
       </c>
       <c r="B22" s="133" t="n">
-        <v>0.1</v>
+        <v>0.15</v>
       </c>
       <c r="C22" s="133" t="n">
-        <v>0.18</v>
+        <v>0.25</v>
       </c>
       <c r="D22" s="133" t="n">
         <v>0</v>
       </c>
       <c r="E22" s="133" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="F22" s="129" t="s">
         <v>493</v>
@@ -8605,16 +8674,16 @@
         <v>494</v>
       </c>
       <c r="B23" s="133" t="n">
-        <v>0.03</v>
+        <v>0.1</v>
       </c>
       <c r="C23" s="133" t="n">
-        <v>0.05</v>
+        <v>0.15</v>
       </c>
       <c r="D23" s="133" t="n">
-        <v>-0.02</v>
+        <v>0</v>
       </c>
       <c r="E23" s="133" t="n">
-        <v>0.01</v>
+        <v>0.15</v>
       </c>
       <c r="F23" s="129" t="s">
         <v>495</v>
@@ -8627,191 +8696,167 @@
       <c r="L23" s="129"/>
       <c r="M23" s="129"/>
     </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="60" t="s">
+    <row r="24" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="127" t="s">
         <v>496</v>
       </c>
-      <c r="B25" s="125"/>
-      <c r="C25" s="125"/>
-      <c r="D25" s="125"/>
-      <c r="E25" s="125"/>
-      <c r="F25" s="125"/>
-      <c r="G25" s="125"/>
-      <c r="H25" s="125"/>
-      <c r="I25" s="125"/>
-      <c r="J25" s="125"/>
-      <c r="K25" s="125"/>
-      <c r="L25" s="125"/>
-      <c r="M25" s="125"/>
-    </row>
-    <row r="26" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="126" t="s">
+      <c r="B24" s="133" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C24" s="133" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="D24" s="133" t="n">
+        <v>0</v>
+      </c>
+      <c r="E24" s="133" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="F24" s="129" t="s">
         <v>497</v>
       </c>
-      <c r="B26" s="126" t="s">
+      <c r="G24" s="129"/>
+      <c r="H24" s="129"/>
+      <c r="I24" s="129"/>
+      <c r="J24" s="129"/>
+      <c r="K24" s="129"/>
+      <c r="L24" s="129"/>
+      <c r="M24" s="129"/>
+    </row>
+    <row r="25" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="127" t="s">
         <v>498</v>
       </c>
-      <c r="C26" s="126" t="s">
+      <c r="B25" s="133" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="C25" s="133" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="D25" s="133" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="E25" s="133" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="F25" s="129" t="s">
         <v>499</v>
       </c>
-      <c r="D26" s="126" t="s">
+      <c r="G25" s="129"/>
+      <c r="H25" s="129"/>
+      <c r="I25" s="129"/>
+      <c r="J25" s="129"/>
+      <c r="K25" s="129"/>
+      <c r="L25" s="129"/>
+      <c r="M25" s="129"/>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="60" t="s">
         <v>500</v>
       </c>
-      <c r="E26" s="126" t="s">
+      <c r="B27" s="125"/>
+      <c r="C27" s="125"/>
+      <c r="D27" s="125"/>
+      <c r="E27" s="125"/>
+      <c r="F27" s="125"/>
+      <c r="G27" s="125"/>
+      <c r="H27" s="125"/>
+      <c r="I27" s="125"/>
+      <c r="J27" s="125"/>
+      <c r="K27" s="125"/>
+      <c r="L27" s="125"/>
+      <c r="M27" s="125"/>
+    </row>
+    <row r="28" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="126" t="s">
         <v>501</v>
       </c>
-      <c r="F26" s="126" t="s">
+      <c r="B28" s="126" t="s">
         <v>502</v>
       </c>
-      <c r="G26" s="126" t="s">
+      <c r="C28" s="126" t="s">
         <v>503</v>
       </c>
-      <c r="H26" s="126" t="s">
+      <c r="D28" s="126" t="s">
         <v>504</v>
       </c>
-      <c r="I26" s="126" t="s">
+      <c r="E28" s="126" t="s">
         <v>505</v>
       </c>
-      <c r="J26" s="126" t="s">
+      <c r="F28" s="126" t="s">
         <v>506</v>
       </c>
-      <c r="K26" s="126" t="s">
+      <c r="G28" s="126" t="s">
         <v>507</v>
       </c>
-      <c r="L26" s="126"/>
-      <c r="M26" s="126" t="s">
+      <c r="H28" s="126" t="s">
         <v>508</v>
       </c>
-    </row>
-    <row r="27" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="127" t="s">
+      <c r="I28" s="126" t="s">
         <v>509</v>
       </c>
-      <c r="B27" s="131" t="n">
-        <v>32</v>
-      </c>
-      <c r="C27" s="135" t="n">
-        <v>1</v>
-      </c>
-      <c r="D27" s="133" t="n">
-        <v>0</v>
-      </c>
-      <c r="E27" s="133" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="F27" s="133" t="n">
-        <v>-0.08</v>
-      </c>
-      <c r="G27" s="133" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="H27" s="130" t="n">
-        <f aca="false">INDEX(B$19:B$23,$C27)+D27</f>
-        <v>0.06</v>
-      </c>
-      <c r="I27" s="130" t="n">
-        <f aca="false">INDEX(C$19:C$23,$C27)+E27</f>
-        <v>0.15</v>
-      </c>
-      <c r="J27" s="130" t="n">
-        <f aca="false">INDEX(D$19:D$23,$C27)+F27</f>
-        <v>-0.1</v>
-      </c>
-      <c r="K27" s="130" t="n">
-        <f aca="false">INDEX(E$19:E$23,$C27)+G27</f>
-        <v>0.17</v>
-      </c>
-      <c r="M27" s="136" t="s">
+      <c r="J28" s="126" t="s">
         <v>510</v>
       </c>
-    </row>
-    <row r="28" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="127" t="s">
+      <c r="K28" s="126" t="s">
         <v>511</v>
       </c>
-      <c r="B28" s="131" t="n">
-        <v>6</v>
-      </c>
-      <c r="C28" s="135" t="n">
-        <v>3</v>
-      </c>
-      <c r="D28" s="133" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="E28" s="133" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="F28" s="133" t="n">
-        <v>-0.02</v>
-      </c>
-      <c r="G28" s="133" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="H28" s="130" t="n">
-        <f aca="false">INDEX(B$19:B$23,$C28)+D28</f>
-        <v>0.25</v>
-      </c>
-      <c r="I28" s="130" t="n">
-        <f aca="false">INDEX(C$19:C$23,$C28)+E28</f>
-        <v>0.43</v>
-      </c>
-      <c r="J28" s="130" t="n">
-        <f aca="false">INDEX(D$19:D$23,$C28)+F28</f>
-        <v>0</v>
-      </c>
-      <c r="K28" s="130" t="n">
-        <f aca="false">INDEX(E$19:E$23,$C28)+G28</f>
-        <v>0.38</v>
-      </c>
-      <c r="M28" s="136" t="s">
+      <c r="L28" s="126" t="s">
         <v>512</v>
+      </c>
+      <c r="M28" s="126" t="s">
+        <v>513</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="127" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="B29" s="131" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="C29" s="135" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D29" s="133" t="n">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="E29" s="133" t="n">
-        <v>0.04</v>
+        <v>0.03</v>
       </c>
       <c r="F29" s="133" t="n">
-        <v>-0.02</v>
+        <v>-0.08</v>
       </c>
       <c r="G29" s="133" t="n">
-        <v>0.04</v>
+        <v>0.03</v>
       </c>
       <c r="H29" s="130" t="n">
-        <f aca="false">INDEX(B$19:B$23,$C29)+D29</f>
-        <v>0.14</v>
+        <f aca="false">INDEX(B$19:B$25,$C29)+D29</f>
+        <v>0.06</v>
       </c>
       <c r="I29" s="130" t="n">
-        <f aca="false">INDEX(C$19:C$23,$C29)+E29</f>
-        <v>0.24</v>
+        <f aca="false">INDEX(C$19:C$25,$C29)+E29</f>
+        <v>0.15</v>
       </c>
       <c r="J29" s="130" t="n">
-        <f aca="false">INDEX(D$19:D$23,$C29)+F29</f>
-        <v>0.01</v>
+        <f aca="false">INDEX(D$19:D$25,$C29)+F29</f>
+        <v>-0.1</v>
       </c>
       <c r="K29" s="130" t="n">
-        <f aca="false">INDEX(E$19:E$23,$C29)+G29</f>
-        <v>0.26</v>
+        <f aca="false">INDEX(E$19:E$25,$C29)+G29</f>
+        <v>0.17</v>
+      </c>
+      <c r="L29" s="130" t="n">
+        <f aca="false">B29/$B$37</f>
+        <v>0.5</v>
       </c>
       <c r="M29" s="136" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="127" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="B30" s="131" t="n">
         <v>4</v>
@@ -8826,37 +8871,41 @@
         <v>0.04</v>
       </c>
       <c r="F30" s="133" t="n">
-        <v>0</v>
+        <v>-0.02</v>
       </c>
       <c r="G30" s="133" t="n">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="H30" s="130" t="n">
-        <f aca="false">INDEX(B$19:B$23,$C30)+D30</f>
-        <v>0.12</v>
+        <f aca="false">INDEX(B$19:B$25,$C30)+D30</f>
+        <v>0.17</v>
       </c>
       <c r="I30" s="130" t="n">
-        <f aca="false">INDEX(C$19:C$23,$C30)+E30</f>
-        <v>0.22</v>
+        <f aca="false">INDEX(C$19:C$25,$C30)+E30</f>
+        <v>0.29</v>
       </c>
       <c r="J30" s="130" t="n">
-        <f aca="false">INDEX(D$19:D$23,$C30)+F30</f>
-        <v>0</v>
+        <f aca="false">INDEX(D$19:D$25,$C30)+F30</f>
+        <v>-0.02</v>
       </c>
       <c r="K30" s="130" t="n">
-        <f aca="false">INDEX(E$19:E$23,$C30)+G30</f>
-        <v>0.23</v>
+        <f aca="false">INDEX(E$19:E$25,$C30)+G30</f>
+        <v>0.34</v>
+      </c>
+      <c r="L30" s="130" t="n">
+        <f aca="false">B30/$B$37</f>
+        <v>0.0666666666666667</v>
       </c>
       <c r="M30" s="136" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="127" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="B31" s="131" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="C31" s="135" t="n">
         <v>5</v>
@@ -8865,985 +8914,837 @@
         <v>0</v>
       </c>
       <c r="E31" s="133" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="F31" s="133" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="G31" s="133" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="H31" s="130" t="n">
+        <f aca="false">INDEX(B$19:B$25,$C31)+D31</f>
+        <v>0.1</v>
+      </c>
+      <c r="I31" s="130" t="n">
+        <f aca="false">INDEX(C$19:C$25,$C31)+E31</f>
+        <v>0.17</v>
+      </c>
+      <c r="J31" s="130" t="n">
+        <f aca="false">INDEX(D$19:D$25,$C31)+F31</f>
+        <v>-0.05</v>
+      </c>
+      <c r="K31" s="130" t="n">
+        <f aca="false">INDEX(E$19:E$25,$C31)+G31</f>
+        <v>0.17</v>
+      </c>
+      <c r="L31" s="130" t="n">
+        <f aca="false">B31/$B$37</f>
+        <v>0.0333333333333333</v>
+      </c>
+      <c r="M31" s="136" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A32" s="127" t="s">
+        <v>520</v>
+      </c>
+      <c r="B32" s="131" t="n">
+        <v>7</v>
+      </c>
+      <c r="C32" s="135" t="n">
+        <v>2</v>
+      </c>
+      <c r="D32" s="133" t="n">
+        <v>0</v>
+      </c>
+      <c r="E32" s="133" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="F32" s="133" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="G32" s="133" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="H32" s="130" t="n">
+        <f aca="false">INDEX(B$19:B$25,$C32)+D32</f>
+        <v>0.2</v>
+      </c>
+      <c r="I32" s="130" t="n">
+        <f aca="false">INDEX(C$19:C$25,$C32)+E32</f>
+        <v>0.3</v>
+      </c>
+      <c r="J32" s="130" t="n">
+        <f aca="false">INDEX(D$19:D$25,$C32)+F32</f>
+        <v>0.04</v>
+      </c>
+      <c r="K32" s="130" t="n">
+        <f aca="false">INDEX(E$19:E$25,$C32)+G32</f>
+        <v>0.32</v>
+      </c>
+      <c r="L32" s="130" t="n">
+        <f aca="false">B32/$B$37</f>
+        <v>0.116666666666667</v>
+      </c>
+      <c r="M32" s="136" t="s">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A33" s="127" t="s">
+        <v>522</v>
+      </c>
+      <c r="B33" s="131" t="n">
+        <v>3</v>
+      </c>
+      <c r="C33" s="135" t="n">
+        <v>1</v>
+      </c>
+      <c r="D33" s="133" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="E33" s="133" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="F33" s="133" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="G33" s="133" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="H33" s="130" t="n">
+        <f aca="false">INDEX(B$19:B$25,$C33)+D33</f>
+        <v>0.11</v>
+      </c>
+      <c r="I33" s="130" t="n">
+        <f aca="false">INDEX(C$19:C$25,$C33)+E33</f>
+        <v>0.2</v>
+      </c>
+      <c r="J33" s="130" t="n">
+        <f aca="false">INDEX(D$19:D$25,$C33)+F33</f>
+        <v>-0.04</v>
+      </c>
+      <c r="K33" s="130" t="n">
+        <f aca="false">INDEX(E$19:E$25,$C33)+G33</f>
+        <v>0.22</v>
+      </c>
+      <c r="L33" s="130" t="n">
+        <f aca="false">B33/$B$37</f>
+        <v>0.05</v>
+      </c>
+      <c r="M33" s="136" t="s">
+        <v>523</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A34" s="127" t="s">
+        <v>524</v>
+      </c>
+      <c r="B34" s="131" t="n">
+        <v>3</v>
+      </c>
+      <c r="C34" s="135" t="n">
+        <v>3</v>
+      </c>
+      <c r="D34" s="133" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="E34" s="133" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="F34" s="133" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="G34" s="133" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="H34" s="130" t="n">
+        <f aca="false">INDEX(B$19:B$25,$C34)+D34</f>
+        <v>0.14</v>
+      </c>
+      <c r="I34" s="130" t="n">
+        <f aca="false">INDEX(C$19:C$25,$C34)+E34</f>
+        <v>0.24</v>
+      </c>
+      <c r="J34" s="130" t="n">
+        <f aca="false">INDEX(D$19:D$25,$C34)+F34</f>
         <v>0.01</v>
       </c>
-      <c r="F31" s="133" t="n">
+      <c r="K34" s="130" t="n">
+        <f aca="false">INDEX(E$19:E$25,$C34)+G34</f>
+        <v>0.26</v>
+      </c>
+      <c r="L34" s="130" t="n">
+        <f aca="false">B34/$B$37</f>
+        <v>0.05</v>
+      </c>
+      <c r="M34" s="136" t="s">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A35" s="127" t="s">
+        <v>526</v>
+      </c>
+      <c r="B35" s="131" t="n">
+        <v>4</v>
+      </c>
+      <c r="C35" s="135" t="n">
+        <v>6</v>
+      </c>
+      <c r="D35" s="133" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="E35" s="133" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="F35" s="133" t="n">
         <v>0</v>
       </c>
-      <c r="G31" s="133" t="n">
+      <c r="G35" s="133" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="H35" s="130" t="n">
+        <f aca="false">INDEX(B$19:B$25,$C35)+D35</f>
+        <v>0.12</v>
+      </c>
+      <c r="I35" s="130" t="n">
+        <f aca="false">INDEX(C$19:C$25,$C35)+E35</f>
+        <v>0.22</v>
+      </c>
+      <c r="J35" s="130" t="n">
+        <f aca="false">INDEX(D$19:D$25,$C35)+F35</f>
         <v>0</v>
       </c>
-      <c r="H31" s="130" t="n">
-        <f aca="false">INDEX(B$19:B$23,$C31)+D31</f>
-        <v>0.03</v>
-      </c>
-      <c r="I31" s="130" t="n">
-        <f aca="false">INDEX(C$19:C$23,$C31)+E31</f>
-        <v>0.06</v>
-      </c>
-      <c r="J31" s="130" t="n">
-        <f aca="false">INDEX(D$19:D$23,$C31)+F31</f>
-        <v>-0.02</v>
-      </c>
-      <c r="K31" s="130" t="n">
-        <f aca="false">INDEX(E$19:E$23,$C31)+G31</f>
-        <v>0.01</v>
-      </c>
-      <c r="M31" s="136" t="s">
-        <v>518</v>
-      </c>
-    </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="137" t="s">
-        <v>519</v>
-      </c>
-      <c r="B32" s="138" t="n">
-        <f aca="false">SUM(B27:B31)</f>
-        <v>60</v>
-      </c>
-      <c r="H32" s="139" t="n">
-        <f aca="false">SUMPRODUCT($B$27:$B$31,H27:H31)/$B$32</f>
-        <v>0.0923333333333333</v>
-      </c>
-      <c r="I32" s="139" t="n">
-        <f aca="false">SUMPRODUCT($B$27:$B$31,I27:I31)/$B$32</f>
-        <v>0.185666666666667</v>
-      </c>
-      <c r="J32" s="139" t="n">
-        <f aca="false">SUMPRODUCT($B$27:$B$31,J27:J31)/$B$32</f>
-        <v>-0.0543333333333333</v>
-      </c>
-      <c r="K32" s="139" t="n">
-        <f aca="false">SUMPRODUCT($B$27:$B$31,K27:K31)/$B$32</f>
-        <v>0.188666666666667</v>
-      </c>
-    </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="60" t="s">
-        <v>520</v>
-      </c>
-      <c r="B34" s="125"/>
-      <c r="C34" s="125"/>
-      <c r="D34" s="125"/>
-      <c r="E34" s="125"/>
-      <c r="F34" s="125"/>
-      <c r="G34" s="125"/>
-      <c r="H34" s="125"/>
-      <c r="I34" s="125"/>
-      <c r="J34" s="125"/>
-      <c r="K34" s="125"/>
-      <c r="L34" s="125"/>
-      <c r="M34" s="125"/>
-    </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A35" s="126" t="s">
-        <v>462</v>
-      </c>
-      <c r="B35" s="126" t="s">
-        <v>36</v>
-      </c>
-      <c r="C35" s="126" t="s">
-        <v>37</v>
-      </c>
-      <c r="D35" s="126" t="s">
-        <v>38</v>
-      </c>
-      <c r="E35" s="126" t="s">
-        <v>39</v>
-      </c>
-      <c r="F35" s="126" t="s">
-        <v>508</v>
-      </c>
-      <c r="G35" s="126"/>
-      <c r="H35" s="126"/>
-      <c r="I35" s="126"/>
-      <c r="J35" s="126"/>
-      <c r="K35" s="126"/>
-      <c r="L35" s="126"/>
-      <c r="M35" s="126"/>
+      <c r="K35" s="130" t="n">
+        <f aca="false">INDEX(E$19:E$25,$C35)+G35</f>
+        <v>0.23</v>
+      </c>
+      <c r="L35" s="130" t="n">
+        <f aca="false">B35/$B$37</f>
+        <v>0.0666666666666667</v>
+      </c>
+      <c r="M35" s="136" t="s">
+        <v>527</v>
+      </c>
     </row>
     <row r="36" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="127" t="s">
-        <v>521</v>
-      </c>
-      <c r="B36" s="133" t="n">
+        <v>528</v>
+      </c>
+      <c r="B36" s="131" t="n">
+        <v>7</v>
+      </c>
+      <c r="C36" s="135" t="n">
+        <v>7</v>
+      </c>
+      <c r="D36" s="133" t="n">
+        <v>0</v>
+      </c>
+      <c r="E36" s="133" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="F36" s="133" t="n">
+        <v>0</v>
+      </c>
+      <c r="G36" s="133" t="n">
+        <v>0</v>
+      </c>
+      <c r="H36" s="130" t="n">
+        <f aca="false">INDEX(B$19:B$25,$C36)+D36</f>
+        <v>0.03</v>
+      </c>
+      <c r="I36" s="130" t="n">
+        <f aca="false">INDEX(C$19:C$25,$C36)+E36</f>
+        <v>0.06</v>
+      </c>
+      <c r="J36" s="130" t="n">
+        <f aca="false">INDEX(D$19:D$25,$C36)+F36</f>
+        <v>-0.02</v>
+      </c>
+      <c r="K36" s="130" t="n">
+        <f aca="false">INDEX(E$19:E$25,$C36)+G36</f>
+        <v>0.01</v>
+      </c>
+      <c r="L36" s="130" t="n">
+        <f aca="false">B36/$B$37</f>
+        <v>0.116666666666667</v>
+      </c>
+      <c r="M36" s="136" t="s">
+        <v>529</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="137" t="s">
+        <v>530</v>
+      </c>
+      <c r="B37" s="138" t="n">
+        <f aca="false">SUM(B29:B36)</f>
+        <v>60</v>
+      </c>
+      <c r="H37" s="139" t="n">
+        <f aca="false">SUMPRODUCT($B$29:$B$36,H29:H36)/$B$37</f>
+        <v>0.092</v>
+      </c>
+      <c r="I37" s="139" t="n">
+        <f aca="false">SUMPRODUCT($B$29:$B$36,I29:I36)/$B$37</f>
+        <v>0.178666666666667</v>
+      </c>
+      <c r="J37" s="139" t="n">
+        <f aca="false">SUMPRODUCT($B$29:$B$36,J29:J36)/$B$37</f>
+        <v>-0.0521666666666667</v>
+      </c>
+      <c r="K37" s="139" t="n">
+        <f aca="false">SUMPRODUCT($B$29:$B$36,K29:K36)/$B$37</f>
+        <v>0.191166666666667</v>
+      </c>
+      <c r="L37" s="139" t="n">
+        <f aca="false">SUM(L29:L36)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="127" t="s">
+        <v>531</v>
+      </c>
+      <c r="L38" s="140" t="n">
+        <f aca="false">SUM(L30:L32)</f>
+        <v>0.216666666666667</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="60" t="s">
+        <v>532</v>
+      </c>
+      <c r="B40" s="125"/>
+      <c r="C40" s="125"/>
+      <c r="D40" s="125"/>
+      <c r="E40" s="125"/>
+      <c r="F40" s="125"/>
+      <c r="G40" s="125"/>
+      <c r="H40" s="125"/>
+      <c r="I40" s="125"/>
+      <c r="J40" s="125"/>
+      <c r="K40" s="125"/>
+      <c r="L40" s="125"/>
+      <c r="M40" s="125"/>
+    </row>
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A41" s="126" t="s">
+        <v>462</v>
+      </c>
+      <c r="B41" s="126" t="s">
+        <v>36</v>
+      </c>
+      <c r="C41" s="126" t="s">
+        <v>37</v>
+      </c>
+      <c r="D41" s="126" t="s">
+        <v>38</v>
+      </c>
+      <c r="E41" s="126" t="s">
+        <v>39</v>
+      </c>
+      <c r="F41" s="126" t="s">
+        <v>513</v>
+      </c>
+      <c r="G41" s="126"/>
+      <c r="H41" s="126"/>
+      <c r="I41" s="126"/>
+      <c r="J41" s="126"/>
+      <c r="K41" s="126"/>
+      <c r="L41" s="126"/>
+      <c r="M41" s="126"/>
+    </row>
+    <row r="42" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A42" s="127" t="s">
+        <v>533</v>
+      </c>
+      <c r="B42" s="135" t="n">
+        <v>3</v>
+      </c>
+      <c r="C42" s="135" t="n">
+        <v>2</v>
+      </c>
+      <c r="D42" s="135" t="n">
+        <v>99</v>
+      </c>
+      <c r="E42" s="135" t="n">
+        <v>2</v>
+      </c>
+      <c r="F42" s="129" t="s">
+        <v>534</v>
+      </c>
+      <c r="G42" s="129"/>
+      <c r="H42" s="129"/>
+      <c r="I42" s="129"/>
+      <c r="J42" s="129"/>
+      <c r="K42" s="129"/>
+      <c r="L42" s="129"/>
+      <c r="M42" s="129"/>
+    </row>
+    <row r="43" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A43" s="127" t="s">
+        <v>535</v>
+      </c>
+      <c r="B43" s="131" t="n">
+        <v>12</v>
+      </c>
+      <c r="C43" s="131" t="n">
+        <v>20</v>
+      </c>
+      <c r="D43" s="131" t="n">
+        <v>0</v>
+      </c>
+      <c r="E43" s="131" t="n">
+        <v>24</v>
+      </c>
+      <c r="F43" s="129" t="s">
+        <v>536</v>
+      </c>
+      <c r="G43" s="129"/>
+      <c r="H43" s="129"/>
+      <c r="I43" s="129"/>
+      <c r="J43" s="129"/>
+      <c r="K43" s="129"/>
+      <c r="L43" s="129"/>
+      <c r="M43" s="129"/>
+    </row>
+    <row r="44" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A44" s="127" t="s">
+        <v>537</v>
+      </c>
+      <c r="B44" s="135" t="n">
+        <v>2</v>
+      </c>
+      <c r="C44" s="135" t="n">
+        <v>2</v>
+      </c>
+      <c r="D44" s="135" t="n">
+        <v>2</v>
+      </c>
+      <c r="E44" s="135" t="n">
+        <v>1</v>
+      </c>
+      <c r="F44" s="129" t="s">
+        <v>538</v>
+      </c>
+      <c r="G44" s="129"/>
+      <c r="H44" s="129"/>
+      <c r="I44" s="129"/>
+      <c r="J44" s="129"/>
+      <c r="K44" s="129"/>
+      <c r="L44" s="129"/>
+      <c r="M44" s="129"/>
+    </row>
+    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A46" s="60" t="s">
+        <v>539</v>
+      </c>
+      <c r="B46" s="125"/>
+      <c r="C46" s="125"/>
+      <c r="D46" s="125"/>
+      <c r="E46" s="125"/>
+      <c r="F46" s="125"/>
+      <c r="G46" s="125"/>
+      <c r="H46" s="125"/>
+      <c r="I46" s="125"/>
+      <c r="J46" s="125"/>
+      <c r="K46" s="125"/>
+      <c r="L46" s="125"/>
+      <c r="M46" s="125"/>
+    </row>
+    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A47" s="126" t="s">
+        <v>462</v>
+      </c>
+      <c r="B47" s="126" t="s">
+        <v>36</v>
+      </c>
+      <c r="C47" s="126" t="s">
+        <v>37</v>
+      </c>
+      <c r="D47" s="126" t="s">
+        <v>38</v>
+      </c>
+      <c r="E47" s="126" t="s">
+        <v>39</v>
+      </c>
+      <c r="F47" s="126" t="s">
+        <v>513</v>
+      </c>
+      <c r="G47" s="126"/>
+      <c r="H47" s="126"/>
+      <c r="I47" s="126"/>
+      <c r="J47" s="126"/>
+      <c r="K47" s="126"/>
+      <c r="L47" s="126"/>
+      <c r="M47" s="126"/>
+    </row>
+    <row r="48" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A48" s="127" t="s">
+        <v>540</v>
+      </c>
+      <c r="B48" s="133" t="n">
         <v>0.16</v>
       </c>
-      <c r="C36" s="133" t="n">
+      <c r="C48" s="133" t="n">
         <v>0.19</v>
       </c>
-      <c r="D36" s="133" t="n">
+      <c r="D48" s="133" t="n">
         <v>0.11</v>
       </c>
-      <c r="E36" s="133" t="n">
+      <c r="E48" s="133" t="n">
         <v>0.18</v>
       </c>
-      <c r="F36" s="129" t="s">
-        <v>522</v>
-      </c>
-      <c r="G36" s="129"/>
-      <c r="H36" s="129"/>
-      <c r="I36" s="129"/>
-      <c r="J36" s="129"/>
-      <c r="K36" s="129"/>
-      <c r="L36" s="129"/>
-      <c r="M36" s="129"/>
-    </row>
-    <row r="37" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A37" s="127" t="s">
-        <v>523</v>
-      </c>
-      <c r="B37" s="140" t="n">
+      <c r="F48" s="129" t="s">
+        <v>541</v>
+      </c>
+      <c r="G48" s="129"/>
+      <c r="H48" s="129"/>
+      <c r="I48" s="129"/>
+      <c r="J48" s="129"/>
+      <c r="K48" s="129"/>
+      <c r="L48" s="129"/>
+      <c r="M48" s="129"/>
+    </row>
+    <row r="49" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A49" s="127" t="s">
+        <v>542</v>
+      </c>
+      <c r="B49" s="141" t="n">
         <v>11</v>
       </c>
-      <c r="C37" s="140" t="n">
+      <c r="C49" s="141" t="n">
         <v>14</v>
       </c>
-      <c r="D37" s="140" t="n">
+      <c r="D49" s="141" t="n">
         <v>7</v>
       </c>
-      <c r="E37" s="140" t="n">
+      <c r="E49" s="141" t="n">
         <v>13</v>
       </c>
-      <c r="F37" s="129" t="s">
-        <v>524</v>
-      </c>
-      <c r="G37" s="129"/>
-      <c r="H37" s="129"/>
-      <c r="I37" s="129"/>
-      <c r="J37" s="129"/>
-      <c r="K37" s="129"/>
-      <c r="L37" s="129"/>
-      <c r="M37" s="129"/>
-    </row>
-    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="60" t="s">
-        <v>525</v>
-      </c>
-      <c r="B39" s="125"/>
-      <c r="C39" s="125"/>
-      <c r="D39" s="125"/>
-      <c r="E39" s="125"/>
-      <c r="F39" s="125"/>
-      <c r="G39" s="125"/>
-      <c r="H39" s="125"/>
-      <c r="I39" s="125"/>
-      <c r="J39" s="125"/>
-      <c r="K39" s="125"/>
-      <c r="L39" s="125"/>
-      <c r="M39" s="125"/>
-    </row>
-    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="126" t="s">
-        <v>526</v>
-      </c>
-      <c r="B40" s="126" t="s">
+      <c r="F49" s="129" t="s">
+        <v>543</v>
+      </c>
+      <c r="G49" s="129"/>
+      <c r="H49" s="129"/>
+      <c r="I49" s="129"/>
+      <c r="J49" s="129"/>
+      <c r="K49" s="129"/>
+      <c r="L49" s="129"/>
+      <c r="M49" s="129"/>
+    </row>
+    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A51" s="60" t="s">
+        <v>544</v>
+      </c>
+      <c r="B51" s="125"/>
+      <c r="C51" s="125"/>
+      <c r="D51" s="125"/>
+      <c r="E51" s="125"/>
+      <c r="F51" s="125"/>
+      <c r="G51" s="125"/>
+      <c r="H51" s="125"/>
+      <c r="I51" s="125"/>
+      <c r="J51" s="125"/>
+      <c r="K51" s="125"/>
+      <c r="L51" s="125"/>
+      <c r="M51" s="125"/>
+    </row>
+    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A52" s="126" t="s">
+        <v>545</v>
+      </c>
+      <c r="B52" s="126" t="s">
         <v>202</v>
       </c>
-      <c r="C40" s="126" t="s">
-        <v>527</v>
-      </c>
-      <c r="D40" s="126" t="s">
-        <v>528</v>
-      </c>
-      <c r="E40" s="126" t="s">
-        <v>529</v>
-      </c>
-      <c r="F40" s="126" t="s">
-        <v>530</v>
-      </c>
-      <c r="G40" s="126" t="s">
-        <v>531</v>
-      </c>
-      <c r="H40" s="126" t="s">
-        <v>532</v>
-      </c>
-      <c r="I40" s="126" t="s">
-        <v>533</v>
-      </c>
-      <c r="J40" s="126" t="s">
-        <v>534</v>
-      </c>
-      <c r="K40" s="126" t="s">
-        <v>535</v>
-      </c>
-      <c r="L40" s="126" t="s">
-        <v>536</v>
-      </c>
-    </row>
-    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="141" t="s">
-        <v>537</v>
-      </c>
-      <c r="B41" s="142" t="n">
+      <c r="C52" s="126" t="s">
+        <v>546</v>
+      </c>
+      <c r="D52" s="126" t="s">
+        <v>547</v>
+      </c>
+      <c r="E52" s="126" t="s">
+        <v>548</v>
+      </c>
+      <c r="F52" s="126" t="s">
+        <v>549</v>
+      </c>
+      <c r="G52" s="126" t="s">
+        <v>550</v>
+      </c>
+      <c r="H52" s="126" t="s">
+        <v>551</v>
+      </c>
+      <c r="I52" s="126" t="s">
+        <v>552</v>
+      </c>
+      <c r="J52" s="126" t="s">
+        <v>553</v>
+      </c>
+      <c r="K52" s="126" t="s">
+        <v>554</v>
+      </c>
+      <c r="L52" s="126" t="s">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A53" s="142" t="s">
+        <v>556</v>
+      </c>
+      <c r="B53" s="143" t="n">
         <v>0</v>
       </c>
-      <c r="C41" s="142" t="n">
+      <c r="C53" s="143" t="n">
         <v>1</v>
       </c>
-      <c r="D41" s="142" t="n">
+      <c r="D53" s="143" t="n">
         <v>2</v>
       </c>
-      <c r="E41" s="142" t="n">
+      <c r="E53" s="143" t="n">
         <v>3</v>
       </c>
-      <c r="F41" s="142" t="n">
+      <c r="F53" s="143" t="n">
         <v>4</v>
       </c>
-      <c r="G41" s="142" t="n">
+      <c r="G53" s="143" t="n">
         <v>5</v>
       </c>
-      <c r="H41" s="142" t="n">
+      <c r="H53" s="143" t="n">
         <v>6</v>
       </c>
-      <c r="I41" s="142" t="n">
+      <c r="I53" s="143" t="n">
         <v>7</v>
       </c>
-      <c r="J41" s="142" t="n">
+      <c r="J53" s="143" t="n">
         <v>8</v>
       </c>
-      <c r="K41" s="142" t="n">
+      <c r="K53" s="143" t="n">
         <v>9</v>
       </c>
-      <c r="L41" s="142" t="n">
+      <c r="L53" s="143" t="n">
         <v>10</v>
       </c>
     </row>
-    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="137" t="s">
-        <v>538</v>
-      </c>
-      <c r="B42" s="143"/>
-      <c r="C42" s="143"/>
-      <c r="D42" s="143"/>
-      <c r="E42" s="143"/>
-      <c r="F42" s="143"/>
-      <c r="G42" s="143"/>
-      <c r="H42" s="143"/>
-      <c r="I42" s="143"/>
-      <c r="J42" s="143"/>
-      <c r="K42" s="143"/>
-      <c r="L42" s="143"/>
-    </row>
-    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="127" t="s">
-        <v>539</v>
-      </c>
-      <c r="B43" s="132" t="n">
-        <f aca="false">SUMPRODUCT($B$27:$B$31,(1+$H$27:$H$31)^B$41)</f>
+    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A54" s="137" t="s">
+        <v>557</v>
+      </c>
+      <c r="B54" s="144"/>
+      <c r="C54" s="144"/>
+      <c r="D54" s="144"/>
+      <c r="E54" s="144"/>
+      <c r="F54" s="144"/>
+      <c r="G54" s="144"/>
+      <c r="H54" s="144"/>
+      <c r="I54" s="144"/>
+      <c r="J54" s="144"/>
+      <c r="K54" s="144"/>
+      <c r="L54" s="144"/>
+    </row>
+    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A55" s="127" t="s">
+        <v>558</v>
+      </c>
+      <c r="B55" s="132" t="n">
+        <f aca="false">SUMPRODUCT($B$29:$B$36,(1+$H$29:$H$36)^B$53)</f>
         <v>60</v>
       </c>
-      <c r="C43" s="132" t="n">
-        <f aca="false">SUMPRODUCT($B$27:$B$31,(1+$H$27:$H$31)^C$41)</f>
-        <v>65.54</v>
-      </c>
-      <c r="D43" s="132" t="n">
-        <f aca="false">SUMPRODUCT($B$27:$B$31,(1+$H$27:$H$31)^D$41)</f>
-        <v>71.831</v>
-      </c>
-      <c r="E43" s="132" t="n">
-        <f aca="false">SUMPRODUCT($B$27:$B$31,(1+$H$27:$H$31)^E$41)</f>
-        <v>79.00823</v>
-      </c>
-      <c r="F43" s="132" t="n">
-        <f aca="false">SUMPRODUCT($B$27:$B$31,(1+$H$27:$H$31)^F$41)</f>
-        <v>87.23544974</v>
-      </c>
-      <c r="G43" s="132" t="n">
-        <f aca="false">SUMPRODUCT($B$27:$B$31,(1+$H$27:$H$31)^G$41)</f>
-        <v>96.7114705094</v>
-      </c>
-      <c r="H43" s="132" t="n">
-        <f aca="false">SUMPRODUCT($B$27:$B$31,(1+$H$27:$H$31)^H$41)</f>
-        <v>107.67823053827</v>
-      </c>
-      <c r="I43" s="132" t="n">
-        <f aca="false">SUMPRODUCT($B$27:$B$31,(1+$H$27:$H$31)^I$41)</f>
-        <v>120.430802245805</v>
-      </c>
-      <c r="J43" s="132" t="n">
-        <f aca="false">SUMPRODUCT($B$27:$B$31,(1+$H$27:$H$31)^J$41)</f>
-        <v>135.329802827174</v>
-      </c>
-      <c r="K43" s="132" t="n">
-        <f aca="false">SUMPRODUCT($B$27:$B$31,(1+$H$27:$H$31)^K$41)</f>
-        <v>152.81679598163</v>
-      </c>
-      <c r="L43" s="132" t="n">
-        <f aca="false">SUMPRODUCT($B$27:$B$31,(1+$H$27:$H$31)^L$41)</f>
-        <v>173.433417775616</v>
-      </c>
-    </row>
-    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="127" t="s">
-        <v>540</v>
-      </c>
-      <c r="B44" s="130" t="n">
-        <f aca="false">$B$11+(B$36-$B$11)*MIN(B$41/$B$15,1)</f>
-        <v>0.14</v>
-      </c>
-      <c r="C44" s="130" t="n">
-        <f aca="false">$B$11+(B$36-$B$11)*MIN(C$41/$B$15,1)</f>
-        <v>0.144</v>
-      </c>
-      <c r="D44" s="130" t="n">
-        <f aca="false">$B$11+(B$36-$B$11)*MIN(D$41/$B$15,1)</f>
-        <v>0.148</v>
-      </c>
-      <c r="E44" s="130" t="n">
-        <f aca="false">$B$11+(B$36-$B$11)*MIN(E$41/$B$15,1)</f>
-        <v>0.152</v>
-      </c>
-      <c r="F44" s="130" t="n">
-        <f aca="false">$B$11+(B$36-$B$11)*MIN(F$41/$B$15,1)</f>
-        <v>0.156</v>
-      </c>
-      <c r="G44" s="130" t="n">
-        <f aca="false">$B$11+(B$36-$B$11)*MIN(G$41/$B$15,1)</f>
-        <v>0.16</v>
-      </c>
-      <c r="H44" s="130" t="n">
-        <f aca="false">$B$11+(B$36-$B$11)*MIN(H$41/$B$15,1)</f>
-        <v>0.16</v>
-      </c>
-      <c r="I44" s="130" t="n">
-        <f aca="false">$B$11+(B$36-$B$11)*MIN(I$41/$B$15,1)</f>
-        <v>0.16</v>
-      </c>
-      <c r="J44" s="130" t="n">
-        <f aca="false">$B$11+(B$36-$B$11)*MIN(J$41/$B$15,1)</f>
-        <v>0.16</v>
-      </c>
-      <c r="K44" s="130" t="n">
-        <f aca="false">$B$11+(B$36-$B$11)*MIN(K$41/$B$15,1)</f>
-        <v>0.16</v>
-      </c>
-      <c r="L44" s="130" t="n">
-        <f aca="false">$B$11+(B$36-$B$11)*MIN(L$41/$B$15,1)</f>
-        <v>0.16</v>
-      </c>
-    </row>
-    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="127" t="s">
-        <v>541</v>
-      </c>
-      <c r="B45" s="132" t="n">
-        <f aca="false">B43*B44</f>
-        <v>8.4</v>
-      </c>
-      <c r="C45" s="132" t="n">
-        <f aca="false">C43*C44</f>
-        <v>9.43776</v>
-      </c>
-      <c r="D45" s="132" t="n">
-        <f aca="false">D43*D44</f>
-        <v>10.630988</v>
-      </c>
-      <c r="E45" s="132" t="n">
-        <f aca="false">E43*E44</f>
-        <v>12.00925096</v>
-      </c>
-      <c r="F45" s="132" t="n">
-        <f aca="false">F43*F44</f>
-        <v>13.60873015944</v>
-      </c>
-      <c r="G45" s="132" t="n">
-        <f aca="false">G43*G44</f>
-        <v>15.473835281504</v>
-      </c>
-      <c r="H45" s="132" t="n">
-        <f aca="false">H43*H44</f>
-        <v>17.2285168861232</v>
-      </c>
-      <c r="I45" s="132" t="n">
-        <f aca="false">I43*I44</f>
-        <v>19.2689283593288</v>
-      </c>
-      <c r="J45" s="132" t="n">
-        <f aca="false">J43*J44</f>
-        <v>21.6527684523478</v>
-      </c>
-      <c r="K45" s="132" t="n">
-        <f aca="false">K43*K44</f>
-        <v>24.4506873570608</v>
-      </c>
-      <c r="L45" s="132" t="n">
-        <f aca="false">L43*L44</f>
-        <v>27.7493468440985</v>
-      </c>
-    </row>
-    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="127" t="s">
-        <v>542</v>
-      </c>
-      <c r="B46" s="132" t="n">
+      <c r="C55" s="132" t="n">
+        <f aca="false">SUMPRODUCT($B$29:$B$36,(1+$H$29:$H$36)^C$53)</f>
+        <v>65.52</v>
+      </c>
+      <c r="D55" s="132" t="n">
+        <f aca="false">SUMPRODUCT($B$29:$B$36,(1+$H$29:$H$36)^D$53)</f>
+        <v>71.7226</v>
+      </c>
+      <c r="E55" s="132" t="n">
+        <f aca="false">SUMPRODUCT($B$29:$B$36,(1+$H$29:$H$36)^E$53)</f>
+        <v>78.711258</v>
+      </c>
+      <c r="F55" s="132" t="n">
+        <f aca="false">SUMPRODUCT($B$29:$B$36,(1+$H$29:$H$36)^F$53)</f>
+        <v>86.60698846</v>
+      </c>
+      <c r="G55" s="132" t="n">
+        <f aca="false">SUMPRODUCT($B$29:$B$36,(1+$H$29:$H$36)^G$53)</f>
+        <v>95.5515229362</v>
+      </c>
+      <c r="H55" s="132" t="n">
+        <f aca="false">SUMPRODUCT($B$29:$B$36,(1+$H$29:$H$36)^H$53)</f>
+        <v>105.711058519486</v>
+      </c>
+      <c r="I55" s="132" t="n">
+        <f aca="false">SUMPRODUCT($B$29:$B$36,(1+$H$29:$H$36)^I$53)</f>
+        <v>117.280705554175</v>
+      </c>
+      <c r="J55" s="132" t="n">
+        <f aca="false">SUMPRODUCT($B$29:$B$36,(1+$H$29:$H$36)^J$53)</f>
+        <v>130.489767529379</v>
+      </c>
+      <c r="K55" s="132" t="n">
+        <f aca="false">SUMPRODUCT($B$29:$B$36,(1+$H$29:$H$36)^K$53)</f>
+        <v>145.608011600067</v>
+      </c>
+      <c r="L55" s="132" t="n">
+        <f aca="false">SUMPRODUCT($B$29:$B$36,(1+$H$29:$H$36)^L$53)</f>
+        <v>162.953118719613</v>
+      </c>
+    </row>
+    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A56" s="127" t="s">
+        <v>559</v>
+      </c>
+      <c r="B56" s="132" t="n">
+        <f aca="false">B$43*MIN(MAX(B$53-B$42+1,0)/B$44,1)</f>
         <v>0</v>
       </c>
-      <c r="C46" s="132" t="n">
-        <f aca="false">B46+C45*$B$14</f>
-        <v>4.246992</v>
-      </c>
-      <c r="D46" s="132" t="n">
-        <f aca="false">C46+D45*$B$14</f>
-        <v>9.0309366</v>
-      </c>
-      <c r="E46" s="132" t="n">
-        <f aca="false">D46+E45*$B$14</f>
-        <v>14.435099532</v>
-      </c>
-      <c r="F46" s="132" t="n">
-        <f aca="false">E46+F45*$B$14</f>
-        <v>20.559028103748</v>
-      </c>
-      <c r="G46" s="132" t="n">
-        <f aca="false">F46+G45*$B$14</f>
-        <v>27.5222539804248</v>
-      </c>
-      <c r="H46" s="132" t="n">
-        <f aca="false">G46+H45*$B$14</f>
-        <v>35.2750865791802</v>
-      </c>
-      <c r="I46" s="132" t="n">
-        <f aca="false">H46+I45*$B$14</f>
-        <v>43.9461043408782</v>
-      </c>
-      <c r="J46" s="132" t="n">
-        <f aca="false">I46+J45*$B$14</f>
-        <v>53.6898501444347</v>
-      </c>
-      <c r="K46" s="132" t="n">
-        <f aca="false">J46+K45*$B$14</f>
-        <v>64.6926594551121</v>
-      </c>
-      <c r="L46" s="132" t="n">
-        <f aca="false">K46+L45*$B$14</f>
-        <v>77.1798655349564</v>
-      </c>
-    </row>
-    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="127" t="s">
-        <v>543</v>
-      </c>
-      <c r="B47" s="132" t="n">
-        <f aca="false">$B$6+$B$9</f>
-        <v>92</v>
-      </c>
-      <c r="C47" s="132" t="n">
-        <f aca="false">C45*B$37</f>
-        <v>103.81536</v>
-      </c>
-      <c r="D47" s="132" t="n">
-        <f aca="false">D45*B$37</f>
-        <v>116.940868</v>
-      </c>
-      <c r="E47" s="132" t="n">
-        <f aca="false">E45*B$37</f>
-        <v>132.10176056</v>
-      </c>
-      <c r="F47" s="132" t="n">
-        <f aca="false">F45*B$37</f>
-        <v>149.69603175384</v>
-      </c>
-      <c r="G47" s="132" t="n">
-        <f aca="false">G45*B$37</f>
-        <v>170.212188096544</v>
-      </c>
-      <c r="H47" s="132" t="n">
-        <f aca="false">H45*B$37</f>
-        <v>189.513685747355</v>
-      </c>
-      <c r="I47" s="132" t="n">
-        <f aca="false">I45*B$37</f>
-        <v>211.958211952616</v>
-      </c>
-      <c r="J47" s="132" t="n">
-        <f aca="false">J45*B$37</f>
-        <v>238.180452975826</v>
-      </c>
-      <c r="K47" s="132" t="n">
-        <f aca="false">K45*B$37</f>
-        <v>268.957560927669</v>
-      </c>
-      <c r="L47" s="132" t="n">
-        <f aca="false">L45*B$37</f>
-        <v>305.242815285083</v>
-      </c>
-    </row>
-    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="144" t="s">
-        <v>544</v>
-      </c>
-      <c r="B48" s="145" t="n">
-        <f aca="false">B47+B46-$B$9</f>
-        <v>92</v>
-      </c>
-      <c r="C48" s="145" t="n">
-        <f aca="false">C47+C46-$B$9</f>
-        <v>108.062352</v>
-      </c>
-      <c r="D48" s="145" t="n">
-        <f aca="false">D47+D46-$B$9</f>
-        <v>125.9718046</v>
-      </c>
-      <c r="E48" s="145" t="n">
-        <f aca="false">E47+E46-$B$9</f>
-        <v>146.536860092</v>
-      </c>
-      <c r="F48" s="145" t="n">
-        <f aca="false">F47+F46-$B$9</f>
-        <v>170.255059857588</v>
-      </c>
-      <c r="G48" s="145" t="n">
-        <f aca="false">G47+G46-$B$9</f>
-        <v>197.734442076969</v>
-      </c>
-      <c r="H48" s="145" t="n">
-        <f aca="false">H47+H46-$B$9</f>
-        <v>224.788772326535</v>
-      </c>
-      <c r="I48" s="145" t="n">
-        <f aca="false">I47+I46-$B$9</f>
-        <v>255.904316293494</v>
-      </c>
-      <c r="J48" s="145" t="n">
-        <f aca="false">J47+J46-$B$9</f>
-        <v>291.870303120261</v>
-      </c>
-      <c r="K48" s="145" t="n">
-        <f aca="false">K47+K46-$B$9</f>
-        <v>333.650220382781</v>
-      </c>
-      <c r="L48" s="145" t="n">
-        <f aca="false">L47+L46-$B$9</f>
-        <v>382.42268082004</v>
-      </c>
-    </row>
-    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="137" t="s">
-        <v>545</v>
-      </c>
-      <c r="B49" s="143"/>
-      <c r="C49" s="143"/>
-      <c r="D49" s="143"/>
-      <c r="E49" s="143"/>
-      <c r="F49" s="143"/>
-      <c r="G49" s="143"/>
-      <c r="H49" s="143"/>
-      <c r="I49" s="143"/>
-      <c r="J49" s="143"/>
-      <c r="K49" s="143"/>
-      <c r="L49" s="143"/>
-    </row>
-    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="127" t="s">
-        <v>539</v>
-      </c>
-      <c r="B50" s="132" t="n">
-        <f aca="false">SUMPRODUCT($B$27:$B$31,(1+$I$27:$I$31)^B$41)</f>
+      <c r="C56" s="132" t="n">
+        <f aca="false">B$43*MIN(MAX(C$53-B$42+1,0)/B$44,1)</f>
+        <v>0</v>
+      </c>
+      <c r="D56" s="132" t="n">
+        <f aca="false">B$43*MIN(MAX(D$53-B$42+1,0)/B$44,1)</f>
+        <v>0</v>
+      </c>
+      <c r="E56" s="132" t="n">
+        <f aca="false">B$43*MIN(MAX(E$53-B$42+1,0)/B$44,1)</f>
+        <v>6</v>
+      </c>
+      <c r="F56" s="132" t="n">
+        <f aca="false">B$43*MIN(MAX(F$53-B$42+1,0)/B$44,1)</f>
+        <v>12</v>
+      </c>
+      <c r="G56" s="132" t="n">
+        <f aca="false">B$43*MIN(MAX(G$53-B$42+1,0)/B$44,1)</f>
+        <v>12</v>
+      </c>
+      <c r="H56" s="132" t="n">
+        <f aca="false">B$43*MIN(MAX(H$53-B$42+1,0)/B$44,1)</f>
+        <v>12</v>
+      </c>
+      <c r="I56" s="132" t="n">
+        <f aca="false">B$43*MIN(MAX(I$53-B$42+1,0)/B$44,1)</f>
+        <v>12</v>
+      </c>
+      <c r="J56" s="132" t="n">
+        <f aca="false">B$43*MIN(MAX(J$53-B$42+1,0)/B$44,1)</f>
+        <v>12</v>
+      </c>
+      <c r="K56" s="132" t="n">
+        <f aca="false">B$43*MIN(MAX(K$53-B$42+1,0)/B$44,1)</f>
+        <v>12</v>
+      </c>
+      <c r="L56" s="132" t="n">
+        <f aca="false">B$43*MIN(MAX(L$53-B$42+1,0)/B$44,1)</f>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A57" s="145" t="s">
+        <v>560</v>
+      </c>
+      <c r="B57" s="146" t="n">
+        <f aca="false">B55+B56</f>
         <v>60</v>
       </c>
-      <c r="C50" s="132" t="n">
-        <f aca="false">SUMPRODUCT($B$27:$B$31,(1+$I$27:$I$31)^C$41)</f>
-        <v>71.14</v>
-      </c>
-      <c r="D50" s="132" t="n">
-        <f aca="false">SUMPRODUCT($B$27:$B$31,(1+$I$27:$I$31)^D$41)</f>
-        <v>84.9078</v>
-      </c>
-      <c r="E50" s="132" t="n">
-        <f aca="false">SUMPRODUCT($B$27:$B$31,(1+$I$27:$I$31)^E$41)</f>
-        <v>102.071002</v>
-      </c>
-      <c r="F50" s="132" t="n">
-        <f aca="false">SUMPRODUCT($B$27:$B$31,(1+$I$27:$I$31)^F$41)</f>
-        <v>123.66118758</v>
-      </c>
-      <c r="G50" s="132" t="n">
-        <f aca="false">SUMPRODUCT($B$27:$B$31,(1+$I$27:$I$31)^G$41)</f>
-        <v>151.0745832634</v>
-      </c>
-      <c r="H50" s="132" t="n">
-        <f aca="false">SUMPRODUCT($B$27:$B$31,(1+$I$27:$I$31)^H$41)</f>
-        <v>186.213383481318</v>
-      </c>
-      <c r="I50" s="132" t="n">
-        <f aca="false">SUMPRODUCT($B$27:$B$31,(1+$I$27:$I$31)^I$41)</f>
-        <v>231.684653373345</v>
-      </c>
-      <c r="J50" s="132" t="n">
-        <f aca="false">SUMPRODUCT($B$27:$B$31,(1+$I$27:$I$31)^J$41)</f>
-        <v>291.080886808682</v>
-      </c>
-      <c r="K50" s="132" t="n">
-        <f aca="false">SUMPRODUCT($B$27:$B$31,(1+$I$27:$I$31)^K$41)</f>
-        <v>369.37649619311</v>
-      </c>
-      <c r="L50" s="132" t="n">
-        <f aca="false">SUMPRODUCT($B$27:$B$31,(1+$I$27:$I$31)^L$41)</f>
-        <v>473.489064118086</v>
-      </c>
-    </row>
-    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="127" t="s">
-        <v>540</v>
-      </c>
-      <c r="B51" s="130" t="n">
-        <f aca="false">$B$11+(C$36-$B$11)*MIN(B$41/$B$15,1)</f>
-        <v>0.14</v>
-      </c>
-      <c r="C51" s="130" t="n">
-        <f aca="false">$B$11+(C$36-$B$11)*MIN(C$41/$B$15,1)</f>
-        <v>0.15</v>
-      </c>
-      <c r="D51" s="130" t="n">
-        <f aca="false">$B$11+(C$36-$B$11)*MIN(D$41/$B$15,1)</f>
-        <v>0.16</v>
-      </c>
-      <c r="E51" s="130" t="n">
-        <f aca="false">$B$11+(C$36-$B$11)*MIN(E$41/$B$15,1)</f>
-        <v>0.17</v>
-      </c>
-      <c r="F51" s="130" t="n">
-        <f aca="false">$B$11+(C$36-$B$11)*MIN(F$41/$B$15,1)</f>
-        <v>0.18</v>
-      </c>
-      <c r="G51" s="130" t="n">
-        <f aca="false">$B$11+(C$36-$B$11)*MIN(G$41/$B$15,1)</f>
-        <v>0.19</v>
-      </c>
-      <c r="H51" s="130" t="n">
-        <f aca="false">$B$11+(C$36-$B$11)*MIN(H$41/$B$15,1)</f>
-        <v>0.19</v>
-      </c>
-      <c r="I51" s="130" t="n">
-        <f aca="false">$B$11+(C$36-$B$11)*MIN(I$41/$B$15,1)</f>
-        <v>0.19</v>
-      </c>
-      <c r="J51" s="130" t="n">
-        <f aca="false">$B$11+(C$36-$B$11)*MIN(J$41/$B$15,1)</f>
-        <v>0.19</v>
-      </c>
-      <c r="K51" s="130" t="n">
-        <f aca="false">$B$11+(C$36-$B$11)*MIN(K$41/$B$15,1)</f>
-        <v>0.19</v>
-      </c>
-      <c r="L51" s="130" t="n">
-        <f aca="false">$B$11+(C$36-$B$11)*MIN(L$41/$B$15,1)</f>
-        <v>0.19</v>
-      </c>
-    </row>
-    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="127" t="s">
-        <v>541</v>
-      </c>
-      <c r="B52" s="132" t="n">
-        <f aca="false">B50*B51</f>
-        <v>8.4</v>
-      </c>
-      <c r="C52" s="132" t="n">
-        <f aca="false">C50*C51</f>
-        <v>10.671</v>
-      </c>
-      <c r="D52" s="132" t="n">
-        <f aca="false">D50*D51</f>
-        <v>13.585248</v>
-      </c>
-      <c r="E52" s="132" t="n">
-        <f aca="false">E50*E51</f>
-        <v>17.35207034</v>
-      </c>
-      <c r="F52" s="132" t="n">
-        <f aca="false">F50*F51</f>
-        <v>22.2590137644</v>
-      </c>
-      <c r="G52" s="132" t="n">
-        <f aca="false">G50*G51</f>
-        <v>28.704170820046</v>
-      </c>
-      <c r="H52" s="132" t="n">
-        <f aca="false">H50*H51</f>
-        <v>35.3805428614504</v>
-      </c>
-      <c r="I52" s="132" t="n">
-        <f aca="false">I50*I51</f>
-        <v>44.0200841409356</v>
-      </c>
-      <c r="J52" s="132" t="n">
-        <f aca="false">J50*J51</f>
-        <v>55.3053684936495</v>
-      </c>
-      <c r="K52" s="132" t="n">
-        <f aca="false">K50*K51</f>
-        <v>70.181534276691</v>
-      </c>
-      <c r="L52" s="132" t="n">
-        <f aca="false">L50*L51</f>
-        <v>89.9629221824364</v>
-      </c>
-    </row>
-    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="127" t="s">
-        <v>542</v>
-      </c>
-      <c r="B53" s="132" t="n">
-        <v>0</v>
-      </c>
-      <c r="C53" s="132" t="n">
-        <f aca="false">B53+C52*$B$14</f>
-        <v>4.80195</v>
-      </c>
-      <c r="D53" s="132" t="n">
-        <f aca="false">C53+D52*$B$14</f>
-        <v>10.9153116</v>
-      </c>
-      <c r="E53" s="132" t="n">
-        <f aca="false">D53+E52*$B$14</f>
-        <v>18.723743253</v>
-      </c>
-      <c r="F53" s="132" t="n">
-        <f aca="false">E53+F52*$B$14</f>
-        <v>28.74029944698</v>
-      </c>
-      <c r="G53" s="132" t="n">
-        <f aca="false">F53+G52*$B$14</f>
-        <v>41.6571763160007</v>
-      </c>
-      <c r="H53" s="132" t="n">
-        <f aca="false">G53+H52*$B$14</f>
-        <v>57.5784206036534</v>
-      </c>
-      <c r="I53" s="132" t="n">
-        <f aca="false">H53+I52*$B$14</f>
-        <v>77.3874584670744</v>
-      </c>
-      <c r="J53" s="132" t="n">
-        <f aca="false">I53+J52*$B$14</f>
-        <v>102.274874289217</v>
-      </c>
-      <c r="K53" s="132" t="n">
-        <f aca="false">J53+K52*$B$14</f>
-        <v>133.856564713728</v>
-      </c>
-      <c r="L53" s="132" t="n">
-        <f aca="false">K53+L52*$B$14</f>
-        <v>174.339879695824</v>
-      </c>
-    </row>
-    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="127" t="s">
-        <v>543</v>
-      </c>
-      <c r="B54" s="132" t="n">
-        <f aca="false">$B$6+$B$9</f>
-        <v>92</v>
-      </c>
-      <c r="C54" s="132" t="n">
-        <f aca="false">C52*C$37</f>
-        <v>149.394</v>
-      </c>
-      <c r="D54" s="132" t="n">
-        <f aca="false">D52*C$37</f>
-        <v>190.193472</v>
-      </c>
-      <c r="E54" s="132" t="n">
-        <f aca="false">E52*C$37</f>
-        <v>242.92898476</v>
-      </c>
-      <c r="F54" s="132" t="n">
-        <f aca="false">F52*C$37</f>
-        <v>311.6261927016</v>
-      </c>
-      <c r="G54" s="132" t="n">
-        <f aca="false">G52*C$37</f>
-        <v>401.858391480644</v>
-      </c>
-      <c r="H54" s="132" t="n">
-        <f aca="false">H52*C$37</f>
-        <v>495.327600060306</v>
-      </c>
-      <c r="I54" s="132" t="n">
-        <f aca="false">I52*C$37</f>
-        <v>616.281177973098</v>
-      </c>
-      <c r="J54" s="132" t="n">
-        <f aca="false">J52*C$37</f>
-        <v>774.275158911093</v>
-      </c>
-      <c r="K54" s="132" t="n">
-        <f aca="false">K52*C$37</f>
-        <v>982.541479873674</v>
-      </c>
-      <c r="L54" s="132" t="n">
-        <f aca="false">L52*C$37</f>
-        <v>1259.48091055411</v>
-      </c>
-    </row>
-    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="144" t="s">
-        <v>544</v>
-      </c>
-      <c r="B55" s="145" t="n">
-        <f aca="false">B54+B53-$B$9</f>
-        <v>92</v>
-      </c>
-      <c r="C55" s="145" t="n">
-        <f aca="false">C54+C53-$B$9</f>
-        <v>154.19595</v>
-      </c>
-      <c r="D55" s="145" t="n">
-        <f aca="false">D54+D53-$B$9</f>
-        <v>201.1087836</v>
-      </c>
-      <c r="E55" s="145" t="n">
-        <f aca="false">E54+E53-$B$9</f>
-        <v>261.652728013</v>
-      </c>
-      <c r="F55" s="145" t="n">
-        <f aca="false">F54+F53-$B$9</f>
-        <v>340.36649214858</v>
-      </c>
-      <c r="G55" s="145" t="n">
-        <f aca="false">G54+G53-$B$9</f>
-        <v>443.515567796645</v>
-      </c>
-      <c r="H55" s="145" t="n">
-        <f aca="false">H54+H53-$B$9</f>
-        <v>552.906020663959</v>
-      </c>
-      <c r="I55" s="145" t="n">
-        <f aca="false">I54+I53-$B$9</f>
-        <v>693.668636440173</v>
-      </c>
-      <c r="J55" s="145" t="n">
-        <f aca="false">J54+J53-$B$9</f>
-        <v>876.550033200309</v>
-      </c>
-      <c r="K55" s="145" t="n">
-        <f aca="false">K54+K53-$B$9</f>
-        <v>1116.3980445874</v>
-      </c>
-      <c r="L55" s="145" t="n">
-        <f aca="false">L54+L53-$B$9</f>
-        <v>1433.82079024993</v>
-      </c>
-    </row>
-    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="137" t="s">
-        <v>546</v>
-      </c>
-      <c r="B56" s="143"/>
-      <c r="C56" s="143"/>
-      <c r="D56" s="143"/>
-      <c r="E56" s="143"/>
-      <c r="F56" s="143"/>
-      <c r="G56" s="143"/>
-      <c r="H56" s="143"/>
-      <c r="I56" s="143"/>
-      <c r="J56" s="143"/>
-      <c r="K56" s="143"/>
-      <c r="L56" s="143"/>
-    </row>
-    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="127" t="s">
-        <v>539</v>
-      </c>
-      <c r="B57" s="132" t="n">
-        <f aca="false">SUMPRODUCT($B$27:$B$31,(1+$J$27:$J$31)^B$41)</f>
-        <v>60</v>
-      </c>
-      <c r="C57" s="132" t="n">
-        <f aca="false">SUMPRODUCT($B$27:$B$31,(1+$J$27:$J$31)^C$41)</f>
-        <v>56.74</v>
-      </c>
-      <c r="D57" s="132" t="n">
-        <f aca="false">SUMPRODUCT($B$27:$B$31,(1+$J$27:$J$31)^D$41)</f>
-        <v>53.8042</v>
-      </c>
-      <c r="E57" s="132" t="n">
-        <f aca="false">SUMPRODUCT($B$27:$B$31,(1+$J$27:$J$31)^E$41)</f>
-        <v>51.160546</v>
-      </c>
-      <c r="F57" s="132" t="n">
-        <f aca="false">SUMPRODUCT($B$27:$B$31,(1+$J$27:$J$31)^F$41)</f>
-        <v>48.78018538</v>
-      </c>
-      <c r="G57" s="132" t="n">
-        <f aca="false">SUMPRODUCT($B$27:$B$31,(1+$J$27:$J$31)^G$41)</f>
-        <v>46.6371468754</v>
-      </c>
-      <c r="H57" s="132" t="n">
-        <f aca="false">SUMPRODUCT($B$27:$B$31,(1+$J$27:$J$31)^H$41)</f>
-        <v>44.708052552922</v>
-      </c>
-      <c r="I57" s="132" t="n">
-        <f aca="false">SUMPRODUCT($B$27:$B$31,(1+$J$27:$J$31)^I$41)</f>
-        <v>42.9718585870439</v>
-      </c>
-      <c r="J57" s="132" t="n">
-        <f aca="false">SUMPRODUCT($B$27:$B$31,(1+$J$27:$J$31)^J$41)</f>
-        <v>41.4096219569351</v>
-      </c>
-      <c r="K57" s="132" t="n">
-        <f aca="false">SUMPRODUCT($B$27:$B$31,(1+$J$27:$J$31)^K$41)</f>
-        <v>40.0042904718848</v>
-      </c>
-      <c r="L57" s="132" t="n">
-        <f aca="false">SUMPRODUCT($B$27:$B$31,(1+$J$27:$J$31)^L$41)</f>
-        <v>38.7405137924124</v>
+      <c r="C57" s="146" t="n">
+        <f aca="false">C55+C56</f>
+        <v>65.52</v>
+      </c>
+      <c r="D57" s="146" t="n">
+        <f aca="false">D55+D56</f>
+        <v>71.7226</v>
+      </c>
+      <c r="E57" s="146" t="n">
+        <f aca="false">E55+E56</f>
+        <v>84.711258</v>
+      </c>
+      <c r="F57" s="146" t="n">
+        <f aca="false">F55+F56</f>
+        <v>98.60698846</v>
+      </c>
+      <c r="G57" s="146" t="n">
+        <f aca="false">G55+G56</f>
+        <v>107.5515229362</v>
+      </c>
+      <c r="H57" s="146" t="n">
+        <f aca="false">H55+H56</f>
+        <v>117.711058519486</v>
+      </c>
+      <c r="I57" s="146" t="n">
+        <f aca="false">I55+I56</f>
+        <v>129.280705554175</v>
+      </c>
+      <c r="J57" s="146" t="n">
+        <f aca="false">J55+J56</f>
+        <v>142.489767529379</v>
+      </c>
+      <c r="K57" s="146" t="n">
+        <f aca="false">K55+K56</f>
+        <v>157.608011600067</v>
+      </c>
+      <c r="L57" s="146" t="n">
+        <f aca="false">L55+L56</f>
+        <v>174.953118719613</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="127" t="s">
-        <v>540</v>
+        <v>561</v>
       </c>
       <c r="B58" s="130" t="n">
-        <f aca="false">$B$11+(D$36-$B$11)*MIN(B$41/$B$15,1)</f>
+        <f aca="false">$B$11+(B$48-$B$11)*MIN(B$53/$B$15,1)</f>
         <v>0.14</v>
       </c>
       <c r="C58" s="130" t="n">
-        <f aca="false">$B$11+(D$36-$B$11)*MIN(C$41/$B$15,1)</f>
-        <v>0.134</v>
+        <f aca="false">$B$11+(B$48-$B$11)*MIN(C$53/$B$15,1)</f>
+        <v>0.144</v>
       </c>
       <c r="D58" s="130" t="n">
-        <f aca="false">$B$11+(D$36-$B$11)*MIN(D$41/$B$15,1)</f>
-        <v>0.128</v>
+        <f aca="false">$B$11+(B$48-$B$11)*MIN(D$53/$B$15,1)</f>
+        <v>0.148</v>
       </c>
       <c r="E58" s="130" t="n">
-        <f aca="false">$B$11+(D$36-$B$11)*MIN(E$41/$B$15,1)</f>
-        <v>0.122</v>
+        <f aca="false">$B$11+(B$48-$B$11)*MIN(E$53/$B$15,1)</f>
+        <v>0.152</v>
       </c>
       <c r="F58" s="130" t="n">
-        <f aca="false">$B$11+(D$36-$B$11)*MIN(F$41/$B$15,1)</f>
-        <v>0.116</v>
+        <f aca="false">$B$11+(B$48-$B$11)*MIN(F$53/$B$15,1)</f>
+        <v>0.156</v>
       </c>
       <c r="G58" s="130" t="n">
-        <f aca="false">$B$11+(D$36-$B$11)*MIN(G$41/$B$15,1)</f>
-        <v>0.11</v>
+        <f aca="false">$B$11+(B$48-$B$11)*MIN(G$53/$B$15,1)</f>
+        <v>0.16</v>
       </c>
       <c r="H58" s="130" t="n">
-        <f aca="false">$B$11+(D$36-$B$11)*MIN(H$41/$B$15,1)</f>
-        <v>0.11</v>
+        <f aca="false">$B$11+(B$48-$B$11)*MIN(H$53/$B$15,1)</f>
+        <v>0.16</v>
       </c>
       <c r="I58" s="130" t="n">
-        <f aca="false">$B$11+(D$36-$B$11)*MIN(I$41/$B$15,1)</f>
-        <v>0.11</v>
+        <f aca="false">$B$11+(B$48-$B$11)*MIN(I$53/$B$15,1)</f>
+        <v>0.16</v>
       </c>
       <c r="J58" s="130" t="n">
-        <f aca="false">$B$11+(D$36-$B$11)*MIN(J$41/$B$15,1)</f>
-        <v>0.11</v>
+        <f aca="false">$B$11+(B$48-$B$11)*MIN(J$53/$B$15,1)</f>
+        <v>0.16</v>
       </c>
       <c r="K58" s="130" t="n">
-        <f aca="false">$B$11+(D$36-$B$11)*MIN(K$41/$B$15,1)</f>
-        <v>0.11</v>
+        <f aca="false">$B$11+(B$48-$B$11)*MIN(K$53/$B$15,1)</f>
+        <v>0.16</v>
       </c>
       <c r="L58" s="130" t="n">
-        <f aca="false">$B$11+(D$36-$B$11)*MIN(L$41/$B$15,1)</f>
-        <v>0.11</v>
+        <f aca="false">$B$11+(B$48-$B$11)*MIN(L$53/$B$15,1)</f>
+        <v>0.16</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="127" t="s">
-        <v>541</v>
+        <v>562</v>
       </c>
       <c r="B59" s="132" t="n">
         <f aca="false">B57*B58</f>
@@ -9851,962 +9752,1938 @@
       </c>
       <c r="C59" s="132" t="n">
         <f aca="false">C57*C58</f>
-        <v>7.60316</v>
+        <v>9.43488</v>
       </c>
       <c r="D59" s="132" t="n">
         <f aca="false">D57*D58</f>
-        <v>6.8869376</v>
+        <v>10.6149448</v>
       </c>
       <c r="E59" s="132" t="n">
         <f aca="false">E57*E58</f>
-        <v>6.241586612</v>
+        <v>12.876111216</v>
       </c>
       <c r="F59" s="132" t="n">
         <f aca="false">F57*F58</f>
-        <v>5.65850150408</v>
+        <v>15.38269019976</v>
       </c>
       <c r="G59" s="132" t="n">
         <f aca="false">G57*G58</f>
-        <v>5.130086156294</v>
+        <v>17.208243669792</v>
       </c>
       <c r="H59" s="132" t="n">
         <f aca="false">H57*H58</f>
-        <v>4.91788578082142</v>
+        <v>18.8337693631178</v>
       </c>
       <c r="I59" s="132" t="n">
         <f aca="false">I57*I58</f>
-        <v>4.72690444457483</v>
+        <v>20.6849128886681</v>
       </c>
       <c r="J59" s="132" t="n">
         <f aca="false">J57*J58</f>
-        <v>4.55505841526286</v>
+        <v>22.7983628047006</v>
       </c>
       <c r="K59" s="132" t="n">
         <f aca="false">K57*K58</f>
-        <v>4.40047195190733</v>
+        <v>25.2172818560107</v>
       </c>
       <c r="L59" s="132" t="n">
         <f aca="false">L57*L58</f>
-        <v>4.26145651716537</v>
+        <v>27.9924989951381</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="127" t="s">
-        <v>542</v>
+        <v>563</v>
       </c>
       <c r="B60" s="132" t="n">
         <v>0</v>
       </c>
       <c r="C60" s="132" t="n">
         <f aca="false">B60+C59*$B$14</f>
-        <v>3.421422</v>
+        <v>4.245696</v>
       </c>
       <c r="D60" s="132" t="n">
         <f aca="false">C60+D59*$B$14</f>
-        <v>6.52054392</v>
+        <v>9.02242116</v>
       </c>
       <c r="E60" s="132" t="n">
         <f aca="false">D60+E59*$B$14</f>
-        <v>9.3292578954</v>
+        <v>14.8166712072</v>
       </c>
       <c r="F60" s="132" t="n">
         <f aca="false">E60+F59*$B$14</f>
-        <v>11.875583572236</v>
+        <v>21.738881797092</v>
       </c>
       <c r="G60" s="132" t="n">
         <f aca="false">F60+G59*$B$14</f>
-        <v>14.1841223425683</v>
+        <v>29.4825914484984</v>
       </c>
       <c r="H60" s="132" t="n">
         <f aca="false">G60+H59*$B$14</f>
-        <v>16.3971709439379</v>
+        <v>37.9577876619014</v>
       </c>
       <c r="I60" s="132" t="n">
         <f aca="false">H60+I59*$B$14</f>
-        <v>18.5242779439966</v>
+        <v>47.265998461802</v>
       </c>
       <c r="J60" s="132" t="n">
         <f aca="false">I60+J59*$B$14</f>
-        <v>20.5740542308649</v>
+        <v>57.5252617239173</v>
       </c>
       <c r="K60" s="132" t="n">
         <f aca="false">J60+K59*$B$14</f>
-        <v>22.5542666092232</v>
+        <v>68.8730385591221</v>
       </c>
       <c r="L60" s="132" t="n">
         <f aca="false">K60+L59*$B$14</f>
-        <v>24.4719220419476</v>
+        <v>81.4696631069343</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="127" t="s">
-        <v>543</v>
+        <v>564</v>
       </c>
       <c r="B61" s="132" t="n">
         <f aca="false">$B$6+$B$9</f>
         <v>92</v>
       </c>
       <c r="C61" s="132" t="n">
-        <f aca="false">C59*D$37</f>
-        <v>53.22212</v>
+        <f aca="false">C59*B$49</f>
+        <v>103.78368</v>
       </c>
       <c r="D61" s="132" t="n">
-        <f aca="false">D59*D$37</f>
-        <v>48.2085632</v>
+        <f aca="false">D59*B$49</f>
+        <v>116.7643928</v>
       </c>
       <c r="E61" s="132" t="n">
-        <f aca="false">E59*D$37</f>
-        <v>43.691106284</v>
+        <f aca="false">E59*B$49</f>
+        <v>141.637223376</v>
       </c>
       <c r="F61" s="132" t="n">
-        <f aca="false">F59*D$37</f>
-        <v>39.60951052856</v>
+        <f aca="false">F59*B$49</f>
+        <v>169.20959219736</v>
       </c>
       <c r="G61" s="132" t="n">
-        <f aca="false">G59*D$37</f>
-        <v>35.910603094058</v>
+        <f aca="false">G59*B$49</f>
+        <v>189.290680367712</v>
       </c>
       <c r="H61" s="132" t="n">
-        <f aca="false">H59*D$37</f>
-        <v>34.4252004657499</v>
+        <f aca="false">H59*B$49</f>
+        <v>207.171462994295</v>
       </c>
       <c r="I61" s="132" t="n">
-        <f aca="false">I59*D$37</f>
-        <v>33.0883311120238</v>
+        <f aca="false">I59*B$49</f>
+        <v>227.534041775349</v>
       </c>
       <c r="J61" s="132" t="n">
-        <f aca="false">J59*D$37</f>
-        <v>31.88540890684</v>
+        <f aca="false">J59*B$49</f>
+        <v>250.781990851706</v>
       </c>
       <c r="K61" s="132" t="n">
-        <f aca="false">K59*D$37</f>
-        <v>30.8033036633513</v>
+        <f aca="false">K59*B$49</f>
+        <v>277.390100416118</v>
       </c>
       <c r="L61" s="132" t="n">
-        <f aca="false">L59*D$37</f>
-        <v>29.8301956201576</v>
+        <f aca="false">L59*B$49</f>
+        <v>307.917488946519</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A62" s="144" t="s">
-        <v>544</v>
-      </c>
-      <c r="B62" s="145" t="n">
+      <c r="A62" s="145" t="s">
+        <v>565</v>
+      </c>
+      <c r="B62" s="146" t="n">
         <f aca="false">B61+B60-$B$9</f>
         <v>92</v>
       </c>
-      <c r="C62" s="145" t="n">
+      <c r="C62" s="146" t="n">
         <f aca="false">C61+C60-$B$9</f>
-        <v>56.643542</v>
-      </c>
-      <c r="D62" s="145" t="n">
+        <v>108.029376</v>
+      </c>
+      <c r="D62" s="146" t="n">
         <f aca="false">D61+D60-$B$9</f>
-        <v>54.72910712</v>
-      </c>
-      <c r="E62" s="145" t="n">
+        <v>125.78681396</v>
+      </c>
+      <c r="E62" s="146" t="n">
         <f aca="false">E61+E60-$B$9</f>
-        <v>53.0203641794</v>
-      </c>
-      <c r="F62" s="145" t="n">
+        <v>156.4538945832</v>
+      </c>
+      <c r="F62" s="146" t="n">
         <f aca="false">F61+F60-$B$9</f>
-        <v>51.485094100796</v>
-      </c>
-      <c r="G62" s="145" t="n">
+        <v>190.948473994452</v>
+      </c>
+      <c r="G62" s="146" t="n">
         <f aca="false">G61+G60-$B$9</f>
-        <v>50.0947254366263</v>
-      </c>
-      <c r="H62" s="145" t="n">
+        <v>218.77327181621</v>
+      </c>
+      <c r="H62" s="146" t="n">
         <f aca="false">H61+H60-$B$9</f>
-        <v>50.8223714096879</v>
-      </c>
-      <c r="I62" s="145" t="n">
+        <v>245.129250656197</v>
+      </c>
+      <c r="I62" s="146" t="n">
         <f aca="false">I61+I60-$B$9</f>
-        <v>51.6126090560204</v>
-      </c>
-      <c r="J62" s="145" t="n">
+        <v>274.800040237151</v>
+      </c>
+      <c r="J62" s="146" t="n">
         <f aca="false">J61+J60-$B$9</f>
-        <v>52.4594631377049</v>
-      </c>
-      <c r="K62" s="145" t="n">
+        <v>308.307252575623</v>
+      </c>
+      <c r="K62" s="146" t="n">
         <f aca="false">K61+K60-$B$9</f>
-        <v>53.3575702725745</v>
-      </c>
-      <c r="L62" s="145" t="n">
+        <v>346.26313897524</v>
+      </c>
+      <c r="L62" s="146" t="n">
         <f aca="false">L61+L60-$B$9</f>
-        <v>54.3021176621052</v>
-      </c>
-    </row>
-    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A63" s="137" t="s">
-        <v>547</v>
-      </c>
-      <c r="B63" s="143"/>
-      <c r="C63" s="143"/>
-      <c r="D63" s="143"/>
-      <c r="E63" s="143"/>
-      <c r="F63" s="143"/>
-      <c r="G63" s="143"/>
-      <c r="H63" s="143"/>
-      <c r="I63" s="143"/>
-      <c r="J63" s="143"/>
-      <c r="K63" s="143"/>
-      <c r="L63" s="143"/>
+        <v>389.387152053454</v>
+      </c>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A64" s="127" t="s">
-        <v>539</v>
-      </c>
-      <c r="B64" s="132" t="n">
-        <f aca="false">SUMPRODUCT($B$27:$B$31,(1+$K$27:$K$31)^B$41)</f>
-        <v>60</v>
-      </c>
-      <c r="C64" s="132" t="n">
-        <f aca="false">SUMPRODUCT($B$27:$B$31,(1+$K$27:$K$31)^C$41)</f>
-        <v>71.32</v>
-      </c>
-      <c r="D64" s="132" t="n">
-        <f aca="false">SUMPRODUCT($B$27:$B$31,(1+$K$27:$K$31)^D$41)</f>
-        <v>85.3196</v>
-      </c>
-      <c r="E64" s="132" t="n">
-        <f aca="false">SUMPRODUCT($B$27:$B$31,(1+$K$27:$K$31)^E$41)</f>
-        <v>102.709684</v>
-      </c>
-      <c r="F64" s="132" t="n">
-        <f aca="false">SUMPRODUCT($B$27:$B$31,(1+$K$27:$K$31)^F$41)</f>
-        <v>124.4098622</v>
-      </c>
-      <c r="G64" s="132" t="n">
-        <f aca="false">SUMPRODUCT($B$27:$B$31,(1+$K$27:$K$31)^G$41)</f>
-        <v>151.6150115572</v>
-      </c>
-      <c r="H64" s="132" t="n">
-        <f aca="false">SUMPRODUCT($B$27:$B$31,(1+$K$27:$K$31)^H$41)</f>
-        <v>185.884335665036</v>
-      </c>
-      <c r="I64" s="132" t="n">
-        <f aca="false">SUMPRODUCT($B$27:$B$31,(1+$K$27:$K$31)^I$41)</f>
-        <v>229.260879571418</v>
-      </c>
-      <c r="J64" s="132" t="n">
-        <f aca="false">SUMPRODUCT($B$27:$B$31,(1+$K$27:$K$31)^J$41)</f>
-        <v>284.432306302705</v>
-      </c>
-      <c r="K64" s="132" t="n">
-        <f aca="false">SUMPRODUCT($B$27:$B$31,(1+$K$27:$K$31)^K$41)</f>
-        <v>354.947669600173</v>
-      </c>
-      <c r="L64" s="132" t="n">
-        <f aca="false">SUMPRODUCT($B$27:$B$31,(1+$K$27:$K$31)^L$41)</f>
-        <v>445.510294818654</v>
-      </c>
+      <c r="A64" s="137" t="s">
+        <v>566</v>
+      </c>
+      <c r="B64" s="144"/>
+      <c r="C64" s="144"/>
+      <c r="D64" s="144"/>
+      <c r="E64" s="144"/>
+      <c r="F64" s="144"/>
+      <c r="G64" s="144"/>
+      <c r="H64" s="144"/>
+      <c r="I64" s="144"/>
+      <c r="J64" s="144"/>
+      <c r="K64" s="144"/>
+      <c r="L64" s="144"/>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="127" t="s">
-        <v>540</v>
-      </c>
-      <c r="B65" s="130" t="n">
-        <f aca="false">$B$11+(E$36-$B$11)*MIN(B$41/$B$15,1)</f>
-        <v>0.14</v>
-      </c>
-      <c r="C65" s="130" t="n">
-        <f aca="false">$B$11+(E$36-$B$11)*MIN(C$41/$B$15,1)</f>
-        <v>0.148</v>
-      </c>
-      <c r="D65" s="130" t="n">
-        <f aca="false">$B$11+(E$36-$B$11)*MIN(D$41/$B$15,1)</f>
-        <v>0.156</v>
-      </c>
-      <c r="E65" s="130" t="n">
-        <f aca="false">$B$11+(E$36-$B$11)*MIN(E$41/$B$15,1)</f>
-        <v>0.164</v>
-      </c>
-      <c r="F65" s="130" t="n">
-        <f aca="false">$B$11+(E$36-$B$11)*MIN(F$41/$B$15,1)</f>
-        <v>0.172</v>
-      </c>
-      <c r="G65" s="130" t="n">
-        <f aca="false">$B$11+(E$36-$B$11)*MIN(G$41/$B$15,1)</f>
-        <v>0.18</v>
-      </c>
-      <c r="H65" s="130" t="n">
-        <f aca="false">$B$11+(E$36-$B$11)*MIN(H$41/$B$15,1)</f>
-        <v>0.18</v>
-      </c>
-      <c r="I65" s="130" t="n">
-        <f aca="false">$B$11+(E$36-$B$11)*MIN(I$41/$B$15,1)</f>
-        <v>0.18</v>
-      </c>
-      <c r="J65" s="130" t="n">
-        <f aca="false">$B$11+(E$36-$B$11)*MIN(J$41/$B$15,1)</f>
-        <v>0.18</v>
-      </c>
-      <c r="K65" s="130" t="n">
-        <f aca="false">$B$11+(E$36-$B$11)*MIN(K$41/$B$15,1)</f>
-        <v>0.18</v>
-      </c>
-      <c r="L65" s="130" t="n">
-        <f aca="false">$B$11+(E$36-$B$11)*MIN(L$41/$B$15,1)</f>
-        <v>0.18</v>
+        <v>558</v>
+      </c>
+      <c r="B65" s="132" t="n">
+        <f aca="false">SUMPRODUCT($B$29:$B$36,(1+$I$29:$I$36)^B$53)</f>
+        <v>60</v>
+      </c>
+      <c r="C65" s="132" t="n">
+        <f aca="false">SUMPRODUCT($B$29:$B$36,(1+$I$29:$I$36)^C$53)</f>
+        <v>70.72</v>
+      </c>
+      <c r="D65" s="132" t="n">
+        <f aca="false">SUMPRODUCT($B$29:$B$36,(1+$I$29:$I$36)^D$53)</f>
+        <v>83.6508</v>
+      </c>
+      <c r="E65" s="132" t="n">
+        <f aca="false">SUMPRODUCT($B$29:$B$36,(1+$I$29:$I$36)^E$53)</f>
+        <v>99.299608</v>
+      </c>
+      <c r="F65" s="132" t="n">
+        <f aca="false">SUMPRODUCT($B$29:$B$36,(1+$I$29:$I$36)^F$53)</f>
+        <v>118.2996954</v>
+      </c>
+      <c r="G65" s="132" t="n">
+        <f aca="false">SUMPRODUCT($B$29:$B$36,(1+$I$29:$I$36)^G$53)</f>
+        <v>141.4435892392</v>
+      </c>
+      <c r="H65" s="132" t="n">
+        <f aca="false">SUMPRODUCT($B$29:$B$36,(1+$I$29:$I$36)^H$53)</f>
+        <v>169.725355877508</v>
+      </c>
+      <c r="I65" s="132" t="n">
+        <f aca="false">SUMPRODUCT($B$29:$B$36,(1+$I$29:$I$36)^I$53)</f>
+        <v>204.394532267048</v>
+      </c>
+      <c r="J65" s="132" t="n">
+        <f aca="false">SUMPRODUCT($B$29:$B$36,(1+$I$29:$I$36)^J$53)</f>
+        <v>247.024992067869</v>
+      </c>
+      <c r="K65" s="132" t="n">
+        <f aca="false">SUMPRODUCT($B$29:$B$36,(1+$I$29:$I$36)^K$53)</f>
+        <v>299.602976459189</v>
+      </c>
+      <c r="L65" s="132" t="n">
+        <f aca="false">SUMPRODUCT($B$29:$B$36,(1+$I$29:$I$36)^L$53)</f>
+        <v>364.639735232899</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="127" t="s">
-        <v>541</v>
+        <v>559</v>
       </c>
       <c r="B66" s="132" t="n">
-        <f aca="false">B64*B65</f>
-        <v>8.4</v>
+        <f aca="false">C$43*MIN(MAX(B$53-C$42+1,0)/C$44,1)</f>
+        <v>0</v>
       </c>
       <c r="C66" s="132" t="n">
-        <f aca="false">C64*C65</f>
-        <v>10.55536</v>
+        <f aca="false">C$43*MIN(MAX(C$53-C$42+1,0)/C$44,1)</f>
+        <v>0</v>
       </c>
       <c r="D66" s="132" t="n">
-        <f aca="false">D64*D65</f>
-        <v>13.3098576</v>
+        <f aca="false">C$43*MIN(MAX(D$53-C$42+1,0)/C$44,1)</f>
+        <v>10</v>
       </c>
       <c r="E66" s="132" t="n">
-        <f aca="false">E64*E65</f>
-        <v>16.844388176</v>
+        <f aca="false">C$43*MIN(MAX(E$53-C$42+1,0)/C$44,1)</f>
+        <v>20</v>
       </c>
       <c r="F66" s="132" t="n">
-        <f aca="false">F64*F65</f>
-        <v>21.3984962984</v>
+        <f aca="false">C$43*MIN(MAX(F$53-C$42+1,0)/C$44,1)</f>
+        <v>20</v>
       </c>
       <c r="G66" s="132" t="n">
-        <f aca="false">G64*G65</f>
-        <v>27.290702080296</v>
+        <f aca="false">C$43*MIN(MAX(G$53-C$42+1,0)/C$44,1)</f>
+        <v>20</v>
       </c>
       <c r="H66" s="132" t="n">
-        <f aca="false">H64*H65</f>
-        <v>33.4591804197065</v>
+        <f aca="false">C$43*MIN(MAX(H$53-C$42+1,0)/C$44,1)</f>
+        <v>20</v>
       </c>
       <c r="I66" s="132" t="n">
-        <f aca="false">I64*I65</f>
-        <v>41.2669583228553</v>
+        <f aca="false">C$43*MIN(MAX(I$53-C$42+1,0)/C$44,1)</f>
+        <v>20</v>
       </c>
       <c r="J66" s="132" t="n">
-        <f aca="false">J64*J65</f>
-        <v>51.1978151344869</v>
+        <f aca="false">C$43*MIN(MAX(J$53-C$42+1,0)/C$44,1)</f>
+        <v>20</v>
       </c>
       <c r="K66" s="132" t="n">
-        <f aca="false">K64*K65</f>
-        <v>63.8905805280312</v>
+        <f aca="false">C$43*MIN(MAX(K$53-C$42+1,0)/C$44,1)</f>
+        <v>20</v>
       </c>
       <c r="L66" s="132" t="n">
-        <f aca="false">L64*L65</f>
-        <v>80.1918530673577</v>
+        <f aca="false">C$43*MIN(MAX(L$53-C$42+1,0)/C$44,1)</f>
+        <v>20</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A67" s="127" t="s">
-        <v>542</v>
-      </c>
-      <c r="B67" s="132" t="n">
-        <v>0</v>
-      </c>
-      <c r="C67" s="132" t="n">
-        <f aca="false">B67+C66*$B$14</f>
-        <v>4.749912</v>
-      </c>
-      <c r="D67" s="132" t="n">
-        <f aca="false">C67+D66*$B$14</f>
-        <v>10.73934792</v>
-      </c>
-      <c r="E67" s="132" t="n">
-        <f aca="false">D67+E66*$B$14</f>
-        <v>18.3193225992</v>
-      </c>
-      <c r="F67" s="132" t="n">
-        <f aca="false">E67+F66*$B$14</f>
-        <v>27.94864593348</v>
-      </c>
-      <c r="G67" s="132" t="n">
-        <f aca="false">F67+G66*$B$14</f>
-        <v>40.2294618696132</v>
-      </c>
-      <c r="H67" s="132" t="n">
-        <f aca="false">G67+H66*$B$14</f>
-        <v>55.2860930584811</v>
-      </c>
-      <c r="I67" s="132" t="n">
-        <f aca="false">H67+I66*$B$14</f>
-        <v>73.856224303766</v>
-      </c>
-      <c r="J67" s="132" t="n">
-        <f aca="false">I67+J66*$B$14</f>
-        <v>96.8952411142851</v>
-      </c>
-      <c r="K67" s="132" t="n">
-        <f aca="false">J67+K66*$B$14</f>
-        <v>125.646002351899</v>
-      </c>
-      <c r="L67" s="132" t="n">
-        <f aca="false">K67+L66*$B$14</f>
-        <v>161.73233623221</v>
+      <c r="A67" s="145" t="s">
+        <v>560</v>
+      </c>
+      <c r="B67" s="146" t="n">
+        <f aca="false">B65+B66</f>
+        <v>60</v>
+      </c>
+      <c r="C67" s="146" t="n">
+        <f aca="false">C65+C66</f>
+        <v>70.72</v>
+      </c>
+      <c r="D67" s="146" t="n">
+        <f aca="false">D65+D66</f>
+        <v>93.6508</v>
+      </c>
+      <c r="E67" s="146" t="n">
+        <f aca="false">E65+E66</f>
+        <v>119.299608</v>
+      </c>
+      <c r="F67" s="146" t="n">
+        <f aca="false">F65+F66</f>
+        <v>138.2996954</v>
+      </c>
+      <c r="G67" s="146" t="n">
+        <f aca="false">G65+G66</f>
+        <v>161.4435892392</v>
+      </c>
+      <c r="H67" s="146" t="n">
+        <f aca="false">H65+H66</f>
+        <v>189.725355877508</v>
+      </c>
+      <c r="I67" s="146" t="n">
+        <f aca="false">I65+I66</f>
+        <v>224.394532267048</v>
+      </c>
+      <c r="J67" s="146" t="n">
+        <f aca="false">J65+J66</f>
+        <v>267.024992067869</v>
+      </c>
+      <c r="K67" s="146" t="n">
+        <f aca="false">K65+K66</f>
+        <v>319.602976459189</v>
+      </c>
+      <c r="L67" s="146" t="n">
+        <f aca="false">L65+L66</f>
+        <v>384.639735232899</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="127" t="s">
-        <v>543</v>
-      </c>
-      <c r="B68" s="132" t="n">
+        <v>561</v>
+      </c>
+      <c r="B68" s="130" t="n">
+        <f aca="false">$B$11+(C$48-$B$11)*MIN(B$53/$B$15,1)</f>
+        <v>0.14</v>
+      </c>
+      <c r="C68" s="130" t="n">
+        <f aca="false">$B$11+(C$48-$B$11)*MIN(C$53/$B$15,1)</f>
+        <v>0.15</v>
+      </c>
+      <c r="D68" s="130" t="n">
+        <f aca="false">$B$11+(C$48-$B$11)*MIN(D$53/$B$15,1)</f>
+        <v>0.16</v>
+      </c>
+      <c r="E68" s="130" t="n">
+        <f aca="false">$B$11+(C$48-$B$11)*MIN(E$53/$B$15,1)</f>
+        <v>0.17</v>
+      </c>
+      <c r="F68" s="130" t="n">
+        <f aca="false">$B$11+(C$48-$B$11)*MIN(F$53/$B$15,1)</f>
+        <v>0.18</v>
+      </c>
+      <c r="G68" s="130" t="n">
+        <f aca="false">$B$11+(C$48-$B$11)*MIN(G$53/$B$15,1)</f>
+        <v>0.19</v>
+      </c>
+      <c r="H68" s="130" t="n">
+        <f aca="false">$B$11+(C$48-$B$11)*MIN(H$53/$B$15,1)</f>
+        <v>0.19</v>
+      </c>
+      <c r="I68" s="130" t="n">
+        <f aca="false">$B$11+(C$48-$B$11)*MIN(I$53/$B$15,1)</f>
+        <v>0.19</v>
+      </c>
+      <c r="J68" s="130" t="n">
+        <f aca="false">$B$11+(C$48-$B$11)*MIN(J$53/$B$15,1)</f>
+        <v>0.19</v>
+      </c>
+      <c r="K68" s="130" t="n">
+        <f aca="false">$B$11+(C$48-$B$11)*MIN(K$53/$B$15,1)</f>
+        <v>0.19</v>
+      </c>
+      <c r="L68" s="130" t="n">
+        <f aca="false">$B$11+(C$48-$B$11)*MIN(L$53/$B$15,1)</f>
+        <v>0.19</v>
+      </c>
+    </row>
+    <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A69" s="127" t="s">
+        <v>562</v>
+      </c>
+      <c r="B69" s="132" t="n">
+        <f aca="false">B67*B68</f>
+        <v>8.4</v>
+      </c>
+      <c r="C69" s="132" t="n">
+        <f aca="false">C67*C68</f>
+        <v>10.608</v>
+      </c>
+      <c r="D69" s="132" t="n">
+        <f aca="false">D67*D68</f>
+        <v>14.984128</v>
+      </c>
+      <c r="E69" s="132" t="n">
+        <f aca="false">E67*E68</f>
+        <v>20.28093336</v>
+      </c>
+      <c r="F69" s="132" t="n">
+        <f aca="false">F67*F68</f>
+        <v>24.893945172</v>
+      </c>
+      <c r="G69" s="132" t="n">
+        <f aca="false">G67*G68</f>
+        <v>30.674281955448</v>
+      </c>
+      <c r="H69" s="132" t="n">
+        <f aca="false">H67*H68</f>
+        <v>36.0478176167265</v>
+      </c>
+      <c r="I69" s="132" t="n">
+        <f aca="false">I67*I68</f>
+        <v>42.6349611307391</v>
+      </c>
+      <c r="J69" s="132" t="n">
+        <f aca="false">J67*J68</f>
+        <v>50.734748492895</v>
+      </c>
+      <c r="K69" s="132" t="n">
+        <f aca="false">K67*K68</f>
+        <v>60.7245655272459</v>
+      </c>
+      <c r="L69" s="132" t="n">
+        <f aca="false">L67*L68</f>
+        <v>73.0815496942508</v>
+      </c>
+    </row>
+    <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A70" s="127" t="s">
+        <v>563</v>
+      </c>
+      <c r="B70" s="132" t="n">
+        <v>0</v>
+      </c>
+      <c r="C70" s="132" t="n">
+        <f aca="false">B70+C69*$B$14</f>
+        <v>4.7736</v>
+      </c>
+      <c r="D70" s="132" t="n">
+        <f aca="false">C70+D69*$B$14</f>
+        <v>11.5164576</v>
+      </c>
+      <c r="E70" s="132" t="n">
+        <f aca="false">D70+E69*$B$14</f>
+        <v>20.642877612</v>
+      </c>
+      <c r="F70" s="132" t="n">
+        <f aca="false">E70+F69*$B$14</f>
+        <v>31.8451529394</v>
+      </c>
+      <c r="G70" s="132" t="n">
+        <f aca="false">F70+G69*$B$14</f>
+        <v>45.6485798193516</v>
+      </c>
+      <c r="H70" s="132" t="n">
+        <f aca="false">G70+H69*$B$14</f>
+        <v>61.8700977468785</v>
+      </c>
+      <c r="I70" s="132" t="n">
+        <f aca="false">H70+I69*$B$14</f>
+        <v>81.0558302557111</v>
+      </c>
+      <c r="J70" s="132" t="n">
+        <f aca="false">I70+J69*$B$14</f>
+        <v>103.886467077514</v>
+      </c>
+      <c r="K70" s="132" t="n">
+        <f aca="false">J70+K69*$B$14</f>
+        <v>131.212521564775</v>
+      </c>
+      <c r="L70" s="132" t="n">
+        <f aca="false">K70+L69*$B$14</f>
+        <v>164.099218927187</v>
+      </c>
+    </row>
+    <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A71" s="127" t="s">
+        <v>564</v>
+      </c>
+      <c r="B71" s="132" t="n">
         <f aca="false">$B$6+$B$9</f>
         <v>92</v>
       </c>
-      <c r="C68" s="132" t="n">
-        <f aca="false">C66*E$37</f>
-        <v>137.21968</v>
-      </c>
-      <c r="D68" s="132" t="n">
-        <f aca="false">D66*E$37</f>
-        <v>173.0281488</v>
-      </c>
-      <c r="E68" s="132" t="n">
-        <f aca="false">E66*E$37</f>
-        <v>218.977046288</v>
-      </c>
-      <c r="F68" s="132" t="n">
-        <f aca="false">F66*E$37</f>
-        <v>278.1804518792</v>
-      </c>
-      <c r="G68" s="132" t="n">
-        <f aca="false">G66*E$37</f>
-        <v>354.779127043848</v>
-      </c>
-      <c r="H68" s="132" t="n">
-        <f aca="false">H66*E$37</f>
-        <v>434.969345456184</v>
-      </c>
-      <c r="I68" s="132" t="n">
-        <f aca="false">I66*E$37</f>
-        <v>536.470458197119</v>
-      </c>
-      <c r="J68" s="132" t="n">
-        <f aca="false">J66*E$37</f>
-        <v>665.57159674833</v>
-      </c>
-      <c r="K68" s="132" t="n">
-        <f aca="false">K66*E$37</f>
-        <v>830.577546864405</v>
-      </c>
-      <c r="L68" s="132" t="n">
-        <f aca="false">L66*E$37</f>
-        <v>1042.49408987565</v>
-      </c>
-    </row>
-    <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A69" s="144" t="s">
-        <v>544</v>
-      </c>
-      <c r="B69" s="145" t="n">
-        <f aca="false">B68+B67-$B$9</f>
+      <c r="C71" s="132" t="n">
+        <f aca="false">C69*C$49</f>
+        <v>148.512</v>
+      </c>
+      <c r="D71" s="132" t="n">
+        <f aca="false">D69*C$49</f>
+        <v>209.777792</v>
+      </c>
+      <c r="E71" s="132" t="n">
+        <f aca="false">E69*C$49</f>
+        <v>283.93306704</v>
+      </c>
+      <c r="F71" s="132" t="n">
+        <f aca="false">F69*C$49</f>
+        <v>348.515232408</v>
+      </c>
+      <c r="G71" s="132" t="n">
+        <f aca="false">G69*C$49</f>
+        <v>429.439947376272</v>
+      </c>
+      <c r="H71" s="132" t="n">
+        <f aca="false">H69*C$49</f>
+        <v>504.669446634171</v>
+      </c>
+      <c r="I71" s="132" t="n">
+        <f aca="false">I69*C$49</f>
+        <v>596.889455830348</v>
+      </c>
+      <c r="J71" s="132" t="n">
+        <f aca="false">J69*C$49</f>
+        <v>710.28647890053</v>
+      </c>
+      <c r="K71" s="132" t="n">
+        <f aca="false">K69*C$49</f>
+        <v>850.143917381442</v>
+      </c>
+      <c r="L71" s="132" t="n">
+        <f aca="false">L69*C$49</f>
+        <v>1023.14169571951</v>
+      </c>
+    </row>
+    <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A72" s="145" t="s">
+        <v>565</v>
+      </c>
+      <c r="B72" s="146" t="n">
+        <f aca="false">B71+B70-$B$9</f>
         <v>92</v>
       </c>
-      <c r="C69" s="145" t="n">
-        <f aca="false">C68+C67-$B$9</f>
-        <v>141.969592</v>
-      </c>
-      <c r="D69" s="145" t="n">
-        <f aca="false">D68+D67-$B$9</f>
-        <v>183.76749672</v>
-      </c>
-      <c r="E69" s="145" t="n">
-        <f aca="false">E68+E67-$B$9</f>
-        <v>237.2963688872</v>
-      </c>
-      <c r="F69" s="145" t="n">
-        <f aca="false">F68+F67-$B$9</f>
-        <v>306.12909781268</v>
-      </c>
-      <c r="G69" s="145" t="n">
-        <f aca="false">G68+G67-$B$9</f>
-        <v>395.008588913461</v>
-      </c>
-      <c r="H69" s="145" t="n">
-        <f aca="false">H68+H67-$B$9</f>
-        <v>490.255438514665</v>
-      </c>
-      <c r="I69" s="145" t="n">
-        <f aca="false">I68+I67-$B$9</f>
-        <v>610.326682500885</v>
-      </c>
-      <c r="J69" s="145" t="n">
-        <f aca="false">J68+J67-$B$9</f>
-        <v>762.466837862615</v>
-      </c>
-      <c r="K69" s="145" t="n">
-        <f aca="false">K68+K67-$B$9</f>
-        <v>956.223549216304</v>
-      </c>
-      <c r="L69" s="145" t="n">
-        <f aca="false">L68+L67-$B$9</f>
-        <v>1204.22642610786</v>
-      </c>
-    </row>
-    <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A71" s="60" t="s">
-        <v>548</v>
-      </c>
-      <c r="B71" s="125"/>
-      <c r="C71" s="125"/>
-      <c r="D71" s="125"/>
-      <c r="E71" s="125"/>
-      <c r="F71" s="125"/>
-      <c r="G71" s="125"/>
-      <c r="H71" s="125"/>
-      <c r="I71" s="125"/>
-      <c r="J71" s="125"/>
-      <c r="K71" s="125"/>
-      <c r="L71" s="125"/>
-      <c r="M71" s="125"/>
-    </row>
-    <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A72" s="126" t="s">
-        <v>27</v>
-      </c>
-      <c r="B72" s="126" t="s">
-        <v>549</v>
-      </c>
-      <c r="C72" s="126" t="s">
-        <v>36</v>
-      </c>
-      <c r="D72" s="126" t="s">
-        <v>37</v>
-      </c>
-      <c r="E72" s="126" t="s">
-        <v>38</v>
-      </c>
-      <c r="F72" s="126" t="s">
-        <v>39</v>
-      </c>
-      <c r="G72" s="126" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A73" s="127" t="s">
-        <v>550</v>
-      </c>
-      <c r="B73" s="146" t="n">
-        <v>5</v>
-      </c>
-      <c r="C73" s="130" t="n">
-        <f aca="false">(G48/$B$6)^(1/$B73)-1</f>
-        <v>0.165356758207305</v>
-      </c>
-      <c r="D73" s="130" t="n">
-        <f aca="false">(G55/$B$6)^(1/$B73)-1</f>
-        <v>0.369696065522081</v>
-      </c>
-      <c r="E73" s="130" t="n">
-        <f aca="false">(G62/$B$6)^(1/$B73)-1</f>
-        <v>-0.114474983635926</v>
-      </c>
-      <c r="F73" s="130" t="n">
-        <f aca="false">(G69/$B$6)^(1/$B73)-1</f>
-        <v>0.338331630451749</v>
-      </c>
-      <c r="G73" s="130" t="n">
-        <f aca="false">C73*'Defense Supercycle'!$B$17+D73*'Defense Supercycle'!$B$18+E73*'Defense Supercycle'!$B$19+F73*'Defense Supercycle'!$B$20</f>
-        <v>0.200413054596181</v>
+      <c r="C72" s="146" t="n">
+        <f aca="false">C71+C70-$B$9</f>
+        <v>153.2856</v>
+      </c>
+      <c r="D72" s="146" t="n">
+        <f aca="false">D71+D70-$B$9</f>
+        <v>221.2942496</v>
+      </c>
+      <c r="E72" s="146" t="n">
+        <f aca="false">E71+E70-$B$9</f>
+        <v>304.575944652</v>
+      </c>
+      <c r="F72" s="146" t="n">
+        <f aca="false">F71+F70-$B$9</f>
+        <v>380.3603853474</v>
+      </c>
+      <c r="G72" s="146" t="n">
+        <f aca="false">G71+G70-$B$9</f>
+        <v>475.088527195624</v>
+      </c>
+      <c r="H72" s="146" t="n">
+        <f aca="false">H71+H70-$B$9</f>
+        <v>566.53954438105</v>
+      </c>
+      <c r="I72" s="146" t="n">
+        <f aca="false">I71+I70-$B$9</f>
+        <v>677.945286086059</v>
+      </c>
+      <c r="J72" s="146" t="n">
+        <f aca="false">J71+J70-$B$9</f>
+        <v>814.172945978044</v>
+      </c>
+      <c r="K72" s="146" t="n">
+        <f aca="false">K71+K70-$B$9</f>
+        <v>981.356438946217</v>
+      </c>
+      <c r="L72" s="146" t="n">
+        <f aca="false">L71+L70-$B$9</f>
+        <v>1187.2409146467</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A74" s="144" t="s">
-        <v>551</v>
-      </c>
-      <c r="B74" s="146" t="n">
-        <v>7</v>
-      </c>
-      <c r="C74" s="147" t="n">
-        <f aca="false">(I48/$B$6)^(1/$B74)-1</f>
-        <v>0.157363999133814</v>
-      </c>
-      <c r="D74" s="147" t="n">
-        <f aca="false">(I55/$B$6)^(1/$B74)-1</f>
-        <v>0.334558904469404</v>
-      </c>
-      <c r="E74" s="147" t="n">
-        <f aca="false">(I62/$B$6)^(1/$B74)-1</f>
-        <v>-0.0792573011585949</v>
-      </c>
-      <c r="F74" s="147" t="n">
-        <f aca="false">(I69/$B$6)^(1/$B74)-1</f>
-        <v>0.310377300892187</v>
-      </c>
-      <c r="G74" s="130" t="n">
-        <f aca="false">C74*'Defense Supercycle'!$B$17+D74*'Defense Supercycle'!$B$18+E74*'Defense Supercycle'!$B$19+F74*'Defense Supercycle'!$B$20</f>
-        <v>0.189121525687606</v>
-      </c>
+      <c r="A74" s="137" t="s">
+        <v>567</v>
+      </c>
+      <c r="B74" s="144"/>
+      <c r="C74" s="144"/>
+      <c r="D74" s="144"/>
+      <c r="E74" s="144"/>
+      <c r="F74" s="144"/>
+      <c r="G74" s="144"/>
+      <c r="H74" s="144"/>
+      <c r="I74" s="144"/>
+      <c r="J74" s="144"/>
+      <c r="K74" s="144"/>
+      <c r="L74" s="144"/>
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="127" t="s">
-        <v>552</v>
-      </c>
-      <c r="B75" s="146" t="n">
-        <v>10</v>
-      </c>
-      <c r="C75" s="130" t="n">
-        <f aca="false">(L48/$B$6)^(1/$B75)-1</f>
-        <v>0.153122858841397</v>
-      </c>
-      <c r="D75" s="130" t="n">
-        <f aca="false">(L55/$B$6)^(1/$B75)-1</f>
-        <v>0.316044894176216</v>
-      </c>
-      <c r="E75" s="130" t="n">
-        <f aca="false">(L62/$B$6)^(1/$B75)-1</f>
-        <v>-0.0513568088964763</v>
-      </c>
-      <c r="F75" s="130" t="n">
-        <f aca="false">(L69/$B$6)^(1/$B75)-1</f>
-        <v>0.293278425129385</v>
-      </c>
-      <c r="G75" s="130" t="n">
-        <f aca="false">C75*'Defense Supercycle'!$B$17+D75*'Defense Supercycle'!$B$18+E75*'Defense Supercycle'!$B$19+F75*'Defense Supercycle'!$B$20</f>
-        <v>0.184204752457619</v>
+        <v>558</v>
+      </c>
+      <c r="B75" s="132" t="n">
+        <f aca="false">SUMPRODUCT($B$29:$B$36,(1+$J$29:$J$36)^B$53)</f>
+        <v>60</v>
+      </c>
+      <c r="C75" s="132" t="n">
+        <f aca="false">SUMPRODUCT($B$29:$B$36,(1+$J$29:$J$36)^C$53)</f>
+        <v>56.87</v>
+      </c>
+      <c r="D75" s="132" t="n">
+        <f aca="false">SUMPRODUCT($B$29:$B$36,(1+$J$29:$J$36)^D$53)</f>
+        <v>54.0657</v>
+      </c>
+      <c r="E75" s="132" t="n">
+        <f aca="false">SUMPRODUCT($B$29:$B$36,(1+$J$29:$J$36)^E$53)</f>
+        <v>51.557021</v>
+      </c>
+      <c r="F75" s="132" t="n">
+        <f aca="false">SUMPRODUCT($B$29:$B$36,(1+$J$29:$J$36)^F$53)</f>
+        <v>49.31692389</v>
+      </c>
+      <c r="G75" s="132" t="n">
+        <f aca="false">SUMPRODUCT($B$29:$B$36,(1+$J$29:$J$36)^G$53)</f>
+        <v>47.3211091997</v>
+      </c>
+      <c r="H75" s="132" t="n">
+        <f aca="false">SUMPRODUCT($B$29:$B$36,(1+$J$29:$J$36)^H$53)</f>
+        <v>45.547746921117</v>
+      </c>
+      <c r="I75" s="132" t="n">
+        <f aca="false">SUMPRODUCT($B$29:$B$36,(1+$J$29:$J$36)^I$53)</f>
+        <v>43.9772334031978</v>
+      </c>
+      <c r="J75" s="132" t="n">
+        <f aca="false">SUMPRODUCT($B$29:$B$36,(1+$J$29:$J$36)^J$53)</f>
+        <v>42.5919726176504</v>
+      </c>
+      <c r="K75" s="132" t="n">
+        <f aca="false">SUMPRODUCT($B$29:$B$36,(1+$J$29:$J$36)^K$53)</f>
+        <v>41.3761793653578</v>
+      </c>
+      <c r="L75" s="132" t="n">
+        <f aca="false">SUMPRODUCT($B$29:$B$36,(1+$J$29:$J$36)^L$53)</f>
+        <v>40.3157022358763</v>
+      </c>
+    </row>
+    <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A76" s="127" t="s">
+        <v>559</v>
+      </c>
+      <c r="B76" s="132" t="n">
+        <f aca="false">D$43*MIN(MAX(B$53-D$42+1,0)/D$44,1)</f>
+        <v>0</v>
+      </c>
+      <c r="C76" s="132" t="n">
+        <f aca="false">D$43*MIN(MAX(C$53-D$42+1,0)/D$44,1)</f>
+        <v>0</v>
+      </c>
+      <c r="D76" s="132" t="n">
+        <f aca="false">D$43*MIN(MAX(D$53-D$42+1,0)/D$44,1)</f>
+        <v>0</v>
+      </c>
+      <c r="E76" s="132" t="n">
+        <f aca="false">D$43*MIN(MAX(E$53-D$42+1,0)/D$44,1)</f>
+        <v>0</v>
+      </c>
+      <c r="F76" s="132" t="n">
+        <f aca="false">D$43*MIN(MAX(F$53-D$42+1,0)/D$44,1)</f>
+        <v>0</v>
+      </c>
+      <c r="G76" s="132" t="n">
+        <f aca="false">D$43*MIN(MAX(G$53-D$42+1,0)/D$44,1)</f>
+        <v>0</v>
+      </c>
+      <c r="H76" s="132" t="n">
+        <f aca="false">D$43*MIN(MAX(H$53-D$42+1,0)/D$44,1)</f>
+        <v>0</v>
+      </c>
+      <c r="I76" s="132" t="n">
+        <f aca="false">D$43*MIN(MAX(I$53-D$42+1,0)/D$44,1)</f>
+        <v>0</v>
+      </c>
+      <c r="J76" s="132" t="n">
+        <f aca="false">D$43*MIN(MAX(J$53-D$42+1,0)/D$44,1)</f>
+        <v>0</v>
+      </c>
+      <c r="K76" s="132" t="n">
+        <f aca="false">D$43*MIN(MAX(K$53-D$42+1,0)/D$44,1)</f>
+        <v>0</v>
+      </c>
+      <c r="L76" s="132" t="n">
+        <f aca="false">D$43*MIN(MAX(L$53-D$42+1,0)/D$44,1)</f>
+        <v>0</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A77" s="60" t="s">
-        <v>553</v>
-      </c>
-      <c r="B77" s="125"/>
-      <c r="C77" s="125"/>
-      <c r="D77" s="125"/>
-      <c r="E77" s="125"/>
-      <c r="F77" s="125"/>
-      <c r="G77" s="125"/>
-      <c r="H77" s="125"/>
-      <c r="I77" s="125"/>
-      <c r="J77" s="125"/>
-      <c r="K77" s="125"/>
-      <c r="L77" s="125"/>
-      <c r="M77" s="125"/>
+      <c r="A77" s="145" t="s">
+        <v>560</v>
+      </c>
+      <c r="B77" s="146" t="n">
+        <f aca="false">B75+B76</f>
+        <v>60</v>
+      </c>
+      <c r="C77" s="146" t="n">
+        <f aca="false">C75+C76</f>
+        <v>56.87</v>
+      </c>
+      <c r="D77" s="146" t="n">
+        <f aca="false">D75+D76</f>
+        <v>54.0657</v>
+      </c>
+      <c r="E77" s="146" t="n">
+        <f aca="false">E75+E76</f>
+        <v>51.557021</v>
+      </c>
+      <c r="F77" s="146" t="n">
+        <f aca="false">F75+F76</f>
+        <v>49.31692389</v>
+      </c>
+      <c r="G77" s="146" t="n">
+        <f aca="false">G75+G76</f>
+        <v>47.3211091997</v>
+      </c>
+      <c r="H77" s="146" t="n">
+        <f aca="false">H75+H76</f>
+        <v>45.547746921117</v>
+      </c>
+      <c r="I77" s="146" t="n">
+        <f aca="false">I75+I76</f>
+        <v>43.9772334031978</v>
+      </c>
+      <c r="J77" s="146" t="n">
+        <f aca="false">J75+J76</f>
+        <v>42.5919726176504</v>
+      </c>
+      <c r="K77" s="146" t="n">
+        <f aca="false">K75+K76</f>
+        <v>41.3761793653578</v>
+      </c>
+      <c r="L77" s="146" t="n">
+        <f aca="false">L75+L76</f>
+        <v>40.3157022358763</v>
+      </c>
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A78" s="126" t="s">
-        <v>554</v>
-      </c>
-      <c r="B78" s="126" t="s">
-        <v>248</v>
-      </c>
-      <c r="C78" s="126" t="s">
-        <v>356</v>
-      </c>
-      <c r="D78" s="126" t="s">
-        <v>359</v>
-      </c>
-      <c r="E78" s="126" t="s">
-        <v>362</v>
-      </c>
-      <c r="F78" s="126" t="s">
-        <v>555</v>
-      </c>
-      <c r="G78" s="126" t="s">
-        <v>556</v>
-      </c>
-      <c r="H78" s="126" t="s">
-        <v>557</v>
-      </c>
-      <c r="I78" s="126" t="s">
-        <v>558</v>
+      <c r="A78" s="127" t="s">
+        <v>561</v>
+      </c>
+      <c r="B78" s="130" t="n">
+        <f aca="false">$B$11+(D$48-$B$11)*MIN(B$53/$B$15,1)</f>
+        <v>0.14</v>
+      </c>
+      <c r="C78" s="130" t="n">
+        <f aca="false">$B$11+(D$48-$B$11)*MIN(C$53/$B$15,1)</f>
+        <v>0.134</v>
+      </c>
+      <c r="D78" s="130" t="n">
+        <f aca="false">$B$11+(D$48-$B$11)*MIN(D$53/$B$15,1)</f>
+        <v>0.128</v>
+      </c>
+      <c r="E78" s="130" t="n">
+        <f aca="false">$B$11+(D$48-$B$11)*MIN(E$53/$B$15,1)</f>
+        <v>0.122</v>
+      </c>
+      <c r="F78" s="130" t="n">
+        <f aca="false">$B$11+(D$48-$B$11)*MIN(F$53/$B$15,1)</f>
+        <v>0.116</v>
+      </c>
+      <c r="G78" s="130" t="n">
+        <f aca="false">$B$11+(D$48-$B$11)*MIN(G$53/$B$15,1)</f>
+        <v>0.11</v>
+      </c>
+      <c r="H78" s="130" t="n">
+        <f aca="false">$B$11+(D$48-$B$11)*MIN(H$53/$B$15,1)</f>
+        <v>0.11</v>
+      </c>
+      <c r="I78" s="130" t="n">
+        <f aca="false">$B$11+(D$48-$B$11)*MIN(I$53/$B$15,1)</f>
+        <v>0.11</v>
+      </c>
+      <c r="J78" s="130" t="n">
+        <f aca="false">$B$11+(D$48-$B$11)*MIN(J$53/$B$15,1)</f>
+        <v>0.11</v>
+      </c>
+      <c r="K78" s="130" t="n">
+        <f aca="false">$B$11+(D$48-$B$11)*MIN(K$53/$B$15,1)</f>
+        <v>0.11</v>
+      </c>
+      <c r="L78" s="130" t="n">
+        <f aca="false">$B$11+(D$48-$B$11)*MIN(L$53/$B$15,1)</f>
+        <v>0.11</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="127" t="s">
+        <v>562</v>
+      </c>
+      <c r="B79" s="132" t="n">
+        <f aca="false">B77*B78</f>
+        <v>8.4</v>
+      </c>
+      <c r="C79" s="132" t="n">
+        <f aca="false">C77*C78</f>
+        <v>7.62058</v>
+      </c>
+      <c r="D79" s="132" t="n">
+        <f aca="false">D77*D78</f>
+        <v>6.9204096</v>
+      </c>
+      <c r="E79" s="132" t="n">
+        <f aca="false">E77*E78</f>
+        <v>6.289956562</v>
+      </c>
+      <c r="F79" s="132" t="n">
+        <f aca="false">F77*F78</f>
+        <v>5.72076317124</v>
+      </c>
+      <c r="G79" s="132" t="n">
+        <f aca="false">G77*G78</f>
+        <v>5.205322011967</v>
+      </c>
+      <c r="H79" s="132" t="n">
+        <f aca="false">H77*H78</f>
+        <v>5.01025216132287</v>
+      </c>
+      <c r="I79" s="132" t="n">
+        <f aca="false">I77*I78</f>
+        <v>4.83749567435176</v>
+      </c>
+      <c r="J79" s="132" t="n">
+        <f aca="false">J77*J78</f>
+        <v>4.68511698794155</v>
+      </c>
+      <c r="K79" s="132" t="n">
+        <f aca="false">K77*K78</f>
+        <v>4.55137973018936</v>
+      </c>
+      <c r="L79" s="132" t="n">
+        <f aca="false">L77*L78</f>
+        <v>4.43472724594639</v>
+      </c>
+    </row>
+    <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A80" s="127" t="s">
+        <v>563</v>
+      </c>
+      <c r="B80" s="132" t="n">
+        <v>0</v>
+      </c>
+      <c r="C80" s="132" t="n">
+        <f aca="false">B80+C79*$B$14</f>
+        <v>3.429261</v>
+      </c>
+      <c r="D80" s="132" t="n">
+        <f aca="false">C80+D79*$B$14</f>
+        <v>6.54344532</v>
+      </c>
+      <c r="E80" s="132" t="n">
+        <f aca="false">D80+E79*$B$14</f>
+        <v>9.3739257729</v>
+      </c>
+      <c r="F80" s="132" t="n">
+        <f aca="false">E80+F79*$B$14</f>
+        <v>11.948269199958</v>
+      </c>
+      <c r="G80" s="132" t="n">
+        <f aca="false">F80+G79*$B$14</f>
+        <v>14.2906641053432</v>
+      </c>
+      <c r="H80" s="132" t="n">
+        <f aca="false">G80+H79*$B$14</f>
+        <v>16.5452775779384</v>
+      </c>
+      <c r="I80" s="132" t="n">
+        <f aca="false">H80+I79*$B$14</f>
+        <v>18.7221506313967</v>
+      </c>
+      <c r="J80" s="132" t="n">
+        <f aca="false">I80+J79*$B$14</f>
+        <v>20.8304532759704</v>
+      </c>
+      <c r="K80" s="132" t="n">
+        <f aca="false">J80+K79*$B$14</f>
+        <v>22.8785741545556</v>
+      </c>
+      <c r="L80" s="132" t="n">
+        <f aca="false">K80+L79*$B$14</f>
+        <v>24.8742014152315</v>
+      </c>
+    </row>
+    <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A81" s="127" t="s">
+        <v>564</v>
+      </c>
+      <c r="B81" s="132" t="n">
+        <f aca="false">$B$6+$B$9</f>
+        <v>92</v>
+      </c>
+      <c r="C81" s="132" t="n">
+        <f aca="false">C79*D$49</f>
+        <v>53.34406</v>
+      </c>
+      <c r="D81" s="132" t="n">
+        <f aca="false">D79*D$49</f>
+        <v>48.4428672</v>
+      </c>
+      <c r="E81" s="132" t="n">
+        <f aca="false">E79*D$49</f>
+        <v>44.029695934</v>
+      </c>
+      <c r="F81" s="132" t="n">
+        <f aca="false">F79*D$49</f>
+        <v>40.04534219868</v>
+      </c>
+      <c r="G81" s="132" t="n">
+        <f aca="false">G79*D$49</f>
+        <v>36.437254083769</v>
+      </c>
+      <c r="H81" s="132" t="n">
+        <f aca="false">H79*D$49</f>
+        <v>35.0717651292601</v>
+      </c>
+      <c r="I81" s="132" t="n">
+        <f aca="false">I79*D$49</f>
+        <v>33.8624697204623</v>
+      </c>
+      <c r="J81" s="132" t="n">
+        <f aca="false">J79*D$49</f>
+        <v>32.7958189155908</v>
+      </c>
+      <c r="K81" s="132" t="n">
+        <f aca="false">K79*D$49</f>
+        <v>31.8596581113255</v>
+      </c>
+      <c r="L81" s="132" t="n">
+        <f aca="false">L79*D$49</f>
+        <v>31.0430907216248</v>
+      </c>
+    </row>
+    <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A82" s="145" t="s">
+        <v>565</v>
+      </c>
+      <c r="B82" s="146" t="n">
+        <f aca="false">B81+B80-$B$9</f>
+        <v>92</v>
+      </c>
+      <c r="C82" s="146" t="n">
+        <f aca="false">C81+C80-$B$9</f>
+        <v>56.773321</v>
+      </c>
+      <c r="D82" s="146" t="n">
+        <f aca="false">D81+D80-$B$9</f>
+        <v>54.98631252</v>
+      </c>
+      <c r="E82" s="146" t="n">
+        <f aca="false">E81+E80-$B$9</f>
+        <v>53.4036217069</v>
+      </c>
+      <c r="F82" s="146" t="n">
+        <f aca="false">F81+F80-$B$9</f>
+        <v>51.993611398638</v>
+      </c>
+      <c r="G82" s="146" t="n">
+        <f aca="false">G81+G80-$B$9</f>
+        <v>50.7279181891122</v>
+      </c>
+      <c r="H82" s="146" t="n">
+        <f aca="false">H81+H80-$B$9</f>
+        <v>51.6170427071985</v>
+      </c>
+      <c r="I82" s="146" t="n">
+        <f aca="false">I81+I80-$B$9</f>
+        <v>52.5846203518591</v>
+      </c>
+      <c r="J82" s="146" t="n">
+        <f aca="false">J81+J80-$B$9</f>
+        <v>53.6262721915613</v>
+      </c>
+      <c r="K82" s="146" t="n">
+        <f aca="false">K81+K80-$B$9</f>
+        <v>54.7382322658811</v>
+      </c>
+      <c r="L82" s="146" t="n">
+        <f aca="false">L81+L80-$B$9</f>
+        <v>55.9172921368563</v>
+      </c>
+    </row>
+    <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A84" s="137" t="s">
+        <v>568</v>
+      </c>
+      <c r="B84" s="144"/>
+      <c r="C84" s="144"/>
+      <c r="D84" s="144"/>
+      <c r="E84" s="144"/>
+      <c r="F84" s="144"/>
+      <c r="G84" s="144"/>
+      <c r="H84" s="144"/>
+      <c r="I84" s="144"/>
+      <c r="J84" s="144"/>
+      <c r="K84" s="144"/>
+      <c r="L84" s="144"/>
+    </row>
+    <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A85" s="127" t="s">
+        <v>558</v>
+      </c>
+      <c r="B85" s="132" t="n">
+        <f aca="false">SUMPRODUCT($B$29:$B$36,(1+$K$29:$K$36)^B$53)</f>
+        <v>60</v>
+      </c>
+      <c r="C85" s="132" t="n">
+        <f aca="false">SUMPRODUCT($B$29:$B$36,(1+$K$29:$K$36)^C$53)</f>
+        <v>71.47</v>
+      </c>
+      <c r="D85" s="132" t="n">
+        <f aca="false">SUMPRODUCT($B$29:$B$36,(1+$K$29:$K$36)^D$53)</f>
+        <v>85.6043</v>
+      </c>
+      <c r="E85" s="132" t="n">
+        <f aca="false">SUMPRODUCT($B$29:$B$36,(1+$K$29:$K$36)^E$53)</f>
+        <v>103.080055</v>
+      </c>
+      <c r="F85" s="132" t="n">
+        <f aca="false">SUMPRODUCT($B$29:$B$36,(1+$K$29:$K$36)^F$53)</f>
+        <v>124.75993115</v>
+      </c>
+      <c r="G85" s="132" t="n">
+        <f aca="false">SUMPRODUCT($B$29:$B$36,(1+$K$29:$K$36)^G$53)</f>
+        <v>151.7459966047</v>
+      </c>
+      <c r="H85" s="132" t="n">
+        <f aca="false">SUMPRODUCT($B$29:$B$36,(1+$K$29:$K$36)^H$53)</f>
+        <v>185.449939221443</v>
+      </c>
+      <c r="I85" s="132" t="n">
+        <f aca="false">SUMPRODUCT($B$29:$B$36,(1+$K$29:$K$36)^I$53)</f>
+        <v>227.684700503528</v>
+      </c>
+      <c r="J85" s="132" t="n">
+        <f aca="false">SUMPRODUCT($B$29:$B$36,(1+$K$29:$K$36)^J$53)</f>
+        <v>280.784231924419</v>
+      </c>
+      <c r="K85" s="132" t="n">
+        <f aca="false">SUMPRODUCT($B$29:$B$36,(1+$K$29:$K$36)^K$53)</f>
+        <v>347.760216570099</v>
+      </c>
+      <c r="L85" s="132" t="n">
+        <f aca="false">SUMPRODUCT($B$29:$B$36,(1+$K$29:$K$36)^L$53)</f>
+        <v>432.507424628937</v>
+      </c>
+    </row>
+    <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A86" s="127" t="s">
         <v>559</v>
       </c>
-      <c r="B79" s="148" t="n">
+      <c r="B86" s="132" t="n">
+        <f aca="false">E$43*MIN(MAX(B$53-E$42+1,0)/E$44,1)</f>
+        <v>0</v>
+      </c>
+      <c r="C86" s="132" t="n">
+        <f aca="false">E$43*MIN(MAX(C$53-E$42+1,0)/E$44,1)</f>
+        <v>0</v>
+      </c>
+      <c r="D86" s="132" t="n">
+        <f aca="false">E$43*MIN(MAX(D$53-E$42+1,0)/E$44,1)</f>
+        <v>24</v>
+      </c>
+      <c r="E86" s="132" t="n">
+        <f aca="false">E$43*MIN(MAX(E$53-E$42+1,0)/E$44,1)</f>
+        <v>24</v>
+      </c>
+      <c r="F86" s="132" t="n">
+        <f aca="false">E$43*MIN(MAX(F$53-E$42+1,0)/E$44,1)</f>
+        <v>24</v>
+      </c>
+      <c r="G86" s="132" t="n">
+        <f aca="false">E$43*MIN(MAX(G$53-E$42+1,0)/E$44,1)</f>
+        <v>24</v>
+      </c>
+      <c r="H86" s="132" t="n">
+        <f aca="false">E$43*MIN(MAX(H$53-E$42+1,0)/E$44,1)</f>
+        <v>24</v>
+      </c>
+      <c r="I86" s="132" t="n">
+        <f aca="false">E$43*MIN(MAX(I$53-E$42+1,0)/E$44,1)</f>
+        <v>24</v>
+      </c>
+      <c r="J86" s="132" t="n">
+        <f aca="false">E$43*MIN(MAX(J$53-E$42+1,0)/E$44,1)</f>
+        <v>24</v>
+      </c>
+      <c r="K86" s="132" t="n">
+        <f aca="false">E$43*MIN(MAX(K$53-E$42+1,0)/E$44,1)</f>
+        <v>24</v>
+      </c>
+      <c r="L86" s="132" t="n">
+        <f aca="false">E$43*MIN(MAX(L$53-E$42+1,0)/E$44,1)</f>
+        <v>24</v>
+      </c>
+    </row>
+    <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A87" s="145" t="s">
+        <v>560</v>
+      </c>
+      <c r="B87" s="146" t="n">
+        <f aca="false">B85+B86</f>
+        <v>60</v>
+      </c>
+      <c r="C87" s="146" t="n">
+        <f aca="false">C85+C86</f>
+        <v>71.47</v>
+      </c>
+      <c r="D87" s="146" t="n">
+        <f aca="false">D85+D86</f>
+        <v>109.6043</v>
+      </c>
+      <c r="E87" s="146" t="n">
+        <f aca="false">E85+E86</f>
+        <v>127.080055</v>
+      </c>
+      <c r="F87" s="146" t="n">
+        <f aca="false">F85+F86</f>
+        <v>148.75993115</v>
+      </c>
+      <c r="G87" s="146" t="n">
+        <f aca="false">G85+G86</f>
+        <v>175.7459966047</v>
+      </c>
+      <c r="H87" s="146" t="n">
+        <f aca="false">H85+H86</f>
+        <v>209.449939221443</v>
+      </c>
+      <c r="I87" s="146" t="n">
+        <f aca="false">I85+I86</f>
+        <v>251.684700503528</v>
+      </c>
+      <c r="J87" s="146" t="n">
+        <f aca="false">J85+J86</f>
+        <v>304.784231924419</v>
+      </c>
+      <c r="K87" s="146" t="n">
+        <f aca="false">K85+K86</f>
+        <v>371.760216570099</v>
+      </c>
+      <c r="L87" s="146" t="n">
+        <f aca="false">L85+L86</f>
+        <v>456.507424628937</v>
+      </c>
+    </row>
+    <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A88" s="127" t="s">
+        <v>561</v>
+      </c>
+      <c r="B88" s="130" t="n">
+        <f aca="false">$B$11+(E$48-$B$11)*MIN(B$53/$B$15,1)</f>
+        <v>0.14</v>
+      </c>
+      <c r="C88" s="130" t="n">
+        <f aca="false">$B$11+(E$48-$B$11)*MIN(C$53/$B$15,1)</f>
+        <v>0.148</v>
+      </c>
+      <c r="D88" s="130" t="n">
+        <f aca="false">$B$11+(E$48-$B$11)*MIN(D$53/$B$15,1)</f>
+        <v>0.156</v>
+      </c>
+      <c r="E88" s="130" t="n">
+        <f aca="false">$B$11+(E$48-$B$11)*MIN(E$53/$B$15,1)</f>
+        <v>0.164</v>
+      </c>
+      <c r="F88" s="130" t="n">
+        <f aca="false">$B$11+(E$48-$B$11)*MIN(F$53/$B$15,1)</f>
+        <v>0.172</v>
+      </c>
+      <c r="G88" s="130" t="n">
+        <f aca="false">$B$11+(E$48-$B$11)*MIN(G$53/$B$15,1)</f>
+        <v>0.18</v>
+      </c>
+      <c r="H88" s="130" t="n">
+        <f aca="false">$B$11+(E$48-$B$11)*MIN(H$53/$B$15,1)</f>
+        <v>0.18</v>
+      </c>
+      <c r="I88" s="130" t="n">
+        <f aca="false">$B$11+(E$48-$B$11)*MIN(I$53/$B$15,1)</f>
+        <v>0.18</v>
+      </c>
+      <c r="J88" s="130" t="n">
+        <f aca="false">$B$11+(E$48-$B$11)*MIN(J$53/$B$15,1)</f>
+        <v>0.18</v>
+      </c>
+      <c r="K88" s="130" t="n">
+        <f aca="false">$B$11+(E$48-$B$11)*MIN(K$53/$B$15,1)</f>
+        <v>0.18</v>
+      </c>
+      <c r="L88" s="130" t="n">
+        <f aca="false">$B$11+(E$48-$B$11)*MIN(L$53/$B$15,1)</f>
+        <v>0.18</v>
+      </c>
+    </row>
+    <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A89" s="127" t="s">
+        <v>562</v>
+      </c>
+      <c r="B89" s="132" t="n">
+        <f aca="false">B87*B88</f>
+        <v>8.4</v>
+      </c>
+      <c r="C89" s="132" t="n">
+        <f aca="false">C87*C88</f>
+        <v>10.57756</v>
+      </c>
+      <c r="D89" s="132" t="n">
+        <f aca="false">D87*D88</f>
+        <v>17.0982708</v>
+      </c>
+      <c r="E89" s="132" t="n">
+        <f aca="false">E87*E88</f>
+        <v>20.84112902</v>
+      </c>
+      <c r="F89" s="132" t="n">
+        <f aca="false">F87*F88</f>
+        <v>25.5867081578</v>
+      </c>
+      <c r="G89" s="132" t="n">
+        <f aca="false">G87*G88</f>
+        <v>31.634279388846</v>
+      </c>
+      <c r="H89" s="132" t="n">
+        <f aca="false">H87*H88</f>
+        <v>37.7009890598597</v>
+      </c>
+      <c r="I89" s="132" t="n">
+        <f aca="false">I87*I88</f>
+        <v>45.303246090635</v>
+      </c>
+      <c r="J89" s="132" t="n">
+        <f aca="false">J87*J88</f>
+        <v>54.8611617463954</v>
+      </c>
+      <c r="K89" s="132" t="n">
+        <f aca="false">K87*K88</f>
+        <v>66.9168389826178</v>
+      </c>
+      <c r="L89" s="132" t="n">
+        <f aca="false">L87*L88</f>
+        <v>82.1713364332087</v>
+      </c>
+    </row>
+    <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A90" s="127" t="s">
+        <v>563</v>
+      </c>
+      <c r="B90" s="132" t="n">
+        <v>0</v>
+      </c>
+      <c r="C90" s="132" t="n">
+        <f aca="false">B90+C89*$B$14</f>
+        <v>4.759902</v>
+      </c>
+      <c r="D90" s="132" t="n">
+        <f aca="false">C90+D89*$B$14</f>
+        <v>12.45412386</v>
+      </c>
+      <c r="E90" s="132" t="n">
+        <f aca="false">D90+E89*$B$14</f>
+        <v>21.832631919</v>
+      </c>
+      <c r="F90" s="132" t="n">
+        <f aca="false">E90+F89*$B$14</f>
+        <v>33.34665059001</v>
+      </c>
+      <c r="G90" s="132" t="n">
+        <f aca="false">F90+G89*$B$14</f>
+        <v>47.5820763149907</v>
+      </c>
+      <c r="H90" s="132" t="n">
+        <f aca="false">G90+H89*$B$14</f>
+        <v>64.5475213919276</v>
+      </c>
+      <c r="I90" s="132" t="n">
+        <f aca="false">H90+I89*$B$14</f>
+        <v>84.9339821327133</v>
+      </c>
+      <c r="J90" s="132" t="n">
+        <f aca="false">I90+J89*$B$14</f>
+        <v>109.621504918591</v>
+      </c>
+      <c r="K90" s="132" t="n">
+        <f aca="false">J90+K89*$B$14</f>
+        <v>139.734082460769</v>
+      </c>
+      <c r="L90" s="132" t="n">
+        <f aca="false">K90+L89*$B$14</f>
+        <v>176.711183855713</v>
+      </c>
+    </row>
+    <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A91" s="127" t="s">
+        <v>564</v>
+      </c>
+      <c r="B91" s="132" t="n">
+        <f aca="false">$B$6+$B$9</f>
+        <v>92</v>
+      </c>
+      <c r="C91" s="132" t="n">
+        <f aca="false">C89*E$49</f>
+        <v>137.50828</v>
+      </c>
+      <c r="D91" s="132" t="n">
+        <f aca="false">D89*E$49</f>
+        <v>222.2775204</v>
+      </c>
+      <c r="E91" s="132" t="n">
+        <f aca="false">E89*E$49</f>
+        <v>270.93467726</v>
+      </c>
+      <c r="F91" s="132" t="n">
+        <f aca="false">F89*E$49</f>
+        <v>332.6272060514</v>
+      </c>
+      <c r="G91" s="132" t="n">
+        <f aca="false">G89*E$49</f>
+        <v>411.245632054998</v>
+      </c>
+      <c r="H91" s="132" t="n">
+        <f aca="false">H89*E$49</f>
+        <v>490.112857778177</v>
+      </c>
+      <c r="I91" s="132" t="n">
+        <f aca="false">I89*E$49</f>
+        <v>588.942199178255</v>
+      </c>
+      <c r="J91" s="132" t="n">
+        <f aca="false">J89*E$49</f>
+        <v>713.19510270314</v>
+      </c>
+      <c r="K91" s="132" t="n">
+        <f aca="false">K89*E$49</f>
+        <v>869.918906774031</v>
+      </c>
+      <c r="L91" s="132" t="n">
+        <f aca="false">L89*E$49</f>
+        <v>1068.22737363171</v>
+      </c>
+    </row>
+    <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A92" s="145" t="s">
+        <v>565</v>
+      </c>
+      <c r="B92" s="146" t="n">
+        <f aca="false">B91+B90-$B$9</f>
+        <v>92</v>
+      </c>
+      <c r="C92" s="146" t="n">
+        <f aca="false">C91+C90-$B$9</f>
+        <v>142.268182</v>
+      </c>
+      <c r="D92" s="146" t="n">
+        <f aca="false">D91+D90-$B$9</f>
+        <v>234.73164426</v>
+      </c>
+      <c r="E92" s="146" t="n">
+        <f aca="false">E91+E90-$B$9</f>
+        <v>292.767309179</v>
+      </c>
+      <c r="F92" s="146" t="n">
+        <f aca="false">F91+F90-$B$9</f>
+        <v>365.97385664141</v>
+      </c>
+      <c r="G92" s="146" t="n">
+        <f aca="false">G91+G90-$B$9</f>
+        <v>458.827708369989</v>
+      </c>
+      <c r="H92" s="146" t="n">
+        <f aca="false">H91+H90-$B$9</f>
+        <v>554.660379170104</v>
+      </c>
+      <c r="I92" s="146" t="n">
+        <f aca="false">I91+I90-$B$9</f>
+        <v>673.876181310968</v>
+      </c>
+      <c r="J92" s="146" t="n">
+        <f aca="false">J91+J90-$B$9</f>
+        <v>822.816607621731</v>
+      </c>
+      <c r="K92" s="146" t="n">
+        <f aca="false">K91+K90-$B$9</f>
+        <v>1009.6529892348</v>
+      </c>
+      <c r="L92" s="146" t="n">
+        <f aca="false">L91+L90-$B$9</f>
+        <v>1244.93855748743</v>
+      </c>
+    </row>
+    <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A94" s="60" t="s">
+        <v>569</v>
+      </c>
+      <c r="B94" s="125"/>
+      <c r="C94" s="125"/>
+      <c r="D94" s="125"/>
+      <c r="E94" s="125"/>
+      <c r="F94" s="125"/>
+      <c r="G94" s="125"/>
+      <c r="H94" s="125"/>
+      <c r="I94" s="125"/>
+      <c r="J94" s="125"/>
+      <c r="K94" s="125"/>
+      <c r="L94" s="125"/>
+      <c r="M94" s="125"/>
+    </row>
+    <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A95" s="126" t="s">
+        <v>27</v>
+      </c>
+      <c r="B95" s="126" t="s">
+        <v>570</v>
+      </c>
+      <c r="C95" s="126" t="s">
+        <v>36</v>
+      </c>
+      <c r="D95" s="126" t="s">
+        <v>37</v>
+      </c>
+      <c r="E95" s="126" t="s">
+        <v>38</v>
+      </c>
+      <c r="F95" s="126" t="s">
+        <v>39</v>
+      </c>
+      <c r="G95" s="126" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A96" s="127" t="s">
+        <v>571</v>
+      </c>
+      <c r="B96" s="147" t="n">
+        <v>5</v>
+      </c>
+      <c r="C96" s="130" t="n">
+        <f aca="false">(G62/$B$6)^(1/$B96)-1</f>
+        <v>0.189162723270954</v>
+      </c>
+      <c r="D96" s="130" t="n">
+        <f aca="false">(G72/$B$6)^(1/$B96)-1</f>
+        <v>0.388664531401775</v>
+      </c>
+      <c r="E96" s="130" t="n">
+        <f aca="false">(G82/$B$6)^(1/$B96)-1</f>
+        <v>-0.11224762572618</v>
+      </c>
+      <c r="F96" s="130" t="n">
+        <f aca="false">(G92/$B$6)^(1/$B96)-1</f>
+        <v>0.379025706305739</v>
+      </c>
+      <c r="G96" s="130" t="n">
+        <f aca="false">C96*'Defense Supercycle'!$B$17+D96*'Defense Supercycle'!$B$18+E96*'Defense Supercycle'!$B$19+F96*'Defense Supercycle'!$B$20</f>
+        <v>0.222306070409307</v>
+      </c>
+    </row>
+    <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A97" s="145" t="s">
+        <v>572</v>
+      </c>
+      <c r="B97" s="147" t="n">
+        <v>7</v>
+      </c>
+      <c r="C97" s="148" t="n">
+        <f aca="false">(I62/$B$6)^(1/$B97)-1</f>
+        <v>0.169202814424438</v>
+      </c>
+      <c r="D97" s="148" t="n">
+        <f aca="false">(I72/$B$6)^(1/$B97)-1</f>
+        <v>0.330194842742812</v>
+      </c>
+      <c r="E97" s="148" t="n">
+        <f aca="false">(I82/$B$6)^(1/$B97)-1</f>
+        <v>-0.076799895310316</v>
+      </c>
+      <c r="F97" s="148" t="n">
+        <f aca="false">(I92/$B$6)^(1/$B97)-1</f>
+        <v>0.32905132917649</v>
+      </c>
+      <c r="G97" s="130" t="n">
+        <f aca="false">C97*'Defense Supercycle'!$B$17+D97*'Defense Supercycle'!$B$18+E97*'Defense Supercycle'!$B$19+F97*'Defense Supercycle'!$B$20</f>
+        <v>0.196527692256626</v>
+      </c>
+    </row>
+    <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A98" s="127" t="s">
+        <v>573</v>
+      </c>
+      <c r="B98" s="147" t="n">
+        <v>10</v>
+      </c>
+      <c r="C98" s="130" t="n">
+        <f aca="false">(L62/$B$6)^(1/$B98)-1</f>
+        <v>0.155205848742441</v>
+      </c>
+      <c r="D98" s="130" t="n">
+        <f aca="false">(L72/$B$6)^(1/$B98)-1</f>
+        <v>0.291442584076479</v>
+      </c>
+      <c r="E98" s="130" t="n">
+        <f aca="false">(L82/$B$6)^(1/$B98)-1</f>
+        <v>-0.0485722143694491</v>
+      </c>
+      <c r="F98" s="130" t="n">
+        <f aca="false">(L92/$B$6)^(1/$B98)-1</f>
+        <v>0.297585575365068</v>
+      </c>
+      <c r="G98" s="130" t="n">
+        <f aca="false">C98*'Defense Supercycle'!$B$17+D98*'Defense Supercycle'!$B$18+E98*'Defense Supercycle'!$B$19+F98*'Defense Supercycle'!$B$20</f>
+        <v>0.180055282102561</v>
+      </c>
+    </row>
+    <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A99" s="127" t="s">
+        <v>574</v>
+      </c>
+      <c r="C99" s="132" t="n">
+        <f aca="false">I57</f>
+        <v>129.280705554175</v>
+      </c>
+      <c r="D99" s="132" t="n">
+        <f aca="false">I67</f>
+        <v>224.394532267048</v>
+      </c>
+      <c r="E99" s="132" t="n">
+        <f aca="false">I77</f>
+        <v>43.9772334031978</v>
+      </c>
+      <c r="F99" s="132" t="n">
+        <f aca="false">I87</f>
+        <v>251.684700503528</v>
+      </c>
+      <c r="G99" s="132" t="n">
+        <f aca="false">C99*'Defense Supercycle'!$B$17+D99*'Defense Supercycle'!$B$18+E99*'Defense Supercycle'!$B$19+F99*'Defense Supercycle'!$B$20</f>
+        <v>158.62424065215</v>
+      </c>
+    </row>
+    <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A100" s="127" t="s">
+        <v>575</v>
+      </c>
+      <c r="C100" s="130" t="n">
+        <f aca="false">I56/I57</f>
+        <v>0.0928212755999492</v>
+      </c>
+      <c r="D100" s="130" t="n">
+        <f aca="false">I66/I67</f>
+        <v>0.0891287314264786</v>
+      </c>
+      <c r="E100" s="130" t="n">
+        <f aca="false">I76/I77</f>
+        <v>0</v>
+      </c>
+      <c r="F100" s="130" t="n">
+        <f aca="false">I86/I87</f>
+        <v>0.0953574053249359</v>
+      </c>
+    </row>
+    <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A102" s="60" t="s">
+        <v>576</v>
+      </c>
+      <c r="B102" s="125"/>
+      <c r="C102" s="125"/>
+      <c r="D102" s="125"/>
+      <c r="E102" s="125"/>
+      <c r="F102" s="125"/>
+      <c r="G102" s="125"/>
+      <c r="H102" s="125"/>
+      <c r="I102" s="125"/>
+      <c r="J102" s="125"/>
+      <c r="K102" s="125"/>
+      <c r="L102" s="125"/>
+      <c r="M102" s="125"/>
+    </row>
+    <row r="103" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A103" s="126" t="s">
+        <v>577</v>
+      </c>
+      <c r="B103" s="126" t="s">
+        <v>248</v>
+      </c>
+      <c r="C103" s="126" t="s">
+        <v>356</v>
+      </c>
+      <c r="D103" s="126" t="s">
+        <v>359</v>
+      </c>
+      <c r="E103" s="126" t="s">
+        <v>362</v>
+      </c>
+      <c r="F103" s="126" t="s">
+        <v>578</v>
+      </c>
+      <c r="G103" s="126" t="s">
+        <v>579</v>
+      </c>
+      <c r="H103" s="126" t="s">
+        <v>580</v>
+      </c>
+      <c r="I103" s="126" t="s">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="104" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A104" s="127" t="s">
+        <v>582</v>
+      </c>
+      <c r="B104" s="149" t="n">
         <f aca="false">'Weapons Sleeve'!B35</f>
         <v>9</v>
       </c>
-      <c r="C79" s="148" t="n">
+      <c r="C104" s="149" t="n">
         <f aca="false">'Weapons Sleeve'!C35</f>
-        <v>17.1941290634076</v>
-      </c>
-      <c r="D79" s="148" t="n">
+        <v>18.0917091503932</v>
+      </c>
+      <c r="D104" s="149" t="n">
         <f aca="false">'Weapons Sleeve'!F35</f>
-        <v>35.0525060947374</v>
-      </c>
-      <c r="E79" s="148" t="n">
+        <v>34.4831264997212</v>
+      </c>
+      <c r="E104" s="149" t="n">
         <f aca="false">'Weapons Sleeve'!I35</f>
-        <v>5.47925806429684</v>
-      </c>
-      <c r="F79" s="148" t="n">
+        <v>5.55276842801235</v>
+      </c>
+      <c r="F104" s="149" t="n">
         <f aca="false">'Weapons Sleeve'!L35</f>
-        <v>31.9898455814136</v>
-      </c>
-      <c r="G79" s="145" t="n">
-        <f aca="false">C79*'Defense Supercycle'!$B$17+D79*'Defense Supercycle'!$B$18+E79*'Defense Supercycle'!$B$19+F79*'Defense Supercycle'!$B$20</f>
-        <v>22.1208501490744</v>
-      </c>
-      <c r="H79" s="149" t="n">
-        <f aca="false">G79/B79</f>
-        <v>2.45787223878604</v>
-      </c>
-      <c r="I79" s="150" t="n">
-        <f aca="false">H79^(1/5)-1</f>
-        <v>0.197048814464429</v>
-      </c>
-    </row>
-    <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A80" s="127" t="s">
-        <v>560</v>
-      </c>
-      <c r="B80" s="148" t="n">
+        <v>34.3351625174457</v>
+      </c>
+      <c r="G104" s="146" t="n">
+        <f aca="false">C104*'Defense Supercycle'!$B$17+D104*'Defense Supercycle'!$B$18+E104*'Defense Supercycle'!$B$19+F104*'Defense Supercycle'!$B$20</f>
+        <v>22.7452403844259</v>
+      </c>
+      <c r="H104" s="150" t="n">
+        <f aca="false">G104/B104</f>
+        <v>2.52724893160288</v>
+      </c>
+      <c r="I104" s="140" t="n">
+        <f aca="false">H104^(1/5)-1</f>
+        <v>0.203731441122826</v>
+      </c>
+    </row>
+    <row r="105" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A105" s="127" t="s">
+        <v>583</v>
+      </c>
+      <c r="B105" s="149" t="n">
         <f aca="false">'Weapons Sleeve'!B50</f>
         <v>9</v>
       </c>
-      <c r="C80" s="148" t="n">
+      <c r="C105" s="149" t="n">
         <f aca="false">'Weapons Sleeve'!C50</f>
-        <v>22.0300237504834</v>
-      </c>
-      <c r="D80" s="148" t="n">
+        <v>23.6566991160678</v>
+      </c>
+      <c r="D105" s="149" t="n">
         <f aca="false">'Weapons Sleeve'!F50</f>
-        <v>59.7158217457192</v>
-      </c>
-      <c r="E80" s="148" t="n">
+        <v>58.3622463674085</v>
+      </c>
+      <c r="E105" s="149" t="n">
         <f aca="false">'Weapons Sleeve'!I50</f>
-        <v>4.44317243177915</v>
-      </c>
-      <c r="F80" s="148" t="n">
+        <v>4.52684992594265</v>
+      </c>
+      <c r="F105" s="149" t="n">
         <f aca="false">'Weapons Sleeve'!L50</f>
-        <v>52.541166580511</v>
-      </c>
-      <c r="G80" s="145" t="n">
-        <f aca="false">C80*'Defense Supercycle'!$B$17+D80*'Defense Supercycle'!$B$18+E80*'Defense Supercycle'!$B$19+F80*'Defense Supercycle'!$B$20</f>
-        <v>33.3901169759909</v>
-      </c>
-      <c r="H80" s="149" t="n">
-        <f aca="false">G80/B80</f>
-        <v>3.71001299733232</v>
-      </c>
-      <c r="I80" s="150" t="n">
-        <f aca="false">H80^(1/7)-1</f>
-        <v>0.205977894533109</v>
-      </c>
-    </row>
-    <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A81" s="127" t="s">
-        <v>561</v>
-      </c>
-      <c r="B81" s="148" t="n">
+        <v>58.0119495215529</v>
+      </c>
+      <c r="G105" s="146" t="n">
+        <f aca="false">C105*'Defense Supercycle'!$B$17+D105*'Defense Supercycle'!$B$18+E105*'Defense Supercycle'!$B$19+F105*'Defense Supercycle'!$B$20</f>
+        <v>34.616896111207</v>
+      </c>
+      <c r="H105" s="150" t="n">
+        <f aca="false">G105/B105</f>
+        <v>3.84632179013411</v>
+      </c>
+      <c r="I105" s="140" t="n">
+        <f aca="false">H105^(1/7)-1</f>
+        <v>0.212210230786541</v>
+      </c>
+    </row>
+    <row r="106" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A106" s="127" t="s">
+        <v>584</v>
+      </c>
+      <c r="B106" s="149" t="n">
         <f aca="false">'Weapons Sleeve'!B65</f>
         <v>9</v>
       </c>
-      <c r="C81" s="148" t="n">
+      <c r="C106" s="149" t="n">
         <f aca="false">'Weapons Sleeve'!C65</f>
-        <v>31.824094318982</v>
-      </c>
-      <c r="D81" s="148" t="n">
+        <v>35.2334266416698</v>
+      </c>
+      <c r="D106" s="149" t="n">
         <f aca="false">'Weapons Sleeve'!F65</f>
-        <v>132.261619209163</v>
-      </c>
-      <c r="E81" s="148" t="n">
+        <v>127.999702113597</v>
+      </c>
+      <c r="E106" s="149" t="n">
         <f aca="false">'Weapons Sleeve'!I65</f>
-        <v>3.23176072868525</v>
-      </c>
-      <c r="F81" s="148" t="n">
+        <v>3.31905777625593</v>
+      </c>
+      <c r="F106" s="149" t="n">
         <f aca="false">'Weapons Sleeve'!L65</f>
-        <v>110.158997671787</v>
-      </c>
-      <c r="G81" s="145" t="n">
-        <f aca="false">C81*'Defense Supercycle'!$B$17+D81*'Defense Supercycle'!$B$18+E81*'Defense Supercycle'!$B$19+F81*'Defense Supercycle'!$B$20</f>
-        <v>64.3948610059034</v>
-      </c>
-      <c r="H81" s="149" t="n">
-        <f aca="false">G81/B81</f>
-        <v>7.15498455621149</v>
-      </c>
-      <c r="I81" s="150" t="n">
-        <f aca="false">H81^(1/10)-1</f>
-        <v>0.217477293203526</v>
-      </c>
-    </row>
-    <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A82" s="127" t="s">
-        <v>562</v>
-      </c>
-      <c r="C82" s="151" t="n">
+        <v>126.903588503139</v>
+      </c>
+      <c r="G106" s="146" t="n">
+        <f aca="false">C106*'Defense Supercycle'!$B$17+D106*'Defense Supercycle'!$B$18+E106*'Defense Supercycle'!$B$19+F106*'Defense Supercycle'!$B$20</f>
+        <v>67.3883644590599</v>
+      </c>
+      <c r="H106" s="150" t="n">
+        <f aca="false">G106/B106</f>
+        <v>7.48759605100665</v>
+      </c>
+      <c r="I106" s="140" t="n">
+        <f aca="false">H106^(1/10)-1</f>
+        <v>0.223021919351566</v>
+      </c>
+    </row>
+    <row r="107" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A107" s="127" t="s">
+        <v>585</v>
+      </c>
+      <c r="C107" s="151" t="n">
         <f aca="false">'Weapons Sleeve'!D50</f>
-        <v>2.44778041672038</v>
-      </c>
-      <c r="D82" s="151" t="n">
+        <v>2.62852212400753</v>
+      </c>
+      <c r="D107" s="151" t="n">
         <f aca="false">'Weapons Sleeve'!G50</f>
-        <v>6.63509130507991</v>
-      </c>
-      <c r="E82" s="151" t="n">
+        <v>6.48469404082317</v>
+      </c>
+      <c r="E107" s="151" t="n">
         <f aca="false">'Weapons Sleeve'!J50</f>
-        <v>0.493685825753239</v>
-      </c>
-      <c r="F82" s="151" t="n">
+        <v>0.502983325104739</v>
+      </c>
+      <c r="F107" s="151" t="n">
         <f aca="false">'Weapons Sleeve'!M50</f>
-        <v>5.83790739783455</v>
-      </c>
-    </row>
-    <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A84" s="60" t="s">
-        <v>563</v>
-      </c>
-      <c r="B84" s="125"/>
-      <c r="C84" s="125"/>
-      <c r="D84" s="125"/>
-      <c r="E84" s="125"/>
-      <c r="F84" s="125"/>
-      <c r="G84" s="125"/>
-      <c r="H84" s="125"/>
-      <c r="I84" s="125"/>
-      <c r="J84" s="125"/>
-      <c r="K84" s="125"/>
-      <c r="L84" s="125"/>
-      <c r="M84" s="125"/>
-    </row>
-    <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A85" s="127" t="s">
-        <v>564</v>
-      </c>
-      <c r="B85" s="144" t="str">
-        <f aca="false">IF(ABS('Weapons Sleeve'!S21-C74)&lt;0.00001,"OK","CHECK")</f>
+        <v>6.44577216906144</v>
+      </c>
+    </row>
+    <row r="109" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A109" s="60" t="s">
+        <v>586</v>
+      </c>
+      <c r="B109" s="125"/>
+      <c r="C109" s="125"/>
+      <c r="D109" s="125"/>
+      <c r="E109" s="125"/>
+      <c r="F109" s="125"/>
+      <c r="G109" s="125"/>
+      <c r="H109" s="125"/>
+      <c r="I109" s="125"/>
+      <c r="J109" s="125"/>
+      <c r="K109" s="125"/>
+      <c r="L109" s="125"/>
+      <c r="M109" s="125"/>
+    </row>
+    <row r="110" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A110" s="127" t="s">
+        <v>587</v>
+      </c>
+      <c r="B110" s="145" t="str">
+        <f aca="false">IF(ABS('Weapons Sleeve'!S21-C97)&lt;0.00001,"OK","CHECK")</f>
         <v>OK</v>
       </c>
     </row>
-    <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A86" s="127" t="s">
-        <v>565</v>
-      </c>
-      <c r="B86" s="144" t="str">
+    <row r="111" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A111" s="127" t="s">
+        <v>588</v>
+      </c>
+      <c r="B111" s="145" t="str">
         <f aca="false">IF(ABS('Weapons Sleeve'!C22-'Weapons Sleeve'!B5)&lt;0.001,"OK","CHECK")</f>
         <v>OK</v>
       </c>
     </row>
-    <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A87" s="127" t="s">
-        <v>566</v>
-      </c>
-      <c r="B87" s="144" t="str">
+    <row r="112" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A112" s="127" t="s">
+        <v>589</v>
+      </c>
+      <c r="B112" s="145" t="str">
         <f aca="false">IF(B7&lt;10,"OK","CHECK")</f>
         <v>OK</v>
       </c>
     </row>
-    <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A88" s="127" t="s">
-        <v>567</v>
-      </c>
-      <c r="B88" s="144" t="str">
-        <f aca="false">IF(ABS(B32-B10)&lt;0.001,"OK","CHECK")</f>
+    <row r="113" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A113" s="127" t="s">
+        <v>590</v>
+      </c>
+      <c r="B113" s="145" t="str">
+        <f aca="false">IF(ABS(L37-1)&lt;0.0001,"OK","CHECK")</f>
         <v>OK</v>
       </c>
     </row>
-    <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A90" s="60" t="s">
+    <row r="115" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A115" s="60" t="s">
         <v>78</v>
       </c>
-      <c r="B90" s="125"/>
-      <c r="C90" s="125"/>
-      <c r="D90" s="125"/>
-      <c r="E90" s="125"/>
-      <c r="F90" s="125"/>
-      <c r="G90" s="125"/>
-      <c r="H90" s="125"/>
-      <c r="I90" s="125"/>
-      <c r="J90" s="125"/>
-      <c r="K90" s="125"/>
-      <c r="L90" s="125"/>
-      <c r="M90" s="125"/>
-    </row>
-    <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A91" s="152" t="str">
+      <c r="B115" s="125"/>
+      <c r="C115" s="125"/>
+      <c r="D115" s="125"/>
+      <c r="E115" s="125"/>
+      <c r="F115" s="125"/>
+      <c r="G115" s="125"/>
+      <c r="H115" s="125"/>
+      <c r="I115" s="125"/>
+      <c r="J115" s="125"/>
+      <c r="K115" s="125"/>
+      <c r="L115" s="125"/>
+      <c r="M115" s="125"/>
+    </row>
+    <row r="116" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A116" s="152" t="str">
         <f aca="false">"• Entry: $"&amp;TEXT(B7,"0.0")&amp;"M for "&amp;TEXT(B8,"0.0%")&amp;" at $"&amp;TEXT(B6,"0")&amp;"M post = "&amp;TEXT(B13,"0.0")&amp;"x FY26E EBITDA of $"&amp;TEXT(B12,"0.0")&amp;"M."</f>
         <v>• Entry: $9.0M for 9.8% at $92M post = 11.0x FY26E EBITDA of $8.4M.</v>
       </c>
-      <c r="B91" s="152"/>
-      <c r="C91" s="152"/>
-      <c r="D91" s="152"/>
-      <c r="E91" s="152"/>
-      <c r="F91" s="152"/>
-      <c r="G91" s="152"/>
-      <c r="H91" s="152"/>
-      <c r="I91" s="152"/>
-      <c r="J91" s="152"/>
-      <c r="K91" s="152"/>
-      <c r="L91" s="152"/>
-      <c r="M91" s="152"/>
-    </row>
-    <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A92" s="152" t="str">
-        <f aca="false">"• 7-yr implied equity CAGR: Base "&amp;TEXT(C74,"0.0%")&amp;" / Bull "&amp;TEXT(D74,"0.0%")&amp;" / Bear "&amp;TEXT(E74,"0.0%")&amp;" / Shock "&amp;TEXT(F74,"0.0%")&amp;"; probability-weighted "&amp;TEXT(G74,"0.0%")&amp;"."</f>
-        <v>• 7-yr implied equity CAGR: Base 15.7% / Bull 33.5% / Bear -7.9% / Shock 31.0%; probability-weighted 18.9%.</v>
-      </c>
-      <c r="B92" s="152"/>
-      <c r="C92" s="152"/>
-      <c r="D92" s="152"/>
-      <c r="E92" s="152"/>
-      <c r="F92" s="152"/>
-      <c r="G92" s="152"/>
-      <c r="H92" s="152"/>
-      <c r="I92" s="152"/>
-      <c r="J92" s="152"/>
-      <c r="K92" s="152"/>
-      <c r="L92" s="152"/>
-      <c r="M92" s="152"/>
-    </row>
-    <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A93" s="152" t="str">
-        <f aca="false">"• 7-yr stake Expected proceeds $"&amp;TEXT(G80,"0.0")&amp;"M on $"&amp;TEXT(B80,"0.0")&amp;"M = "&amp;TEXT(H80,"0.00")&amp;"x / "&amp;TEXT(I80,"0.0%")&amp;" gross IRR (after 0.88 retention)."</f>
-        <v>• 7-yr stake Expected proceeds $33.4M on $9.0M = 3.71x / 20.6% gross IRR (after 0.88 retention).</v>
-      </c>
-      <c r="B93" s="152"/>
-      <c r="C93" s="152"/>
-      <c r="D93" s="152"/>
-      <c r="E93" s="152"/>
-      <c r="F93" s="152"/>
-      <c r="G93" s="152"/>
-      <c r="H93" s="152"/>
-      <c r="I93" s="152"/>
-      <c r="J93" s="152"/>
-      <c r="K93" s="152"/>
-      <c r="L93" s="152"/>
-      <c r="M93" s="152"/>
-    </row>
-    <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A94" s="152" t="s">
-        <v>568</v>
-      </c>
-      <c r="B94" s="152"/>
-      <c r="C94" s="152"/>
-      <c r="D94" s="152"/>
-      <c r="E94" s="152"/>
-      <c r="F94" s="152"/>
-      <c r="G94" s="152"/>
-      <c r="H94" s="152"/>
-      <c r="I94" s="152"/>
-      <c r="J94" s="152"/>
-      <c r="K94" s="152"/>
-      <c r="L94" s="152"/>
-      <c r="M94" s="152"/>
-    </row>
-    <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A95" s="152" t="s">
-        <v>569</v>
-      </c>
-      <c r="B95" s="152"/>
-      <c r="C95" s="152"/>
-      <c r="D95" s="152"/>
-      <c r="E95" s="152"/>
-      <c r="F95" s="152"/>
-      <c r="G95" s="152"/>
-      <c r="H95" s="152"/>
-      <c r="I95" s="152"/>
-      <c r="J95" s="152"/>
-      <c r="K95" s="152"/>
-      <c r="L95" s="152"/>
-      <c r="M95" s="152"/>
+      <c r="B116" s="152"/>
+      <c r="C116" s="152"/>
+      <c r="D116" s="152"/>
+      <c r="E116" s="152"/>
+      <c r="F116" s="152"/>
+      <c r="G116" s="152"/>
+      <c r="H116" s="152"/>
+      <c r="I116" s="152"/>
+      <c r="J116" s="152"/>
+      <c r="K116" s="152"/>
+      <c r="L116" s="152"/>
+      <c r="M116" s="152"/>
+    </row>
+    <row r="117" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A117" s="152" t="str">
+        <f aca="false">"• Program mix FY26E: BLU-136/B "&amp;TEXT(L29,"0%")&amp;"; NGP + MOP + TLAM "&amp;TEXT(L38,"0%")&amp;". NGP production step adds $"&amp;TEXT(B43,"0")&amp;"M/yr at full rate in Base from year "&amp;B42&amp;"."</f>
+        <v>• Program mix FY26E: BLU-136/B 50%; NGP + MOP + TLAM 22%. NGP production step adds $12M/yr at full rate in Base from year 3.</v>
+      </c>
+      <c r="B117" s="152"/>
+      <c r="C117" s="152"/>
+      <c r="D117" s="152"/>
+      <c r="E117" s="152"/>
+      <c r="F117" s="152"/>
+      <c r="G117" s="152"/>
+      <c r="H117" s="152"/>
+      <c r="I117" s="152"/>
+      <c r="J117" s="152"/>
+      <c r="K117" s="152"/>
+      <c r="L117" s="152"/>
+      <c r="M117" s="152"/>
+    </row>
+    <row r="118" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A118" s="152" t="str">
+        <f aca="false">"• 7-yr implied equity CAGR: Base "&amp;TEXT(C97,"0.0%")&amp;" / Bull "&amp;TEXT(D97,"0.0%")&amp;" / Bear "&amp;TEXT(E97,"0.0%")&amp;" / Shock "&amp;TEXT(F97,"0.0%")&amp;"; probability-weighted "&amp;TEXT(G97,"0.0%")&amp;"."</f>
+        <v>• 7-yr implied equity CAGR: Base 16.9% / Bull 33.0% / Bear -7.7% / Shock 32.9%; probability-weighted 19.7%.</v>
+      </c>
+      <c r="B118" s="152"/>
+      <c r="C118" s="152"/>
+      <c r="D118" s="152"/>
+      <c r="E118" s="152"/>
+      <c r="F118" s="152"/>
+      <c r="G118" s="152"/>
+      <c r="H118" s="152"/>
+      <c r="I118" s="152"/>
+      <c r="J118" s="152"/>
+      <c r="K118" s="152"/>
+      <c r="L118" s="152"/>
+      <c r="M118" s="152"/>
+    </row>
+    <row r="119" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A119" s="152" t="str">
+        <f aca="false">"• 7-yr stake Expected proceeds $"&amp;TEXT(G105,"0.0")&amp;"M on $"&amp;TEXT(B105,"0.0")&amp;"M = "&amp;TEXT(H105,"0.00")&amp;"x / "&amp;TEXT(I105,"0.0%")&amp;" gross IRR (after 0.88 retention)."</f>
+        <v>• 7-yr stake Expected proceeds $34.6M on $9.0M = 3.85x / 21.2% gross IRR (after 0.88 retention).</v>
+      </c>
+      <c r="B119" s="152"/>
+      <c r="C119" s="152"/>
+      <c r="D119" s="152"/>
+      <c r="E119" s="152"/>
+      <c r="F119" s="152"/>
+      <c r="G119" s="152"/>
+      <c r="H119" s="152"/>
+      <c r="I119" s="152"/>
+      <c r="J119" s="152"/>
+      <c r="K119" s="152"/>
+      <c r="L119" s="152"/>
+      <c r="M119" s="152"/>
+    </row>
+    <row r="120" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A120" s="152" t="s">
+        <v>591</v>
+      </c>
+      <c r="B120" s="152"/>
+      <c r="C120" s="152"/>
+      <c r="D120" s="152"/>
+      <c r="E120" s="152"/>
+      <c r="F120" s="152"/>
+      <c r="G120" s="152"/>
+      <c r="H120" s="152"/>
+      <c r="I120" s="152"/>
+      <c r="J120" s="152"/>
+      <c r="K120" s="152"/>
+      <c r="L120" s="152"/>
+      <c r="M120" s="152"/>
+    </row>
+    <row r="121" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A121" s="152" t="s">
+        <v>592</v>
+      </c>
+      <c r="B121" s="152"/>
+      <c r="C121" s="152"/>
+      <c r="D121" s="152"/>
+      <c r="E121" s="152"/>
+      <c r="F121" s="152"/>
+      <c r="G121" s="152"/>
+      <c r="H121" s="152"/>
+      <c r="I121" s="152"/>
+      <c r="J121" s="152"/>
+      <c r="K121" s="152"/>
+      <c r="L121" s="152"/>
+      <c r="M121" s="152"/>
     </row>
   </sheetData>
-  <mergeCells count="26">
+  <mergeCells count="33">
     <mergeCell ref="A2:M2"/>
     <mergeCell ref="C5:M5"/>
     <mergeCell ref="C6:M6"/>
@@ -10825,14 +11702,21 @@
     <mergeCell ref="F21:M21"/>
     <mergeCell ref="F22:M22"/>
     <mergeCell ref="F23:M23"/>
-    <mergeCell ref="F35:M35"/>
-    <mergeCell ref="F36:M36"/>
-    <mergeCell ref="F37:M37"/>
-    <mergeCell ref="A91:M91"/>
-    <mergeCell ref="A92:M92"/>
-    <mergeCell ref="A93:M93"/>
-    <mergeCell ref="A94:M94"/>
-    <mergeCell ref="A95:M95"/>
+    <mergeCell ref="F24:M24"/>
+    <mergeCell ref="F25:M25"/>
+    <mergeCell ref="F41:M41"/>
+    <mergeCell ref="F42:M42"/>
+    <mergeCell ref="F43:M43"/>
+    <mergeCell ref="F44:M44"/>
+    <mergeCell ref="F47:M47"/>
+    <mergeCell ref="F48:M48"/>
+    <mergeCell ref="F49:M49"/>
+    <mergeCell ref="A116:M116"/>
+    <mergeCell ref="A117:M117"/>
+    <mergeCell ref="A118:M118"/>
+    <mergeCell ref="A119:M119"/>
+    <mergeCell ref="A120:M120"/>
+    <mergeCell ref="A121:M121"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -10866,7 +11750,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="10" t="s">
-        <v>570</v>
+        <v>593</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -10884,7 +11768,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="41" t="s">
-        <v>571</v>
+        <v>594</v>
       </c>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -11063,7 +11947,7 @@
         <v>249</v>
       </c>
       <c r="E11" s="43" t="s">
-        <v>572</v>
+        <v>595</v>
       </c>
       <c r="F11" s="43" t="s">
         <v>36</v>
@@ -11087,7 +11971,7 @@
     </row>
     <row r="12" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="44" t="s">
-        <v>573</v>
+        <v>596</v>
       </c>
       <c r="B12" s="79" t="n">
         <v>10100</v>
@@ -11100,7 +11984,7 @@
         <v>0.00346534653465347</v>
       </c>
       <c r="E12" s="47" t="s">
-        <v>574</v>
+        <v>597</v>
       </c>
       <c r="F12" s="80" t="n">
         <v>0.28</v>
@@ -11115,7 +11999,7 @@
         <v>-0.18</v>
       </c>
       <c r="J12" s="75" t="s">
-        <v>575</v>
+        <v>598</v>
       </c>
       <c r="K12" s="1"/>
       <c r="L12" s="1"/>
@@ -11124,7 +12008,7 @@
     </row>
     <row r="13" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="44" t="s">
-        <v>576</v>
+        <v>599</v>
       </c>
       <c r="B13" s="79" t="n">
         <v>10100</v>
@@ -11137,7 +12021,7 @@
         <v>0.00311881188118812</v>
       </c>
       <c r="E13" s="47" t="s">
-        <v>577</v>
+        <v>600</v>
       </c>
       <c r="F13" s="80" t="n">
         <v>0.27</v>
@@ -11152,7 +12036,7 @@
         <v>-0.16</v>
       </c>
       <c r="J13" s="75" t="s">
-        <v>578</v>
+        <v>601</v>
       </c>
       <c r="K13" s="1"/>
       <c r="L13" s="1"/>
@@ -11161,7 +12045,7 @@
     </row>
     <row r="14" customFormat="false" ht="71.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="44" t="s">
-        <v>579</v>
+        <v>602</v>
       </c>
       <c r="B14" s="79" t="n">
         <v>3760</v>
@@ -11174,7 +12058,7 @@
         <v>0.00651595744680851</v>
       </c>
       <c r="E14" s="47" t="s">
-        <v>580</v>
+        <v>603</v>
       </c>
       <c r="F14" s="80" t="n">
         <v>0.22</v>
@@ -11189,7 +12073,7 @@
         <v>-0.05</v>
       </c>
       <c r="J14" s="75" t="s">
-        <v>581</v>
+        <v>604</v>
       </c>
       <c r="K14" s="1"/>
       <c r="L14" s="1"/>
@@ -11198,7 +12082,7 @@
     </row>
     <row r="15" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="44" t="s">
-        <v>582</v>
+        <v>605</v>
       </c>
       <c r="B15" s="79" t="n">
         <v>280</v>
@@ -11211,7 +12095,7 @@
         <v>0.0625</v>
       </c>
       <c r="E15" s="47" t="s">
-        <v>583</v>
+        <v>606</v>
       </c>
       <c r="F15" s="80" t="n">
         <v>0.14</v>
@@ -11226,7 +12110,7 @@
         <v>-0.14</v>
       </c>
       <c r="J15" s="75" t="s">
-        <v>584</v>
+        <v>607</v>
       </c>
       <c r="K15" s="1"/>
       <c r="L15" s="1"/>
@@ -11235,7 +12119,7 @@
     </row>
     <row r="16" customFormat="false" ht="82.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="44" t="s">
-        <v>585</v>
+        <v>608</v>
       </c>
       <c r="B16" s="79" t="n">
         <v>945</v>
@@ -11248,7 +12132,7 @@
         <v>0.0148148148148148</v>
       </c>
       <c r="E16" s="47" t="s">
-        <v>586</v>
+        <v>609</v>
       </c>
       <c r="F16" s="80" t="n">
         <v>0.07</v>
@@ -11263,7 +12147,7 @@
         <v>-0.08</v>
       </c>
       <c r="J16" s="75" t="s">
-        <v>587</v>
+        <v>610</v>
       </c>
       <c r="K16" s="1"/>
       <c r="L16" s="1"/>
@@ -11272,7 +12156,7 @@
     </row>
     <row r="17" customFormat="false" ht="93.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="44" t="s">
-        <v>588</v>
+        <v>611</v>
       </c>
       <c r="B17" s="79" t="n">
         <v>110</v>
@@ -11285,7 +12169,7 @@
         <v>0.0636363636363636</v>
       </c>
       <c r="E17" s="47" t="s">
-        <v>589</v>
+        <v>612</v>
       </c>
       <c r="F17" s="80" t="n">
         <v>0.2</v>
@@ -11300,7 +12184,7 @@
         <v>-0.28</v>
       </c>
       <c r="J17" s="75" t="s">
-        <v>590</v>
+        <v>613</v>
       </c>
       <c r="K17" s="1"/>
       <c r="L17" s="1"/>
@@ -11309,7 +12193,7 @@
     </row>
     <row r="18" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="44" t="s">
-        <v>591</v>
+        <v>614</v>
       </c>
       <c r="B18" s="79" t="n">
         <v>18000</v>
@@ -11322,7 +12206,7 @@
         <v>0.000583333333333333</v>
       </c>
       <c r="E18" s="47" t="s">
-        <v>592</v>
+        <v>615</v>
       </c>
       <c r="F18" s="80" t="n">
         <v>0.25</v>
@@ -11337,7 +12221,7 @@
         <v>-0.12</v>
       </c>
       <c r="J18" s="75" t="s">
-        <v>593</v>
+        <v>616</v>
       </c>
       <c r="K18" s="1"/>
       <c r="L18" s="1"/>
@@ -11346,7 +12230,7 @@
     </row>
     <row r="19" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="44" t="s">
-        <v>594</v>
+        <v>617</v>
       </c>
       <c r="B19" s="79" t="n">
         <v>3730</v>
@@ -11359,7 +12243,7 @@
         <v>0.00402144772117963</v>
       </c>
       <c r="E19" s="47" t="s">
-        <v>595</v>
+        <v>618</v>
       </c>
       <c r="F19" s="80" t="n">
         <v>0.15</v>
@@ -11374,7 +12258,7 @@
         <v>-0.16</v>
       </c>
       <c r="J19" s="75" t="s">
-        <v>596</v>
+        <v>619</v>
       </c>
       <c r="K19" s="1"/>
       <c r="L19" s="1"/>
@@ -11383,7 +12267,7 @@
     </row>
     <row r="20" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="44" t="s">
-        <v>597</v>
+        <v>620</v>
       </c>
       <c r="B20" s="79" t="n">
         <v>159000</v>
@@ -11396,7 +12280,7 @@
         <v>0.000283018867924528</v>
       </c>
       <c r="E20" s="47" t="s">
-        <v>598</v>
+        <v>621</v>
       </c>
       <c r="F20" s="80" t="n">
         <v>0.18</v>
@@ -11411,7 +12295,7 @@
         <v>-0.08</v>
       </c>
       <c r="J20" s="75" t="s">
-        <v>599</v>
+        <v>622</v>
       </c>
       <c r="K20" s="1"/>
       <c r="L20" s="1"/>
@@ -11420,7 +12304,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="16" t="s">
-        <v>600</v>
+        <v>623</v>
       </c>
       <c r="B21" s="1"/>
       <c r="C21" s="50" t="n">
@@ -13476,7 +14360,7 @@
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="42" t="s">
-        <v>601</v>
+        <v>624</v>
       </c>
       <c r="B65" s="1"/>
       <c r="C65" s="1"/>
@@ -13494,7 +14378,7 @@
     </row>
     <row r="66" customFormat="false" ht="159.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A66" s="11" t="s">
-        <v>602</v>
+        <v>625</v>
       </c>
       <c r="B66" s="11"/>
       <c r="C66" s="11"/>
@@ -13542,7 +14426,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="161" t="s">
-        <v>603</v>
+        <v>626</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -13552,7 +14436,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="41" t="s">
-        <v>604</v>
+        <v>627</v>
       </c>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -13570,7 +14454,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="42" t="s">
-        <v>605</v>
+        <v>628</v>
       </c>
       <c r="B4" s="1"/>
       <c r="C4" s="1"/>
@@ -13604,7 +14488,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="41" t="s">
-        <v>606</v>
+        <v>629</v>
       </c>
       <c r="B7" s="1"/>
       <c r="C7" s="1"/>
@@ -13622,7 +14506,7 @@
     </row>
     <row r="9" customFormat="false" ht="36.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="11" t="s">
-        <v>607</v>
+        <v>630</v>
       </c>
       <c r="B9" s="11"/>
       <c r="C9" s="11"/>
@@ -13640,7 +14524,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="60" t="s">
-        <v>608</v>
+        <v>631</v>
       </c>
       <c r="B11" s="1"/>
       <c r="C11" s="1"/>
@@ -13695,7 +14579,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="44" t="s">
-        <v>609</v>
+        <v>632</v>
       </c>
       <c r="B14" s="68" t="n">
         <f aca="false">'Fund Economics'!B12/Assumptions!$B$5</f>
@@ -13720,7 +14604,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="44" t="s">
-        <v>610</v>
+        <v>633</v>
       </c>
       <c r="B15" s="68" t="n">
         <f aca="false">'Fund Economics'!B6/Assumptions!$B$5</f>
@@ -13770,7 +14654,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="44" t="s">
-        <v>611</v>
+        <v>634</v>
       </c>
       <c r="B17" s="68" t="n">
         <f aca="false">(1+'PME, DPI &amp; Sensitivity'!$B$5)^5</f>
@@ -13795,7 +14679,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="65" t="s">
-        <v>612</v>
+        <v>635</v>
       </c>
       <c r="B18" s="67" t="n">
         <f aca="false">'Fund Economics'!B14/(1+'PME, DPI &amp; Sensitivity'!$B$5)^5</f>
@@ -13820,7 +14704,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="44" t="s">
-        <v>613</v>
+        <v>636</v>
       </c>
       <c r="B19" s="46" t="n">
         <f aca="false">('Fund Economics'!B14/(1+'PME, DPI &amp; Sensitivity'!$B$5)^5)^(1/5)-1</f>
@@ -13845,7 +14729,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="44" t="s">
-        <v>614</v>
+        <v>637</v>
       </c>
       <c r="B20" s="68" t="n">
         <f aca="false">(1+'PME, DPI &amp; Sensitivity'!$B$6)^5</f>
@@ -13870,7 +14754,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="65" t="s">
-        <v>615</v>
+        <v>638</v>
       </c>
       <c r="B21" s="67" t="n">
         <f aca="false">'Fund Economics'!B14/(1+'PME, DPI &amp; Sensitivity'!$B$6)^5</f>
@@ -13895,7 +14779,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="44" t="s">
-        <v>616</v>
+        <v>639</v>
       </c>
       <c r="B22" s="46" t="n">
         <f aca="false">('Fund Economics'!B14/(1+'PME, DPI &amp; Sensitivity'!$B$6)^5)^(1/5)-1</f>
@@ -13920,7 +14804,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="55" t="s">
-        <v>617</v>
+        <v>640</v>
       </c>
       <c r="B23" s="68" t="n">
         <f aca="false">('Fund Economics'!B6/Assumptions!$B$5)/(1+'PME, DPI &amp; Sensitivity'!$B$5)^5</f>
@@ -13945,7 +14829,7 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="55" t="s">
-        <v>618</v>
+        <v>641</v>
       </c>
       <c r="B24" s="68" t="n">
         <f aca="false">('Fund Economics'!B6/Assumptions!$B$5)/(1+'PME, DPI &amp; Sensitivity'!$B$6)^5</f>
@@ -13986,7 +14870,7 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="60" t="s">
-        <v>619</v>
+        <v>642</v>
       </c>
       <c r="B27" s="1"/>
       <c r="C27" s="1"/>
@@ -14041,7 +14925,7 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="44" t="s">
-        <v>609</v>
+        <v>632</v>
       </c>
       <c r="B30" s="68" t="n">
         <f aca="false">'Fund Economics'!B28/Assumptions!$B$5</f>
@@ -14066,7 +14950,7 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="44" t="s">
-        <v>610</v>
+        <v>633</v>
       </c>
       <c r="B31" s="68" t="n">
         <f aca="false">'Fund Economics'!B22/Assumptions!$B$5</f>
@@ -14116,7 +15000,7 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="44" t="s">
-        <v>611</v>
+        <v>634</v>
       </c>
       <c r="B33" s="68" t="n">
         <f aca="false">(1+'PME, DPI &amp; Sensitivity'!$B$5)^7</f>
@@ -14141,7 +15025,7 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="65" t="s">
-        <v>612</v>
+        <v>635</v>
       </c>
       <c r="B34" s="67" t="n">
         <f aca="false">'Fund Economics'!B30/(1+'PME, DPI &amp; Sensitivity'!$B$5)^7</f>
@@ -14166,7 +15050,7 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="44" t="s">
-        <v>613</v>
+        <v>636</v>
       </c>
       <c r="B35" s="46" t="n">
         <f aca="false">('Fund Economics'!B30/(1+'PME, DPI &amp; Sensitivity'!$B$5)^7)^(1/7)-1</f>
@@ -14191,7 +15075,7 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="44" t="s">
-        <v>614</v>
+        <v>637</v>
       </c>
       <c r="B36" s="68" t="n">
         <f aca="false">(1+'PME, DPI &amp; Sensitivity'!$B$6)^7</f>
@@ -14216,7 +15100,7 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="65" t="s">
-        <v>615</v>
+        <v>638</v>
       </c>
       <c r="B37" s="67" t="n">
         <f aca="false">'Fund Economics'!B30/(1+'PME, DPI &amp; Sensitivity'!$B$6)^7</f>
@@ -14241,7 +15125,7 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="44" t="s">
-        <v>616</v>
+        <v>639</v>
       </c>
       <c r="B38" s="46" t="n">
         <f aca="false">('Fund Economics'!B30/(1+'PME, DPI &amp; Sensitivity'!$B$6)^7)^(1/7)-1</f>
@@ -14266,7 +15150,7 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="55" t="s">
-        <v>617</v>
+        <v>640</v>
       </c>
       <c r="B39" s="68" t="n">
         <f aca="false">('Fund Economics'!B22/Assumptions!$B$5)/(1+'PME, DPI &amp; Sensitivity'!$B$5)^7</f>
@@ -14291,7 +15175,7 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="55" t="s">
-        <v>618</v>
+        <v>641</v>
       </c>
       <c r="B40" s="68" t="n">
         <f aca="false">('Fund Economics'!B22/Assumptions!$B$5)/(1+'PME, DPI &amp; Sensitivity'!$B$6)^7</f>
@@ -14332,7 +15216,7 @@
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="60" t="s">
-        <v>620</v>
+        <v>643</v>
       </c>
       <c r="B43" s="1"/>
       <c r="C43" s="1"/>
@@ -14387,7 +15271,7 @@
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="44" t="s">
-        <v>609</v>
+        <v>632</v>
       </c>
       <c r="B46" s="68" t="n">
         <f aca="false">'Fund Economics'!B44/Assumptions!$B$5</f>
@@ -14412,7 +15296,7 @@
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="44" t="s">
-        <v>610</v>
+        <v>633</v>
       </c>
       <c r="B47" s="68" t="n">
         <f aca="false">'Fund Economics'!B38/Assumptions!$B$5</f>
@@ -14462,7 +15346,7 @@
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A49" s="44" t="s">
-        <v>611</v>
+        <v>634</v>
       </c>
       <c r="B49" s="68" t="n">
         <f aca="false">(1+'PME, DPI &amp; Sensitivity'!$B$5)^10</f>
@@ -14487,7 +15371,7 @@
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A50" s="65" t="s">
-        <v>612</v>
+        <v>635</v>
       </c>
       <c r="B50" s="67" t="n">
         <f aca="false">'Fund Economics'!B46/(1+'PME, DPI &amp; Sensitivity'!$B$5)^10</f>
@@ -14512,7 +15396,7 @@
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A51" s="44" t="s">
-        <v>613</v>
+        <v>636</v>
       </c>
       <c r="B51" s="46" t="n">
         <f aca="false">('Fund Economics'!B46/(1+'PME, DPI &amp; Sensitivity'!$B$5)^10)^(1/10)-1</f>
@@ -14537,7 +15421,7 @@
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A52" s="44" t="s">
-        <v>614</v>
+        <v>637</v>
       </c>
       <c r="B52" s="68" t="n">
         <f aca="false">(1+'PME, DPI &amp; Sensitivity'!$B$6)^10</f>
@@ -14562,7 +15446,7 @@
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A53" s="65" t="s">
-        <v>615</v>
+        <v>638</v>
       </c>
       <c r="B53" s="67" t="n">
         <f aca="false">'Fund Economics'!B46/(1+'PME, DPI &amp; Sensitivity'!$B$6)^10</f>
@@ -14587,7 +15471,7 @@
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A54" s="44" t="s">
-        <v>616</v>
+        <v>639</v>
       </c>
       <c r="B54" s="46" t="n">
         <f aca="false">('Fund Economics'!B46/(1+'PME, DPI &amp; Sensitivity'!$B$6)^10)^(1/10)-1</f>
@@ -14612,7 +15496,7 @@
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A55" s="55" t="s">
-        <v>617</v>
+        <v>640</v>
       </c>
       <c r="B55" s="68" t="n">
         <f aca="false">('Fund Economics'!B38/Assumptions!$B$5)/(1+'PME, DPI &amp; Sensitivity'!$B$5)^10</f>
@@ -14637,7 +15521,7 @@
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A56" s="55" t="s">
-        <v>618</v>
+        <v>641</v>
       </c>
       <c r="B56" s="68" t="n">
         <f aca="false">('Fund Economics'!B38/Assumptions!$B$5)/(1+'PME, DPI &amp; Sensitivity'!$B$6)^10</f>
@@ -14678,7 +15562,7 @@
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A59" s="162" t="s">
-        <v>621</v>
+        <v>644</v>
       </c>
       <c r="B59" s="1"/>
       <c r="C59" s="1"/>
@@ -14688,7 +15572,7 @@
     </row>
     <row r="60" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A60" s="11" t="s">
-        <v>622</v>
+        <v>645</v>
       </c>
       <c r="B60" s="11"/>
       <c r="C60" s="11"/>
@@ -14698,19 +15582,19 @@
     </row>
     <row r="61" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A61" s="53" t="s">
-        <v>623</v>
+        <v>646</v>
       </c>
       <c r="B61" s="43" t="s">
-        <v>624</v>
+        <v>647</v>
       </c>
       <c r="C61" s="43" t="s">
-        <v>625</v>
+        <v>648</v>
       </c>
       <c r="D61" s="43" t="s">
-        <v>626</v>
+        <v>649</v>
       </c>
       <c r="E61" s="43" t="s">
-        <v>627</v>
+        <v>650</v>
       </c>
       <c r="F61" s="54"/>
     </row>
@@ -14731,7 +15615,7 @@
         <v>0.182691512588688</v>
       </c>
       <c r="E62" s="75" t="s">
-        <v>628</v>
+        <v>651</v>
       </c>
       <c r="F62" s="163"/>
     </row>
@@ -14891,7 +15775,7 @@
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="166" t="s">
-        <v>629</v>
+        <v>652</v>
       </c>
       <c r="B72" s="166"/>
       <c r="C72" s="166"/>
@@ -14904,13 +15788,13 @@
         <v>27</v>
       </c>
       <c r="B73" s="167" t="s">
-        <v>630</v>
+        <v>653</v>
       </c>
       <c r="C73" s="167" t="s">
-        <v>631</v>
+        <v>654</v>
       </c>
       <c r="D73" s="167" t="s">
-        <v>632</v>
+        <v>655</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14919,15 +15803,15 @@
       </c>
       <c r="B74" s="169" t="n">
         <f aca="false">'Holdco Summary'!F38</f>
-        <v>2.28451548509776</v>
+        <v>2.2851127678349</v>
       </c>
       <c r="C74" s="169" t="n">
         <f aca="false">'Holdco Summary'!F59</f>
-        <v>3.47172430306552</v>
+        <v>3.47289565262861</v>
       </c>
       <c r="D74" s="169" t="n">
         <f aca="false">'Holdco Summary'!F80</f>
-        <v>6.97372679912634</v>
+        <v>6.97658087254771</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14936,15 +15820,15 @@
       </c>
       <c r="B75" s="169" t="n">
         <f aca="false">'Holdco Summary'!F39</f>
-        <v>2.28451548509776</v>
+        <v>2.2851127678349</v>
       </c>
       <c r="C75" s="169" t="n">
         <f aca="false">'Holdco Summary'!F60</f>
-        <v>3.47172430306552</v>
+        <v>3.47289565262861</v>
       </c>
       <c r="D75" s="169" t="n">
         <f aca="false">'Holdco Summary'!F81</f>
-        <v>6.97372679912634</v>
+        <v>6.97658087254771</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14953,66 +15837,66 @@
       </c>
       <c r="B76" s="170" t="n">
         <f aca="false">'Holdco Summary'!F40</f>
-        <v>0.179665344698351</v>
+        <v>0.179727022553126</v>
       </c>
       <c r="C76" s="170" t="n">
         <f aca="false">'Holdco Summary'!F61</f>
-        <v>0.19459514970068</v>
+        <v>0.194652720360569</v>
       </c>
       <c r="D76" s="170" t="n">
         <f aca="false">'Holdco Summary'!F82</f>
-        <v>0.214357314188665</v>
+        <v>0.214407003929896</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="171" t="s">
-        <v>612</v>
+        <v>635</v>
       </c>
       <c r="B77" s="172" t="n">
         <f aca="false">'Holdco Summary'!F41</f>
-        <v>1.48477831624963</v>
+        <v>1.48516650904698</v>
       </c>
       <c r="C77" s="172" t="n">
         <f aca="false">'Holdco Summary'!F62</f>
-        <v>1.89915208243164</v>
+        <v>1.89979285075533</v>
       </c>
       <c r="D77" s="172" t="n">
         <f aca="false">'Holdco Summary'!F83</f>
-        <v>2.94577756428905</v>
+        <v>2.94698315574591</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="171" t="s">
-        <v>615</v>
+        <v>638</v>
       </c>
       <c r="B78" s="172" t="n">
         <f aca="false">'Holdco Summary'!F42</f>
-        <v>1.23994347848141</v>
+        <v>1.24026765962159</v>
       </c>
       <c r="C78" s="172" t="n">
         <f aca="false">'Holdco Summary'!F63</f>
-        <v>1.47569336717015</v>
+        <v>1.47619126176949</v>
       </c>
       <c r="D78" s="172" t="n">
         <f aca="false">'Holdco Summary'!F84</f>
-        <v>2.05437865803752</v>
+        <v>2.05521943481215</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="171" t="s">
-        <v>633</v>
+        <v>656</v>
       </c>
       <c r="B79" s="172" t="n">
         <f aca="false">'Holdco Summary'!F43</f>
-        <v>1.1358079506193</v>
+        <v>1.13610490570059</v>
       </c>
       <c r="C79" s="172" t="n">
         <f aca="false">'Holdco Summary'!F64</f>
-        <v>1.30514975792351</v>
+        <v>1.30559011161098</v>
       </c>
       <c r="D79" s="172" t="n">
         <f aca="false">'Holdco Summary'!F85</f>
-        <v>1.72379860941622</v>
+        <v>1.72450409271614</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15021,42 +15905,42 @@
       </c>
       <c r="B80" s="173" t="n">
         <f aca="false">'Holdco Summary'!F44</f>
-        <v>0.02579595191161</v>
+        <v>0.0258495848288052</v>
       </c>
       <c r="C80" s="173" t="n">
         <f aca="false">'Holdco Summary'!F65</f>
-        <v>0.0387783910440698</v>
+        <v>0.0388284524874518</v>
       </c>
       <c r="D80" s="173" t="n">
         <f aca="false">'Holdco Summary'!F86</f>
-        <v>0.0559628819031874</v>
+        <v>0.0560060903738222</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="174" t="s">
-        <v>613</v>
+        <v>636</v>
       </c>
       <c r="B81" s="175" t="n">
         <f aca="false">B77^(1/5)-1</f>
-        <v>0.0822617841269278</v>
+        <v>0.0823183693147944</v>
       </c>
       <c r="C81" s="175" t="n">
         <f aca="false">C77^(1/7)-1</f>
-        <v>0.0959588529364037</v>
+        <v>0.0960116700555682</v>
       </c>
       <c r="D81" s="175" t="n">
         <f aca="false">D77^(1/10)-1</f>
-        <v>0.11408927907217</v>
+        <v>0.11413486599073</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="176" t="s">
-        <v>634</v>
+        <v>657</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="177" t="s">
-        <v>635</v>
+        <v>658</v>
       </c>
       <c r="B84" s="177"/>
       <c r="C84" s="177"/>
@@ -15066,24 +15950,24 @@
     </row>
     <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="176" t="s">
-        <v>636</v>
+        <v>659</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="167" t="s">
-        <v>623</v>
+        <v>646</v>
       </c>
       <c r="B86" s="167" t="s">
-        <v>624</v>
+        <v>647</v>
       </c>
       <c r="C86" s="167" t="s">
-        <v>625</v>
+        <v>648</v>
       </c>
       <c r="D86" s="167" t="s">
-        <v>626</v>
+        <v>649</v>
       </c>
       <c r="E86" s="167" t="s">
-        <v>627</v>
+        <v>650</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15092,18 +15976,18 @@
       </c>
       <c r="B87" s="179" t="n">
         <f aca="false">(((1-$A87)*('Defense Supercycle'!$B$17*'Holdco Summary'!B37+'Defense Supercycle'!$B$18*'Holdco Summary'!C37+'Defense Supercycle'!$B$19*'Holdco Summary'!D37)/('Defense Supercycle'!$B$17+'Defense Supercycle'!$B$18+'Defense Supercycle'!$B$19)+$A87*'Holdco Summary'!E37)/'Holdco Summary'!$B$9)^(1/5)-1</f>
-        <v>0.173141650238326</v>
+        <v>0.173174224896486</v>
       </c>
       <c r="C87" s="179" t="n">
         <f aca="false">(((1-$A87)*('Defense Supercycle'!$B$17*'Holdco Summary'!B58+'Defense Supercycle'!$B$18*'Holdco Summary'!C58+'Defense Supercycle'!$B$19*'Holdco Summary'!D58)/('Defense Supercycle'!$B$17+'Defense Supercycle'!$B$18+'Defense Supercycle'!$B$19)+$A87*'Holdco Summary'!E58)/'Holdco Summary'!$B$9)^(1/7)-1</f>
-        <v>0.186730550788601</v>
+        <v>0.186754003689585</v>
       </c>
       <c r="D87" s="179" t="n">
         <f aca="false">(((1-$A87)*('Defense Supercycle'!$B$17*'Holdco Summary'!B79+'Defense Supercycle'!$B$18*'Holdco Summary'!C79+'Defense Supercycle'!$B$19*'Holdco Summary'!D79)/('Defense Supercycle'!$B$17+'Defense Supercycle'!$B$18+'Defense Supercycle'!$B$19)+$A87*'Holdco Summary'!E79)/'Holdco Summary'!$B$9)^(1/10)-1</f>
-        <v>0.20519676084264</v>
+        <v>0.205206892364696</v>
       </c>
       <c r="E87" s="180" t="s">
-        <v>628</v>
+        <v>651</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15112,15 +15996,15 @@
       </c>
       <c r="B88" s="179" t="n">
         <f aca="false">(((1-$A88)*('Defense Supercycle'!$B$17*'Holdco Summary'!B37+'Defense Supercycle'!$B$18*'Holdco Summary'!C37+'Defense Supercycle'!$B$19*'Holdco Summary'!D37)/('Defense Supercycle'!$B$17+'Defense Supercycle'!$B$18+'Defense Supercycle'!$B$19)+$A88*'Holdco Summary'!E37)/'Holdco Summary'!$B$9)^(1/5)-1</f>
-        <v>0.175332337955289</v>
+        <v>0.175374757397879</v>
       </c>
       <c r="C88" s="179" t="n">
         <f aca="false">(((1-$A88)*('Defense Supercycle'!$B$17*'Holdco Summary'!B58+'Defense Supercycle'!$B$18*'Holdco Summary'!C58+'Defense Supercycle'!$B$19*'Holdco Summary'!D58)/('Defense Supercycle'!$B$17+'Defense Supercycle'!$B$18+'Defense Supercycle'!$B$19)+$A88*'Holdco Summary'!E58)/'Holdco Summary'!$B$9)^(1/7)-1</f>
-        <v>0.189386878722851</v>
+        <v>0.189422006262584</v>
       </c>
       <c r="D88" s="179" t="n">
         <f aca="false">(((1-$A88)*('Defense Supercycle'!$B$17*'Holdco Summary'!B79+'Defense Supercycle'!$B$18*'Holdco Summary'!C79+'Defense Supercycle'!$B$19*'Holdco Summary'!D79)/('Defense Supercycle'!$B$17+'Defense Supercycle'!$B$18+'Defense Supercycle'!$B$19)+$A88*'Holdco Summary'!E79)/'Holdco Summary'!$B$9)^(1/10)-1</f>
-        <v>0.208320186999566</v>
+        <v>0.208344110235947</v>
       </c>
       <c r="E88" s="180" t="str">
         <f aca="false">IF(ABS($A88-'Defense Supercycle'!$B$20)&lt;0.0001,"current base case","")</f>
@@ -15133,15 +16017,15 @@
       </c>
       <c r="B89" s="179" t="n">
         <f aca="false">(((1-$A89)*('Defense Supercycle'!$B$17*'Holdco Summary'!B37+'Defense Supercycle'!$B$18*'Holdco Summary'!C37+'Defense Supercycle'!$B$19*'Holdco Summary'!D37)/('Defense Supercycle'!$B$17+'Defense Supercycle'!$B$18+'Defense Supercycle'!$B$19)+$A89*'Holdco Summary'!E37)/'Holdco Summary'!$B$9)^(1/5)-1</f>
-        <v>0.177506813617036</v>
+        <v>0.17755893293387</v>
       </c>
       <c r="C89" s="179" t="n">
         <f aca="false">(((1-$A89)*('Defense Supercycle'!$B$17*'Holdco Summary'!B58+'Defense Supercycle'!$B$18*'Holdco Summary'!C58+'Defense Supercycle'!$B$19*'Holdco Summary'!D58)/('Defense Supercycle'!$B$17+'Defense Supercycle'!$B$18+'Defense Supercycle'!$B$19)+$A89*'Holdco Summary'!E58)/'Holdco Summary'!$B$9)^(1/7)-1</f>
-        <v>0.192008081331104</v>
+        <v>0.192054577162227</v>
       </c>
       <c r="D89" s="179" t="n">
         <f aca="false">(((1-$A89)*('Defense Supercycle'!$B$17*'Holdco Summary'!B79+'Defense Supercycle'!$B$18*'Holdco Summary'!C79+'Defense Supercycle'!$B$19*'Holdco Summary'!D79)/('Defense Supercycle'!$B$17+'Defense Supercycle'!$B$18+'Defense Supercycle'!$B$19)+$A89*'Holdco Summary'!E79)/'Holdco Summary'!$B$9)^(1/10)-1</f>
-        <v>0.21137259645321</v>
+        <v>0.211409691402099</v>
       </c>
       <c r="E89" s="180" t="str">
         <f aca="false">IF(ABS($A89-'Defense Supercycle'!$B$20)&lt;0.0001,"current base case","")</f>
@@ -15154,15 +16038,15 @@
       </c>
       <c r="B90" s="179" t="n">
         <f aca="false">(((1-$A90)*('Defense Supercycle'!$B$17*'Holdco Summary'!B37+'Defense Supercycle'!$B$18*'Holdco Summary'!C37+'Defense Supercycle'!$B$19*'Holdco Summary'!D37)/('Defense Supercycle'!$B$17+'Defense Supercycle'!$B$18+'Defense Supercycle'!$B$19)+$A90*'Holdco Summary'!E37)/'Holdco Summary'!$B$9)^(1/5)-1</f>
-        <v>0.179665344698351</v>
+        <v>0.179727022553126</v>
       </c>
       <c r="C90" s="179" t="n">
         <f aca="false">(((1-$A90)*('Defense Supercycle'!$B$17*'Holdco Summary'!B58+'Defense Supercycle'!$B$18*'Holdco Summary'!C58+'Defense Supercycle'!$B$19*'Holdco Summary'!D58)/('Defense Supercycle'!$B$17+'Defense Supercycle'!$B$18+'Defense Supercycle'!$B$19)+$A90*'Holdco Summary'!E58)/'Holdco Summary'!$B$9)^(1/7)-1</f>
-        <v>0.19459514970068</v>
+        <v>0.194652720360569</v>
       </c>
       <c r="D90" s="179" t="n">
         <f aca="false">(((1-$A90)*('Defense Supercycle'!$B$17*'Holdco Summary'!B79+'Defense Supercycle'!$B$18*'Holdco Summary'!C79+'Defense Supercycle'!$B$19*'Holdco Summary'!D79)/('Defense Supercycle'!$B$17+'Defense Supercycle'!$B$18+'Defense Supercycle'!$B$19)+$A90*'Holdco Summary'!E79)/'Holdco Summary'!$B$9)^(1/10)-1</f>
-        <v>0.214357314188665</v>
+        <v>0.214407003929896</v>
       </c>
       <c r="E90" s="180" t="str">
         <f aca="false">IF(ABS($A90-'Defense Supercycle'!$B$20)&lt;0.0001,"current base case","")</f>
@@ -15175,15 +16059,15 @@
       </c>
       <c r="B91" s="179" t="n">
         <f aca="false">(((1-$A91)*('Defense Supercycle'!$B$17*'Holdco Summary'!B37+'Defense Supercycle'!$B$18*'Holdco Summary'!C37+'Defense Supercycle'!$B$19*'Holdco Summary'!D37)/('Defense Supercycle'!$B$17+'Defense Supercycle'!$B$18+'Defense Supercycle'!$B$19)+$A91*'Holdco Summary'!E37)/'Holdco Summary'!$B$9)^(1/5)-1</f>
-        <v>0.181808191871745</v>
+        <v>0.181879290381203</v>
       </c>
       <c r="C91" s="179" t="n">
         <f aca="false">(((1-$A91)*('Defense Supercycle'!$B$17*'Holdco Summary'!B58+'Defense Supercycle'!$B$18*'Holdco Summary'!C58+'Defense Supercycle'!$B$19*'Holdco Summary'!D58)/('Defense Supercycle'!$B$17+'Defense Supercycle'!$B$18+'Defense Supercycle'!$B$19)+$A91*'Holdco Summary'!E58)/'Holdco Summary'!$B$9)^(1/7)-1</f>
-        <v>0.197149032539893</v>
+        <v>0.197217396720327</v>
       </c>
       <c r="D91" s="179" t="n">
         <f aca="false">(((1-$A91)*('Defense Supercycle'!$B$17*'Holdco Summary'!B79+'Defense Supercycle'!$B$18*'Holdco Summary'!C79+'Defense Supercycle'!$B$19*'Holdco Summary'!D79)/('Defense Supercycle'!$B$17+'Defense Supercycle'!$B$18+'Defense Supercycle'!$B$19)+$A91*'Holdco Summary'!E79)/'Holdco Summary'!$B$9)^(1/10)-1</f>
-        <v>0.217277433283862</v>
+        <v>0.217339180013493</v>
       </c>
       <c r="E91" s="180" t="str">
         <f aca="false">IF(ABS($A91-'Defense Supercycle'!$B$20)&lt;0.0001,"current base case","")</f>
@@ -15196,15 +16080,15 @@
       </c>
       <c r="B92" s="179" t="n">
         <f aca="false">(((1-$A92)*('Defense Supercycle'!$B$17*'Holdco Summary'!B37+'Defense Supercycle'!$B$18*'Holdco Summary'!C37+'Defense Supercycle'!$B$19*'Holdco Summary'!D37)/('Defense Supercycle'!$B$17+'Defense Supercycle'!$B$18+'Defense Supercycle'!$B$19)+$A92*'Holdco Summary'!E37)/'Holdco Summary'!$B$9)^(1/5)-1</f>
-        <v>0.183935609240115</v>
+        <v>0.184015993858367</v>
       </c>
       <c r="C92" s="179" t="n">
         <f aca="false">(((1-$A92)*('Defense Supercycle'!$B$17*'Holdco Summary'!B58+'Defense Supercycle'!$B$18*'Holdco Summary'!C58+'Defense Supercycle'!$B$19*'Holdco Summary'!D58)/('Defense Supercycle'!$B$17+'Defense Supercycle'!$B$18+'Defense Supercycle'!$B$19)+$A92*'Holdco Summary'!E58)/'Holdco Summary'!$B$9)^(1/7)-1</f>
-        <v>0.199670638588412</v>
+        <v>0.199749526456868</v>
       </c>
       <c r="D92" s="179" t="n">
         <f aca="false">(((1-$A92)*('Defense Supercycle'!$B$17*'Holdco Summary'!B79+'Defense Supercycle'!$B$18*'Holdco Summary'!C79+'Defense Supercycle'!$B$19*'Holdco Summary'!D79)/('Defense Supercycle'!$B$17+'Defense Supercycle'!$B$18+'Defense Supercycle'!$B$19)+$A92*'Holdco Summary'!E79)/'Holdco Summary'!$B$9)^(1/10)-1</f>
-        <v>0.22013583615207</v>
+        <v>0.220209137666471</v>
       </c>
       <c r="E92" s="180" t="str">
         <f aca="false">IF(ABS($A92-'Defense Supercycle'!$B$20)&lt;0.0001,"current base case","")</f>
@@ -15217,15 +16101,15 @@
       </c>
       <c r="B93" s="179" t="n">
         <f aca="false">(((1-$A93)*('Defense Supercycle'!$B$17*'Holdco Summary'!B37+'Defense Supercycle'!$B$18*'Holdco Summary'!C37+'Defense Supercycle'!$B$19*'Holdco Summary'!D37)/('Defense Supercycle'!$B$17+'Defense Supercycle'!$B$18+'Defense Supercycle'!$B$19)+$A93*'Holdco Summary'!E37)/'Holdco Summary'!$B$9)^(1/5)-1</f>
-        <v>0.186047844559448</v>
+        <v>0.186137383967178</v>
       </c>
       <c r="C93" s="179" t="n">
         <f aca="false">(((1-$A93)*('Defense Supercycle'!$B$17*'Holdco Summary'!B58+'Defense Supercycle'!$B$18*'Holdco Summary'!C58+'Defense Supercycle'!$B$19*'Holdco Summary'!D58)/('Defense Supercycle'!$B$17+'Defense Supercycle'!$B$18+'Defense Supercycle'!$B$19)+$A93*'Holdco Summary'!E58)/'Holdco Summary'!$B$9)^(1/7)-1</f>
-        <v>0.20216083885748</v>
+        <v>0.202249991425713</v>
       </c>
       <c r="D93" s="179" t="n">
         <f aca="false">(((1-$A93)*('Defense Supercycle'!$B$17*'Holdco Summary'!B79+'Defense Supercycle'!$B$18*'Holdco Summary'!C79+'Defense Supercycle'!$B$19*'Holdco Summary'!D79)/('Defense Supercycle'!$B$17+'Defense Supercycle'!$B$18+'Defense Supercycle'!$B$19)+$A93*'Holdco Summary'!E79)/'Holdco Summary'!$B$9)^(1/10)-1</f>
-        <v>0.222935213395674</v>
+        <v>0.223019599965047</v>
       </c>
       <c r="E93" s="180" t="str">
         <f aca="false">IF(ABS($A93-'Defense Supercycle'!$B$20)&lt;0.0001,"current base case","")</f>
@@ -15238,15 +16122,15 @@
       </c>
       <c r="B94" s="182" t="n">
         <f aca="false">(((1-$A94)*('Defense Supercycle'!$B$17*'Holdco Summary'!B37+'Defense Supercycle'!$B$18*'Holdco Summary'!C37+'Defense Supercycle'!$B$19*'Holdco Summary'!D37)/('Defense Supercycle'!$B$17+'Defense Supercycle'!$B$18+'Defense Supercycle'!$B$19)+$A94*'Holdco Summary'!E37)/'Holdco Summary'!$B$9)^(1/5)-1</f>
-        <v>0.190227729610919</v>
+        <v>0.190335197019601</v>
       </c>
       <c r="C94" s="182" t="n">
         <f aca="false">(((1-$A94)*('Defense Supercycle'!$B$17*'Holdco Summary'!B58+'Defense Supercycle'!$B$18*'Holdco Summary'!C58+'Defense Supercycle'!$B$19*'Holdco Summary'!D58)/('Defense Supercycle'!$B$17+'Defense Supercycle'!$B$18+'Defense Supercycle'!$B$19)+$A94*'Holdco Summary'!E58)/'Holdco Summary'!$B$9)^(1/7)-1</f>
-        <v>0.207050329823379</v>
+        <v>0.207159275303053</v>
       </c>
       <c r="D94" s="182" t="n">
         <f aca="false">(((1-$A94)*('Defense Supercycle'!$B$17*'Holdco Summary'!B79+'Defense Supercycle'!$B$18*'Holdco Summary'!C79+'Defense Supercycle'!$B$19*'Holdco Summary'!D79)/('Defense Supercycle'!$B$17+'Defense Supercycle'!$B$18+'Defense Supercycle'!$B$19)+$A94*'Holdco Summary'!E79)/'Holdco Summary'!$B$9)^(1/10)-1</f>
-        <v>0.228366793247366</v>
+        <v>0.228472056988375</v>
       </c>
       <c r="E94" s="183" t="str">
         <f aca="false">IF(ABS($A94-'Defense Supercycle'!$B$20)&lt;0.0001,"current base case","")</f>
@@ -15255,7 +16139,7 @@
     </row>
     <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A97" s="184" t="s">
-        <v>637</v>
+        <v>660</v>
       </c>
       <c r="B97" s="184"/>
       <c r="C97" s="184"/>
@@ -15265,7 +16149,7 @@
     </row>
     <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A98" s="185" t="s">
-        <v>638</v>
+        <v>661</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15273,18 +16157,18 @@
         <v>27</v>
       </c>
       <c r="B99" s="186" t="s">
-        <v>630</v>
+        <v>653</v>
       </c>
       <c r="C99" s="186" t="s">
-        <v>631</v>
+        <v>654</v>
       </c>
       <c r="D99" s="186" t="s">
-        <v>632</v>
+        <v>655</v>
       </c>
     </row>
     <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A100" s="0" t="s">
-        <v>639</v>
+        <v>662</v>
       </c>
       <c r="B100" s="187" t="n">
         <v>5</v>
@@ -15298,7 +16182,7 @@
     </row>
     <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A101" s="0" t="s">
-        <v>640</v>
+        <v>663</v>
       </c>
       <c r="B101" s="188" t="n">
         <f aca="false">'Holdco Summary'!$B$7</f>
@@ -15315,19 +16199,19 @@
     </row>
     <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A102" s="0" t="s">
-        <v>641</v>
+        <v>664</v>
       </c>
       <c r="B102" s="188" t="n">
         <f aca="false">'Holdco Summary'!F29</f>
-        <v>1109.64248108031</v>
+        <v>1110.26687131566</v>
       </c>
       <c r="C102" s="188" t="n">
         <f aca="false">'Holdco Summary'!F50</f>
-        <v>1772.166109012</v>
+        <v>1773.39288814722</v>
       </c>
       <c r="D102" s="188" t="n">
         <f aca="false">'Holdco Summary'!F71</f>
-        <v>3775.62412119169</v>
+        <v>3778.61762464484</v>
       </c>
     </row>
     <row r="103" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15336,15 +16220,15 @@
       </c>
       <c r="B103" s="189" t="n">
         <f aca="false">B102/B101</f>
-        <v>2.84523713097515</v>
+        <v>2.84683813157862</v>
       </c>
       <c r="C103" s="189" t="n">
         <f aca="false">C102/C101</f>
-        <v>4.54401566413334</v>
+        <v>4.54716125165954</v>
       </c>
       <c r="D103" s="189" t="n">
         <f aca="false">D102/D101</f>
-        <v>9.6810874902351</v>
+        <v>9.68876314011498</v>
       </c>
     </row>
     <row r="104" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15353,66 +16237,66 @@
       </c>
       <c r="B104" s="190" t="n">
         <f aca="false">B103^(1/B$100)-1</f>
-        <v>0.232604342815886</v>
+        <v>0.232743027655623</v>
       </c>
       <c r="C104" s="190" t="n">
         <f aca="false">C103^(1/C$100)-1</f>
-        <v>0.241423534266358</v>
+        <v>0.241546265494162</v>
       </c>
       <c r="D104" s="190" t="n">
         <f aca="false">D103^(1/D$100)-1</f>
-        <v>0.254851732162265</v>
+        <v>0.254951187598683</v>
       </c>
     </row>
     <row r="105" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A105" s="0" t="s">
-        <v>642</v>
+        <v>665</v>
       </c>
       <c r="B105" s="191" t="n">
         <f aca="false">'Holdco Summary'!F37/'Holdco Summary'!F31</f>
-        <v>0.866658232025072</v>
+        <v>0.866640436189444</v>
       </c>
       <c r="C105" s="191" t="n">
         <f aca="false">'Holdco Summary'!F58/'Holdco Summary'!F52</f>
-        <v>0.842870397175403</v>
+        <v>0.842855927273608</v>
       </c>
       <c r="D105" s="191" t="n">
         <f aca="false">'Holdco Summary'!F79/'Holdco Summary'!F73</f>
-        <v>0.822644074066539</v>
+        <v>0.822634926456576</v>
       </c>
     </row>
     <row r="106" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A106" s="0" t="s">
-        <v>643</v>
+        <v>666</v>
       </c>
       <c r="B106" s="192" t="n">
         <f aca="false">B102*B105</f>
-        <v>961.680790832976</v>
+        <v>962.202165643694</v>
       </c>
       <c r="C106" s="192" t="n">
         <f aca="false">C102*C105</f>
-        <v>1493.70635216374</v>
+        <v>1494.71470715975</v>
       </c>
       <c r="D106" s="192" t="n">
         <f aca="false">D102*D105</f>
-        <v>3105.99480920103</v>
+        <v>3108.42283175723</v>
       </c>
     </row>
     <row r="107" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A107" s="0" t="s">
-        <v>644</v>
+        <v>667</v>
       </c>
       <c r="B107" s="189" t="n">
         <f aca="false">B106/B101</f>
-        <v>2.46584818162302</v>
+        <v>2.46718504011204</v>
       </c>
       <c r="C107" s="189" t="n">
         <f aca="false">C106/C101</f>
-        <v>3.83001628759932</v>
+        <v>3.83260181323012</v>
       </c>
       <c r="D107" s="189" t="n">
         <f aca="false">D106/D101</f>
-        <v>7.96408925436161</v>
+        <v>7.97031495322367</v>
       </c>
     </row>
     <row r="108" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15421,66 +16305,66 @@
       </c>
       <c r="B108" s="190" t="n">
         <f aca="false">B107^(1/B$100)-1</f>
-        <v>0.197824707030125</v>
+        <v>0.197954558899382</v>
       </c>
       <c r="C108" s="190" t="n">
         <f aca="false">C107^(1/C$100)-1</f>
-        <v>0.211474771103909</v>
+        <v>0.211591570056223</v>
       </c>
       <c r="D108" s="190" t="n">
         <f aca="false">D107^(1/D$100)-1</f>
-        <v>0.230590652413204</v>
+        <v>0.230686816492574</v>
       </c>
     </row>
     <row r="109" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A109" s="193" t="s">
-        <v>612</v>
+        <v>635</v>
       </c>
       <c r="B109" s="194" t="n">
         <f aca="false">B107/(1+'Holdco Summary'!$B$21)^B$100</f>
-        <v>1.6026321270835</v>
+        <v>1.60350099337455</v>
       </c>
       <c r="C109" s="194" t="n">
         <f aca="false">C107/(1+'Holdco Summary'!$B$21)^C$100</f>
-        <v>2.0951500676245</v>
+        <v>2.09656443868547</v>
       </c>
       <c r="D109" s="194" t="n">
         <f aca="false">D107/(1+'Holdco Summary'!$B$21)^D$100</f>
-        <v>3.36411736812417</v>
+        <v>3.36674717060399</v>
       </c>
     </row>
     <row r="110" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A110" s="193" t="s">
-        <v>615</v>
+        <v>638</v>
       </c>
       <c r="B110" s="194" t="n">
         <f aca="false">B107/(1+'Holdco Summary'!$B$22)^B$100</f>
-        <v>1.33836360124206</v>
+        <v>1.33908919447001</v>
       </c>
       <c r="C110" s="194" t="n">
         <f aca="false">C107/(1+'Holdco Summary'!$B$22)^C$100</f>
-        <v>1.62798918876518</v>
+        <v>1.62908819395423</v>
       </c>
       <c r="D110" s="194" t="n">
         <f aca="false">D107/(1+'Holdco Summary'!$B$22)^D$100</f>
-        <v>2.34612789777141</v>
+        <v>2.34796191611512</v>
       </c>
     </row>
     <row r="111" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A111" s="193" t="s">
-        <v>633</v>
+        <v>656</v>
       </c>
       <c r="B111" s="194" t="n">
         <f aca="false">B107/(1+'Holdco Summary'!$B$23)^B$100</f>
-        <v>1.22596234868056</v>
+        <v>1.22662700361968</v>
       </c>
       <c r="C111" s="194" t="n">
         <f aca="false">C107/(1+'Holdco Summary'!$B$23)^C$100</f>
-        <v>1.43984498601732</v>
+        <v>1.44081698086961</v>
       </c>
       <c r="D111" s="194" t="n">
         <f aca="false">D107/(1+'Holdco Summary'!$B$23)^D$100</f>
-        <v>1.96860106186768</v>
+        <v>1.97013995941131</v>
       </c>
     </row>
     <row r="112" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15489,37 +16373,37 @@
       </c>
       <c r="B112" s="195" t="n">
         <f aca="false">B111^(1/B$100)-1</f>
-        <v>0.0415867017653258</v>
+        <v>0.0416996164342449</v>
       </c>
       <c r="C112" s="195" t="n">
         <f aca="false">C111^(1/C$100)-1</f>
-        <v>0.0534563226990517</v>
+        <v>0.0535578870054112</v>
       </c>
       <c r="D112" s="195" t="n">
         <f aca="false">D111^(1/D$100)-1</f>
-        <v>0.070078828185395</v>
+        <v>0.0701624491239776</v>
       </c>
     </row>
     <row r="113" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A113" s="0" t="s">
-        <v>613</v>
+        <v>636</v>
       </c>
       <c r="B113" s="195" t="n">
         <f aca="false">B109^(1/B$100)-1</f>
-        <v>0.0989217495689216</v>
+        <v>0.0990408797242033</v>
       </c>
       <c r="C113" s="195" t="n">
         <f aca="false">C109^(1/C$100)-1</f>
-        <v>0.111444744132027</v>
+        <v>0.111551899134149</v>
       </c>
       <c r="D113" s="195" t="n">
         <f aca="false">D109^(1/D$100)-1</f>
-        <v>0.128982249920371</v>
+        <v>0.129070473846398</v>
       </c>
     </row>
     <row r="115" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A115" s="184" t="s">
-        <v>645</v>
+        <v>668</v>
       </c>
       <c r="B115" s="184"/>
       <c r="C115" s="184"/>
@@ -15549,7 +16433,7 @@
     </row>
     <row r="117" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A117" s="0" t="s">
-        <v>646</v>
+        <v>669</v>
       </c>
       <c r="B117" s="197" t="n">
         <f aca="false">'Defense Supercycle'!B17</f>
@@ -15574,27 +16458,27 @@
     </row>
     <row r="118" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A118" s="0" t="s">
-        <v>647</v>
+        <v>670</v>
       </c>
       <c r="B118" s="188" t="n">
         <f aca="false">'Weapons Sleeve'!C51</f>
-        <v>1336.32523759324</v>
+        <v>1337.95191295883</v>
       </c>
       <c r="C118" s="188" t="n">
         <f aca="false">'Weapons Sleeve'!F51</f>
-        <v>2757.09590712155</v>
+        <v>2755.74233174324</v>
       </c>
       <c r="D118" s="188" t="n">
         <f aca="false">'Weapons Sleeve'!I51</f>
-        <v>457.170363684206</v>
+        <v>457.254041178369</v>
       </c>
       <c r="E118" s="200" t="n">
         <f aca="false">'Weapons Sleeve'!L51</f>
-        <v>2753.13480508018</v>
+        <v>2758.60558802122</v>
       </c>
       <c r="F118" s="201" t="n">
         <f aca="false">SUMPRODUCT(B117:E117,B118:E118)</f>
-        <v>1772.166109012</v>
+        <v>1773.39288814722</v>
       </c>
     </row>
     <row r="119" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15603,23 +16487,23 @@
       </c>
       <c r="B119" s="202" t="n">
         <f aca="false">'Weapons Sleeve'!D51</f>
-        <v>3.4264749681878</v>
+        <v>3.43064593066365</v>
       </c>
       <c r="C119" s="202" t="n">
         <f aca="false">'Weapons Sleeve'!G51</f>
-        <v>7.06947668492704</v>
+        <v>7.06600597882881</v>
       </c>
       <c r="D119" s="202" t="n">
         <f aca="false">'Weapons Sleeve'!J51</f>
-        <v>1.17223170175437</v>
+        <v>1.17244625943172</v>
       </c>
       <c r="E119" s="203" t="n">
         <f aca="false">'Weapons Sleeve'!M51</f>
-        <v>7.05932001302611</v>
+        <v>7.07334766159288</v>
       </c>
       <c r="F119" s="204" t="n">
         <f aca="false">F118/'Weapons Sleeve'!B51</f>
-        <v>4.54401566413334</v>
+        <v>4.54716125165954</v>
       </c>
     </row>
     <row r="120" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15628,48 +16512,48 @@
       </c>
       <c r="B120" s="197" t="n">
         <f aca="false">'Weapons Sleeve'!E51</f>
-        <v>0.192358342854872</v>
+        <v>0.192565581630973</v>
       </c>
       <c r="C120" s="197" t="n">
         <f aca="false">'Weapons Sleeve'!H51</f>
-        <v>0.322333614426532</v>
+        <v>0.322240853523934</v>
       </c>
       <c r="D120" s="197" t="n">
         <f aca="false">'Weapons Sleeve'!K51</f>
-        <v>0.0229609748393165</v>
+        <v>0.0229877207603559</v>
       </c>
       <c r="E120" s="198" t="n">
         <f aca="false">'Weapons Sleeve'!N51</f>
-        <v>0.322062048850876</v>
+        <v>0.322437027249076</v>
       </c>
       <c r="F120" s="199" t="n">
         <f aca="false">F119^(1/$C$100)-1</f>
-        <v>0.241423534266358</v>
+        <v>0.241546265494162</v>
       </c>
     </row>
     <row r="121" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A121" s="193" t="s">
-        <v>648</v>
+        <v>671</v>
       </c>
       <c r="B121" s="194" t="n">
         <f aca="false">B119/(1+'Holdco Summary'!$B$23)^$C$100</f>
-        <v>1.28813885691109</v>
+        <v>1.2897068761979</v>
       </c>
       <c r="C121" s="194" t="n">
         <f aca="false">C119/(1+'Holdco Summary'!$B$23)^$C$100</f>
-        <v>2.65767813873679</v>
+        <v>2.65637337175978</v>
       </c>
       <c r="D121" s="194" t="n">
         <f aca="false">D119/(1+'Holdco Summary'!$B$23)^$C$100</f>
-        <v>0.440685316061549</v>
+        <v>0.440765976239662</v>
       </c>
       <c r="E121" s="194" t="n">
         <f aca="false">E119/(1+'Holdco Summary'!$B$23)^$C$100</f>
-        <v>2.65385986956688</v>
+        <v>2.65913338224616</v>
       </c>
       <c r="F121" s="194" t="n">
         <f aca="false">F119/(1+'Holdco Summary'!$B$23)^$C$100</f>
-        <v>1.70826379813845</v>
+        <v>1.70944634100187</v>
       </c>
     </row>
   </sheetData>
@@ -15704,7 +16588,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="10" t="s">
-        <v>649</v>
+        <v>672</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -15714,7 +16598,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="41" t="s">
-        <v>650</v>
+        <v>673</v>
       </c>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -15732,7 +16616,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="60" t="s">
-        <v>651</v>
+        <v>674</v>
       </c>
       <c r="B4" s="1"/>
       <c r="C4" s="1"/>
@@ -15853,7 +16737,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="60" t="s">
-        <v>652</v>
+        <v>675</v>
       </c>
       <c r="B11" s="1"/>
       <c r="C11" s="1"/>
@@ -15974,7 +16858,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="60" t="s">
-        <v>653</v>
+        <v>676</v>
       </c>
       <c r="B18" s="1"/>
       <c r="C18" s="1"/>
@@ -16105,7 +16989,7 @@
     </row>
     <row r="26" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="73" t="s">
-        <v>654</v>
+        <v>677</v>
       </c>
       <c r="B26" s="73"/>
       <c r="C26" s="73"/>
@@ -16115,7 +16999,7 @@
     </row>
     <row r="27" customFormat="false" ht="40.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="73" t="s">
-        <v>655</v>
+        <v>678</v>
       </c>
       <c r="B27" s="73"/>
       <c r="C27" s="73"/>
@@ -16125,7 +17009,7 @@
     </row>
     <row r="28" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="73" t="s">
-        <v>656</v>
+        <v>679</v>
       </c>
       <c r="B28" s="73"/>
       <c r="C28" s="73"/>
@@ -16243,23 +17127,23 @@
       </c>
       <c r="B6" s="17" t="n">
         <f aca="false">'Holdco Summary'!F61</f>
-        <v>0.19459514970068</v>
+        <v>0.194652720360569</v>
       </c>
       <c r="C6" s="18" t="n">
         <f aca="false">'Holdco Summary'!F59</f>
-        <v>3.47172430306552</v>
+        <v>3.47289565262861</v>
       </c>
       <c r="D6" s="19" t="n">
         <f aca="false">'Holdco Summary'!F58</f>
-        <v>2916.24841457503</v>
+        <v>2917.23234820803</v>
       </c>
       <c r="E6" s="18" t="n">
         <f aca="false">'Holdco Summary'!F64</f>
-        <v>1.30514975792351</v>
+        <v>1.30559011161098</v>
       </c>
       <c r="F6" s="18" t="n">
         <f aca="false">'Holdco Summary'!F62</f>
-        <v>1.89915208243164</v>
+        <v>1.89979285075533</v>
       </c>
       <c r="G6" s="1"/>
     </row>
@@ -16310,23 +17194,23 @@
       </c>
       <c r="B10" s="21" t="n">
         <f aca="false">'Holdco Summary'!B40</f>
-        <v>0.157243958288965</v>
+        <v>0.157339269213003</v>
       </c>
       <c r="C10" s="21" t="n">
         <f aca="false">'Holdco Summary'!C40</f>
-        <v>0.274327717124122</v>
+        <v>0.27428658831713</v>
       </c>
       <c r="D10" s="21" t="n">
         <f aca="false">'Holdco Summary'!D40</f>
-        <v>-0.052367093493212</v>
+        <v>-0.0523453905389164</v>
       </c>
       <c r="E10" s="21" t="n">
         <f aca="false">'Holdco Summary'!E40</f>
-        <v>0.214150335471341</v>
+        <v>0.214355832416136</v>
       </c>
       <c r="F10" s="17" t="n">
         <f aca="false">'Holdco Summary'!F40</f>
-        <v>0.179665344698351</v>
+        <v>0.179727022553126</v>
       </c>
       <c r="G10" s="1"/>
     </row>
@@ -16336,23 +17220,23 @@
       </c>
       <c r="B11" s="21" t="n">
         <f aca="false">'Holdco Summary'!B61</f>
-        <v>0.161215917984854</v>
+        <v>0.16130616532457</v>
       </c>
       <c r="C11" s="21" t="n">
         <f aca="false">'Holdco Summary'!C61</f>
-        <v>0.283088507815498</v>
+        <v>0.283047231841675</v>
       </c>
       <c r="D11" s="21" t="n">
         <f aca="false">'Holdco Summary'!D61</f>
-        <v>-0.0494830765823161</v>
+        <v>-0.0494637815384494</v>
       </c>
       <c r="E11" s="21" t="n">
         <f aca="false">'Holdco Summary'!E61</f>
-        <v>0.234139541472284</v>
+        <v>0.234350090993351</v>
       </c>
       <c r="F11" s="17" t="n">
         <f aca="false">'Holdco Summary'!F61</f>
-        <v>0.19459514970068</v>
+        <v>0.194652720360569</v>
       </c>
       <c r="G11" s="1"/>
     </row>
@@ -16362,23 +17246,23 @@
       </c>
       <c r="B12" s="21" t="n">
         <f aca="false">'Holdco Summary'!B82</f>
-        <v>0.166899500084111</v>
+        <v>0.166980417765083</v>
       </c>
       <c r="C12" s="21" t="n">
         <f aca="false">'Holdco Summary'!C82</f>
-        <v>0.294141283782538</v>
+        <v>0.29410141429248</v>
       </c>
       <c r="D12" s="21" t="n">
         <f aca="false">'Holdco Summary'!D82</f>
-        <v>-0.0449438255077614</v>
+        <v>-0.0449281064013584</v>
       </c>
       <c r="E12" s="21" t="n">
         <f aca="false">'Holdco Summary'!E82</f>
-        <v>0.257095367940983</v>
+        <v>0.257298629469196</v>
       </c>
       <c r="F12" s="17" t="n">
         <f aca="false">'Holdco Summary'!F82</f>
-        <v>0.214357314188665</v>
+        <v>0.214407003929896</v>
       </c>
       <c r="G12" s="1"/>
     </row>
@@ -16429,23 +17313,23 @@
       </c>
       <c r="B16" s="22" t="n">
         <f aca="false">'Holdco Summary'!B38</f>
-        <v>2.07550895025053</v>
+        <v>2.07636378842861</v>
       </c>
       <c r="C16" s="22" t="n">
         <f aca="false">'Holdco Summary'!C38</f>
-        <v>3.36051351556337</v>
+        <v>3.3599712492824</v>
       </c>
       <c r="D16" s="22" t="n">
         <f aca="false">'Holdco Summary'!D38</f>
-        <v>0.764188795576073</v>
+        <v>0.76427630791383</v>
       </c>
       <c r="E16" s="22" t="n">
         <f aca="false">'Holdco Summary'!E38</f>
-        <v>2.63853172838515</v>
+        <v>2.64076536356232</v>
       </c>
       <c r="F16" s="18" t="n">
         <f aca="false">'Holdco Summary'!F38</f>
-        <v>2.28451548509776</v>
+        <v>2.2851127678349</v>
       </c>
       <c r="G16" s="1"/>
     </row>
@@ -16455,23 +17339,23 @@
       </c>
       <c r="B17" s="22" t="n">
         <f aca="false">'Holdco Summary'!B59</f>
-        <v>2.84702226580075</v>
+        <v>2.84857148043464</v>
       </c>
       <c r="C17" s="22" t="n">
         <f aca="false">'Holdco Summary'!C59</f>
-        <v>5.72527439820433</v>
+        <v>5.72398527879642</v>
       </c>
       <c r="D17" s="22" t="n">
         <f aca="false">'Holdco Summary'!D59</f>
-        <v>0.701001545519636</v>
+        <v>0.701101161584116</v>
       </c>
       <c r="E17" s="22" t="n">
         <f aca="false">'Holdco Summary'!E59</f>
-        <v>4.36063634717432</v>
+        <v>4.36584661664198</v>
       </c>
       <c r="F17" s="18" t="n">
         <f aca="false">'Holdco Summary'!F59</f>
-        <v>3.47172430306552</v>
+        <v>3.47289565262861</v>
       </c>
       <c r="G17" s="1"/>
     </row>
@@ -16481,23 +17365,23 @@
       </c>
       <c r="B18" s="22" t="n">
         <f aca="false">'Holdco Summary'!B80</f>
-        <v>4.68095577339018</v>
+        <v>4.68420275655465</v>
       </c>
       <c r="C18" s="22" t="n">
         <f aca="false">'Holdco Summary'!C80</f>
-        <v>13.1770112426267</v>
+        <v>13.1729522739643</v>
       </c>
       <c r="D18" s="22" t="n">
         <f aca="false">'Holdco Summary'!D80</f>
-        <v>0.631377595246464</v>
+        <v>0.631481520303096</v>
       </c>
       <c r="E18" s="22" t="n">
         <f aca="false">'Holdco Summary'!E80</f>
-        <v>9.85558167438073</v>
+        <v>9.87152890374393</v>
       </c>
       <c r="F18" s="18" t="n">
         <f aca="false">'Holdco Summary'!F80</f>
-        <v>6.97372679912634</v>
+        <v>6.97658087254771</v>
       </c>
       <c r="G18" s="1"/>
     </row>
@@ -16548,23 +17432,23 @@
       </c>
       <c r="B22" s="23" t="n">
         <f aca="false">'Holdco Summary'!B37</f>
-        <v>1743.42751821045</v>
+        <v>1744.14558228004</v>
       </c>
       <c r="C22" s="23" t="n">
         <f aca="false">'Holdco Summary'!C37</f>
-        <v>2822.83135307323</v>
+        <v>2822.37584939722</v>
       </c>
       <c r="D22" s="23" t="n">
         <f aca="false">'Holdco Summary'!D37</f>
-        <v>641.918588283901</v>
+        <v>641.992098647617</v>
       </c>
       <c r="E22" s="23" t="n">
         <f aca="false">'Holdco Summary'!E37</f>
-        <v>2216.36665184352</v>
+        <v>2218.24290539235</v>
       </c>
       <c r="F22" s="19" t="n">
         <f aca="false">'Holdco Summary'!F37</f>
-        <v>1918.99300748212</v>
+        <v>1919.49472498131</v>
       </c>
       <c r="G22" s="1"/>
     </row>
@@ -16574,23 +17458,23 @@
       </c>
       <c r="B23" s="23" t="n">
         <f aca="false">'Holdco Summary'!B58</f>
-        <v>2391.49870327263</v>
+        <v>2392.8000435651</v>
       </c>
       <c r="C23" s="23" t="n">
         <f aca="false">'Holdco Summary'!C58</f>
-        <v>4809.23049449164</v>
+        <v>4808.14763418899</v>
       </c>
       <c r="D23" s="23" t="n">
         <f aca="false">'Holdco Summary'!D58</f>
-        <v>588.841298236494</v>
+        <v>588.924975730658</v>
       </c>
       <c r="E23" s="23" t="n">
         <f aca="false">'Holdco Summary'!E58</f>
-        <v>3662.93453162643</v>
+        <v>3667.31115797926</v>
       </c>
       <c r="F23" s="19" t="n">
         <f aca="false">'Holdco Summary'!F58</f>
-        <v>2916.24841457503</v>
+        <v>2917.23234820803</v>
       </c>
       <c r="G23" s="1"/>
     </row>
@@ -16600,23 +17484,23 @@
       </c>
       <c r="B24" s="23" t="n">
         <f aca="false">'Holdco Summary'!B79</f>
-        <v>3932.00284964775</v>
+        <v>3934.7303155059</v>
       </c>
       <c r="C24" s="23" t="n">
         <f aca="false">'Holdco Summary'!C79</f>
-        <v>11068.6894438064</v>
+        <v>11065.27991013</v>
       </c>
       <c r="D24" s="23" t="n">
         <f aca="false">'Holdco Summary'!D79</f>
-        <v>530.35718000703</v>
+        <v>530.444477054601</v>
       </c>
       <c r="E24" s="23" t="n">
         <f aca="false">'Holdco Summary'!E79</f>
-        <v>8278.68860647982</v>
+        <v>8292.0842791449</v>
       </c>
       <c r="F24" s="19" t="n">
         <f aca="false">'Holdco Summary'!F79</f>
-        <v>5857.93051126612</v>
+        <v>5860.32793294008</v>
       </c>
       <c r="G24" s="1"/>
     </row>
@@ -16667,23 +17551,23 @@
       </c>
       <c r="B28" s="22" t="n">
         <f aca="false">'Holdco Summary'!B43</f>
-        <v>1.03189476396794</v>
+        <v>1.03231976962253</v>
       </c>
       <c r="C28" s="22" t="n">
         <f aca="false">'Holdco Summary'!C43</f>
-        <v>1.67076913859357</v>
+        <v>1.67049953641434</v>
       </c>
       <c r="D28" s="22" t="n">
         <f aca="false">'Holdco Summary'!D43</f>
-        <v>0.379936890536044</v>
+        <v>0.379980399634428</v>
       </c>
       <c r="E28" s="22" t="n">
         <f aca="false">'Holdco Summary'!E43</f>
-        <v>1.31181659069948</v>
+        <v>1.31292710214472</v>
       </c>
       <c r="F28" s="18" t="n">
         <f aca="false">'Holdco Summary'!F43</f>
-        <v>1.1358079506193</v>
+        <v>1.13610490570059</v>
       </c>
       <c r="G28" s="1"/>
     </row>
@@ -16693,23 +17577,23 @@
       </c>
       <c r="B29" s="22" t="n">
         <f aca="false">'Holdco Summary'!B64</f>
-        <v>1.07030112320027</v>
+        <v>1.07088353036394</v>
       </c>
       <c r="C29" s="22" t="n">
         <f aca="false">'Holdco Summary'!C64</f>
-        <v>2.1523427100084</v>
+        <v>2.15185808227408</v>
       </c>
       <c r="D29" s="22" t="n">
         <f aca="false">'Holdco Summary'!D64</f>
-        <v>0.263532446004165</v>
+        <v>0.263569895372574</v>
       </c>
       <c r="E29" s="22" t="n">
         <f aca="false">'Holdco Summary'!E64</f>
-        <v>1.63932472053776</v>
+        <v>1.64128345381863</v>
       </c>
       <c r="F29" s="18" t="n">
         <f aca="false">'Holdco Summary'!F64</f>
-        <v>1.30514975792351</v>
+        <v>1.30559011161098</v>
       </c>
       <c r="G29" s="1"/>
     </row>
@@ -16719,23 +17603,23 @@
       </c>
       <c r="B30" s="22" t="n">
         <f aca="false">'Holdco Summary'!B85</f>
-        <v>1.1570606772149</v>
+        <v>1.15786328179419</v>
       </c>
       <c r="C30" s="22" t="n">
         <f aca="false">'Holdco Summary'!C85</f>
-        <v>3.2571556515732</v>
+        <v>3.25615233659722</v>
       </c>
       <c r="D30" s="22" t="n">
         <f aca="false">'Holdco Summary'!D85</f>
-        <v>0.156066885332928</v>
+        <v>0.15609257401751</v>
       </c>
       <c r="E30" s="22" t="n">
         <f aca="false">'Holdco Summary'!E85</f>
-        <v>2.43614905984185</v>
+        <v>2.44009097104545</v>
       </c>
       <c r="F30" s="18" t="n">
         <f aca="false">'Holdco Summary'!F85</f>
-        <v>1.72379860941622</v>
+        <v>1.72450409271614</v>
       </c>
       <c r="G30" s="1"/>
     </row>
@@ -16786,23 +17670,23 @@
       </c>
       <c r="B34" s="22" t="n">
         <f aca="false">'Holdco Summary'!B41</f>
-        <v>1.34893840931095</v>
+        <v>1.34949399547309</v>
       </c>
       <c r="C34" s="22" t="n">
         <f aca="false">'Holdco Summary'!C41</f>
-        <v>2.18410320784443</v>
+        <v>2.18375077196869</v>
       </c>
       <c r="D34" s="22" t="n">
         <f aca="false">'Holdco Summary'!D41</f>
-        <v>0.49667028330242</v>
+        <v>0.496727160317416</v>
       </c>
       <c r="E34" s="22" t="n">
         <f aca="false">'Holdco Summary'!E41</f>
-        <v>1.71486458402153</v>
+        <v>1.71631629362871</v>
       </c>
       <c r="F34" s="18" t="n">
         <f aca="false">'Holdco Summary'!F41</f>
-        <v>1.48477831624963</v>
+        <v>1.48516650904698</v>
       </c>
       <c r="G34" s="1"/>
     </row>
@@ -16812,23 +17696,23 @@
       </c>
       <c r="B35" s="22" t="n">
         <f aca="false">'Holdco Summary'!B62</f>
-        <v>1.55741867522442</v>
+        <v>1.55826614868177</v>
       </c>
       <c r="C35" s="22" t="n">
         <f aca="false">'Holdco Summary'!C62</f>
-        <v>3.13192115694248</v>
+        <v>3.13121596448066</v>
       </c>
       <c r="D35" s="22" t="n">
         <f aca="false">'Holdco Summary'!D62</f>
-        <v>0.383471851087332</v>
+        <v>0.38352634448594</v>
       </c>
       <c r="E35" s="22" t="n">
         <f aca="false">'Holdco Summary'!E62</f>
-        <v>2.38541741121283</v>
+        <v>2.3882676070365</v>
       </c>
       <c r="F35" s="18" t="n">
         <f aca="false">'Holdco Summary'!F62</f>
-        <v>1.89915208243164</v>
+        <v>1.89979285075533</v>
       </c>
       <c r="G35" s="1"/>
     </row>
@@ -16838,23 +17722,23 @@
       </c>
       <c r="B36" s="22" t="n">
         <f aca="false">'Holdco Summary'!B83</f>
-        <v>1.97728630528078</v>
+        <v>1.97865786605926</v>
       </c>
       <c r="C36" s="22" t="n">
         <f aca="false">'Holdco Summary'!C83</f>
-        <v>5.56611195147151</v>
+        <v>5.56439739924364</v>
       </c>
       <c r="D36" s="22" t="n">
         <f aca="false">'Holdco Summary'!D83</f>
-        <v>0.266700719463919</v>
+        <v>0.266744618530947</v>
       </c>
       <c r="E36" s="22" t="n">
         <f aca="false">'Holdco Summary'!E83</f>
-        <v>4.16310420750153</v>
+        <v>4.16984048952459</v>
       </c>
       <c r="F36" s="18" t="n">
         <f aca="false">'Holdco Summary'!F83</f>
-        <v>2.94577756428905</v>
+        <v>2.94698315574591</v>
       </c>
       <c r="G36" s="1"/>
     </row>
@@ -17051,23 +17935,23 @@
       </c>
       <c r="B48" s="31" t="n">
         <f aca="false">'Holdco Summary'!B29/'Holdco Summary'!$B$7</f>
-        <v>2.40021175324052</v>
+        <v>2.40251324064305</v>
       </c>
       <c r="C48" s="31" t="n">
         <f aca="false">'Holdco Summary'!C29/'Holdco Summary'!$B$7</f>
-        <v>3.99136061796123</v>
+        <v>3.9899006702817</v>
       </c>
       <c r="D48" s="31" t="n">
         <f aca="false">'Holdco Summary'!D29/'Holdco Summary'!$B$7</f>
-        <v>1.12396447768245</v>
+        <v>1.12415296579454</v>
       </c>
       <c r="E48" s="31" t="n">
         <f aca="false">'Holdco Summary'!E29/'Holdco Summary'!$B$7</f>
-        <v>3.99138010582829</v>
+        <v>3.9973937389976</v>
       </c>
       <c r="F48" s="31" t="n">
         <f aca="false">'Holdco Summary'!F29/'Holdco Summary'!$B$7</f>
-        <v>2.84523713097515</v>
+        <v>2.84683813157862</v>
       </c>
       <c r="G48" s="1"/>
     </row>
@@ -17103,23 +17987,23 @@
       </c>
       <c r="B50" s="32" t="n">
         <f aca="false">'Holdco Summary'!B31/'Holdco Summary'!$B$9</f>
-        <v>2.35205416861317</v>
+        <v>2.35312271633577</v>
       </c>
       <c r="C50" s="32" t="n">
         <f aca="false">'Holdco Summary'!C31/'Holdco Summary'!$B$9</f>
-        <v>3.95830987525421</v>
+        <v>3.957632042403</v>
       </c>
       <c r="D50" s="32" t="n">
         <f aca="false">'Holdco Summary'!D31/'Holdco Summary'!$B$9</f>
-        <v>0.864188795576073</v>
+        <v>0.86427630791383</v>
       </c>
       <c r="E50" s="32" t="n">
         <f aca="false">'Holdco Summary'!E31/'Holdco Summary'!$B$9</f>
-        <v>3.05583264128143</v>
+        <v>3.0586246852529</v>
       </c>
       <c r="F50" s="32" t="n">
         <f aca="false">'Holdco Summary'!F31/'Holdco Summary'!$B$9</f>
-        <v>2.6360050602181</v>
+        <v>2.63674838192685</v>
       </c>
       <c r="G50" s="1"/>
     </row>
@@ -17196,23 +18080,23 @@
       </c>
       <c r="B55" s="31" t="n">
         <f aca="false">'Holdco Summary'!B50/'Holdco Summary'!$B$7</f>
-        <v>3.4264749681878</v>
+        <v>3.43064593066365</v>
       </c>
       <c r="C55" s="31" t="n">
         <f aca="false">'Holdco Summary'!C50/'Holdco Summary'!$B$7</f>
-        <v>7.06947668492704</v>
+        <v>7.06600597882881</v>
       </c>
       <c r="D55" s="31" t="n">
         <f aca="false">'Holdco Summary'!D50/'Holdco Summary'!$B$7</f>
-        <v>1.17223170175437</v>
+        <v>1.17244625943172</v>
       </c>
       <c r="E55" s="31" t="n">
         <f aca="false">'Holdco Summary'!E50/'Holdco Summary'!$B$7</f>
-        <v>7.05932001302611</v>
+        <v>7.07334766159288</v>
       </c>
       <c r="F55" s="31" t="n">
         <f aca="false">'Holdco Summary'!F50/'Holdco Summary'!$B$7</f>
-        <v>4.54401566413334</v>
+        <v>4.54716125165954</v>
       </c>
       <c r="G55" s="1"/>
     </row>
@@ -17248,23 +18132,23 @@
       </c>
       <c r="B57" s="32" t="n">
         <f aca="false">'Holdco Summary'!B52/'Holdco Summary'!$B$9</f>
-        <v>3.30532176505606</v>
+        <v>3.30725828334842</v>
       </c>
       <c r="C57" s="32" t="n">
         <f aca="false">'Holdco Summary'!C52/'Holdco Summary'!$B$9</f>
-        <v>6.90313693056053</v>
+        <v>6.90152553130064</v>
       </c>
       <c r="D57" s="32" t="n">
         <f aca="false">'Holdco Summary'!D52/'Holdco Summary'!$B$9</f>
-        <v>0.841001545519636</v>
+        <v>0.841101161584116</v>
       </c>
       <c r="E57" s="32" t="n">
         <f aca="false">'Holdco Summary'!E52/'Holdco Summary'!$B$9</f>
-        <v>5.19733936677302</v>
+        <v>5.20385220360759</v>
       </c>
       <c r="F57" s="32" t="n">
         <f aca="false">'Holdco Summary'!F52/'Holdco Summary'!$B$9</f>
-        <v>4.11893016375926</v>
+        <v>4.12039061511071</v>
       </c>
       <c r="G57" s="1"/>
     </row>
@@ -17341,23 +18225,23 @@
       </c>
       <c r="B62" s="31" t="n">
         <f aca="false">'Holdco Summary'!B71/'Holdco Summary'!$B$7</f>
-        <v>5.92527048397637</v>
+        <v>5.93401236172685</v>
       </c>
       <c r="C62" s="31" t="n">
         <f aca="false">'Holdco Summary'!C71/'Holdco Summary'!$B$7</f>
-        <v>17.0902218964353</v>
+        <v>17.0792939038826</v>
       </c>
       <c r="D62" s="31" t="n">
         <f aca="false">'Holdco Summary'!D71/'Holdco Summary'!$B$7</f>
-        <v>1.25117237985455</v>
+        <v>1.25139621843807</v>
       </c>
       <c r="E62" s="31" t="n">
         <f aca="false">'Holdco Summary'!E71/'Holdco Summary'!$B$7</f>
-        <v>17.0298962757248</v>
+        <v>17.0728311240104</v>
       </c>
       <c r="F62" s="31" t="n">
         <f aca="false">'Holdco Summary'!F71/'Holdco Summary'!$B$7</f>
-        <v>9.6810874902351</v>
+        <v>9.68876314011498</v>
       </c>
       <c r="G62" s="1"/>
     </row>
@@ -17393,23 +18277,23 @@
       </c>
       <c r="B64" s="32" t="n">
         <f aca="false">'Holdco Summary'!B73/'Holdco Summary'!$B$9</f>
-        <v>5.56146346741953</v>
+        <v>5.56552219637511</v>
       </c>
       <c r="C64" s="32" t="n">
         <f aca="false">'Holdco Summary'!C73/'Holdco Summary'!$B$9</f>
-        <v>16.1815328039652</v>
+        <v>16.1764590931371</v>
       </c>
       <c r="D64" s="32" t="n">
         <f aca="false">'Holdco Summary'!D73/'Holdco Summary'!$B$9</f>
-        <v>0.831377595246464</v>
+        <v>0.831481520303096</v>
       </c>
       <c r="E64" s="32" t="n">
         <f aca="false">'Holdco Summary'!E73/'Holdco Summary'!$B$9</f>
-        <v>12.0297458436577</v>
+        <v>12.0496798803617</v>
       </c>
       <c r="F64" s="32" t="n">
         <f aca="false">'Holdco Summary'!F73/'Holdco Summary'!$B$9</f>
-        <v>8.47721027716571</v>
+        <v>8.4807739717528</v>
       </c>
       <c r="G64" s="1"/>
     </row>
@@ -17657,11 +18541,11 @@
       </c>
       <c r="B79" s="34" t="n">
         <f aca="false">'Holdco Summary'!F52</f>
-        <v>3459.90133755778</v>
+        <v>3461.12811669299</v>
       </c>
       <c r="C79" s="34" t="n">
         <f aca="false">'Fund Economics'!F22+'Holdco Summary'!F50+'Holdco Summary'!F51</f>
-        <v>3459.90133755778</v>
+        <v>3461.12811669299</v>
       </c>
       <c r="D79" s="36" t="str">
         <f aca="false">IF(ABS(B79-C79)&lt;0.001,"OK","CHECK")</f>
@@ -18183,23 +19067,23 @@
       </c>
       <c r="B29" s="62" t="n">
         <f aca="false">'Weapons Sleeve'!C36</f>
-        <v>936.082583763805</v>
+        <v>936.98016385079</v>
       </c>
       <c r="C29" s="62" t="n">
         <f aca="false">'Weapons Sleeve'!F36</f>
-        <v>1556.63064100488</v>
+        <v>1556.06126140986</v>
       </c>
       <c r="D29" s="62" t="n">
         <f aca="false">'Weapons Sleeve'!I36</f>
-        <v>438.346146296154</v>
+        <v>438.419656659869</v>
       </c>
       <c r="E29" s="63" t="n">
         <f aca="false">'Weapons Sleeve'!L36</f>
-        <v>1556.63824127303</v>
+        <v>1558.98355820907</v>
       </c>
       <c r="F29" s="64" t="n">
         <f aca="false">B29*'Defense Supercycle'!$B$17+C29*'Defense Supercycle'!$B$18+D29*'Defense Supercycle'!$B$19+E29*'Defense Supercycle'!$B$20</f>
-        <v>1109.64248108031</v>
+        <v>1110.26687131566</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -18233,23 +19117,23 @@
       </c>
       <c r="B31" s="66" t="n">
         <f aca="false">B28+B29+B30</f>
-        <v>1975.72550163506</v>
+        <v>1976.62308172204</v>
       </c>
       <c r="C31" s="66" t="n">
         <f aca="false">C28+C29+C30</f>
-        <v>3324.98029521354</v>
+        <v>3324.41091561852</v>
       </c>
       <c r="D31" s="66" t="n">
         <f aca="false">D28+D29+D30</f>
-        <v>725.918588283901</v>
+        <v>725.992098647617</v>
       </c>
       <c r="E31" s="66" t="n">
         <f aca="false">E28+E29+E30</f>
-        <v>2566.8994186764</v>
+        <v>2569.24473561243</v>
       </c>
       <c r="F31" s="66" t="n">
         <f aca="false">F28+F29+F30</f>
-        <v>2214.24425058321</v>
+        <v>2214.86864081856</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -18308,11 +19192,11 @@
       </c>
       <c r="B34" s="62" t="n">
         <f aca="false">MAX(0,B31+B32+B33)</f>
-        <v>741.489917123059</v>
+        <v>742.387497210044</v>
       </c>
       <c r="C34" s="62" t="n">
         <f aca="false">MAX(0,C31+C32+C33)</f>
-        <v>2090.74471070154</v>
+        <v>2090.17533110652</v>
       </c>
       <c r="D34" s="62" t="n">
         <f aca="false">MAX(0,D31+D32+D33)</f>
@@ -18320,11 +19204,11 @@
       </c>
       <c r="E34" s="63" t="n">
         <f aca="false">MAX(0,E31+E32+E33)</f>
-        <v>1332.6638341644</v>
+        <v>1335.00915110043</v>
       </c>
       <c r="F34" s="64" t="n">
         <f aca="false">B34*'Defense Supercycle'!$B$17+C34*'Defense Supercycle'!$B$18+D34*'Defense Supercycle'!$B$19+E34*'Defense Supercycle'!$B$20</f>
-        <v>1056.25621550542</v>
+        <v>1056.86957918621</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -18333,11 +19217,11 @@
       </c>
       <c r="B35" s="62" t="n">
         <f aca="false">-Assumptions!$B$9*B34</f>
-        <v>-148.297983424612</v>
+        <v>-148.477499442009</v>
       </c>
       <c r="C35" s="62" t="n">
         <f aca="false">-Assumptions!$B$9*C34</f>
-        <v>-418.148942140307</v>
+        <v>-418.035066221304</v>
       </c>
       <c r="D35" s="62" t="n">
         <f aca="false">-Assumptions!$B$9*D34</f>
@@ -18345,11 +19229,11 @@
       </c>
       <c r="E35" s="63" t="n">
         <f aca="false">-Assumptions!$B$9*E34</f>
-        <v>-266.53276683288</v>
+        <v>-267.001830220087</v>
       </c>
       <c r="F35" s="64" t="n">
         <f aca="false">B35*'Defense Supercycle'!$B$17+C35*'Defense Supercycle'!$B$18+D35*'Defense Supercycle'!$B$19+E35*'Defense Supercycle'!$B$20</f>
-        <v>-211.251243101084</v>
+        <v>-211.373915837243</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -18383,23 +19267,23 @@
       </c>
       <c r="B37" s="66" t="n">
         <f aca="false">B31+B35+B36</f>
-        <v>1743.42751821045</v>
+        <v>1744.14558228004</v>
       </c>
       <c r="C37" s="66" t="n">
         <f aca="false">C31+C35+C36</f>
-        <v>2822.83135307323</v>
+        <v>2822.37584939722</v>
       </c>
       <c r="D37" s="66" t="n">
         <f aca="false">D31+D35+D36</f>
-        <v>641.918588283901</v>
+        <v>641.992098647617</v>
       </c>
       <c r="E37" s="66" t="n">
         <f aca="false">E31+E35+E36</f>
-        <v>2216.36665184352</v>
+        <v>2218.24290539235</v>
       </c>
       <c r="F37" s="66" t="n">
         <f aca="false">F31+F35+F36</f>
-        <v>1918.99300748212</v>
+        <v>1919.49472498131</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -18408,23 +19292,23 @@
       </c>
       <c r="B38" s="67" t="n">
         <f aca="false">B37/'Holdco Summary'!$B$9</f>
-        <v>2.07550895025053</v>
+        <v>2.07636378842861</v>
       </c>
       <c r="C38" s="67" t="n">
         <f aca="false">C37/'Holdco Summary'!$B$9</f>
-        <v>3.36051351556337</v>
+        <v>3.3599712492824</v>
       </c>
       <c r="D38" s="67" t="n">
         <f aca="false">D37/'Holdco Summary'!$B$9</f>
-        <v>0.764188795576073</v>
+        <v>0.76427630791383</v>
       </c>
       <c r="E38" s="67" t="n">
         <f aca="false">E37/'Holdco Summary'!$B$9</f>
-        <v>2.63853172838515</v>
+        <v>2.64076536356232</v>
       </c>
       <c r="F38" s="67" t="n">
         <f aca="false">F37/'Holdco Summary'!$B$9</f>
-        <v>2.28451548509776</v>
+        <v>2.2851127678349</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -18433,23 +19317,23 @@
       </c>
       <c r="B39" s="68" t="n">
         <f aca="false">B37/'Holdco Summary'!$B$9</f>
-        <v>2.07550895025053</v>
+        <v>2.07636378842861</v>
       </c>
       <c r="C39" s="68" t="n">
         <f aca="false">C37/'Holdco Summary'!$B$9</f>
-        <v>3.36051351556337</v>
+        <v>3.3599712492824</v>
       </c>
       <c r="D39" s="68" t="n">
         <f aca="false">D37/'Holdco Summary'!$B$9</f>
-        <v>0.764188795576073</v>
+        <v>0.76427630791383</v>
       </c>
       <c r="E39" s="69" t="n">
         <f aca="false">E37/'Holdco Summary'!$B$9</f>
-        <v>2.63853172838515</v>
+        <v>2.64076536356232</v>
       </c>
       <c r="F39" s="70" t="n">
         <f aca="false">F37/'Holdco Summary'!$B$9</f>
-        <v>2.28451548509776</v>
+        <v>2.2851127678349</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -18458,23 +19342,23 @@
       </c>
       <c r="B40" s="51" t="n">
         <f aca="false">(B37/'Holdco Summary'!$B$9)^(1/5)-1</f>
-        <v>0.157243958288965</v>
+        <v>0.157339269213003</v>
       </c>
       <c r="C40" s="51" t="n">
         <f aca="false">(C37/'Holdco Summary'!$B$9)^(1/5)-1</f>
-        <v>0.274327717124122</v>
+        <v>0.27428658831713</v>
       </c>
       <c r="D40" s="51" t="n">
         <f aca="false">(D37/'Holdco Summary'!$B$9)^(1/5)-1</f>
-        <v>-0.052367093493212</v>
+        <v>-0.0523453905389164</v>
       </c>
       <c r="E40" s="51" t="n">
         <f aca="false">(E37/'Holdco Summary'!$B$9)^(1/5)-1</f>
-        <v>0.214150335471341</v>
+        <v>0.214355832416136</v>
       </c>
       <c r="F40" s="51" t="n">
         <f aca="false">(F37/'Holdco Summary'!$B$9)^(1/5)-1</f>
-        <v>0.179665344698351</v>
+        <v>0.179727022553126</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -18483,23 +19367,23 @@
       </c>
       <c r="B41" s="68" t="n">
         <f aca="false">B38/(1+'Holdco Summary'!$B$21)^5</f>
-        <v>1.34893840931095</v>
+        <v>1.34949399547309</v>
       </c>
       <c r="C41" s="68" t="n">
         <f aca="false">C38/(1+'Holdco Summary'!$B$21)^5</f>
-        <v>2.18410320784443</v>
+        <v>2.18375077196869</v>
       </c>
       <c r="D41" s="68" t="n">
         <f aca="false">D38/(1+'Holdco Summary'!$B$21)^5</f>
-        <v>0.49667028330242</v>
+        <v>0.496727160317416</v>
       </c>
       <c r="E41" s="69" t="n">
         <f aca="false">E38/(1+'Holdco Summary'!$B$21)^5</f>
-        <v>1.71486458402153</v>
+        <v>1.71631629362871</v>
       </c>
       <c r="F41" s="70" t="n">
         <f aca="false">F38/(1+'Holdco Summary'!$B$21)^5</f>
-        <v>1.48477831624963</v>
+        <v>1.48516650904698</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -18508,23 +19392,23 @@
       </c>
       <c r="B42" s="68" t="n">
         <f aca="false">B38/(1+'Holdco Summary'!$B$22)^5</f>
-        <v>1.12650310500426</v>
+        <v>1.12696707691909</v>
       </c>
       <c r="C42" s="68" t="n">
         <f aca="false">C38/(1+'Holdco Summary'!$B$22)^5</f>
-        <v>1.82395210063246</v>
+        <v>1.8236577802205</v>
       </c>
       <c r="D42" s="68" t="n">
         <f aca="false">D38/(1+'Holdco Summary'!$B$22)^5</f>
-        <v>0.414771061778365</v>
+        <v>0.414818559969205</v>
       </c>
       <c r="E42" s="69" t="n">
         <f aca="false">E38/(1+'Holdco Summary'!$B$22)^5</f>
-        <v>1.43208931203084</v>
+        <v>1.43330163971664</v>
       </c>
       <c r="F42" s="70" t="n">
         <f aca="false">F38/(1+'Holdco Summary'!$B$22)^5</f>
-        <v>1.23994347848141</v>
+        <v>1.24026765962159</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -18533,23 +19417,23 @@
       </c>
       <c r="B43" s="67" t="n">
         <f aca="false">B38/(1+'Holdco Summary'!$B$23)^5</f>
-        <v>1.03189476396794</v>
+        <v>1.03231976962253</v>
       </c>
       <c r="C43" s="67" t="n">
         <f aca="false">C38/(1+'Holdco Summary'!$B$23)^5</f>
-        <v>1.67076913859357</v>
+        <v>1.67049953641434</v>
       </c>
       <c r="D43" s="67" t="n">
         <f aca="false">D38/(1+'Holdco Summary'!$B$23)^5</f>
-        <v>0.379936890536044</v>
+        <v>0.379980399634428</v>
       </c>
       <c r="E43" s="67" t="n">
         <f aca="false">E38/(1+'Holdco Summary'!$B$23)^5</f>
-        <v>1.31181659069948</v>
+        <v>1.31292710214472</v>
       </c>
       <c r="F43" s="67" t="n">
         <f aca="false">F38/(1+'Holdco Summary'!$B$23)^5</f>
-        <v>1.1358079506193</v>
+        <v>1.13610490570059</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -18558,23 +19442,23 @@
       </c>
       <c r="B44" s="46" t="n">
         <f aca="false">(B38/(1+'Holdco Summary'!$B$23)^5)^(1/5)-1</f>
-        <v>0.00629909416431729</v>
+        <v>0.00638197322869805</v>
       </c>
       <c r="C44" s="46" t="n">
         <f aca="false">(C38/(1+'Holdco Summary'!$B$23)^5)^(1/5)-1</f>
-        <v>0.108111058368801</v>
+        <v>0.108075294188809</v>
       </c>
       <c r="D44" s="46" t="n">
         <f aca="false">(D38/(1+'Holdco Summary'!$B$23)^5)^(1/5)-1</f>
-        <v>-0.175971385646271</v>
+        <v>-0.175952513512101</v>
       </c>
       <c r="E44" s="71" t="n">
         <f aca="false">(E38/(1+'Holdco Summary'!$B$23)^5)^(1/5)-1</f>
-        <v>0.0557829004098618</v>
+        <v>0.0559615934053355</v>
       </c>
       <c r="F44" s="72" t="n">
         <f aca="false">(F38/(1+'Holdco Summary'!$B$23)^5)^(1/5)-1</f>
-        <v>0.02579595191161</v>
+        <v>0.0258495848288052</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -18654,23 +19538,23 @@
       </c>
       <c r="B50" s="62" t="n">
         <f aca="false">'Weapons Sleeve'!C51</f>
-        <v>1336.32523759324</v>
+        <v>1337.95191295883</v>
       </c>
       <c r="C50" s="62" t="n">
         <f aca="false">'Weapons Sleeve'!F51</f>
-        <v>2757.09590712155</v>
+        <v>2755.74233174324</v>
       </c>
       <c r="D50" s="62" t="n">
         <f aca="false">'Weapons Sleeve'!I51</f>
-        <v>457.170363684206</v>
+        <v>457.254041178369</v>
       </c>
       <c r="E50" s="63" t="n">
         <f aca="false">'Weapons Sleeve'!L51</f>
-        <v>2753.13480508018</v>
+        <v>2758.60558802122</v>
       </c>
       <c r="F50" s="64" t="n">
         <f aca="false">B50*'Defense Supercycle'!$B$17+C50*'Defense Supercycle'!$B$18+D50*'Defense Supercycle'!$B$19+E50*'Defense Supercycle'!$B$20</f>
-        <v>1772.166109012</v>
+        <v>1773.39288814722</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -18704,23 +19588,23 @@
       </c>
       <c r="B52" s="66" t="n">
         <f aca="false">B49+B50+B51</f>
-        <v>2776.47028264709</v>
+        <v>2778.09695801268</v>
       </c>
       <c r="C52" s="66" t="n">
         <f aca="false">C49+C50+C51</f>
-        <v>5798.63502167085</v>
+        <v>5797.28144629254</v>
       </c>
       <c r="D52" s="66" t="n">
         <f aca="false">D49+D50+D51</f>
-        <v>706.441298236494</v>
+        <v>706.524975730658</v>
       </c>
       <c r="E52" s="66" t="n">
         <f aca="false">E49+E50+E51</f>
-        <v>4365.76506808934</v>
+        <v>4371.23585103038</v>
       </c>
       <c r="F52" s="66" t="n">
         <f aca="false">F49+F50+F51</f>
-        <v>3459.90133755778</v>
+        <v>3461.12811669299</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -18779,11 +19663,11 @@
       </c>
       <c r="B55" s="62" t="n">
         <f aca="false">MAX(0,B52+B53+B54)</f>
-        <v>1336.85789687229</v>
+        <v>1338.48457223788</v>
       </c>
       <c r="C55" s="62" t="n">
         <f aca="false">MAX(0,C52+C53+C54)</f>
-        <v>4359.02263589605</v>
+        <v>4357.66906051774</v>
       </c>
       <c r="D55" s="62" t="n">
         <f aca="false">MAX(0,D52+D53+D54)</f>
@@ -18791,11 +19675,11 @@
       </c>
       <c r="E55" s="63" t="n">
         <f aca="false">MAX(0,E52+E53+E54)</f>
-        <v>2926.15268231454</v>
+        <v>2931.62346525558</v>
       </c>
       <c r="F55" s="64" t="n">
         <f aca="false">B55*'Defense Supercycle'!$B$17+C55*'Defense Supercycle'!$B$18+D55*'Defense Supercycle'!$B$19+E55*'Defense Supercycle'!$B$20</f>
-        <v>2130.26461491373</v>
+        <v>2131.47884242482</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -18804,11 +19688,11 @@
       </c>
       <c r="B56" s="62" t="n">
         <f aca="false">-Assumptions!$B$9*B55</f>
-        <v>-267.371579374459</v>
+        <v>-267.696914447575</v>
       </c>
       <c r="C56" s="62" t="n">
         <f aca="false">-Assumptions!$B$9*C55</f>
-        <v>-871.80452717921</v>
+        <v>-871.533812103548</v>
       </c>
       <c r="D56" s="62" t="n">
         <f aca="false">-Assumptions!$B$9*D55</f>
@@ -18816,11 +19700,11 @@
       </c>
       <c r="E56" s="63" t="n">
         <f aca="false">-Assumptions!$B$9*E55</f>
-        <v>-585.230536462908</v>
+        <v>-586.324693051116</v>
       </c>
       <c r="F56" s="64" t="n">
         <f aca="false">B56*'Defense Supercycle'!$B$17+C56*'Defense Supercycle'!$B$18+D56*'Defense Supercycle'!$B$19+E56*'Defense Supercycle'!$B$20</f>
-        <v>-426.052922982745</v>
+        <v>-426.295768484963</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -18854,23 +19738,23 @@
       </c>
       <c r="B58" s="66" t="n">
         <f aca="false">B52+B56+B57</f>
-        <v>2391.49870327263</v>
+        <v>2392.8000435651</v>
       </c>
       <c r="C58" s="66" t="n">
         <f aca="false">C52+C56+C57</f>
-        <v>4809.23049449164</v>
+        <v>4808.14763418899</v>
       </c>
       <c r="D58" s="66" t="n">
         <f aca="false">D52+D56+D57</f>
-        <v>588.841298236494</v>
+        <v>588.924975730658</v>
       </c>
       <c r="E58" s="66" t="n">
         <f aca="false">E52+E56+E57</f>
-        <v>3662.93453162643</v>
+        <v>3667.31115797926</v>
       </c>
       <c r="F58" s="66" t="n">
         <f aca="false">F52+F56+F57</f>
-        <v>2916.24841457503</v>
+        <v>2917.23234820803</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -18879,23 +19763,23 @@
       </c>
       <c r="B59" s="67" t="n">
         <f aca="false">B58/'Holdco Summary'!$B$9</f>
-        <v>2.84702226580075</v>
+        <v>2.84857148043464</v>
       </c>
       <c r="C59" s="67" t="n">
         <f aca="false">C58/'Holdco Summary'!$B$9</f>
-        <v>5.72527439820433</v>
+        <v>5.72398527879642</v>
       </c>
       <c r="D59" s="67" t="n">
         <f aca="false">D58/'Holdco Summary'!$B$9</f>
-        <v>0.701001545519636</v>
+        <v>0.701101161584116</v>
       </c>
       <c r="E59" s="67" t="n">
         <f aca="false">E58/'Holdco Summary'!$B$9</f>
-        <v>4.36063634717432</v>
+        <v>4.36584661664198</v>
       </c>
       <c r="F59" s="67" t="n">
         <f aca="false">F58/'Holdco Summary'!$B$9</f>
-        <v>3.47172430306552</v>
+        <v>3.47289565262861</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -18904,23 +19788,23 @@
       </c>
       <c r="B60" s="68" t="n">
         <f aca="false">B58/'Holdco Summary'!$B$9</f>
-        <v>2.84702226580075</v>
+        <v>2.84857148043464</v>
       </c>
       <c r="C60" s="68" t="n">
         <f aca="false">C58/'Holdco Summary'!$B$9</f>
-        <v>5.72527439820433</v>
+        <v>5.72398527879642</v>
       </c>
       <c r="D60" s="68" t="n">
         <f aca="false">D58/'Holdco Summary'!$B$9</f>
-        <v>0.701001545519636</v>
+        <v>0.701101161584116</v>
       </c>
       <c r="E60" s="69" t="n">
         <f aca="false">E58/'Holdco Summary'!$B$9</f>
-        <v>4.36063634717432</v>
+        <v>4.36584661664198</v>
       </c>
       <c r="F60" s="70" t="n">
         <f aca="false">F58/'Holdco Summary'!$B$9</f>
-        <v>3.47172430306552</v>
+        <v>3.47289565262861</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -18929,23 +19813,23 @@
       </c>
       <c r="B61" s="51" t="n">
         <f aca="false">(B58/'Holdco Summary'!$B$9)^(1/7)-1</f>
-        <v>0.161215917984854</v>
+        <v>0.16130616532457</v>
       </c>
       <c r="C61" s="51" t="n">
         <f aca="false">(C58/'Holdco Summary'!$B$9)^(1/7)-1</f>
-        <v>0.283088507815498</v>
+        <v>0.283047231841675</v>
       </c>
       <c r="D61" s="51" t="n">
         <f aca="false">(D58/'Holdco Summary'!$B$9)^(1/7)-1</f>
-        <v>-0.0494830765823161</v>
+        <v>-0.0494637815384494</v>
       </c>
       <c r="E61" s="51" t="n">
         <f aca="false">(E58/'Holdco Summary'!$B$9)^(1/7)-1</f>
-        <v>0.234139541472284</v>
+        <v>0.234350090993351</v>
       </c>
       <c r="F61" s="51" t="n">
         <f aca="false">(F58/'Holdco Summary'!$B$9)^(1/7)-1</f>
-        <v>0.19459514970068</v>
+        <v>0.194652720360569</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -18954,23 +19838,23 @@
       </c>
       <c r="B62" s="68" t="n">
         <f aca="false">B59/(1+'Holdco Summary'!$B$21)^7</f>
-        <v>1.55741867522442</v>
+        <v>1.55826614868177</v>
       </c>
       <c r="C62" s="68" t="n">
         <f aca="false">C59/(1+'Holdco Summary'!$B$21)^7</f>
-        <v>3.13192115694248</v>
+        <v>3.13121596448066</v>
       </c>
       <c r="D62" s="68" t="n">
         <f aca="false">D59/(1+'Holdco Summary'!$B$21)^7</f>
-        <v>0.383471851087332</v>
+        <v>0.38352634448594</v>
       </c>
       <c r="E62" s="69" t="n">
         <f aca="false">E59/(1+'Holdco Summary'!$B$21)^7</f>
-        <v>2.38541741121283</v>
+        <v>2.3882676070365</v>
       </c>
       <c r="F62" s="70" t="n">
         <f aca="false">F59/(1+'Holdco Summary'!$B$21)^7</f>
-        <v>1.89915208243164</v>
+        <v>1.89979285075533</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -18979,23 +19863,23 @@
       </c>
       <c r="B63" s="68" t="n">
         <f aca="false">B59/(1+'Holdco Summary'!$B$22)^7</f>
-        <v>1.21015711706087</v>
+        <v>1.21081562723045</v>
       </c>
       <c r="C63" s="68" t="n">
         <f aca="false">C59/(1+'Holdco Summary'!$B$22)^7</f>
-        <v>2.43358882132404</v>
+        <v>2.43304086739864</v>
       </c>
       <c r="D63" s="68" t="n">
         <f aca="false">D59/(1+'Holdco Summary'!$B$22)^7</f>
-        <v>0.297968168205617</v>
+        <v>0.298010511074112</v>
       </c>
       <c r="E63" s="69" t="n">
         <f aca="false">E59/(1+'Holdco Summary'!$B$22)^7</f>
-        <v>1.85353489287274</v>
+        <v>1.85574957336675</v>
       </c>
       <c r="F63" s="70" t="n">
         <f aca="false">F59/(1+'Holdco Summary'!$B$22)^7</f>
-        <v>1.47569336717015</v>
+        <v>1.47619126176949</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -19004,23 +19888,23 @@
       </c>
       <c r="B64" s="67" t="n">
         <f aca="false">B59/(1+'Holdco Summary'!$B$23)^7</f>
-        <v>1.07030112320027</v>
+        <v>1.07088353036394</v>
       </c>
       <c r="C64" s="67" t="n">
         <f aca="false">C59/(1+'Holdco Summary'!$B$23)^7</f>
-        <v>2.1523427100084</v>
+        <v>2.15185808227408</v>
       </c>
       <c r="D64" s="67" t="n">
         <f aca="false">D59/(1+'Holdco Summary'!$B$23)^7</f>
-        <v>0.263532446004165</v>
+        <v>0.263569895372574</v>
       </c>
       <c r="E64" s="67" t="n">
         <f aca="false">E59/(1+'Holdco Summary'!$B$23)^7</f>
-        <v>1.63932472053776</v>
+        <v>1.64128345381863</v>
       </c>
       <c r="F64" s="67" t="n">
         <f aca="false">F59/(1+'Holdco Summary'!$B$23)^7</f>
-        <v>1.30514975792351</v>
+        <v>1.30559011161098</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -19029,23 +19913,23 @@
       </c>
       <c r="B65" s="46" t="n">
         <f aca="false">(B59/(1+'Holdco Summary'!$B$23)^7)^(1/7)-1</f>
-        <v>0.00975297216074256</v>
+        <v>0.00983144810832193</v>
       </c>
       <c r="C65" s="46" t="n">
         <f aca="false">(C59/(1+'Holdco Summary'!$B$23)^7)^(1/7)-1</f>
-        <v>0.115729137230868</v>
+        <v>0.115693245079717</v>
       </c>
       <c r="D65" s="46" t="n">
         <f aca="false">(D59/(1+'Holdco Summary'!$B$23)^7)^(1/7)-1</f>
-        <v>-0.173463544854188</v>
+        <v>-0.173446766555173</v>
       </c>
       <c r="E65" s="71" t="n">
         <f aca="false">(E59/(1+'Holdco Summary'!$B$23)^7)^(1/7)-1</f>
-        <v>0.0731648186715515</v>
+        <v>0.0733479052116093</v>
       </c>
       <c r="F65" s="72" t="n">
         <f aca="false">(F59/(1+'Holdco Summary'!$B$23)^7)^(1/7)-1</f>
-        <v>0.0387783910440698</v>
+        <v>0.0388284524874518</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -19125,23 +20009,23 @@
       </c>
       <c r="B71" s="62" t="n">
         <f aca="false">'Weapons Sleeve'!C66</f>
-        <v>2310.85548875078</v>
+        <v>2314.26482107347</v>
       </c>
       <c r="C71" s="62" t="n">
         <f aca="false">'Weapons Sleeve'!F66</f>
-        <v>6665.18653960977</v>
+        <v>6660.9246225142</v>
       </c>
       <c r="D71" s="62" t="n">
         <f aca="false">'Weapons Sleeve'!I66</f>
-        <v>487.957228143275</v>
+        <v>488.044525190846</v>
       </c>
       <c r="E71" s="63" t="n">
         <f aca="false">'Weapons Sleeve'!L66</f>
-        <v>6641.65954753269</v>
+        <v>6658.40413836404</v>
       </c>
       <c r="F71" s="64" t="n">
         <f aca="false">B71*'Defense Supercycle'!$B$17+C71*'Defense Supercycle'!$B$18+D71*'Defense Supercycle'!$B$19+E71*'Defense Supercycle'!$B$20</f>
-        <v>3775.62412119169</v>
+        <v>3778.61762464484</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -19175,23 +20059,23 @@
       </c>
       <c r="B73" s="66" t="n">
         <f aca="false">B70+B71+B72</f>
-        <v>4671.62931263241</v>
+        <v>4675.03864495509</v>
       </c>
       <c r="C73" s="66" t="n">
         <f aca="false">C70+C71+C72</f>
-        <v>13592.4875553308</v>
+        <v>13588.2256382352</v>
       </c>
       <c r="D73" s="66" t="n">
         <f aca="false">D70+D71+D72</f>
-        <v>698.35718000703</v>
+        <v>698.444477054601</v>
       </c>
       <c r="E73" s="66" t="n">
         <f aca="false">E70+E71+E72</f>
-        <v>10104.9865086725</v>
+        <v>10121.7310995038</v>
       </c>
       <c r="F73" s="66" t="n">
         <f aca="false">F70+F71+F72</f>
-        <v>7120.8566328192</v>
+        <v>7123.85013627235</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -19250,11 +20134,11 @@
       </c>
       <c r="B76" s="62" t="n">
         <f aca="false">MAX(0,B73+B74+B75)</f>
-        <v>2858.13231492327</v>
+        <v>2861.54164724595</v>
       </c>
       <c r="C76" s="62" t="n">
         <f aca="false">MAX(0,C73+C74+C75)</f>
-        <v>11778.9905576216</v>
+        <v>11774.728640526</v>
       </c>
       <c r="D76" s="62" t="n">
         <f aca="false">MAX(0,D73+D74+D75)</f>
@@ -19262,11 +20146,11 @@
       </c>
       <c r="E76" s="63" t="n">
         <f aca="false">MAX(0,E73+E74+E75)</f>
-        <v>8291.48951096334</v>
+        <v>8308.2341017947</v>
       </c>
       <c r="F76" s="64" t="n">
         <f aca="false">B76*'Defense Supercycle'!$B$17+C76*'Defense Supercycle'!$B$18+D76*'Defense Supercycle'!$B$19+E76*'Defense Supercycle'!$B$20</f>
-        <v>5474.63060776537</v>
+        <v>5477.61101666139</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -19275,11 +20159,11 @@
       </c>
       <c r="B77" s="62" t="n">
         <f aca="false">-Assumptions!$B$9*B76</f>
-        <v>-571.626462984653</v>
+        <v>-572.30832944919</v>
       </c>
       <c r="C77" s="62" t="n">
         <f aca="false">-Assumptions!$B$9*C76</f>
-        <v>-2355.79811152432</v>
+        <v>-2354.94572810521</v>
       </c>
       <c r="D77" s="62" t="n">
         <f aca="false">-Assumptions!$B$9*D76</f>
@@ -19287,11 +20171,11 @@
       </c>
       <c r="E77" s="63" t="n">
         <f aca="false">-Assumptions!$B$9*E76</f>
-        <v>-1658.29790219267</v>
+        <v>-1661.64682035894</v>
       </c>
       <c r="F77" s="64" t="n">
         <f aca="false">B77*'Defense Supercycle'!$B$17+C77*'Defense Supercycle'!$B$18+D77*'Defense Supercycle'!$B$19+E77*'Defense Supercycle'!$B$20</f>
-        <v>-1094.92612155307</v>
+        <v>-1095.52220333228</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -19325,23 +20209,23 @@
       </c>
       <c r="B79" s="66" t="n">
         <f aca="false">B73+B77+B78</f>
-        <v>3932.00284964775</v>
+        <v>3934.7303155059</v>
       </c>
       <c r="C79" s="66" t="n">
         <f aca="false">C73+C77+C78</f>
-        <v>11068.6894438064</v>
+        <v>11065.27991013</v>
       </c>
       <c r="D79" s="66" t="n">
         <f aca="false">D73+D77+D78</f>
-        <v>530.35718000703</v>
+        <v>530.444477054601</v>
       </c>
       <c r="E79" s="66" t="n">
         <f aca="false">E73+E77+E78</f>
-        <v>8278.68860647982</v>
+        <v>8292.0842791449</v>
       </c>
       <c r="F79" s="66" t="n">
         <f aca="false">F73+F77+F78</f>
-        <v>5857.93051126612</v>
+        <v>5860.32793294008</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -19350,23 +20234,23 @@
       </c>
       <c r="B80" s="67" t="n">
         <f aca="false">B79/'Holdco Summary'!$B$9</f>
-        <v>4.68095577339018</v>
+        <v>4.68420275655465</v>
       </c>
       <c r="C80" s="67" t="n">
         <f aca="false">C79/'Holdco Summary'!$B$9</f>
-        <v>13.1770112426267</v>
+        <v>13.1729522739643</v>
       </c>
       <c r="D80" s="67" t="n">
         <f aca="false">D79/'Holdco Summary'!$B$9</f>
-        <v>0.631377595246464</v>
+        <v>0.631481520303096</v>
       </c>
       <c r="E80" s="67" t="n">
         <f aca="false">E79/'Holdco Summary'!$B$9</f>
-        <v>9.85558167438073</v>
+        <v>9.87152890374393</v>
       </c>
       <c r="F80" s="67" t="n">
         <f aca="false">F79/'Holdco Summary'!$B$9</f>
-        <v>6.97372679912634</v>
+        <v>6.97658087254771</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -19375,23 +20259,23 @@
       </c>
       <c r="B81" s="68" t="n">
         <f aca="false">B79/'Holdco Summary'!$B$9</f>
-        <v>4.68095577339018</v>
+        <v>4.68420275655465</v>
       </c>
       <c r="C81" s="68" t="n">
         <f aca="false">C79/'Holdco Summary'!$B$9</f>
-        <v>13.1770112426267</v>
+        <v>13.1729522739643</v>
       </c>
       <c r="D81" s="68" t="n">
         <f aca="false">D79/'Holdco Summary'!$B$9</f>
-        <v>0.631377595246464</v>
+        <v>0.631481520303096</v>
       </c>
       <c r="E81" s="69" t="n">
         <f aca="false">E79/'Holdco Summary'!$B$9</f>
-        <v>9.85558167438073</v>
+        <v>9.87152890374393</v>
       </c>
       <c r="F81" s="70" t="n">
         <f aca="false">F79/'Holdco Summary'!$B$9</f>
-        <v>6.97372679912634</v>
+        <v>6.97658087254771</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -19400,23 +20284,23 @@
       </c>
       <c r="B82" s="51" t="n">
         <f aca="false">(B79/'Holdco Summary'!$B$9)^(1/10)-1</f>
-        <v>0.166899500084111</v>
+        <v>0.166980417765083</v>
       </c>
       <c r="C82" s="51" t="n">
         <f aca="false">(C79/'Holdco Summary'!$B$9)^(1/10)-1</f>
-        <v>0.294141283782538</v>
+        <v>0.29410141429248</v>
       </c>
       <c r="D82" s="51" t="n">
         <f aca="false">(D79/'Holdco Summary'!$B$9)^(1/10)-1</f>
-        <v>-0.0449438255077614</v>
+        <v>-0.0449281064013584</v>
       </c>
       <c r="E82" s="51" t="n">
         <f aca="false">(E79/'Holdco Summary'!$B$9)^(1/10)-1</f>
-        <v>0.257095367940983</v>
+        <v>0.257298629469196</v>
       </c>
       <c r="F82" s="51" t="n">
         <f aca="false">(F79/'Holdco Summary'!$B$9)^(1/10)-1</f>
-        <v>0.214357314188665</v>
+        <v>0.214407003929896</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -19425,23 +20309,23 @@
       </c>
       <c r="B83" s="68" t="n">
         <f aca="false">B80/(1+'Holdco Summary'!$B$21)^10</f>
-        <v>1.97728630528078</v>
+        <v>1.97865786605926</v>
       </c>
       <c r="C83" s="68" t="n">
         <f aca="false">C80/(1+'Holdco Summary'!$B$21)^10</f>
-        <v>5.56611195147151</v>
+        <v>5.56439739924364</v>
       </c>
       <c r="D83" s="68" t="n">
         <f aca="false">D80/(1+'Holdco Summary'!$B$21)^10</f>
-        <v>0.266700719463919</v>
+        <v>0.266744618530947</v>
       </c>
       <c r="E83" s="69" t="n">
         <f aca="false">E80/(1+'Holdco Summary'!$B$21)^10</f>
-        <v>4.16310420750153</v>
+        <v>4.16984048952459</v>
       </c>
       <c r="F83" s="70" t="n">
         <f aca="false">F80/(1+'Holdco Summary'!$B$21)^10</f>
-        <v>2.94577756428905</v>
+        <v>2.94698315574591</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -19450,23 +20334,23 @@
       </c>
       <c r="B84" s="68" t="n">
         <f aca="false">B80/(1+'Holdco Summary'!$B$22)^10</f>
-        <v>1.37895502893446</v>
+        <v>1.37991155234128</v>
       </c>
       <c r="C84" s="68" t="n">
         <f aca="false">C80/(1+'Holdco Summary'!$B$22)^10</f>
-        <v>3.88179397520479</v>
+        <v>3.88059825033142</v>
       </c>
       <c r="D84" s="68" t="n">
         <f aca="false">D80/(1+'Holdco Summary'!$B$22)^10</f>
-        <v>0.185996482827501</v>
+        <v>0.186027097938263</v>
       </c>
       <c r="E84" s="69" t="n">
         <f aca="false">E80/(1+'Holdco Summary'!$B$22)^10</f>
-        <v>2.90333952527793</v>
+        <v>2.90803739323323</v>
       </c>
       <c r="F84" s="70" t="n">
         <f aca="false">F80/(1+'Holdco Summary'!$B$22)^10</f>
-        <v>2.05437865803752</v>
+        <v>2.05521943481215</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -19475,23 +20359,23 @@
       </c>
       <c r="B85" s="67" t="n">
         <f aca="false">B80/(1+'Holdco Summary'!$B$23)^10</f>
-        <v>1.1570606772149</v>
+        <v>1.15786328179419</v>
       </c>
       <c r="C85" s="67" t="n">
         <f aca="false">C80/(1+'Holdco Summary'!$B$23)^10</f>
-        <v>3.2571556515732</v>
+        <v>3.25615233659722</v>
       </c>
       <c r="D85" s="67" t="n">
         <f aca="false">D80/(1+'Holdco Summary'!$B$23)^10</f>
-        <v>0.156066885332928</v>
+        <v>0.15609257401751</v>
       </c>
       <c r="E85" s="67" t="n">
         <f aca="false">E80/(1+'Holdco Summary'!$B$23)^10</f>
-        <v>2.43614905984185</v>
+        <v>2.44009097104545</v>
       </c>
       <c r="F85" s="67" t="n">
         <f aca="false">F80/(1+'Holdco Summary'!$B$23)^10</f>
-        <v>1.72379860941622</v>
+        <v>1.72450409271614</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -19500,23 +20384,23 @@
       </c>
       <c r="B86" s="46" t="n">
         <f aca="false">(B80/(1+'Holdco Summary'!$B$23)^10)^(1/10)-1</f>
-        <v>0.0146952174644448</v>
+        <v>0.0147655806652895</v>
       </c>
       <c r="C86" s="46" t="n">
         <f aca="false">(C80/(1+'Holdco Summary'!$B$23)^10)^(1/10)-1</f>
-        <v>0.125340246767424</v>
+        <v>0.125305577645635</v>
       </c>
       <c r="D86" s="46" t="n">
         <f aca="false">(D80/(1+'Holdco Summary'!$B$23)^10)^(1/10)-1</f>
-        <v>-0.169516370006749</v>
+        <v>-0.169502701218572</v>
       </c>
       <c r="E86" s="71" t="n">
         <f aca="false">(E80/(1+'Holdco Summary'!$B$23)^10)^(1/10)-1</f>
-        <v>0.0931264069052031</v>
+        <v>0.0933031560601707</v>
       </c>
       <c r="F86" s="72" t="n">
         <f aca="false">(F80/(1+'Holdco Summary'!$B$23)^10)^(1/10)-1</f>
-        <v>0.0559628819031874</v>
+        <v>0.0560060903738222</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">

--- a/models/Leviathan_PE_HOLDCO_Model_IC_VLetalis_Faxon.xlsx
+++ b/models/Leviathan_PE_HOLDCO_Model_IC_VLetalis_Faxon.xlsx
@@ -62,18 +62,6 @@
           </rPr>
           <t xml:space="preserve">Microsoft Office User:
 PLACEHOLDER — no public valuation data found for Superior &amp; Grand Valley. $400M EV is an assumed mid-market forging mark; replace with actual data.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="C12" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <rFont val="Arial"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">Trimmed $70M -&gt; $55M to fund the $15M L3Harris Missile Solutions pre-IPO stake inside the fixed $390M sleeve. Saronic was the largest position; trim keeps the sleeve at $390M.</t>
         </r>
       </text>
     </comment>
@@ -218,6 +206,28 @@
 </comments>
 </file>
 
+<file path=xl/comments3.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <authors>
+    <author>Unknown Author</author>
+  </authors>
+  <commentList>
+    <comment ref="B7" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Raised $390M -&gt; $405M: +$15M new commitment to fund the L3Harris Missile Solutions pre-IPO stake (IC, 9/2026). No existing Weapons position trimmed for it. Holdco $840M -&gt; $855M.</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/comments6.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <authors>
@@ -269,10 +279,10 @@
     <t xml:space="preserve">PURPOSE</t>
   </si>
   <si>
-    <t xml:space="preserve">Leviathan's core PE holdco is an $840M vehicle across THREE sub-funds: IQT-mirror deep-tech ($250M), Weapons ($390M), and Consumer/Value ($200M). All three sleeves are modeled bottom-up from individual holdings — IQT-mirror (nine In-Q-Tel names), Weapons (eleven physical-layer holdings, incl. a pre-IPO stake in L3Harris Missile Solutions (IPO Q1 2027), incl. The Ellwood Group and Superior &amp; Grand Valley for missile-procurement metal forging, and Faxon Machining for NGP / MOP / TLAM / BLU-136 warhead-case and missile machining), Consumer/Value (nine DTC/spending-cycle names) — each across four scenarios, 5/7/10-yr holds, gross-to-net waterfall, and PME, and roll up to a blended holdco return on the Holdco Summary tab. Start there for the top-down view; the sleeve tabs hold the detail.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Scope: Leviathan runs four vehicles (~$1.5B AUM total); this workbook models only the core PE holdco vehicle ($840M) and its equity targets — not the other three vehicles.</t>
+    <t xml:space="preserve">Leviathan's core PE holdco is an $855M vehicle across THREE sub-funds: IQT-mirror deep-tech ($250M), Weapons ($405M), and Consumer/Value ($200M). All three sleeves are modeled bottom-up from individual holdings — IQT-mirror (nine In-Q-Tel names), Weapons (eleven physical-layer holdings, incl. a pre-IPO stake in L3Harris Missile Solutions (IPO Q1 2027), incl. The Ellwood Group and Superior &amp; Grand Valley for missile-procurement metal forging, and Faxon Machining for NGP / MOP / TLAM / BLU-136 warhead-case and missile machining), Consumer/Value (nine DTC/spending-cycle names) — each across four scenarios, 5/7/10-yr holds, gross-to-net waterfall, and PME, and roll up to a blended holdco return on the Holdco Summary tab. Start there for the top-down view; the sleeve tabs hold the detail.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Scope: Leviathan runs four vehicles (~$1.5B AUM total); this workbook models only the core PE holdco vehicle ($855M) and its equity targets — not the other three vehicles.</t>
   </si>
   <si>
     <t xml:space="preserve">THE DEFENSE-SUPERCYCLE THESIS (now wired into returns)</t>
@@ -333,7 +343,7 @@
     <t xml:space="preserve">LEVIATHAN CORE PE HOLDCO — IC SUMMARY</t>
   </si>
   <si>
-    <t xml:space="preserve">$840M tripartite holdco (IQT-mirror / Weapons / Consumer-Value). USD $M. Expected = probability-weighted across Base/Bull/Bear/TSMC-Shock (weights on Defense Supercycle tab). Every figure links live to the model — no inputs on this page.</t>
+    <t xml:space="preserve">$855M tripartite holdco (IQT-mirror / Weapons / Consumer-Value). USD $M. Expected = probability-weighted across Base/Bull/Bear/TSMC-Shock (weights on Defense Supercycle tab). Every figure links live to the model — no inputs on this page.</t>
   </si>
   <si>
     <t xml:space="preserve">HEADLINE — RECOMMENDED 7-YEAR VEHICLE (Expected case, net to LP)</t>
@@ -465,7 +475,7 @@
     <t xml:space="preserve">Status</t>
   </si>
   <si>
-    <t xml:space="preserve">Holdco size = $840M</t>
+    <t xml:space="preserve">Holdco size = $855M</t>
   </si>
   <si>
     <t xml:space="preserve">IQT-mirror deployed = committed</t>
@@ -501,7 +511,7 @@
     <t xml:space="preserve">• Six of nine IQT entry marks and most Weapons marks are estimates — see Assumptions col J / Weapons Sleeve col J. Confirm via primary diligence before IC vote.</t>
   </si>
   <si>
-    <t xml:space="preserve">LEVIATHAN — CORE PE HOLDCO ($840M) — TRIPARTITE ROLL-UP</t>
+    <t xml:space="preserve">LEVIATHAN — CORE PE HOLDCO ($855M) — TRIPARTITE ROLL-UP</t>
   </si>
   <si>
     <t xml:space="preserve">Three sub-funds rolled up to a blended holdco return. Blue = lever. All three sleeves — IQT-mirror, Weapons, Consumer/Value — flow in bottom-up.</t>
@@ -555,7 +565,7 @@
     <t xml:space="preserve">Ballast + near-term DPI engine</t>
   </si>
   <si>
-    <t xml:space="preserve">TOTAL (must = $840M)</t>
+    <t xml:space="preserve">TOTAL (must = $855M)</t>
   </si>
   <si>
     <t xml:space="preserve">IQT-mirror: Substrate, EUV Tech, ThinTronics, EdgeCortix, Syntiant, Infleqtion, Diraq, Mueon, DefendEye</t>
@@ -1467,7 +1477,7 @@
     <t xml:space="preserve">Read: sized by strategic function, the sleeve is ~53% TSMC-alternative packaging/substrates (the sovereign core), ~25% denied-environment edge AI, ~20% next-gen compute, ~3% adjacent autonomy — a deliberate overweight to the domestic fail-safe chokepoints that re-rate hardest in a Taiwan/TSMC shock.</t>
   </si>
   <si>
-    <t xml:space="preserve">WEAPONS SLEEVE — BOTTOM-UP ($390M)</t>
+    <t xml:space="preserve">WEAPONS SLEEVE — BOTTOM-UP ($405M)</t>
   </si>
   <si>
     <t xml:space="preserve">Physical-layer defense holdings. Blue = input. Most entry marks are estimates; several names are access-constrained (see flags). Proceeds use munitions/FMS-adjusted CAGRs (cols S:V).</t>
@@ -1632,7 +1642,7 @@
     <t xml:space="preserve">Pre-IPO = 22x 2027E EBIT IPO value less 15% discount — see MSL Build</t>
   </si>
   <si>
-    <t xml:space="preserve">TOTAL (=$390M)</t>
+    <t xml:space="preserve">TOTAL (=$405M)</t>
   </si>
   <si>
     <t xml:space="preserve">5-YEAR HOLD — GROSS PROCEEDS</t>
@@ -1668,7 +1678,7 @@
     <t xml:space="preserve">Check size ($M)</t>
   </si>
   <si>
-    <t xml:space="preserve">User input: sub-$10M minority stake. Funded inside the fixed $390M sleeve by trimming Superior &amp; Grand Valley $40M -&gt; $31M.</t>
+    <t xml:space="preserve">User input: sub-$10M minority stake. Funded inside the Weapons sleeve by trimming Superior &amp; Grand Valley $40M -&gt; $31M.</t>
   </si>
   <si>
     <t xml:space="preserve">Ownership %</t>
@@ -2031,7 +2041,7 @@
     <t xml:space="preserve">Sleeve Adj. Base CAGR = build 7-yr Base CAGR</t>
   </si>
   <si>
-    <t xml:space="preserve">Weapons sleeve still fully deployed ($390M)</t>
+    <t xml:space="preserve">Weapons sleeve fully deployed (= committed)</t>
   </si>
   <si>
     <t xml:space="preserve">Stake &lt; $10M (user constraint)</t>
@@ -2103,7 +2113,7 @@
     <t xml:space="preserve">Pre-IPO post-money used for the Weapons Sleeve entry mark.</t>
   </si>
   <si>
-    <t xml:space="preserve">Sized per IC discussion (9/2026). Funded by trimming Saronic $70M -&gt; $55M.</t>
+    <t xml:space="preserve">Sized per IC discussion (9/2026). Funded by +$15M NEW commitment to the Weapons sleeve ($390M -&gt; $405M; holdco $840M -&gt; $855M) — no existing position trimmed.</t>
   </si>
   <si>
     <t xml:space="preserve">Check / entry valuation.</t>
@@ -2343,7 +2353,7 @@
     <t xml:space="preserve">PME, DPI &amp; PROBABILITY PRESSURE TEST</t>
   </si>
   <si>
-    <t xml:space="preserve">DPI/TVPI, KS-PME &amp; Direct Alpha vs SPX/NDX, and Expected Net IRR sensitivity to the TSMC-Shock probability. Rows 11-69 = IQT-mirror sleeve ($250M) only; rows 72+ = total $840M holdco (all three sleeves) — ties to IC Summary headline.</t>
+    <t xml:space="preserve">DPI/TVPI, KS-PME &amp; Direct Alpha vs SPX/NDX, and Expected Net IRR sensitivity to the TSMC-Shock probability. Rows 11-69 = IQT-mirror sleeve ($250M) only; rows 72+ = total $855M holdco (all three sleeves) — ties to IC Summary headline.</t>
   </si>
   <si>
     <t xml:space="preserve">PUBLIC-MARKET BENCHMARK ASSUMPTIONS (blue = lever)</t>
@@ -2418,7 +2428,7 @@
     <t xml:space="preserve">shock excluded</t>
   </si>
   <si>
-    <t xml:space="preserve">TOTAL HOLDCO ($840M) — DPI &amp; PME BY HOLD (Expected, probability-weighted)</t>
+    <t xml:space="preserve">TOTAL HOLDCO ($855M) — DPI &amp; PME BY HOLD (Expected, probability-weighted)</t>
   </si>
   <si>
     <t xml:space="preserve">5-yr</t>
@@ -2433,16 +2443,16 @@
     <t xml:space="preserve">Net KS-PME vs Defense+Semis basket</t>
   </si>
   <si>
-    <t xml:space="preserve">Links to Holdco Summary roll-ups (rows 38-44 / 59-65 / 80-86). Holdco = IQT-mirror + Weapons + Consumer/Value, 2%/8%/20% on $840M.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TOTAL HOLDCO ($840M) — TSMC-SHOCK PROBABILITY PRESSURE TEST</t>
+    <t xml:space="preserve">Links to Holdco Summary roll-ups (rows 38-44 / 59-65 / 80-86). Holdco = IQT-mirror + Weapons + Consumer/Value, 2%/8%/20% on $855M.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TOTAL HOLDCO ($855M) — TSMC-SHOCK PROBABILITY PRESSURE TEST</t>
   </si>
   <si>
     <t xml:space="preserve">Expected holdco Net IRR to LP as the TSMC-Shock probability varies (all three sleeves). Base/Bull/Bear keep their current relative weights; shock takes the remainder.</t>
   </si>
   <si>
-    <t xml:space="preserve">WEAPONS BOOK SLEEVE ($390M) — DPI &amp; PME BY HOLD (Expected, probability-weighted)</t>
+    <t xml:space="preserve">WEAPONS BOOK SLEEVE ($405M) — DPI &amp; PME BY HOLD (Expected, probability-weighted)</t>
   </si>
   <si>
     <t xml:space="preserve">Gross = sleeve proceeds from Weapons Sleeve tab. Net = gross × holdco expected net/gross ratio (pro-rata allocation of carry + fees; fees/carry are charged at holdco level).</t>
@@ -2648,15 +2658,15 @@
     </font>
     <font>
       <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
       <color rgb="FF0000FF"/>
       <name val="Arial"/>
       <family val="0"/>
       <charset val="1"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
       <b val="true"/>
@@ -3312,11 +3322,11 @@
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="171" fontId="17" fillId="4" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="171" fontId="18" fillId="4" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="172" fontId="17" fillId="4" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="172" fontId="18" fillId="4" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -3332,7 +3342,7 @@
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="174" fontId="17" fillId="4" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="174" fontId="18" fillId="4" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -3452,7 +3462,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="172" fontId="17" fillId="3" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="172" fontId="18" fillId="3" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -3508,7 +3518,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="173" fontId="17" fillId="13" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="173" fontId="18" fillId="13" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -3520,7 +3530,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="173" fontId="17" fillId="4" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="173" fontId="18" fillId="4" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -3528,7 +3538,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="17" fillId="4" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="18" fillId="4" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -3536,7 +3546,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="169" fontId="17" fillId="4" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="169" fontId="18" fillId="4" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -3560,7 +3570,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="176" fontId="17" fillId="4" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="176" fontId="18" fillId="4" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -3612,7 +3622,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="17" fillId="13" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="18" fillId="13" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -3620,7 +3630,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="171" fontId="17" fillId="4" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="171" fontId="18" fillId="4" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -4412,7 +4422,7 @@
       </c>
       <c r="E6" s="46" t="n">
         <f aca="false">C6/'Holdco Summary'!$B$9</f>
-        <v>0.157738095238095</v>
+        <v>0.154970760233918</v>
       </c>
       <c r="F6" s="92" t="n">
         <f aca="false">AVERAGE('Defense Supercycle'!G24,'Defense Supercycle'!G25,'Defense Supercycle'!G26)</f>
@@ -4443,7 +4453,7 @@
       </c>
       <c r="E7" s="46" t="n">
         <f aca="false">C7/'Holdco Summary'!$B$9</f>
-        <v>0.0738095238095238</v>
+        <v>0.0725146198830409</v>
       </c>
       <c r="F7" s="92" t="n">
         <f aca="false">AVERAGE('Defense Supercycle'!G27,'Defense Supercycle'!G28)</f>
@@ -4474,7 +4484,7 @@
       </c>
       <c r="E8" s="46" t="n">
         <f aca="false">C8/'Holdco Summary'!$B$9</f>
-        <v>0.0583333333333333</v>
+        <v>0.0573099415204678</v>
       </c>
       <c r="F8" s="92" t="n">
         <f aca="false">AVERAGE('Defense Supercycle'!G29,'Defense Supercycle'!G30,'Defense Supercycle'!G31)</f>
@@ -4505,7 +4515,7 @@
       </c>
       <c r="E9" s="46" t="n">
         <f aca="false">C9/'Holdco Summary'!$B$9</f>
-        <v>0.00773809523809524</v>
+        <v>0.00760233918128655</v>
       </c>
       <c r="F9" s="92" t="n">
         <f aca="false">AVERAGE('Defense Supercycle'!G32)</f>
@@ -5471,7 +5481,7 @@
       </c>
       <c r="B5" s="78" t="n">
         <f aca="false">'Holdco Summary'!$B$7</f>
-        <v>390</v>
+        <v>405</v>
       </c>
       <c r="C5" s="1"/>
       <c r="D5" s="1"/>
@@ -5669,11 +5679,11 @@
         <v>9250</v>
       </c>
       <c r="C12" s="79" t="n">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="D12" s="46" t="n">
         <f aca="false">C12/B12</f>
-        <v>0.00594594594594595</v>
+        <v>0.00756756756756757</v>
       </c>
       <c r="E12" s="47" t="s">
         <v>426</v>
@@ -6373,7 +6383,7 @@
       <c r="B23" s="1"/>
       <c r="C23" s="50" t="n">
         <f aca="false">SUM(C12:C22)</f>
-        <v>390</v>
+        <v>405</v>
       </c>
       <c r="D23" s="1"/>
       <c r="E23" s="1"/>
@@ -6472,11 +6482,11 @@
       </c>
       <c r="B27" s="91" t="n">
         <f aca="false">C12</f>
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="C27" s="95" t="n">
         <f aca="false">B27*(1+S12)^5*'Weapons Sleeve'!$B$6</f>
-        <v>168.826054829529</v>
+        <v>214.869524328492</v>
       </c>
       <c r="D27" s="68" t="n">
         <f aca="false">C27/B27</f>
@@ -6488,7 +6498,7 @@
       </c>
       <c r="F27" s="95" t="n">
         <f aca="false">B27*(1+T12)^5*'Weapons Sleeve'!$B$6</f>
-        <v>292.14081651392</v>
+        <v>371.81558465408</v>
       </c>
       <c r="G27" s="68" t="n">
         <f aca="false">F27/B27</f>
@@ -6500,7 +6510,7 @@
       </c>
       <c r="I27" s="95" t="n">
         <f aca="false">B27*(1+U12)^5*'Weapons Sleeve'!$B$6</f>
-        <v>53.18110853506</v>
+        <v>67.68504722644</v>
       </c>
       <c r="J27" s="68" t="n">
         <f aca="false">I27/B27</f>
@@ -6508,11 +6518,11 @@
       </c>
       <c r="K27" s="46" t="n">
         <f aca="false">(I27/B27)^(1/5)-1</f>
-        <v>-0.00670342208525587</v>
+        <v>-0.00670342208525598</v>
       </c>
       <c r="L27" s="96" t="n">
         <f aca="false">B27*(1+V12)^5*'Weapons Sleeve'!$B$6</f>
-        <v>267.313907851217</v>
+        <v>340.217700901549</v>
       </c>
       <c r="M27" s="69" t="n">
         <f aca="false">L27/B27</f>
@@ -7109,55 +7119,55 @@
       </c>
       <c r="B38" s="97" t="n">
         <f aca="false">SUM(B27:B37)</f>
-        <v>390</v>
+        <v>405</v>
       </c>
       <c r="C38" s="97" t="n">
         <f aca="false">SUM(C27:C37)</f>
-        <v>915.68570629413</v>
+        <v>961.729175793093</v>
       </c>
       <c r="D38" s="98" t="n">
         <f aca="false">C38/B38</f>
-        <v>2.34791206742085</v>
+        <v>2.37463994022986</v>
       </c>
       <c r="E38" s="99" t="n">
         <f aca="false">(C38/B38)^(1/5)-1</f>
-        <v>0.186141130155831</v>
+        <v>0.188829446220983</v>
       </c>
       <c r="F38" s="97" t="n">
         <f aca="false">SUM(F27:F37)</f>
-        <v>1518.01135428847</v>
+        <v>1597.68612242863</v>
       </c>
       <c r="G38" s="98" t="n">
         <f aca="false">F38/B38</f>
-        <v>3.89233680586787</v>
+        <v>3.94490400599662</v>
       </c>
       <c r="H38" s="99" t="n">
         <f aca="false">(F38/B38)^(1/5)-1</f>
-        <v>0.312327055698143</v>
+        <v>0.315852736366111</v>
       </c>
       <c r="I38" s="97" t="n">
         <f aca="false">SUM(I27:I37)</f>
-        <v>433.967166232866</v>
+        <v>448.471104924246</v>
       </c>
       <c r="J38" s="98" t="n">
         <f aca="false">I38/B38</f>
-        <v>1.11273632367401</v>
+        <v>1.10733606154135</v>
       </c>
       <c r="K38" s="99" t="n">
         <f aca="false">(I38/B38)^(1/5)-1</f>
-        <v>0.0215942810159535</v>
+        <v>0.0206007630100915</v>
       </c>
       <c r="L38" s="100" t="n">
         <f aca="false">SUM(L27:L37)</f>
-        <v>1531.53081758509</v>
+        <v>1604.43461063542</v>
       </c>
       <c r="M38" s="101" t="n">
         <f aca="false">L38/B38</f>
-        <v>3.92700209637202</v>
+        <v>3.96156693984054</v>
       </c>
       <c r="N38" s="102" t="n">
         <f aca="false">(L38/B38)^(1/5)-1</f>
-        <v>0.314656299001643</v>
+        <v>0.31696247263922</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7261,11 +7271,11 @@
       </c>
       <c r="B43" s="91" t="n">
         <f aca="false">C12</f>
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="C43" s="95" t="n">
         <f aca="false">B43*(1+S12)^7*'Weapons Sleeve'!$B$7</f>
-        <v>261.486877295751</v>
+        <v>332.801480194592</v>
       </c>
       <c r="D43" s="68" t="n">
         <f aca="false">C43/B43</f>
@@ -7277,7 +7287,7 @@
       </c>
       <c r="F43" s="95" t="n">
         <f aca="false">B43*(1+T12)^7*'Weapons Sleeve'!$B$7</f>
-        <v>563.460884052639</v>
+        <v>717.132034248813</v>
       </c>
       <c r="G43" s="68" t="n">
         <f aca="false">F43/B43</f>
@@ -7289,7 +7299,7 @@
       </c>
       <c r="I43" s="95" t="n">
         <f aca="false">B43*(1+U12)^7*'Weapons Sleeve'!$B$7</f>
-        <v>51.8913510419793</v>
+        <v>66.0435376897918</v>
       </c>
       <c r="J43" s="68" t="n">
         <f aca="false">I43/B43</f>
@@ -7301,7 +7311,7 @@
       </c>
       <c r="L43" s="96" t="n">
         <f aca="false">B43*(1+V12)^7*'Weapons Sleeve'!$B$7</f>
-        <v>497.582175894592</v>
+        <v>633.286405684026</v>
       </c>
       <c r="M43" s="69" t="n">
         <f aca="false">L43/B43</f>
@@ -7898,55 +7908,55 @@
       </c>
       <c r="B54" s="97" t="n">
         <f aca="false">SUM(B43:B53)</f>
-        <v>390</v>
+        <v>405</v>
       </c>
       <c r="C54" s="97" t="n">
         <f aca="false">SUM(C43:C53)</f>
-        <v>1296.54096147776</v>
+        <v>1367.85556437661</v>
       </c>
       <c r="D54" s="98" t="n">
         <f aca="false">C54/B54</f>
-        <v>3.32446400378914</v>
+        <v>3.3774211466089</v>
       </c>
       <c r="E54" s="99" t="n">
         <f aca="false">(C54/B54)^(1/7)-1</f>
-        <v>0.187221251956986</v>
+        <v>0.189904683804596</v>
       </c>
       <c r="F54" s="97" t="n">
         <f aca="false">SUM(F43:F53)</f>
-        <v>2663.99206233137</v>
+        <v>2817.66321252754</v>
       </c>
       <c r="G54" s="98" t="n">
         <f aca="false">F54/B54</f>
-        <v>6.83074887777274</v>
+        <v>6.95719311735195</v>
       </c>
       <c r="H54" s="99" t="n">
         <f aca="false">(F54/B54)^(1/7)-1</f>
-        <v>0.315860226153021</v>
+        <v>0.319312637995968</v>
       </c>
       <c r="I54" s="97" t="n">
         <f aca="false">SUM(I43:I53)</f>
-        <v>451.571462496729</v>
+        <v>465.723649144541</v>
       </c>
       <c r="J54" s="98" t="n">
         <f aca="false">I54/B54</f>
-        <v>1.15787554486341</v>
+        <v>1.14993493615936</v>
       </c>
       <c r="K54" s="99" t="n">
         <f aca="false">(I54/B54)^(1/7)-1</f>
-        <v>0.0211617866038758</v>
+        <v>0.0201583997119177</v>
       </c>
       <c r="L54" s="100" t="n">
         <f aca="false">SUM(L43:L53)</f>
-        <v>2692.9346809097</v>
+        <v>2828.63891069913</v>
       </c>
       <c r="M54" s="101" t="n">
         <f aca="false">L54/B54</f>
-        <v>6.90496072028128</v>
+        <v>6.98429360666453</v>
       </c>
       <c r="N54" s="102" t="n">
         <f aca="false">(L54/B54)^(1/7)-1</f>
-        <v>0.317893066655618</v>
+        <v>0.32004557875878</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8050,11 +8060,11 @@
       </c>
       <c r="B59" s="91" t="n">
         <f aca="false">C12</f>
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="C59" s="95" t="n">
         <f aca="false">B59*(1+S12)^10*'Weapons Sleeve'!$B$8</f>
-        <v>502.058647689221</v>
+        <v>638.983733422645</v>
       </c>
       <c r="D59" s="68" t="n">
         <f aca="false">C59/B59</f>
@@ -8066,7 +8076,7 @@
       </c>
       <c r="F59" s="95" t="n">
         <f aca="false">B59*(1+T12)^10*'Weapons Sleeve'!$B$8</f>
-        <v>1503.34959770159</v>
+        <v>1913.35403343838</v>
       </c>
       <c r="G59" s="68" t="n">
         <f aca="false">F59/B59</f>
@@ -8078,7 +8088,7 @@
       </c>
       <c r="I59" s="95" t="n">
         <f aca="false">B59*(1+U12)^10*'Weapons Sleeve'!$B$8</f>
-        <v>49.8184578560453</v>
+        <v>63.4053099986031</v>
       </c>
       <c r="J59" s="68" t="n">
         <f aca="false">I59/B59</f>
@@ -8090,7 +8100,7 @@
       </c>
       <c r="L59" s="96" t="n">
         <f aca="false">B59*(1+V12)^10*'Weapons Sleeve'!$B$8</f>
-        <v>1258.68952507228</v>
+        <v>1601.96848645563</v>
       </c>
       <c r="M59" s="69" t="n">
         <f aca="false">L59/B59</f>
@@ -8687,55 +8697,55 @@
       </c>
       <c r="B70" s="97" t="n">
         <f aca="false">SUM(B59:B69)</f>
-        <v>390</v>
+        <v>405</v>
       </c>
       <c r="C70" s="97" t="n">
         <f aca="false">SUM(C59:C69)</f>
-        <v>2216.90031706174</v>
+        <v>2353.82540279516</v>
       </c>
       <c r="D70" s="98" t="n">
         <f aca="false">C70/B70</f>
-        <v>5.68435978733779</v>
+        <v>5.81191457480287</v>
       </c>
       <c r="E70" s="99" t="n">
         <f aca="false">(C70/B70)^(1/10)-1</f>
-        <v>0.189784086386249</v>
+        <v>0.192427332423751</v>
       </c>
       <c r="F70" s="97" t="n">
         <f aca="false">SUM(F59:F69)</f>
-        <v>6362.82597009198</v>
+        <v>6772.83040582878</v>
       </c>
       <c r="G70" s="98" t="n">
         <f aca="false">F70/B70</f>
-        <v>16.3149383848512</v>
+        <v>16.7230380390834</v>
       </c>
       <c r="H70" s="99" t="n">
         <f aca="false">(F70/B70)^(1/10)-1</f>
-        <v>0.32208246088706</v>
+        <v>0.325352854416582</v>
       </c>
       <c r="I70" s="97" t="n">
         <f aca="false">SUM(I59:I69)</f>
-        <v>480.983029224514</v>
+        <v>494.569881367072</v>
       </c>
       <c r="J70" s="98" t="n">
         <f aca="false">I70/B70</f>
-        <v>1.2332898185244</v>
+        <v>1.22116020090635</v>
       </c>
       <c r="K70" s="99" t="n">
         <f aca="false">(I70/B70)^(1/10)-1</f>
-        <v>0.0211899089834458</v>
+        <v>0.0201810781311162</v>
       </c>
       <c r="L70" s="100" t="n">
         <f aca="false">SUM(L59:L69)</f>
-        <v>6448.54944420373</v>
+        <v>6791.82840558708</v>
       </c>
       <c r="M70" s="101" t="n">
         <f aca="false">L70/B70</f>
-        <v>16.534742164625</v>
+        <v>16.7699466804619</v>
       </c>
       <c r="N70" s="102" t="n">
         <f aca="false">(L70/B70)^(1/10)-1</f>
-        <v>0.323852935316205</v>
+        <v>0.325724151576512</v>
       </c>
     </row>
   </sheetData>
@@ -19058,15 +19068,15 @@
       </c>
       <c r="B74" s="175" t="n">
         <f aca="false">'Holdco Summary'!F38</f>
-        <v>2.26221016237823</v>
+        <v>2.27595084398942</v>
       </c>
       <c r="C74" s="175" t="n">
         <f aca="false">'Holdco Summary'!F59</f>
-        <v>3.42290649540101</v>
+        <v>3.45301348617188</v>
       </c>
       <c r="D74" s="175" t="n">
         <f aca="false">'Holdco Summary'!F80</f>
-        <v>6.83263713490145</v>
+        <v>6.9198197348059</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19075,15 +19085,15 @@
       </c>
       <c r="B75" s="175" t="n">
         <f aca="false">'Holdco Summary'!F39</f>
-        <v>2.26221016237823</v>
+        <v>2.27595084398942</v>
       </c>
       <c r="C75" s="175" t="n">
         <f aca="false">'Holdco Summary'!F60</f>
-        <v>3.42290649540101</v>
+        <v>3.45301348617188</v>
       </c>
       <c r="D75" s="175" t="n">
         <f aca="false">'Holdco Summary'!F81</f>
-        <v>6.83263713490145</v>
+        <v>6.9198197348059</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19092,15 +19102,15 @@
       </c>
       <c r="B76" s="176" t="n">
         <f aca="false">'Holdco Summary'!F40</f>
-        <v>0.177352715458623</v>
+        <v>0.178779502986822</v>
       </c>
       <c r="C76" s="176" t="n">
         <f aca="false">'Holdco Summary'!F61</f>
-        <v>0.192180867725363</v>
+        <v>0.193673267252674</v>
       </c>
       <c r="D76" s="176" t="n">
         <f aca="false">'Holdco Summary'!F82</f>
-        <v>0.211877816332995</v>
+        <v>0.213415331908954</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19109,15 +19119,15 @@
       </c>
       <c r="B77" s="178" t="n">
         <f aca="false">'Holdco Summary'!F41</f>
-        <v>1.47028138693269</v>
+        <v>1.47921188718093</v>
       </c>
       <c r="C77" s="178" t="n">
         <f aca="false">'Holdco Summary'!F62</f>
-        <v>1.87244706988098</v>
+        <v>1.88891662484182</v>
       </c>
       <c r="D77" s="178" t="n">
         <f aca="false">'Holdco Summary'!F83</f>
-        <v>2.88617976537917</v>
+        <v>2.92300663775207</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19126,15 +19136,15 @@
       </c>
       <c r="B78" s="178" t="n">
         <f aca="false">'Holdco Summary'!F42</f>
-        <v>1.22783704294971</v>
+        <v>1.23529493442159</v>
       </c>
       <c r="C78" s="178" t="n">
         <f aca="false">'Holdco Summary'!F63</f>
-        <v>1.454942838418</v>
+        <v>1.46774013529633</v>
       </c>
       <c r="D78" s="178" t="n">
         <f aca="false">'Holdco Summary'!F84</f>
-        <v>2.01281528691584</v>
+        <v>2.03849826500703</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19143,15 +19153,15 @@
       </c>
       <c r="B79" s="178" t="n">
         <f aca="false">'Holdco Summary'!F43</f>
-        <v>1.12471826308982</v>
+        <v>1.13154981031405</v>
       </c>
       <c r="C79" s="178" t="n">
         <f aca="false">'Holdco Summary'!F64</f>
-        <v>1.28679733581458</v>
+        <v>1.29811566880597</v>
       </c>
       <c r="D79" s="178" t="n">
         <f aca="false">'Holdco Summary'!F85</f>
-        <v>1.68892340222796</v>
+        <v>1.71047360756428</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19160,15 +19170,15 @@
       </c>
       <c r="B80" s="179" t="n">
         <f aca="false">'Holdco Summary'!F44</f>
-        <v>0.02378496996402</v>
+        <v>0.0250256547711496</v>
       </c>
       <c r="C80" s="179" t="n">
         <f aca="false">'Holdco Summary'!F65</f>
-        <v>0.0366790154133589</v>
+        <v>0.0379767541327605</v>
       </c>
       <c r="D80" s="179" t="n">
         <f aca="false">'Holdco Summary'!F86</f>
-        <v>0.0538067968112996</v>
+        <v>0.0551437668773511</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19177,15 +19187,15 @@
       </c>
       <c r="B81" s="181" t="n">
         <f aca="false">B77^(1/5)-1</f>
-        <v>0.0801401059253422</v>
+        <v>0.0814490853090109</v>
       </c>
       <c r="C81" s="181" t="n">
         <f aca="false">C77^(1/7)-1</f>
-        <v>0.0937439153443693</v>
+        <v>0.0951130892226371</v>
       </c>
       <c r="D81" s="181" t="n">
         <f aca="false">D77^(1/10)-1</f>
-        <v>0.111814510397243</v>
+        <v>0.113225075145829</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19231,15 +19241,15 @@
       </c>
       <c r="B87" s="185" t="n">
         <f aca="false">(((1-$A87)*('Defense Supercycle'!$B$17*'Holdco Summary'!B37+'Defense Supercycle'!$B$18*'Holdco Summary'!C37+'Defense Supercycle'!$B$19*'Holdco Summary'!D37)/('Defense Supercycle'!$B$17+'Defense Supercycle'!$B$18+'Defense Supercycle'!$B$19)+$A87*'Holdco Summary'!E37)/'Holdco Summary'!$B$9)^(1/5)-1</f>
-        <v>0.170807063973927</v>
+        <v>0.172041492331849</v>
       </c>
       <c r="C87" s="185" t="n">
         <f aca="false">(((1-$A87)*('Defense Supercycle'!$B$17*'Holdco Summary'!B58+'Defense Supercycle'!$B$18*'Holdco Summary'!C58+'Defense Supercycle'!$B$19*'Holdco Summary'!D58)/('Defense Supercycle'!$B$17+'Defense Supercycle'!$B$18+'Defense Supercycle'!$B$19)+$A87*'Holdco Summary'!E58)/'Holdco Summary'!$B$9)^(1/7)-1</f>
-        <v>0.18429576547191</v>
+        <v>0.185622386660826</v>
       </c>
       <c r="D87" s="185" t="n">
         <f aca="false">(((1-$A87)*('Defense Supercycle'!$B$17*'Holdco Summary'!B79+'Defense Supercycle'!$B$18*'Holdco Summary'!C79+'Defense Supercycle'!$B$19*'Holdco Summary'!D79)/('Defense Supercycle'!$B$17+'Defense Supercycle'!$B$18+'Defense Supercycle'!$B$19)+$A87*'Holdco Summary'!E79)/'Holdco Summary'!$B$9)^(1/10)-1</f>
-        <v>0.202684088385577</v>
+        <v>0.204103263202339</v>
       </c>
       <c r="E87" s="186" t="s">
         <v>719</v>
@@ -19251,15 +19261,15 @@
       </c>
       <c r="B88" s="185" t="n">
         <f aca="false">(((1-$A88)*('Defense Supercycle'!$B$17*'Holdco Summary'!B37+'Defense Supercycle'!$B$18*'Holdco Summary'!C37+'Defense Supercycle'!$B$19*'Holdco Summary'!D37)/('Defense Supercycle'!$B$17+'Defense Supercycle'!$B$18+'Defense Supercycle'!$B$19)+$A88*'Holdco Summary'!E37)/'Holdco Summary'!$B$9)^(1/5)-1</f>
-        <v>0.173005211773832</v>
+        <v>0.174304711633184</v>
       </c>
       <c r="C88" s="185" t="n">
         <f aca="false">(((1-$A88)*('Defense Supercycle'!$B$17*'Holdco Summary'!B58+'Defense Supercycle'!$B$18*'Holdco Summary'!C58+'Defense Supercycle'!$B$19*'Holdco Summary'!D58)/('Defense Supercycle'!$B$17+'Defense Supercycle'!$B$18+'Defense Supercycle'!$B$19)+$A88*'Holdco Summary'!E58)/'Holdco Summary'!$B$9)^(1/7)-1</f>
-        <v>0.186959181637902</v>
+        <v>0.188342511590328</v>
       </c>
       <c r="D88" s="185" t="n">
         <f aca="false">(((1-$A88)*('Defense Supercycle'!$B$17*'Holdco Summary'!B79+'Defense Supercycle'!$B$18*'Holdco Summary'!C79+'Defense Supercycle'!$B$19*'Holdco Summary'!D79)/('Defense Supercycle'!$B$17+'Defense Supercycle'!$B$18+'Defense Supercycle'!$B$19)+$A88*'Holdco Summary'!E79)/'Holdco Summary'!$B$9)^(1/10)-1</f>
-        <v>0.205819228650319</v>
+        <v>0.207279596577157</v>
       </c>
       <c r="E88" s="186" t="str">
         <f aca="false">IF(ABS($A88-'Defense Supercycle'!$B$20)&lt;0.0001,"current base case","")</f>
@@ -19272,15 +19282,15 @@
       </c>
       <c r="B89" s="185" t="n">
         <f aca="false">(((1-$A89)*('Defense Supercycle'!$B$17*'Holdco Summary'!B37+'Defense Supercycle'!$B$18*'Holdco Summary'!C37+'Defense Supercycle'!$B$19*'Holdco Summary'!D37)/('Defense Supercycle'!$B$17+'Defense Supercycle'!$B$18+'Defense Supercycle'!$B$19)+$A89*'Holdco Summary'!E37)/'Holdco Summary'!$B$9)^(1/5)-1</f>
-        <v>0.175187005183742</v>
+        <v>0.176550616781995</v>
       </c>
       <c r="C89" s="185" t="n">
         <f aca="false">(((1-$A89)*('Defense Supercycle'!$B$17*'Holdco Summary'!B58+'Defense Supercycle'!$B$18*'Holdco Summary'!C58+'Defense Supercycle'!$B$19*'Holdco Summary'!D58)/('Defense Supercycle'!$B$17+'Defense Supercycle'!$B$18+'Defense Supercycle'!$B$19)+$A89*'Holdco Summary'!E58)/'Holdco Summary'!$B$9)^(1/7)-1</f>
-        <v>0.189587214743112</v>
+        <v>0.191025783454299</v>
       </c>
       <c r="D89" s="185" t="n">
         <f aca="false">(((1-$A89)*('Defense Supercycle'!$B$17*'Holdco Summary'!B79+'Defense Supercycle'!$B$18*'Holdco Summary'!C79+'Defense Supercycle'!$B$19*'Holdco Summary'!D79)/('Defense Supercycle'!$B$17+'Defense Supercycle'!$B$18+'Defense Supercycle'!$B$19)+$A89*'Holdco Summary'!E79)/'Holdco Summary'!$B$9)^(1/10)-1</f>
-        <v>0.208882679587533</v>
+        <v>0.210382453298415</v>
       </c>
       <c r="E89" s="186" t="str">
         <f aca="false">IF(ABS($A89-'Defense Supercycle'!$B$20)&lt;0.0001,"current base case","")</f>
@@ -19293,15 +19303,15 @@
       </c>
       <c r="B90" s="185" t="n">
         <f aca="false">(((1-$A90)*('Defense Supercycle'!$B$17*'Holdco Summary'!B37+'Defense Supercycle'!$B$18*'Holdco Summary'!C37+'Defense Supercycle'!$B$19*'Holdco Summary'!D37)/('Defense Supercycle'!$B$17+'Defense Supercycle'!$B$18+'Defense Supercycle'!$B$19)+$A90*'Holdco Summary'!E37)/'Holdco Summary'!$B$9)^(1/5)-1</f>
-        <v>0.177352715458623</v>
+        <v>0.178779502986822</v>
       </c>
       <c r="C90" s="185" t="n">
         <f aca="false">(((1-$A90)*('Defense Supercycle'!$B$17*'Holdco Summary'!B58+'Defense Supercycle'!$B$18*'Holdco Summary'!C58+'Defense Supercycle'!$B$19*'Holdco Summary'!D58)/('Defense Supercycle'!$B$17+'Defense Supercycle'!$B$18+'Defense Supercycle'!$B$19)+$A90*'Holdco Summary'!E58)/'Holdco Summary'!$B$9)^(1/7)-1</f>
-        <v>0.192180867725362</v>
+        <v>0.193673267252674</v>
       </c>
       <c r="D90" s="185" t="n">
         <f aca="false">(((1-$A90)*('Defense Supercycle'!$B$17*'Holdco Summary'!B79+'Defense Supercycle'!$B$18*'Holdco Summary'!C79+'Defense Supercycle'!$B$19*'Holdco Summary'!D79)/('Defense Supercycle'!$B$17+'Defense Supercycle'!$B$18+'Defense Supercycle'!$B$19)+$A90*'Holdco Summary'!E79)/'Holdco Summary'!$B$9)^(1/10)-1</f>
-        <v>0.211877816332995</v>
+        <v>0.213415331908954</v>
       </c>
       <c r="E90" s="186" t="str">
         <f aca="false">IF(ABS($A90-'Defense Supercycle'!$B$20)&lt;0.0001,"current base case","")</f>
@@ -19314,15 +19324,15 @@
       </c>
       <c r="B91" s="185" t="n">
         <f aca="false">(((1-$A91)*('Defense Supercycle'!$B$17*'Holdco Summary'!B37+'Defense Supercycle'!$B$18*'Holdco Summary'!C37+'Defense Supercycle'!$B$19*'Holdco Summary'!D37)/('Defense Supercycle'!$B$17+'Defense Supercycle'!$B$18+'Defense Supercycle'!$B$19)+$A91*'Holdco Summary'!E37)/'Holdco Summary'!$B$9)^(1/5)-1</f>
-        <v>0.179502606918758</v>
+        <v>0.180991657699962</v>
       </c>
       <c r="C91" s="185" t="n">
         <f aca="false">(((1-$A91)*('Defense Supercycle'!$B$17*'Holdco Summary'!B58+'Defense Supercycle'!$B$18*'Holdco Summary'!C58+'Defense Supercycle'!$B$19*'Holdco Summary'!D58)/('Defense Supercycle'!$B$17+'Defense Supercycle'!$B$18+'Defense Supercycle'!$B$19)+$A91*'Holdco Summary'!E58)/'Holdco Summary'!$B$9)^(1/7)-1</f>
-        <v>0.194741100443027</v>
+        <v>0.196285981360697</v>
       </c>
       <c r="D91" s="185" t="n">
         <f aca="false">(((1-$A91)*('Defense Supercycle'!$B$17*'Holdco Summary'!B79+'Defense Supercycle'!$B$18*'Holdco Summary'!C79+'Defense Supercycle'!$B$19*'Holdco Summary'!D79)/('Defense Supercycle'!$B$17+'Defense Supercycle'!$B$18+'Defense Supercycle'!$B$19)+$A91*'Holdco Summary'!E79)/'Holdco Summary'!$B$9)^(1/10)-1</f>
-        <v>0.21480777734036</v>
+        <v>0.216381482898982</v>
       </c>
       <c r="E91" s="186" t="str">
         <f aca="false">IF(ABS($A91-'Defense Supercycle'!$B$20)&lt;0.0001,"current base case","")</f>
@@ -19335,15 +19345,15 @@
       </c>
       <c r="B92" s="185" t="n">
         <f aca="false">(((1-$A92)*('Defense Supercycle'!$B$17*'Holdco Summary'!B37+'Defense Supercycle'!$B$18*'Holdco Summary'!C37+'Defense Supercycle'!$B$19*'Holdco Summary'!D37)/('Defense Supercycle'!$B$17+'Defense Supercycle'!$B$18+'Defense Supercycle'!$B$19)+$A92*'Holdco Summary'!E37)/'Holdco Summary'!$B$9)^(1/5)-1</f>
-        <v>0.181636937188174</v>
+        <v>0.183187360891462</v>
       </c>
       <c r="C92" s="185" t="n">
         <f aca="false">(((1-$A92)*('Defense Supercycle'!$B$17*'Holdco Summary'!B58+'Defense Supercycle'!$B$18*'Holdco Summary'!C58+'Defense Supercycle'!$B$19*'Holdco Summary'!D58)/('Defense Supercycle'!$B$17+'Defense Supercycle'!$B$18+'Defense Supercycle'!$B$19)+$A92*'Holdco Summary'!E58)/'Holdco Summary'!$B$9)^(1/7)-1</f>
-        <v>0.197268832136125</v>
+        <v>0.198864900242989</v>
       </c>
       <c r="D92" s="185" t="n">
         <f aca="false">(((1-$A92)*('Defense Supercycle'!$B$17*'Holdco Summary'!B79+'Defense Supercycle'!$B$18*'Holdco Summary'!C79+'Defense Supercycle'!$B$19*'Holdco Summary'!D79)/('Defense Supercycle'!$B$17+'Defense Supercycle'!$B$18+'Defense Supercycle'!$B$19)+$A92*'Holdco Summary'!E79)/'Holdco Summary'!$B$9)^(1/10)-1</f>
-        <v>0.217675486175901</v>
+        <v>0.219283931794773</v>
       </c>
       <c r="E92" s="186" t="str">
         <f aca="false">IF(ABS($A92-'Defense Supercycle'!$B$20)&lt;0.0001,"current base case","")</f>
@@ -19356,15 +19366,15 @@
       </c>
       <c r="B93" s="185" t="n">
         <f aca="false">(((1-$A93)*('Defense Supercycle'!$B$17*'Holdco Summary'!B37+'Defense Supercycle'!$B$18*'Holdco Summary'!C37+'Defense Supercycle'!$B$19*'Holdco Summary'!D37)/('Defense Supercycle'!$B$17+'Defense Supercycle'!$B$18+'Defense Supercycle'!$B$19)+$A93*'Holdco Summary'!E37)/'Holdco Summary'!$B$9)^(1/5)-1</f>
-        <v>0.183755957422806</v>
+        <v>0.18536688531101</v>
       </c>
       <c r="C93" s="185" t="n">
         <f aca="false">(((1-$A93)*('Defense Supercycle'!$B$17*'Holdco Summary'!B58+'Defense Supercycle'!$B$18*'Holdco Summary'!C58+'Defense Supercycle'!$B$19*'Holdco Summary'!D58)/('Defense Supercycle'!$B$17+'Defense Supercycle'!$B$18+'Defense Supercycle'!$B$19)+$A93*'Holdco Summary'!E58)/'Holdco Summary'!$B$9)^(1/7)-1</f>
-        <v>0.199764943712947</v>
+        <v>0.20141095697163</v>
       </c>
       <c r="D93" s="185" t="n">
         <f aca="false">(((1-$A93)*('Defense Supercycle'!$B$17*'Holdco Summary'!B79+'Defense Supercycle'!$B$18*'Holdco Summary'!C79+'Defense Supercycle'!$B$19*'Holdco Summary'!D79)/('Defense Supercycle'!$B$17+'Defense Supercycle'!$B$18+'Defense Supercycle'!$B$19)+$A93*'Holdco Summary'!E79)/'Holdco Summary'!$B$9)^(1/10)-1</f>
-        <v>0.220483670849732</v>
+        <v>0.222125499610033</v>
       </c>
       <c r="E93" s="186" t="str">
         <f aca="false">IF(ABS($A93-'Defense Supercycle'!$B$20)&lt;0.0001,"current base case","")</f>
@@ -19377,15 +19387,15 @@
       </c>
       <c r="B94" s="188" t="n">
         <f aca="false">(((1-$A94)*('Defense Supercycle'!$B$17*'Holdco Summary'!B37+'Defense Supercycle'!$B$18*'Holdco Summary'!C37+'Defense Supercycle'!$B$19*'Holdco Summary'!D37)/('Defense Supercycle'!$B$17+'Defense Supercycle'!$B$18+'Defense Supercycle'!$B$19)+$A94*'Holdco Summary'!E37)/'Holdco Summary'!$B$9)^(1/5)-1</f>
-        <v>0.187949041372367</v>
+        <v>0.189678454222763</v>
       </c>
       <c r="C94" s="188" t="n">
         <f aca="false">(((1-$A94)*('Defense Supercycle'!$B$17*'Holdco Summary'!B58+'Defense Supercycle'!$B$18*'Holdco Summary'!C58+'Defense Supercycle'!$B$19*'Holdco Summary'!D58)/('Defense Supercycle'!$B$17+'Defense Supercycle'!$B$18+'Defense Supercycle'!$B$19)+$A94*'Holdco Summary'!E58)/'Holdco Summary'!$B$9)^(1/7)-1</f>
-        <v>0.204665651106906</v>
+        <v>0.206408023162932</v>
       </c>
       <c r="D94" s="188" t="n">
         <f aca="false">(((1-$A94)*('Defense Supercycle'!$B$17*'Holdco Summary'!B79+'Defense Supercycle'!$B$18*'Holdco Summary'!C79+'Defense Supercycle'!$B$19*'Holdco Summary'!D79)/('Defense Supercycle'!$B$17+'Defense Supercycle'!$B$18+'Defense Supercycle'!$B$19)+$A94*'Holdco Summary'!E79)/'Holdco Summary'!$B$9)^(1/10)-1</f>
-        <v>0.225931503286711</v>
+        <v>0.227636360519233</v>
       </c>
       <c r="E94" s="189" t="str">
         <f aca="false">IF(ABS($A94-'Defense Supercycle'!$B$20)&lt;0.0001,"current base case","")</f>
@@ -19441,15 +19451,15 @@
       </c>
       <c r="B101" s="194" t="n">
         <f aca="false">'Holdco Summary'!$B$7</f>
-        <v>390</v>
+        <v>405</v>
       </c>
       <c r="C101" s="194" t="n">
         <f aca="false">'Holdco Summary'!$B$7</f>
-        <v>390</v>
+        <v>405</v>
       </c>
       <c r="D101" s="194" t="n">
         <f aca="false">'Holdco Summary'!$B$7</f>
-        <v>390</v>
+        <v>405</v>
       </c>
     </row>
     <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19458,15 +19468,15 @@
       </c>
       <c r="B102" s="194" t="n">
         <f aca="false">'Holdco Summary'!F29</f>
-        <v>1086.38610397717</v>
+        <v>1140.135517048</v>
       </c>
       <c r="C102" s="194" t="n">
         <f aca="false">'Holdco Summary'!F50</f>
-        <v>1721.1173697588</v>
+        <v>1814.10519107791</v>
       </c>
       <c r="D102" s="194" t="n">
         <f aca="false">'Holdco Summary'!F71</f>
-        <v>3627.74150621502</v>
+        <v>3845.38877575814</v>
       </c>
     </row>
     <row r="103" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19475,15 +19485,15 @@
       </c>
       <c r="B103" s="195" t="n">
         <f aca="false">B102/B101</f>
-        <v>2.78560539481325</v>
+        <v>2.81514942480987</v>
       </c>
       <c r="C103" s="195" t="n">
         <f aca="false">C102/C101</f>
-        <v>4.41312146092</v>
+        <v>4.47927207673558</v>
       </c>
       <c r="D103" s="195" t="n">
         <f aca="false">D102/D101</f>
-        <v>9.30190129798722</v>
+        <v>9.49478710063738</v>
       </c>
     </row>
     <row r="104" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19492,15 +19502,15 @@
       </c>
       <c r="B104" s="196" t="n">
         <f aca="false">B103^(1/B$100)-1</f>
-        <v>0.227393782460184</v>
+        <v>0.229986345820906</v>
       </c>
       <c r="C104" s="196" t="n">
         <f aca="false">C103^(1/C$100)-1</f>
-        <v>0.236250710960596</v>
+        <v>0.23888112043644</v>
       </c>
       <c r="D104" s="196" t="n">
         <f aca="false">D103^(1/D$100)-1</f>
-        <v>0.249847922597485</v>
+        <v>0.252415757426635</v>
       </c>
     </row>
     <row r="105" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19509,15 +19519,15 @@
       </c>
       <c r="B105" s="197" t="n">
         <f aca="false">'Holdco Summary'!F37/'Holdco Summary'!F31</f>
-        <v>0.867305820994541</v>
+        <v>0.866888959910737</v>
       </c>
       <c r="C105" s="197" t="n">
         <f aca="false">'Holdco Summary'!F58/'Holdco Summary'!F52</f>
-        <v>0.843463122332387</v>
+        <v>0.843078546393105</v>
       </c>
       <c r="D105" s="197" t="n">
         <f aca="false">'Holdco Summary'!F79/'Holdco Summary'!F73</f>
-        <v>0.823094303611507</v>
+        <v>0.822800372429311</v>
       </c>
     </row>
     <row r="106" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19526,15 +19536,15 @@
       </c>
       <c r="B106" s="198" t="n">
         <f aca="false">B102*B105</f>
-        <v>942.228991826979</v>
+        <v>988.370892531031</v>
       </c>
       <c r="C106" s="198" t="n">
         <f aca="false">C102*C105</f>
-        <v>1451.69903059726</v>
+        <v>1529.43316749815</v>
       </c>
       <c r="D106" s="198" t="n">
         <f aca="false">D102*D105</f>
-        <v>2985.97336874061</v>
+        <v>3163.98731682929</v>
       </c>
     </row>
     <row r="107" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19543,15 +19553,15 @@
       </c>
       <c r="B107" s="195" t="n">
         <f aca="false">B106/B101</f>
-        <v>2.41597177391533</v>
+        <v>2.44042195686674</v>
       </c>
       <c r="C107" s="195" t="n">
         <f aca="false">C106/C101</f>
-        <v>3.72230520665965</v>
+        <v>3.77637819135345</v>
       </c>
       <c r="D107" s="195" t="n">
         <f aca="false">D106/D101</f>
-        <v>7.65634197112976</v>
+        <v>7.81231436254146</v>
       </c>
     </row>
     <row r="108" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19560,15 +19570,15 @@
       </c>
       <c r="B108" s="196" t="n">
         <f aca="false">B107^(1/B$100)-1</f>
-        <v>0.192939368853149</v>
+        <v>0.195344216874197</v>
       </c>
       <c r="C108" s="196" t="n">
         <f aca="false">C107^(1/C$100)-1</f>
-        <v>0.206547901240161</v>
+        <v>0.209036339363743</v>
       </c>
       <c r="D108" s="196" t="n">
         <f aca="false">D107^(1/D$100)-1</f>
-        <v>0.225750650228251</v>
+        <v>0.228225107618929</v>
       </c>
     </row>
     <row r="109" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19577,15 +19587,15 @@
       </c>
       <c r="B109" s="200" t="n">
         <f aca="false">B107/(1+'Holdco Summary'!$B$21)^B$100</f>
-        <v>1.57021588427846</v>
+        <v>1.58610682557932</v>
       </c>
       <c r="C109" s="200" t="n">
         <f aca="false">C107/(1+'Holdco Summary'!$B$21)^C$100</f>
-        <v>2.03622841780141</v>
+        <v>2.06580819214981</v>
       </c>
       <c r="D109" s="200" t="n">
         <f aca="false">D107/(1+'Holdco Summary'!$B$21)^D$100</f>
-        <v>3.23412158989425</v>
+        <v>3.30000601360392</v>
       </c>
     </row>
     <row r="110" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19594,15 +19604,15 @@
       </c>
       <c r="B110" s="200" t="n">
         <f aca="false">B107/(1+'Holdco Summary'!$B$22)^B$100</f>
-        <v>1.31129268538676</v>
+        <v>1.32456326512064</v>
       </c>
       <c r="C110" s="200" t="n">
         <f aca="false">C107/(1+'Holdco Summary'!$B$22)^C$100</f>
-        <v>1.58220544736237</v>
+        <v>1.60518974504559</v>
       </c>
       <c r="D110" s="200" t="n">
         <f aca="false">D107/(1+'Holdco Summary'!$B$22)^D$100</f>
-        <v>2.25546913396384</v>
+        <v>2.30141678310309</v>
       </c>
     </row>
     <row r="111" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19611,15 +19621,15 @@
       </c>
       <c r="B111" s="200" t="n">
         <f aca="false">B107/(1+'Holdco Summary'!$B$23)^B$100</f>
-        <v>1.20116495912804</v>
+        <v>1.21332102126527</v>
       </c>
       <c r="C111" s="200" t="n">
         <f aca="false">C107/(1+'Holdco Summary'!$B$23)^C$100</f>
-        <v>1.39935240108194</v>
+        <v>1.41968043888754</v>
       </c>
       <c r="D111" s="200" t="n">
         <f aca="false">D107/(1+'Holdco Summary'!$B$23)^D$100</f>
-        <v>1.89253064010222</v>
+        <v>1.93108462983644</v>
       </c>
     </row>
     <row r="112" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19628,15 +19638,15 @@
       </c>
       <c r="B112" s="201" t="n">
         <f aca="false">B111^(1/B$100)-1</f>
-        <v>0.037338581611434</v>
+        <v>0.0394297538036497</v>
       </c>
       <c r="C112" s="201" t="n">
         <f aca="false">C111^(1/C$100)-1</f>
-        <v>0.0491720880349229</v>
+        <v>0.0513359472728199</v>
       </c>
       <c r="D112" s="201" t="n">
         <f aca="false">D111^(1/D$100)-1</f>
-        <v>0.0658701306332621</v>
+        <v>0.0680218327121123</v>
       </c>
     </row>
     <row r="113" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19645,15 +19655,15 @@
       </c>
       <c r="B113" s="201" t="n">
         <f aca="false">B109^(1/B$100)-1</f>
-        <v>0.0944397879386689</v>
+        <v>0.0966460705267862</v>
       </c>
       <c r="C113" s="201" t="n">
         <f aca="false">C109^(1/C$100)-1</f>
-        <v>0.106924680036845</v>
+        <v>0.109207650792424</v>
       </c>
       <c r="D113" s="201" t="n">
         <f aca="false">D109^(1/D$100)-1</f>
-        <v>0.12454188094335</v>
+        <v>0.126812025338467</v>
       </c>
     </row>
     <row r="115" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19717,23 +19727,23 @@
       </c>
       <c r="B118" s="194" t="n">
         <f aca="false">'Weapons Sleeve'!C54</f>
-        <v>1296.54096147776</v>
+        <v>1367.85556437661</v>
       </c>
       <c r="C118" s="194" t="n">
         <f aca="false">'Weapons Sleeve'!F54</f>
-        <v>2663.99206233137</v>
+        <v>2817.66321252754</v>
       </c>
       <c r="D118" s="194" t="n">
         <f aca="false">'Weapons Sleeve'!I54</f>
-        <v>451.571462496729</v>
+        <v>465.723649144541</v>
       </c>
       <c r="E118" s="206" t="n">
         <f aca="false">'Weapons Sleeve'!L54</f>
-        <v>2692.9346809097</v>
+        <v>2828.63891069913</v>
       </c>
       <c r="F118" s="207" t="n">
         <f aca="false">SUMPRODUCT(B117:E117,B118:E118)</f>
-        <v>1721.1173697588</v>
+        <v>1814.10519107791</v>
       </c>
     </row>
     <row r="119" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19742,23 +19752,23 @@
       </c>
       <c r="B119" s="208" t="n">
         <f aca="false">'Weapons Sleeve'!D54</f>
-        <v>3.32446400378914</v>
+        <v>3.3774211466089</v>
       </c>
       <c r="C119" s="208" t="n">
         <f aca="false">'Weapons Sleeve'!G54</f>
-        <v>6.83074887777274</v>
+        <v>6.95719311735195</v>
       </c>
       <c r="D119" s="208" t="n">
         <f aca="false">'Weapons Sleeve'!J54</f>
-        <v>1.15787554486341</v>
+        <v>1.14993493615936</v>
       </c>
       <c r="E119" s="209" t="n">
         <f aca="false">'Weapons Sleeve'!M54</f>
-        <v>6.90496072028128</v>
+        <v>6.98429360666453</v>
       </c>
       <c r="F119" s="210" t="n">
         <f aca="false">F118/'Weapons Sleeve'!B54</f>
-        <v>4.41312146092</v>
+        <v>4.47927207673558</v>
       </c>
     </row>
     <row r="120" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19767,23 +19777,23 @@
       </c>
       <c r="B120" s="203" t="n">
         <f aca="false">'Weapons Sleeve'!E54</f>
-        <v>0.187221251956986</v>
+        <v>0.189904683804596</v>
       </c>
       <c r="C120" s="203" t="n">
         <f aca="false">'Weapons Sleeve'!H54</f>
-        <v>0.315860226153021</v>
+        <v>0.319312637995968</v>
       </c>
       <c r="D120" s="203" t="n">
         <f aca="false">'Weapons Sleeve'!K54</f>
-        <v>0.0211617866038758</v>
+        <v>0.0201583997119177</v>
       </c>
       <c r="E120" s="204" t="n">
         <f aca="false">'Weapons Sleeve'!N54</f>
-        <v>0.317893066655618</v>
+        <v>0.32004557875878</v>
       </c>
       <c r="F120" s="205" t="n">
         <f aca="false">F119^(1/$C$100)-1</f>
-        <v>0.236250710960596</v>
+        <v>0.23888112043644</v>
       </c>
     </row>
     <row r="121" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19792,23 +19802,23 @@
       </c>
       <c r="B121" s="200" t="n">
         <f aca="false">B119/(1+'Holdco Summary'!$B$23)^$C$100</f>
-        <v>1.24978915691536</v>
+        <v>1.26969770842981</v>
       </c>
       <c r="C121" s="200" t="n">
         <f aca="false">C119/(1+'Holdco Summary'!$B$23)^$C$100</f>
-        <v>2.56793151356787</v>
+        <v>2.61546658671061</v>
       </c>
       <c r="D121" s="200" t="n">
         <f aca="false">D119/(1+'Holdco Summary'!$B$23)^$C$100</f>
-        <v>0.435288304935287</v>
+        <v>0.432303136003901</v>
       </c>
       <c r="E121" s="200" t="n">
         <f aca="false">E119/(1+'Holdco Summary'!$B$23)^$C$100</f>
-        <v>2.59583049396777</v>
+        <v>2.62565466444324</v>
       </c>
       <c r="F121" s="200" t="n">
         <f aca="false">F119/(1+'Holdco Summary'!$B$23)^$C$100</f>
-        <v>1.65905581883934</v>
+        <v>1.68392428553814</v>
       </c>
     </row>
   </sheetData>
@@ -20382,23 +20392,23 @@
       </c>
       <c r="B6" s="17" t="n">
         <f aca="false">'Holdco Summary'!F61</f>
-        <v>0.192180867725363</v>
+        <v>0.193673267252674</v>
       </c>
       <c r="C6" s="18" t="n">
         <f aca="false">'Holdco Summary'!F59</f>
-        <v>3.42290649540101</v>
+        <v>3.45301348617188</v>
       </c>
       <c r="D6" s="19" t="n">
         <f aca="false">'Holdco Summary'!F58</f>
-        <v>2875.24145613685</v>
+        <v>2952.32653067696</v>
       </c>
       <c r="E6" s="18" t="n">
         <f aca="false">'Holdco Summary'!F64</f>
-        <v>1.28679733581458</v>
+        <v>1.29811566880597</v>
       </c>
       <c r="F6" s="18" t="n">
         <f aca="false">'Holdco Summary'!F62</f>
-        <v>1.87244706988098</v>
+        <v>1.88891662484182</v>
       </c>
       <c r="G6" s="1"/>
     </row>
@@ -20449,23 +20459,23 @@
       </c>
       <c r="B10" s="21" t="n">
         <f aca="false">'Holdco Summary'!B40</f>
-        <v>0.155069571921647</v>
+        <v>0.156236964998106</v>
       </c>
       <c r="C10" s="21" t="n">
         <f aca="false">'Holdco Summary'!C40</f>
-        <v>0.271525962366753</v>
+        <v>0.273025081505314</v>
       </c>
       <c r="D10" s="21" t="n">
         <f aca="false">'Holdco Summary'!D40</f>
-        <v>-0.053663530570773</v>
+        <v>-0.053191710305405</v>
       </c>
       <c r="E10" s="21" t="n">
         <f aca="false">'Holdco Summary'!E40</f>
-        <v>0.211941654166605</v>
+        <v>0.214318971802798</v>
       </c>
       <c r="F10" s="17" t="n">
         <f aca="false">'Holdco Summary'!F40</f>
-        <v>0.177352715458623</v>
+        <v>0.178779502986822</v>
       </c>
       <c r="G10" s="1"/>
     </row>
@@ -20475,23 +20485,23 @@
       </c>
       <c r="B11" s="21" t="n">
         <f aca="false">'Holdco Summary'!B61</f>
-        <v>0.158995489652759</v>
+        <v>0.160229366235885</v>
       </c>
       <c r="C11" s="21" t="n">
         <f aca="false">'Holdco Summary'!C61</f>
-        <v>0.280230644478965</v>
+        <v>0.281797106824369</v>
       </c>
       <c r="D11" s="21" t="n">
         <f aca="false">'Holdco Summary'!D61</f>
-        <v>-0.0507794883216116</v>
+        <v>-0.0504059739765521</v>
       </c>
       <c r="E11" s="21" t="n">
         <f aca="false">'Holdco Summary'!E61</f>
-        <v>0.231808313482553</v>
+        <v>0.234046609741583</v>
       </c>
       <c r="F11" s="17" t="n">
         <f aca="false">'Holdco Summary'!F61</f>
-        <v>0.192180867725363</v>
+        <v>0.193673267252674</v>
       </c>
       <c r="G11" s="1"/>
     </row>
@@ -20501,23 +20511,23 @@
       </c>
       <c r="B12" s="21" t="n">
         <f aca="false">'Holdco Summary'!B82</f>
-        <v>0.164649431844847</v>
+        <v>0.165952502895083</v>
       </c>
       <c r="C12" s="21" t="n">
         <f aca="false">'Holdco Summary'!C82</f>
-        <v>0.291284942436493</v>
+        <v>0.292894592849268</v>
       </c>
       <c r="D12" s="21" t="n">
         <f aca="false">'Holdco Summary'!D82</f>
-        <v>-0.0462072190141125</v>
+        <v>-0.045985312895805</v>
       </c>
       <c r="E12" s="21" t="n">
         <f aca="false">'Holdco Summary'!E82</f>
-        <v>0.25472957508494</v>
+        <v>0.256733550220737</v>
       </c>
       <c r="F12" s="17" t="n">
         <f aca="false">'Holdco Summary'!F82</f>
-        <v>0.211877816332995</v>
+        <v>0.213415331908954</v>
       </c>
       <c r="G12" s="1"/>
     </row>
@@ -20568,23 +20578,23 @@
       </c>
       <c r="B16" s="22" t="n">
         <f aca="false">'Holdco Summary'!B38</f>
-        <v>2.05608335266037</v>
+        <v>2.06649447492898</v>
       </c>
       <c r="C16" s="22" t="n">
         <f aca="false">'Holdco Summary'!C38</f>
-        <v>3.32373324250012</v>
+        <v>3.3433727747867</v>
       </c>
       <c r="D16" s="22" t="n">
         <f aca="false">'Holdco Summary'!D38</f>
-        <v>0.758975724072158</v>
+        <v>0.760869645511103</v>
       </c>
       <c r="E16" s="22" t="n">
         <f aca="false">'Holdco Summary'!E38</f>
-        <v>2.61461989630139</v>
+        <v>2.64036459832027</v>
       </c>
       <c r="F16" s="18" t="n">
         <f aca="false">'Holdco Summary'!F38</f>
-        <v>2.26221016237823</v>
+        <v>2.27595084398942</v>
       </c>
       <c r="G16" s="1"/>
     </row>
@@ -20594,23 +20604,23 @@
       </c>
       <c r="B17" s="22" t="n">
         <f aca="false">'Holdco Summary'!B59</f>
-        <v>2.80913247902411</v>
+        <v>2.83013384503586</v>
       </c>
       <c r="C17" s="22" t="n">
         <f aca="false">'Holdco Summary'!C59</f>
-        <v>5.63660406983273</v>
+        <v>5.68505942879856</v>
       </c>
       <c r="D17" s="22" t="n">
         <f aca="false">'Holdco Summary'!D59</f>
-        <v>0.694336186963116</v>
+        <v>0.696250975084011</v>
       </c>
       <c r="E17" s="22" t="n">
         <f aca="false">'Holdco Summary'!E59</f>
-        <v>4.30330289558338</v>
+        <v>4.35833834962331</v>
       </c>
       <c r="F17" s="18" t="n">
         <f aca="false">'Holdco Summary'!F59</f>
-        <v>3.42290649540101</v>
+        <v>3.45301348617188</v>
       </c>
       <c r="G17" s="1"/>
     </row>
@@ -20620,23 +20630,23 @@
       </c>
       <c r="B18" s="22" t="n">
         <f aca="false">'Holdco Summary'!B80</f>
-        <v>4.59147465749586</v>
+        <v>4.64310591330418</v>
       </c>
       <c r="C18" s="22" t="n">
         <f aca="false">'Holdco Summary'!C80</f>
-        <v>12.8890487954669</v>
+        <v>13.0506214172789</v>
       </c>
       <c r="D18" s="22" t="n">
         <f aca="false">'Holdco Summary'!D80</f>
-        <v>0.623074977486035</v>
+        <v>0.62452612073781</v>
       </c>
       <c r="E18" s="22" t="n">
         <f aca="false">'Holdco Summary'!E80</f>
-        <v>9.67166729025792</v>
+        <v>9.82725200925749</v>
       </c>
       <c r="F18" s="18" t="n">
         <f aca="false">'Holdco Summary'!F80</f>
-        <v>6.83263713490145</v>
+        <v>6.9198197348059</v>
       </c>
       <c r="G18" s="1"/>
     </row>
@@ -20687,23 +20697,23 @@
       </c>
       <c r="B22" s="23" t="n">
         <f aca="false">'Holdco Summary'!B37</f>
-        <v>1727.11001623471</v>
+        <v>1766.85277606428</v>
       </c>
       <c r="C22" s="23" t="n">
         <f aca="false">'Holdco Summary'!C37</f>
-        <v>2791.9359237001</v>
+        <v>2858.58372244263</v>
       </c>
       <c r="D22" s="23" t="n">
         <f aca="false">'Holdco Summary'!D37</f>
-        <v>637.539608220613</v>
+        <v>650.543546911993</v>
       </c>
       <c r="E22" s="23" t="n">
         <f aca="false">'Holdco Summary'!E37</f>
-        <v>2196.28071289317</v>
+        <v>2257.51173156383</v>
       </c>
       <c r="F22" s="19" t="n">
         <f aca="false">'Holdco Summary'!F37</f>
-        <v>1900.25653639771</v>
+        <v>1945.93797161096</v>
       </c>
       <c r="G22" s="1"/>
     </row>
@@ -20713,23 +20723,23 @@
       </c>
       <c r="B23" s="23" t="n">
         <f aca="false">'Holdco Summary'!B58</f>
-        <v>2359.67128238025</v>
+        <v>2419.76443750566</v>
       </c>
       <c r="C23" s="23" t="n">
         <f aca="false">'Holdco Summary'!C58</f>
-        <v>4734.74741865949</v>
+        <v>4860.72581162277</v>
       </c>
       <c r="D23" s="23" t="n">
         <f aca="false">'Holdco Summary'!D58</f>
-        <v>583.242397049017</v>
+        <v>595.29458369683</v>
       </c>
       <c r="E23" s="23" t="n">
         <f aca="false">'Holdco Summary'!E58</f>
-        <v>3614.77443229004</v>
+        <v>3726.37928892793</v>
       </c>
       <c r="F23" s="19" t="n">
         <f aca="false">'Holdco Summary'!F58</f>
-        <v>2875.24145613685</v>
+        <v>2952.32653067696</v>
       </c>
       <c r="G23" s="1"/>
     </row>
@@ -20739,23 +20749,23 @@
       </c>
       <c r="B24" s="23" t="n">
         <f aca="false">'Holdco Summary'!B79</f>
-        <v>3856.83871229652</v>
+        <v>3969.85555587508</v>
       </c>
       <c r="C24" s="23" t="n">
         <f aca="false">'Holdco Summary'!C79</f>
-        <v>10826.8009881922</v>
+        <v>11158.2813117735</v>
       </c>
       <c r="D24" s="23" t="n">
         <f aca="false">'Holdco Summary'!D79</f>
-        <v>523.38298108827</v>
+        <v>533.969833230827</v>
       </c>
       <c r="E24" s="23" t="n">
         <f aca="false">'Holdco Summary'!E79</f>
-        <v>8124.20052381665</v>
+        <v>8402.30046791515</v>
       </c>
       <c r="F24" s="19" t="n">
         <f aca="false">'Holdco Summary'!F79</f>
-        <v>5739.41519331722</v>
+        <v>5916.44587325905</v>
       </c>
       <c r="G24" s="1"/>
     </row>
@@ -20806,23 +20816,23 @@
       </c>
       <c r="B28" s="22" t="n">
         <f aca="false">'Holdco Summary'!B43</f>
-        <v>1.02223680877684</v>
+        <v>1.02741297655714</v>
       </c>
       <c r="C28" s="22" t="n">
         <f aca="false">'Holdco Summary'!C43</f>
-        <v>1.65248284250861</v>
+        <v>1.66224716105364</v>
       </c>
       <c r="D28" s="22" t="n">
         <f aca="false">'Holdco Summary'!D43</f>
-        <v>0.377345072664851</v>
+        <v>0.378286686342777</v>
       </c>
       <c r="E28" s="22" t="n">
         <f aca="false">'Holdco Summary'!E43</f>
-        <v>1.29992818408908</v>
+        <v>1.31272785099005</v>
       </c>
       <c r="F28" s="18" t="n">
         <f aca="false">'Holdco Summary'!F43</f>
-        <v>1.12471826308982</v>
+        <v>1.13154981031405</v>
       </c>
       <c r="G28" s="1"/>
     </row>
@@ -20832,23 +20842,23 @@
       </c>
       <c r="B29" s="22" t="n">
         <f aca="false">'Holdco Summary'!B64</f>
-        <v>1.05605694891614</v>
+        <v>1.06395214028894</v>
       </c>
       <c r="C29" s="22" t="n">
         <f aca="false">'Holdco Summary'!C64</f>
-        <v>2.11900824923137</v>
+        <v>2.1372244134494</v>
       </c>
       <c r="D29" s="22" t="n">
         <f aca="false">'Holdco Summary'!D64</f>
-        <v>0.261026690838401</v>
+        <v>0.26174653061665</v>
       </c>
       <c r="E29" s="22" t="n">
         <f aca="false">'Holdco Summary'!E64</f>
-        <v>1.61777095245809</v>
+        <v>1.63846081814068</v>
       </c>
       <c r="F29" s="18" t="n">
         <f aca="false">'Holdco Summary'!F64</f>
-        <v>1.28679733581458</v>
+        <v>1.29811566880597</v>
       </c>
       <c r="G29" s="1"/>
     </row>
@@ -20858,23 +20868,23 @@
       </c>
       <c r="B30" s="22" t="n">
         <f aca="false">'Holdco Summary'!B85</f>
-        <v>1.13494231387911</v>
+        <v>1.14770477067279</v>
       </c>
       <c r="C30" s="22" t="n">
         <f aca="false">'Holdco Summary'!C85</f>
-        <v>3.18597573869788</v>
+        <v>3.22591401973781</v>
       </c>
       <c r="D30" s="22" t="n">
         <f aca="false">'Holdco Summary'!D85</f>
-        <v>0.154014605201774</v>
+        <v>0.154373305620004</v>
       </c>
       <c r="E30" s="22" t="n">
         <f aca="false">'Holdco Summary'!E85</f>
-        <v>2.39068823685087</v>
+        <v>2.42914639989383</v>
       </c>
       <c r="F30" s="18" t="n">
         <f aca="false">'Holdco Summary'!F85</f>
-        <v>1.68892340222796</v>
+        <v>1.71047360756428</v>
       </c>
       <c r="G30" s="1"/>
     </row>
@@ -20925,23 +20935,23 @@
       </c>
       <c r="B34" s="22" t="n">
         <f aca="false">'Holdco Summary'!B41</f>
-        <v>1.3363131037395</v>
+        <v>1.34307961886846</v>
       </c>
       <c r="C34" s="22" t="n">
         <f aca="false">'Holdco Summary'!C41</f>
-        <v>2.160198553984</v>
+        <v>2.17296290242927</v>
       </c>
       <c r="D34" s="22" t="n">
         <f aca="false">'Holdco Summary'!D41</f>
-        <v>0.493282144513008</v>
+        <v>0.494513063499362</v>
       </c>
       <c r="E34" s="22" t="n">
         <f aca="false">'Holdco Summary'!E41</f>
-        <v>1.6993235338464</v>
+        <v>1.71605582371937</v>
       </c>
       <c r="F34" s="18" t="n">
         <f aca="false">'Holdco Summary'!F41</f>
-        <v>1.47028138693269</v>
+        <v>1.47921188718093</v>
       </c>
       <c r="G34" s="1"/>
     </row>
@@ -20951,23 +20961,23 @@
       </c>
       <c r="B35" s="22" t="n">
         <f aca="false">'Holdco Summary'!B62</f>
-        <v>1.53669166432779</v>
+        <v>1.54818013072471</v>
       </c>
       <c r="C35" s="22" t="n">
         <f aca="false">'Holdco Summary'!C62</f>
-        <v>3.08341545082172</v>
+        <v>3.1099221915222</v>
       </c>
       <c r="D35" s="22" t="n">
         <f aca="false">'Holdco Summary'!D62</f>
-        <v>0.379825671702756</v>
+        <v>0.380873126376505</v>
       </c>
       <c r="E35" s="22" t="n">
         <f aca="false">'Holdco Summary'!E62</f>
-        <v>2.35405404981752</v>
+        <v>2.38416032785786</v>
       </c>
       <c r="F35" s="18" t="n">
         <f aca="false">'Holdco Summary'!F62</f>
-        <v>1.87244706988098</v>
+        <v>1.88891662484182</v>
       </c>
       <c r="G35" s="1"/>
     </row>
@@ -20977,23 +20987,23 @@
       </c>
       <c r="B36" s="22" t="n">
         <f aca="false">'Holdco Summary'!B83</f>
-        <v>1.93948851491393</v>
+        <v>1.96129811534096</v>
       </c>
       <c r="C36" s="22" t="n">
         <f aca="false">'Holdco Summary'!C83</f>
-        <v>5.44447350181108</v>
+        <v>5.51272352336294</v>
       </c>
       <c r="D36" s="22" t="n">
         <f aca="false">'Holdco Summary'!D83</f>
-        <v>0.263193603996389</v>
+        <v>0.263806582588293</v>
       </c>
       <c r="E36" s="22" t="n">
         <f aca="false">'Holdco Summary'!E83</f>
-        <v>4.08541678410449</v>
+        <v>4.15113745079773</v>
       </c>
       <c r="F36" s="18" t="n">
         <f aca="false">'Holdco Summary'!F83</f>
-        <v>2.88617976537917</v>
+        <v>2.92300663775207</v>
       </c>
       <c r="G36" s="1"/>
     </row>
@@ -21045,7 +21055,7 @@
       </c>
       <c r="C40" s="21" t="n">
         <f aca="false">'Holdco Summary'!C6</f>
-        <v>0.297619047619048</v>
+        <v>0.292397660818713</v>
       </c>
       <c r="D40" s="26" t="n">
         <f aca="false">COUNT(Assumptions!C18:C26)</f>
@@ -21062,11 +21072,11 @@
       </c>
       <c r="B41" s="25" t="n">
         <f aca="false">'Holdco Summary'!B7</f>
-        <v>390</v>
+        <v>405</v>
       </c>
       <c r="C41" s="21" t="n">
         <f aca="false">'Holdco Summary'!C7</f>
-        <v>0.464285714285714</v>
+        <v>0.473684210526316</v>
       </c>
       <c r="D41" s="26" t="n">
         <f aca="false">COUNT('Weapons Sleeve'!C12:C22)</f>
@@ -21087,7 +21097,7 @@
       </c>
       <c r="C42" s="21" t="n">
         <f aca="false">'Holdco Summary'!C8</f>
-        <v>0.238095238095238</v>
+        <v>0.233918128654971</v>
       </c>
       <c r="D42" s="26" t="n">
         <f aca="false">COUNT('Consumer Sleeve'!C12:C20)</f>
@@ -21103,7 +21113,7 @@
       </c>
       <c r="B43" s="28" t="n">
         <f aca="false">SUM(B40:B42)</f>
-        <v>840</v>
+        <v>855</v>
       </c>
       <c r="C43" s="29" t="n">
         <f aca="false">SUM(C40:C42)</f>
@@ -21190,23 +21200,23 @@
       </c>
       <c r="B48" s="31" t="n">
         <f aca="false">'Holdco Summary'!B29/'Holdco Summary'!$B$7</f>
-        <v>2.34791206742085</v>
+        <v>2.37463994022986</v>
       </c>
       <c r="C48" s="31" t="n">
         <f aca="false">'Holdco Summary'!C29/'Holdco Summary'!$B$7</f>
-        <v>3.89233680586787</v>
+        <v>3.94490400599662</v>
       </c>
       <c r="D48" s="31" t="n">
         <f aca="false">'Holdco Summary'!D29/'Holdco Summary'!$B$7</f>
-        <v>1.11273632367401</v>
+        <v>1.10733606154135</v>
       </c>
       <c r="E48" s="31" t="n">
         <f aca="false">'Holdco Summary'!E29/'Holdco Summary'!$B$7</f>
-        <v>3.92700209637202</v>
+        <v>3.96156693984054</v>
       </c>
       <c r="F48" s="31" t="n">
         <f aca="false">'Holdco Summary'!F29/'Holdco Summary'!$B$7</f>
-        <v>2.78560539481325</v>
+        <v>2.81514942480987</v>
       </c>
       <c r="G48" s="1"/>
     </row>
@@ -21242,23 +21252,23 @@
       </c>
       <c r="B50" s="32" t="n">
         <f aca="false">'Holdco Summary'!B31/'Holdco Summary'!$B$9</f>
-        <v>2.32777217162546</v>
+        <v>2.34078607446123</v>
       </c>
       <c r="C50" s="32" t="n">
         <f aca="false">'Holdco Summary'!C31/'Holdco Summary'!$B$9</f>
-        <v>3.91233453392515</v>
+        <v>3.93688394928338</v>
       </c>
       <c r="D50" s="32" t="n">
         <f aca="false">'Holdco Summary'!D31/'Holdco Summary'!$B$9</f>
-        <v>0.858975724072158</v>
+        <v>0.860869645511103</v>
       </c>
       <c r="E50" s="32" t="n">
         <f aca="false">'Holdco Summary'!E31/'Holdco Summary'!$B$9</f>
-        <v>3.02594285117673</v>
+        <v>3.05812372870034</v>
       </c>
       <c r="F50" s="32" t="n">
         <f aca="false">'Holdco Summary'!F31/'Holdco Summary'!$B$9</f>
-        <v>2.60831889700008</v>
+        <v>2.62542372696011</v>
       </c>
       <c r="G50" s="1"/>
     </row>
@@ -21335,23 +21345,23 @@
       </c>
       <c r="B55" s="31" t="n">
         <f aca="false">'Holdco Summary'!B50/'Holdco Summary'!$B$7</f>
-        <v>3.32446400378914</v>
+        <v>3.3774211466089</v>
       </c>
       <c r="C55" s="31" t="n">
         <f aca="false">'Holdco Summary'!C50/'Holdco Summary'!$B$7</f>
-        <v>6.83074887777274</v>
+        <v>6.95719311735195</v>
       </c>
       <c r="D55" s="31" t="n">
         <f aca="false">'Holdco Summary'!D50/'Holdco Summary'!$B$7</f>
-        <v>1.15787554486341</v>
+        <v>1.14993493615936</v>
       </c>
       <c r="E55" s="31" t="n">
         <f aca="false">'Holdco Summary'!E50/'Holdco Summary'!$B$7</f>
-        <v>6.90496072028128</v>
+        <v>6.98429360666453</v>
       </c>
       <c r="F55" s="31" t="n">
         <f aca="false">'Holdco Summary'!F50/'Holdco Summary'!$B$7</f>
-        <v>4.41312146092</v>
+        <v>4.47927207673558</v>
       </c>
       <c r="G55" s="1"/>
     </row>
@@ -21387,23 +21397,23 @@
       </c>
       <c r="B57" s="32" t="n">
         <f aca="false">'Holdco Summary'!B52/'Holdco Summary'!$B$9</f>
-        <v>3.25795953158525</v>
+        <v>3.28421123909995</v>
       </c>
       <c r="C57" s="32" t="n">
         <f aca="false">'Holdco Summary'!C52/'Holdco Summary'!$B$9</f>
-        <v>6.79229902009603</v>
+        <v>6.85286821880332</v>
       </c>
       <c r="D57" s="32" t="n">
         <f aca="false">'Holdco Summary'!D52/'Holdco Summary'!$B$9</f>
-        <v>0.834336186963116</v>
+        <v>0.836250975084011</v>
       </c>
       <c r="E57" s="32" t="n">
         <f aca="false">'Holdco Summary'!E52/'Holdco Summary'!$B$9</f>
-        <v>5.12567255228435</v>
+        <v>5.19446686983425</v>
       </c>
       <c r="F57" s="32" t="n">
         <f aca="false">'Holdco Summary'!F52/'Holdco Summary'!$B$9</f>
-        <v>4.05815785512449</v>
+        <v>4.09571978903355</v>
       </c>
       <c r="G57" s="1"/>
     </row>
@@ -21480,23 +21490,23 @@
       </c>
       <c r="B62" s="31" t="n">
         <f aca="false">'Holdco Summary'!B71/'Holdco Summary'!$B$7</f>
-        <v>5.68435978733779</v>
+        <v>5.81191457480287</v>
       </c>
       <c r="C62" s="31" t="n">
         <f aca="false">'Holdco Summary'!C71/'Holdco Summary'!$B$7</f>
-        <v>16.3149383848512</v>
+        <v>16.7230380390834</v>
       </c>
       <c r="D62" s="31" t="n">
         <f aca="false">'Holdco Summary'!D71/'Holdco Summary'!$B$7</f>
-        <v>1.2332898185244</v>
+        <v>1.22116020090635</v>
       </c>
       <c r="E62" s="31" t="n">
         <f aca="false">'Holdco Summary'!E71/'Holdco Summary'!$B$7</f>
-        <v>16.534742164625</v>
+        <v>16.7699466804619</v>
       </c>
       <c r="F62" s="31" t="n">
         <f aca="false">'Holdco Summary'!F71/'Holdco Summary'!$B$7</f>
-        <v>9.30190129798722</v>
+        <v>9.49478710063738</v>
       </c>
       <c r="G62" s="1"/>
     </row>
@@ -21532,23 +21542,23 @@
       </c>
       <c r="B64" s="32" t="n">
         <f aca="false">'Holdco Summary'!B73/'Holdco Summary'!$B$9</f>
-        <v>5.44961207255162</v>
+        <v>5.51415114231203</v>
       </c>
       <c r="C64" s="32" t="n">
         <f aca="false">'Holdco Summary'!C73/'Holdco Summary'!$B$9</f>
-        <v>15.8215797450154</v>
+        <v>16.0235455222804</v>
       </c>
       <c r="D64" s="32" t="n">
         <f aca="false">'Holdco Summary'!D73/'Holdco Summary'!$B$9</f>
-        <v>0.823074977486035</v>
+        <v>0.82452612073781</v>
       </c>
       <c r="E64" s="32" t="n">
         <f aca="false">'Holdco Summary'!E73/'Holdco Summary'!$B$9</f>
-        <v>11.7998528635042</v>
+        <v>11.9943337622537</v>
       </c>
       <c r="F64" s="32" t="n">
         <f aca="false">'Holdco Summary'!F73/'Holdco Summary'!$B$9</f>
-        <v>8.30115954505063</v>
+        <v>8.41008337705924</v>
       </c>
       <c r="G64" s="1"/>
     </row>
@@ -21660,10 +21670,10 @@
       </c>
       <c r="B72" s="34" t="n">
         <f aca="false">'Holdco Summary'!B9</f>
-        <v>840</v>
+        <v>855</v>
       </c>
       <c r="C72" s="35" t="n">
-        <v>840</v>
+        <v>855</v>
       </c>
       <c r="D72" s="36" t="str">
         <f aca="false">IF(ABS(B72-C72)&lt;0.001,"OK","CHECK")</f>
@@ -21699,11 +21709,11 @@
       </c>
       <c r="B74" s="34" t="n">
         <f aca="false">'Weapons Sleeve'!C23</f>
-        <v>390</v>
+        <v>405</v>
       </c>
       <c r="C74" s="34" t="n">
         <f aca="false">'Weapons Sleeve'!B5</f>
-        <v>390</v>
+        <v>405</v>
       </c>
       <c r="D74" s="36" t="str">
         <f aca="false">IF(ABS(B74-C74)&lt;0.001,"OK","CHECK")</f>
@@ -21796,11 +21806,11 @@
       </c>
       <c r="B79" s="34" t="n">
         <f aca="false">'Holdco Summary'!F52</f>
-        <v>3408.85259830457</v>
+        <v>3501.84041962368</v>
       </c>
       <c r="C79" s="34" t="n">
         <f aca="false">'Fund Economics'!F22+'Holdco Summary'!F50+'Holdco Summary'!F51</f>
-        <v>3408.85259830457</v>
+        <v>3501.84041962368</v>
       </c>
       <c r="D79" s="36" t="str">
         <f aca="false">IF(ABS(B79-C79)&lt;0.001,"OK","CHECK")</f>
@@ -21847,7 +21857,7 @@
     <row r="83" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A83" s="40" t="str">
         <f aca="false">"• Underwrite to Expected: 7-yr holdco net IRR "&amp;TEXT('Holdco Summary'!F61,"0.0%")&amp;" / "&amp;TEXT('Holdco Summary'!F59,"0.00")&amp;"x net MOIC; Base "&amp;TEXT('Holdco Summary'!B61,"0.0%")&amp;", Bear "&amp;TEXT('Holdco Summary'!D61,"0.0%")&amp;"."</f>
-        <v>• Underwrite to Expected: 7-yr holdco net IRR 19.2% / 3.42x net MOIC; Base 15.9%, Bear -5.1%.</v>
+        <v>• Underwrite to Expected: 7-yr holdco net IRR 19.4% / 3.45x net MOIC; Base 16.0%, Bear -5.0%.</v>
       </c>
       <c r="B83" s="40"/>
       <c r="C83" s="40"/>
@@ -21859,7 +21869,7 @@
     <row r="84" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A84" s="40" t="str">
         <f aca="false">"• Thematic scoreboard: 7-yr Expected KS-PME vs Defense+Semis basket "&amp;TEXT('Holdco Summary'!F64,"0.00")&amp;"x (Base "&amp;TEXT('Holdco Summary'!B64,"0.00")&amp;"x) — &gt;1.00x means the holdco beats owning ITA/SOXX."</f>
-        <v>• Thematic scoreboard: 7-yr Expected KS-PME vs Defense+Semis basket 1.29x (Base 1.06x) — &gt;1.00x means the holdco beats owning ITA/SOXX.</v>
+        <v>• Thematic scoreboard: 7-yr Expected KS-PME vs Defense+Semis basket 1.30x (Base 1.06x) — &gt;1.00x means the holdco beats owning ITA/SOXX.</v>
       </c>
       <c r="B84" s="40"/>
       <c r="C84" s="40"/>
@@ -22005,7 +22015,7 @@
       </c>
       <c r="C6" s="46" t="n">
         <f aca="false">B6/$B$9</f>
-        <v>0.297619047619048</v>
+        <v>0.292397660818713</v>
       </c>
       <c r="D6" s="47" t="s">
         <v>89</v>
@@ -22022,11 +22032,11 @@
         <v>92</v>
       </c>
       <c r="B7" s="49" t="n">
-        <v>390</v>
+        <v>405</v>
       </c>
       <c r="C7" s="46" t="n">
         <f aca="false">B7/$B$9</f>
-        <v>0.464285714285714</v>
+        <v>0.473684210526316</v>
       </c>
       <c r="D7" s="47" t="s">
         <v>93</v>
@@ -22047,7 +22057,7 @@
       </c>
       <c r="C8" s="46" t="n">
         <f aca="false">B8/$B$9</f>
-        <v>0.238095238095238</v>
+        <v>0.233918128654971</v>
       </c>
       <c r="D8" s="47" t="s">
         <v>96</v>
@@ -22065,7 +22075,7 @@
       </c>
       <c r="B9" s="50" t="n">
         <f aca="false">SUM(B6:B8)</f>
-        <v>840</v>
+        <v>855</v>
       </c>
       <c r="C9" s="51" t="n">
         <f aca="false">SUM(C6:C8)</f>
@@ -22322,23 +22332,23 @@
       </c>
       <c r="B29" s="62" t="n">
         <f aca="false">'Weapons Sleeve'!C38</f>
-        <v>915.68570629413</v>
+        <v>961.729175793093</v>
       </c>
       <c r="C29" s="62" t="n">
         <f aca="false">'Weapons Sleeve'!F38</f>
-        <v>1518.01135428847</v>
+        <v>1597.68612242863</v>
       </c>
       <c r="D29" s="62" t="n">
         <f aca="false">'Weapons Sleeve'!I38</f>
-        <v>433.967166232866</v>
+        <v>448.471104924246</v>
       </c>
       <c r="E29" s="63" t="n">
         <f aca="false">'Weapons Sleeve'!L38</f>
-        <v>1531.53081758509</v>
+        <v>1604.43461063542</v>
       </c>
       <c r="F29" s="64" t="n">
         <f aca="false">B29*'Defense Supercycle'!$B$17+C29*'Defense Supercycle'!$B$18+D29*'Defense Supercycle'!$B$19+E29*'Defense Supercycle'!$B$20</f>
-        <v>1086.38610397717</v>
+        <v>1140.135517048</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -22372,23 +22382,23 @@
       </c>
       <c r="B31" s="66" t="n">
         <f aca="false">B28+B29+B30</f>
-        <v>1955.32862416539</v>
+        <v>2001.37209366435</v>
       </c>
       <c r="C31" s="66" t="n">
         <f aca="false">C28+C29+C30</f>
-        <v>3286.36100849713</v>
+        <v>3366.03577663729</v>
       </c>
       <c r="D31" s="66" t="n">
         <f aca="false">D28+D29+D30</f>
-        <v>721.539608220613</v>
+        <v>736.043546911993</v>
       </c>
       <c r="E31" s="66" t="n">
         <f aca="false">E28+E29+E30</f>
-        <v>2541.79199498846</v>
+        <v>2614.69578803879</v>
       </c>
       <c r="F31" s="66" t="n">
         <f aca="false">F28+F29+F30</f>
-        <v>2190.98787348007</v>
+        <v>2244.7372865509</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -22397,23 +22407,23 @@
       </c>
       <c r="B32" s="62" t="n">
         <f aca="false">-'Holdco Summary'!$B$9</f>
-        <v>-840</v>
+        <v>-855</v>
       </c>
       <c r="C32" s="62" t="n">
         <f aca="false">-'Holdco Summary'!$B$9</f>
-        <v>-840</v>
+        <v>-855</v>
       </c>
       <c r="D32" s="62" t="n">
         <f aca="false">-'Holdco Summary'!$B$9</f>
-        <v>-840</v>
+        <v>-855</v>
       </c>
       <c r="E32" s="63" t="n">
         <f aca="false">-'Holdco Summary'!$B$9</f>
-        <v>-840</v>
+        <v>-855</v>
       </c>
       <c r="F32" s="64" t="n">
         <f aca="false">-'Holdco Summary'!$B$9</f>
-        <v>-840</v>
+        <v>-855</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -22422,23 +22432,23 @@
       </c>
       <c r="B33" s="62" t="n">
         <f aca="false">-'Holdco Summary'!$B$9*((1+Assumptions!$B$10)^5-1)</f>
-        <v>-394.235584512</v>
+        <v>-401.275505664001</v>
       </c>
       <c r="C33" s="62" t="n">
         <f aca="false">-'Holdco Summary'!$B$9*((1+Assumptions!$B$10)^5-1)</f>
-        <v>-394.235584512</v>
+        <v>-401.275505664001</v>
       </c>
       <c r="D33" s="62" t="n">
         <f aca="false">-'Holdco Summary'!$B$9*((1+Assumptions!$B$10)^5-1)</f>
-        <v>-394.235584512</v>
+        <v>-401.275505664001</v>
       </c>
       <c r="E33" s="63" t="n">
         <f aca="false">-'Holdco Summary'!$B$9*((1+Assumptions!$B$10)^5-1)</f>
-        <v>-394.235584512</v>
+        <v>-401.275505664001</v>
       </c>
       <c r="F33" s="64" t="n">
         <f aca="false">-'Holdco Summary'!$B$9*((1+Assumptions!$B$10)^5-1)</f>
-        <v>-394.235584512</v>
+        <v>-401.275505664001</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -22447,11 +22457,11 @@
       </c>
       <c r="B34" s="62" t="n">
         <f aca="false">MAX(0,B31+B32+B33)</f>
-        <v>721.093039653385</v>
+        <v>745.096588000347</v>
       </c>
       <c r="C34" s="62" t="n">
         <f aca="false">MAX(0,C31+C32+C33)</f>
-        <v>2052.12542398512</v>
+        <v>2109.76027097329</v>
       </c>
       <c r="D34" s="62" t="n">
         <f aca="false">MAX(0,D31+D32+D33)</f>
@@ -22459,11 +22469,11 @@
       </c>
       <c r="E34" s="63" t="n">
         <f aca="false">MAX(0,E31+E32+E33)</f>
-        <v>1307.55641047646</v>
+        <v>1358.42028237479</v>
       </c>
       <c r="F34" s="64" t="n">
         <f aca="false">B34*'Defense Supercycle'!$B$17+C34*'Defense Supercycle'!$B$18+D34*'Defense Supercycle'!$B$19+E34*'Defense Supercycle'!$B$20</f>
-        <v>1033.65668541177</v>
+        <v>1066.4965746997</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -22472,11 +22482,11 @@
       </c>
       <c r="B35" s="62" t="n">
         <f aca="false">-Assumptions!$B$9*B34</f>
-        <v>-144.218607930677</v>
+        <v>-149.019317600069</v>
       </c>
       <c r="C35" s="62" t="n">
         <f aca="false">-Assumptions!$B$9*C34</f>
-        <v>-410.425084797025</v>
+        <v>-421.952054194657</v>
       </c>
       <c r="D35" s="62" t="n">
         <f aca="false">-Assumptions!$B$9*D34</f>
@@ -22484,11 +22494,11 @@
       </c>
       <c r="E35" s="63" t="n">
         <f aca="false">-Assumptions!$B$9*E34</f>
-        <v>-261.511282095291</v>
+        <v>-271.684056474957</v>
       </c>
       <c r="F35" s="64" t="n">
         <f aca="false">B35*'Defense Supercycle'!$B$17+C35*'Defense Supercycle'!$B$18+D35*'Defense Supercycle'!$B$19+E35*'Defense Supercycle'!$B$20</f>
-        <v>-206.731337082355</v>
+        <v>-213.299314939939</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -22497,23 +22507,23 @@
       </c>
       <c r="B36" s="62" t="n">
         <f aca="false">-'Holdco Summary'!$B$9*Assumptions!$B$8*5</f>
-        <v>-84</v>
+        <v>-85.5</v>
       </c>
       <c r="C36" s="62" t="n">
         <f aca="false">-'Holdco Summary'!$B$9*Assumptions!$B$8*5</f>
-        <v>-84</v>
+        <v>-85.5</v>
       </c>
       <c r="D36" s="62" t="n">
         <f aca="false">-'Holdco Summary'!$B$9*Assumptions!$B$8*5</f>
-        <v>-84</v>
+        <v>-85.5</v>
       </c>
       <c r="E36" s="63" t="n">
         <f aca="false">-'Holdco Summary'!$B$9*Assumptions!$B$8*5</f>
-        <v>-84</v>
+        <v>-85.5</v>
       </c>
       <c r="F36" s="64" t="n">
         <f aca="false">-'Holdco Summary'!$B$9*Assumptions!$B$8*5</f>
-        <v>-84</v>
+        <v>-85.5</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -22522,23 +22532,23 @@
       </c>
       <c r="B37" s="66" t="n">
         <f aca="false">B31+B35+B36</f>
-        <v>1727.11001623471</v>
+        <v>1766.85277606428</v>
       </c>
       <c r="C37" s="66" t="n">
         <f aca="false">C31+C35+C36</f>
-        <v>2791.9359237001</v>
+        <v>2858.58372244263</v>
       </c>
       <c r="D37" s="66" t="n">
         <f aca="false">D31+D35+D36</f>
-        <v>637.539608220613</v>
+        <v>650.543546911993</v>
       </c>
       <c r="E37" s="66" t="n">
         <f aca="false">E31+E35+E36</f>
-        <v>2196.28071289317</v>
+        <v>2257.51173156383</v>
       </c>
       <c r="F37" s="66" t="n">
         <f aca="false">F31+F35+F36</f>
-        <v>1900.25653639771</v>
+        <v>1945.93797161096</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -22547,23 +22557,23 @@
       </c>
       <c r="B38" s="67" t="n">
         <f aca="false">B37/'Holdco Summary'!$B$9</f>
-        <v>2.05608335266037</v>
+        <v>2.06649447492898</v>
       </c>
       <c r="C38" s="67" t="n">
         <f aca="false">C37/'Holdco Summary'!$B$9</f>
-        <v>3.32373324250012</v>
+        <v>3.3433727747867</v>
       </c>
       <c r="D38" s="67" t="n">
         <f aca="false">D37/'Holdco Summary'!$B$9</f>
-        <v>0.758975724072158</v>
+        <v>0.760869645511103</v>
       </c>
       <c r="E38" s="67" t="n">
         <f aca="false">E37/'Holdco Summary'!$B$9</f>
-        <v>2.61461989630139</v>
+        <v>2.64036459832027</v>
       </c>
       <c r="F38" s="67" t="n">
         <f aca="false">F37/'Holdco Summary'!$B$9</f>
-        <v>2.26221016237823</v>
+        <v>2.27595084398942</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -22572,23 +22582,23 @@
       </c>
       <c r="B39" s="68" t="n">
         <f aca="false">B37/'Holdco Summary'!$B$9</f>
-        <v>2.05608335266037</v>
+        <v>2.06649447492898</v>
       </c>
       <c r="C39" s="68" t="n">
         <f aca="false">C37/'Holdco Summary'!$B$9</f>
-        <v>3.32373324250012</v>
+        <v>3.3433727747867</v>
       </c>
       <c r="D39" s="68" t="n">
         <f aca="false">D37/'Holdco Summary'!$B$9</f>
-        <v>0.758975724072158</v>
+        <v>0.760869645511103</v>
       </c>
       <c r="E39" s="69" t="n">
         <f aca="false">E37/'Holdco Summary'!$B$9</f>
-        <v>2.61461989630139</v>
+        <v>2.64036459832027</v>
       </c>
       <c r="F39" s="70" t="n">
         <f aca="false">F37/'Holdco Summary'!$B$9</f>
-        <v>2.26221016237823</v>
+        <v>2.27595084398942</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -22597,23 +22607,23 @@
       </c>
       <c r="B40" s="51" t="n">
         <f aca="false">(B37/'Holdco Summary'!$B$9)^(1/5)-1</f>
-        <v>0.155069571921647</v>
+        <v>0.156236964998106</v>
       </c>
       <c r="C40" s="51" t="n">
         <f aca="false">(C37/'Holdco Summary'!$B$9)^(1/5)-1</f>
-        <v>0.271525962366753</v>
+        <v>0.273025081505314</v>
       </c>
       <c r="D40" s="51" t="n">
         <f aca="false">(D37/'Holdco Summary'!$B$9)^(1/5)-1</f>
-        <v>-0.053663530570773</v>
+        <v>-0.053191710305405</v>
       </c>
       <c r="E40" s="51" t="n">
         <f aca="false">(E37/'Holdco Summary'!$B$9)^(1/5)-1</f>
-        <v>0.211941654166605</v>
+        <v>0.214318971802798</v>
       </c>
       <c r="F40" s="51" t="n">
         <f aca="false">(F37/'Holdco Summary'!$B$9)^(1/5)-1</f>
-        <v>0.177352715458623</v>
+        <v>0.178779502986822</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -22622,23 +22632,23 @@
       </c>
       <c r="B41" s="68" t="n">
         <f aca="false">B38/(1+'Holdco Summary'!$B$21)^5</f>
-        <v>1.3363131037395</v>
+        <v>1.34307961886846</v>
       </c>
       <c r="C41" s="68" t="n">
         <f aca="false">C38/(1+'Holdco Summary'!$B$21)^5</f>
-        <v>2.160198553984</v>
+        <v>2.17296290242927</v>
       </c>
       <c r="D41" s="68" t="n">
         <f aca="false">D38/(1+'Holdco Summary'!$B$21)^5</f>
-        <v>0.493282144513008</v>
+        <v>0.494513063499362</v>
       </c>
       <c r="E41" s="69" t="n">
         <f aca="false">E38/(1+'Holdco Summary'!$B$21)^5</f>
-        <v>1.6993235338464</v>
+        <v>1.71605582371937</v>
       </c>
       <c r="F41" s="70" t="n">
         <f aca="false">F38/(1+'Holdco Summary'!$B$21)^5</f>
-        <v>1.47028138693269</v>
+        <v>1.47921188718093</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -22647,23 +22657,23 @@
       </c>
       <c r="B42" s="68" t="n">
         <f aca="false">B38/(1+'Holdco Summary'!$B$22)^5</f>
-        <v>1.11595966889947</v>
+        <v>1.12161040895567</v>
       </c>
       <c r="C42" s="68" t="n">
         <f aca="false">C38/(1+'Holdco Summary'!$B$22)^5</f>
-        <v>1.8039892419786</v>
+        <v>1.81464879326553</v>
       </c>
       <c r="D42" s="68" t="n">
         <f aca="false">D38/(1+'Holdco Summary'!$B$22)^5</f>
-        <v>0.41194161542254</v>
+        <v>0.412969560101529</v>
       </c>
       <c r="E42" s="69" t="n">
         <f aca="false">E38/(1+'Holdco Summary'!$B$22)^5</f>
-        <v>1.41911092757943</v>
+        <v>1.43308412039952</v>
       </c>
       <c r="F42" s="70" t="n">
         <f aca="false">F38/(1+'Holdco Summary'!$B$22)^5</f>
-        <v>1.22783704294971</v>
+        <v>1.23529493442159</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -22672,23 +22682,23 @@
       </c>
       <c r="B43" s="67" t="n">
         <f aca="false">B38/(1+'Holdco Summary'!$B$23)^5</f>
-        <v>1.02223680877684</v>
+        <v>1.02741297655714</v>
       </c>
       <c r="C43" s="67" t="n">
         <f aca="false">C38/(1+'Holdco Summary'!$B$23)^5</f>
-        <v>1.65248284250861</v>
+        <v>1.66224716105364</v>
       </c>
       <c r="D43" s="67" t="n">
         <f aca="false">D38/(1+'Holdco Summary'!$B$23)^5</f>
-        <v>0.377345072664851</v>
+        <v>0.378286686342777</v>
       </c>
       <c r="E43" s="67" t="n">
         <f aca="false">E38/(1+'Holdco Summary'!$B$23)^5</f>
-        <v>1.29992818408908</v>
+        <v>1.31272785099005</v>
       </c>
       <c r="F43" s="67" t="n">
         <f aca="false">F38/(1+'Holdco Summary'!$B$23)^5</f>
-        <v>1.12471826308982</v>
+        <v>1.13154981031405</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -22697,23 +22707,23 @@
       </c>
       <c r="B44" s="46" t="n">
         <f aca="false">(B38/(1+'Holdco Summary'!$B$23)^5)^(1/5)-1</f>
-        <v>0.00440832341012798</v>
+        <v>0.00542344782444015</v>
       </c>
       <c r="C44" s="46" t="n">
         <f aca="false">(C38/(1+'Holdco Summary'!$B$23)^5)^(1/5)-1</f>
-        <v>0.105674749884133</v>
+        <v>0.106978331743751</v>
       </c>
       <c r="D44" s="46" t="n">
         <f aca="false">(D38/(1+'Holdco Summary'!$B$23)^5)^(1/5)-1</f>
-        <v>-0.177098722235455</v>
+        <v>-0.17668844374383</v>
       </c>
       <c r="E44" s="71" t="n">
         <f aca="false">(E38/(1+'Holdco Summary'!$B$23)^5)^(1/5)-1</f>
-        <v>0.053862307970961</v>
+        <v>0.0559295406980851</v>
       </c>
       <c r="F44" s="72" t="n">
         <f aca="false">(F38/(1+'Holdco Summary'!$B$23)^5)^(1/5)-1</f>
-        <v>0.02378496996402</v>
+        <v>0.0250256547711496</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -22793,23 +22803,23 @@
       </c>
       <c r="B50" s="62" t="n">
         <f aca="false">'Weapons Sleeve'!C54</f>
-        <v>1296.54096147776</v>
+        <v>1367.85556437661</v>
       </c>
       <c r="C50" s="62" t="n">
         <f aca="false">'Weapons Sleeve'!F54</f>
-        <v>2663.99206233137</v>
+        <v>2817.66321252754</v>
       </c>
       <c r="D50" s="62" t="n">
         <f aca="false">'Weapons Sleeve'!I54</f>
-        <v>451.571462496729</v>
+        <v>465.723649144541</v>
       </c>
       <c r="E50" s="63" t="n">
         <f aca="false">'Weapons Sleeve'!L54</f>
-        <v>2692.9346809097</v>
+        <v>2828.63891069913</v>
       </c>
       <c r="F50" s="64" t="n">
         <f aca="false">B50*'Defense Supercycle'!$B$17+C50*'Defense Supercycle'!$B$18+D50*'Defense Supercycle'!$B$19+E50*'Defense Supercycle'!$B$20</f>
-        <v>1721.1173697588</v>
+        <v>1814.10519107791</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -22843,23 +22853,23 @@
       </c>
       <c r="B52" s="66" t="n">
         <f aca="false">B49+B50+B51</f>
-        <v>2736.68600653161</v>
+        <v>2808.00060943046</v>
       </c>
       <c r="C52" s="66" t="n">
         <f aca="false">C49+C50+C51</f>
-        <v>5705.53117688067</v>
+        <v>5859.20232707684</v>
       </c>
       <c r="D52" s="66" t="n">
         <f aca="false">D49+D50+D51</f>
-        <v>700.842397049017</v>
+        <v>714.99458369683</v>
       </c>
       <c r="E52" s="66" t="n">
         <f aca="false">E49+E50+E51</f>
-        <v>4305.56494391885</v>
+        <v>4441.26917370829</v>
       </c>
       <c r="F52" s="66" t="n">
         <f aca="false">F49+F50+F51</f>
-        <v>3408.85259830457</v>
+        <v>3501.84041962368</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -22868,23 +22878,23 @@
       </c>
       <c r="B53" s="62" t="n">
         <f aca="false">-'Holdco Summary'!$B$9</f>
-        <v>-840</v>
+        <v>-855</v>
       </c>
       <c r="C53" s="62" t="n">
         <f aca="false">-'Holdco Summary'!$B$9</f>
-        <v>-840</v>
+        <v>-855</v>
       </c>
       <c r="D53" s="62" t="n">
         <f aca="false">-'Holdco Summary'!$B$9</f>
-        <v>-840</v>
+        <v>-855</v>
       </c>
       <c r="E53" s="63" t="n">
         <f aca="false">-'Holdco Summary'!$B$9</f>
-        <v>-840</v>
+        <v>-855</v>
       </c>
       <c r="F53" s="64" t="n">
         <f aca="false">-'Holdco Summary'!$B$9</f>
-        <v>-840</v>
+        <v>-855</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -22893,23 +22903,23 @@
       </c>
       <c r="B54" s="62" t="n">
         <f aca="false">-'Holdco Summary'!$B$9*((1+Assumptions!$B$10)^7-1)</f>
-        <v>-599.612385774798</v>
+        <v>-610.31974980649</v>
       </c>
       <c r="C54" s="62" t="n">
         <f aca="false">-'Holdco Summary'!$B$9*((1+Assumptions!$B$10)^7-1)</f>
-        <v>-599.612385774798</v>
+        <v>-610.31974980649</v>
       </c>
       <c r="D54" s="62" t="n">
         <f aca="false">-'Holdco Summary'!$B$9*((1+Assumptions!$B$10)^7-1)</f>
-        <v>-599.612385774798</v>
+        <v>-610.31974980649</v>
       </c>
       <c r="E54" s="63" t="n">
         <f aca="false">-'Holdco Summary'!$B$9*((1+Assumptions!$B$10)^7-1)</f>
-        <v>-599.612385774798</v>
+        <v>-610.31974980649</v>
       </c>
       <c r="F54" s="64" t="n">
         <f aca="false">-'Holdco Summary'!$B$9*((1+Assumptions!$B$10)^7-1)</f>
-        <v>-599.612385774798</v>
+        <v>-610.31974980649</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -22918,11 +22928,11 @@
       </c>
       <c r="B55" s="62" t="n">
         <f aca="false">MAX(0,B52+B53+B54)</f>
-        <v>1297.07362075682</v>
+        <v>1342.68085962396</v>
       </c>
       <c r="C55" s="62" t="n">
         <f aca="false">MAX(0,C52+C53+C54)</f>
-        <v>4265.91879110587</v>
+        <v>4393.88257727035</v>
       </c>
       <c r="D55" s="62" t="n">
         <f aca="false">MAX(0,D52+D53+D54)</f>
@@ -22930,11 +22940,11 @@
       </c>
       <c r="E55" s="63" t="n">
         <f aca="false">MAX(0,E52+E53+E54)</f>
-        <v>2865.95255814406</v>
+        <v>2975.9494239018</v>
       </c>
       <c r="F55" s="64" t="n">
         <f aca="false">B55*'Defense Supercycle'!$B$17+C55*'Defense Supercycle'!$B$18+D55*'Defense Supercycle'!$B$19+E55*'Defense Supercycle'!$B$20</f>
-        <v>2080.05571083864</v>
+        <v>2149.06944473364</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -22943,11 +22953,11 @@
       </c>
       <c r="B56" s="62" t="n">
         <f aca="false">-Assumptions!$B$9*B55</f>
-        <v>-259.414724151363</v>
+        <v>-268.536171924793</v>
       </c>
       <c r="C56" s="62" t="n">
         <f aca="false">-Assumptions!$B$9*C55</f>
-        <v>-853.183758221174</v>
+        <v>-878.776515454071</v>
       </c>
       <c r="D56" s="62" t="n">
         <f aca="false">-Assumptions!$B$9*D55</f>
@@ -22955,11 +22965,11 @@
       </c>
       <c r="E56" s="63" t="n">
         <f aca="false">-Assumptions!$B$9*E55</f>
-        <v>-573.190511628811</v>
+        <v>-595.189884780359</v>
       </c>
       <c r="F56" s="64" t="n">
         <f aca="false">B56*'Defense Supercycle'!$B$17+C56*'Defense Supercycle'!$B$18+D56*'Defense Supercycle'!$B$19+E56*'Defense Supercycle'!$B$20</f>
-        <v>-416.011142167729</v>
+        <v>-429.813888946728</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -22968,23 +22978,23 @@
       </c>
       <c r="B57" s="62" t="n">
         <f aca="false">-'Holdco Summary'!$B$9*Assumptions!$B$8*7</f>
-        <v>-117.6</v>
+        <v>-119.7</v>
       </c>
       <c r="C57" s="62" t="n">
         <f aca="false">-'Holdco Summary'!$B$9*Assumptions!$B$8*7</f>
-        <v>-117.6</v>
+        <v>-119.7</v>
       </c>
       <c r="D57" s="62" t="n">
         <f aca="false">-'Holdco Summary'!$B$9*Assumptions!$B$8*7</f>
-        <v>-117.6</v>
+        <v>-119.7</v>
       </c>
       <c r="E57" s="63" t="n">
         <f aca="false">-'Holdco Summary'!$B$9*Assumptions!$B$8*7</f>
-        <v>-117.6</v>
+        <v>-119.7</v>
       </c>
       <c r="F57" s="64" t="n">
         <f aca="false">-'Holdco Summary'!$B$9*Assumptions!$B$8*7</f>
-        <v>-117.6</v>
+        <v>-119.7</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -22993,23 +23003,23 @@
       </c>
       <c r="B58" s="66" t="n">
         <f aca="false">B52+B56+B57</f>
-        <v>2359.67128238025</v>
+        <v>2419.76443750566</v>
       </c>
       <c r="C58" s="66" t="n">
         <f aca="false">C52+C56+C57</f>
-        <v>4734.74741865949</v>
+        <v>4860.72581162277</v>
       </c>
       <c r="D58" s="66" t="n">
         <f aca="false">D52+D56+D57</f>
-        <v>583.242397049017</v>
+        <v>595.29458369683</v>
       </c>
       <c r="E58" s="66" t="n">
         <f aca="false">E52+E56+E57</f>
-        <v>3614.77443229004</v>
+        <v>3726.37928892793</v>
       </c>
       <c r="F58" s="66" t="n">
         <f aca="false">F52+F56+F57</f>
-        <v>2875.24145613685</v>
+        <v>2952.32653067696</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -23018,23 +23028,23 @@
       </c>
       <c r="B59" s="67" t="n">
         <f aca="false">B58/'Holdco Summary'!$B$9</f>
-        <v>2.80913247902411</v>
+        <v>2.83013384503586</v>
       </c>
       <c r="C59" s="67" t="n">
         <f aca="false">C58/'Holdco Summary'!$B$9</f>
-        <v>5.63660406983273</v>
+        <v>5.68505942879856</v>
       </c>
       <c r="D59" s="67" t="n">
         <f aca="false">D58/'Holdco Summary'!$B$9</f>
-        <v>0.694336186963116</v>
+        <v>0.696250975084011</v>
       </c>
       <c r="E59" s="67" t="n">
         <f aca="false">E58/'Holdco Summary'!$B$9</f>
-        <v>4.30330289558338</v>
+        <v>4.35833834962331</v>
       </c>
       <c r="F59" s="67" t="n">
         <f aca="false">F58/'Holdco Summary'!$B$9</f>
-        <v>3.42290649540101</v>
+        <v>3.45301348617188</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -23043,23 +23053,23 @@
       </c>
       <c r="B60" s="68" t="n">
         <f aca="false">B58/'Holdco Summary'!$B$9</f>
-        <v>2.80913247902411</v>
+        <v>2.83013384503586</v>
       </c>
       <c r="C60" s="68" t="n">
         <f aca="false">C58/'Holdco Summary'!$B$9</f>
-        <v>5.63660406983273</v>
+        <v>5.68505942879856</v>
       </c>
       <c r="D60" s="68" t="n">
         <f aca="false">D58/'Holdco Summary'!$B$9</f>
-        <v>0.694336186963116</v>
+        <v>0.696250975084011</v>
       </c>
       <c r="E60" s="69" t="n">
         <f aca="false">E58/'Holdco Summary'!$B$9</f>
-        <v>4.30330289558338</v>
+        <v>4.35833834962331</v>
       </c>
       <c r="F60" s="70" t="n">
         <f aca="false">F58/'Holdco Summary'!$B$9</f>
-        <v>3.42290649540101</v>
+        <v>3.45301348617188</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -23068,23 +23078,23 @@
       </c>
       <c r="B61" s="51" t="n">
         <f aca="false">(B58/'Holdco Summary'!$B$9)^(1/7)-1</f>
-        <v>0.158995489652759</v>
+        <v>0.160229366235885</v>
       </c>
       <c r="C61" s="51" t="n">
         <f aca="false">(C58/'Holdco Summary'!$B$9)^(1/7)-1</f>
-        <v>0.280230644478965</v>
+        <v>0.281797106824369</v>
       </c>
       <c r="D61" s="51" t="n">
         <f aca="false">(D58/'Holdco Summary'!$B$9)^(1/7)-1</f>
-        <v>-0.0507794883216116</v>
+        <v>-0.0504059739765521</v>
       </c>
       <c r="E61" s="51" t="n">
         <f aca="false">(E58/'Holdco Summary'!$B$9)^(1/7)-1</f>
-        <v>0.231808313482553</v>
+        <v>0.234046609741583</v>
       </c>
       <c r="F61" s="51" t="n">
         <f aca="false">(F58/'Holdco Summary'!$B$9)^(1/7)-1</f>
-        <v>0.192180867725363</v>
+        <v>0.193673267252674</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -23093,23 +23103,23 @@
       </c>
       <c r="B62" s="68" t="n">
         <f aca="false">B59/(1+'Holdco Summary'!$B$21)^7</f>
-        <v>1.53669166432779</v>
+        <v>1.54818013072471</v>
       </c>
       <c r="C62" s="68" t="n">
         <f aca="false">C59/(1+'Holdco Summary'!$B$21)^7</f>
-        <v>3.08341545082172</v>
+        <v>3.1099221915222</v>
       </c>
       <c r="D62" s="68" t="n">
         <f aca="false">D59/(1+'Holdco Summary'!$B$21)^7</f>
-        <v>0.379825671702756</v>
+        <v>0.380873126376505</v>
       </c>
       <c r="E62" s="69" t="n">
         <f aca="false">E59/(1+'Holdco Summary'!$B$21)^7</f>
-        <v>2.35405404981752</v>
+        <v>2.38416032785786</v>
       </c>
       <c r="F62" s="70" t="n">
         <f aca="false">F59/(1+'Holdco Summary'!$B$21)^7</f>
-        <v>1.87244706988098</v>
+        <v>1.88891662484182</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -23118,23 +23128,23 @@
       </c>
       <c r="B63" s="68" t="n">
         <f aca="false">B59/(1+'Holdco Summary'!$B$22)^7</f>
-        <v>1.19405165990218</v>
+        <v>1.20297851405869</v>
       </c>
       <c r="C63" s="68" t="n">
         <f aca="false">C59/(1+'Holdco Summary'!$B$22)^7</f>
-        <v>2.39589855446522</v>
+        <v>2.41649502054019</v>
       </c>
       <c r="D63" s="68" t="n">
         <f aca="false">D59/(1+'Holdco Summary'!$B$22)^7</f>
-        <v>0.295134986606784</v>
+        <v>0.295948887678089</v>
       </c>
       <c r="E63" s="69" t="n">
         <f aca="false">E59/(1+'Holdco Summary'!$B$22)^7</f>
-        <v>1.82916469903131</v>
+        <v>1.85255810455438</v>
       </c>
       <c r="F63" s="70" t="n">
         <f aca="false">F59/(1+'Holdco Summary'!$B$22)^7</f>
-        <v>1.454942838418</v>
+        <v>1.46774013529633</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -23143,23 +23153,23 @@
       </c>
       <c r="B64" s="67" t="n">
         <f aca="false">B59/(1+'Holdco Summary'!$B$23)^7</f>
-        <v>1.05605694891614</v>
+        <v>1.06395214028894</v>
       </c>
       <c r="C64" s="67" t="n">
         <f aca="false">C59/(1+'Holdco Summary'!$B$23)^7</f>
-        <v>2.11900824923137</v>
+        <v>2.1372244134494</v>
       </c>
       <c r="D64" s="67" t="n">
         <f aca="false">D59/(1+'Holdco Summary'!$B$23)^7</f>
-        <v>0.261026690838401</v>
+        <v>0.26174653061665</v>
       </c>
       <c r="E64" s="67" t="n">
         <f aca="false">E59/(1+'Holdco Summary'!$B$23)^7</f>
-        <v>1.61777095245809</v>
+        <v>1.63846081814068</v>
       </c>
       <c r="F64" s="67" t="n">
         <f aca="false">F59/(1+'Holdco Summary'!$B$23)^7</f>
-        <v>1.28679733581458</v>
+        <v>1.29811566880597</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -23168,23 +23178,23 @@
       </c>
       <c r="B65" s="46" t="n">
         <f aca="false">(B59/(1+'Holdco Summary'!$B$23)^7)^(1/7)-1</f>
-        <v>0.00782216491544263</v>
+        <v>0.00889510107468294</v>
       </c>
       <c r="C65" s="46" t="n">
         <f aca="false">(C59/(1+'Holdco Summary'!$B$23)^7)^(1/7)-1</f>
-        <v>0.113244038677361</v>
+        <v>0.114606179847278</v>
       </c>
       <c r="D65" s="46" t="n">
         <f aca="false">(D59/(1+'Holdco Summary'!$B$23)^7)^(1/7)-1</f>
-        <v>-0.174590859410097</v>
+        <v>-0.174266064327437</v>
       </c>
       <c r="E65" s="71" t="n">
         <f aca="false">(E59/(1+'Holdco Summary'!$B$23)^7)^(1/7)-1</f>
-        <v>0.0711376638978727</v>
+        <v>0.0730840084709419</v>
       </c>
       <c r="F65" s="72" t="n">
         <f aca="false">(F59/(1+'Holdco Summary'!$B$23)^7)^(1/7)-1</f>
-        <v>0.0366790154133589</v>
+        <v>0.0379767541327605</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -23264,23 +23274,23 @@
       </c>
       <c r="B71" s="62" t="n">
         <f aca="false">'Weapons Sleeve'!C70</f>
-        <v>2216.90031706174</v>
+        <v>2353.82540279516</v>
       </c>
       <c r="C71" s="62" t="n">
         <f aca="false">'Weapons Sleeve'!F70</f>
-        <v>6362.82597009198</v>
+        <v>6772.83040582878</v>
       </c>
       <c r="D71" s="62" t="n">
         <f aca="false">'Weapons Sleeve'!I70</f>
-        <v>480.983029224514</v>
+        <v>494.569881367072</v>
       </c>
       <c r="E71" s="63" t="n">
         <f aca="false">'Weapons Sleeve'!L70</f>
-        <v>6448.54944420373</v>
+        <v>6791.82840558708</v>
       </c>
       <c r="F71" s="64" t="n">
         <f aca="false">B71*'Defense Supercycle'!$B$17+C71*'Defense Supercycle'!$B$18+D71*'Defense Supercycle'!$B$19+E71*'Defense Supercycle'!$B$20</f>
-        <v>3627.74150621502</v>
+        <v>3845.38877575814</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -23314,23 +23324,23 @@
       </c>
       <c r="B73" s="66" t="n">
         <f aca="false">B70+B71+B72</f>
-        <v>4577.67414094336</v>
+        <v>4714.59922667679</v>
       </c>
       <c r="C73" s="66" t="n">
         <f aca="false">C70+C71+C72</f>
-        <v>13290.126985813</v>
+        <v>13700.1314215498</v>
       </c>
       <c r="D73" s="66" t="n">
         <f aca="false">D70+D71+D72</f>
-        <v>691.38298108827</v>
+        <v>704.969833230827</v>
       </c>
       <c r="E73" s="66" t="n">
         <f aca="false">E70+E71+E72</f>
-        <v>9911.87640534353</v>
+        <v>10255.1553667269</v>
       </c>
       <c r="F73" s="66" t="n">
         <f aca="false">F70+F71+F72</f>
-        <v>6972.97401784252</v>
+        <v>7190.62128738565</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -23339,23 +23349,23 @@
       </c>
       <c r="B74" s="62" t="n">
         <f aca="false">-'Holdco Summary'!$B$9</f>
-        <v>-840</v>
+        <v>-855</v>
       </c>
       <c r="C74" s="62" t="n">
         <f aca="false">-'Holdco Summary'!$B$9</f>
-        <v>-840</v>
+        <v>-855</v>
       </c>
       <c r="D74" s="62" t="n">
         <f aca="false">-'Holdco Summary'!$B$9</f>
-        <v>-840</v>
+        <v>-855</v>
       </c>
       <c r="E74" s="63" t="n">
         <f aca="false">-'Holdco Summary'!$B$9</f>
-        <v>-840</v>
+        <v>-855</v>
       </c>
       <c r="F74" s="64" t="n">
         <f aca="false">-'Holdco Summary'!$B$9</f>
-        <v>-840</v>
+        <v>-855</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -23364,23 +23374,23 @@
       </c>
       <c r="B75" s="62" t="n">
         <f aca="false">-'Holdco Summary'!$B$9*((1+Assumptions!$B$10)^10-1)</f>
-        <v>-973.496997709142</v>
+        <v>-990.880872668234</v>
       </c>
       <c r="C75" s="62" t="n">
         <f aca="false">-'Holdco Summary'!$B$9*((1+Assumptions!$B$10)^10-1)</f>
-        <v>-973.496997709142</v>
+        <v>-990.880872668234</v>
       </c>
       <c r="D75" s="62" t="n">
         <f aca="false">-'Holdco Summary'!$B$9*((1+Assumptions!$B$10)^10-1)</f>
-        <v>-973.496997709142</v>
+        <v>-990.880872668234</v>
       </c>
       <c r="E75" s="63" t="n">
         <f aca="false">-'Holdco Summary'!$B$9*((1+Assumptions!$B$10)^10-1)</f>
-        <v>-973.496997709142</v>
+        <v>-990.880872668234</v>
       </c>
       <c r="F75" s="64" t="n">
         <f aca="false">-'Holdco Summary'!$B$9*((1+Assumptions!$B$10)^10-1)</f>
-        <v>-973.496997709142</v>
+        <v>-990.880872668234</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -23389,11 +23399,11 @@
       </c>
       <c r="B76" s="62" t="n">
         <f aca="false">MAX(0,B73+B74+B75)</f>
-        <v>2764.17714323422</v>
+        <v>2868.71835400855</v>
       </c>
       <c r="C76" s="62" t="n">
         <f aca="false">MAX(0,C73+C74+C75)</f>
-        <v>11476.6299881038</v>
+        <v>11854.2505488815</v>
       </c>
       <c r="D76" s="62" t="n">
         <f aca="false">MAX(0,D73+D74+D75)</f>
@@ -23401,11 +23411,11 @@
       </c>
       <c r="E76" s="63" t="n">
         <f aca="false">MAX(0,E73+E74+E75)</f>
-        <v>8098.37940763439</v>
+        <v>8409.27449405865</v>
       </c>
       <c r="F76" s="64" t="n">
         <f aca="false">B76*'Defense Supercycle'!$B$17+C76*'Defense Supercycle'!$B$18+D76*'Defense Supercycle'!$B$19+E76*'Defense Supercycle'!$B$20</f>
-        <v>5327.79412262651</v>
+        <v>5515.87707063303</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -23414,11 +23424,11 @@
       </c>
       <c r="B77" s="62" t="n">
         <f aca="false">-Assumptions!$B$9*B76</f>
-        <v>-552.835428646844</v>
+        <v>-573.743670801711</v>
       </c>
       <c r="C77" s="62" t="n">
         <f aca="false">-Assumptions!$B$9*C76</f>
-        <v>-2295.32599762077</v>
+        <v>-2370.85010977631</v>
       </c>
       <c r="D77" s="62" t="n">
         <f aca="false">-Assumptions!$B$9*D76</f>
@@ -23426,11 +23436,11 @@
       </c>
       <c r="E77" s="63" t="n">
         <f aca="false">-Assumptions!$B$9*E76</f>
-        <v>-1619.67588152688</v>
+        <v>-1681.85489881173</v>
       </c>
       <c r="F77" s="64" t="n">
         <f aca="false">B77*'Defense Supercycle'!$B$17+C77*'Defense Supercycle'!$B$18+D77*'Defense Supercycle'!$B$19+E77*'Defense Supercycle'!$B$20</f>
-        <v>-1065.5588245253</v>
+        <v>-1103.17541412661</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -23439,23 +23449,23 @@
       </c>
       <c r="B78" s="62" t="n">
         <f aca="false">-'Holdco Summary'!$B$9*Assumptions!$B$8*10</f>
-        <v>-168</v>
+        <v>-171</v>
       </c>
       <c r="C78" s="62" t="n">
         <f aca="false">-'Holdco Summary'!$B$9*Assumptions!$B$8*10</f>
-        <v>-168</v>
+        <v>-171</v>
       </c>
       <c r="D78" s="62" t="n">
         <f aca="false">-'Holdco Summary'!$B$9*Assumptions!$B$8*10</f>
-        <v>-168</v>
+        <v>-171</v>
       </c>
       <c r="E78" s="63" t="n">
         <f aca="false">-'Holdco Summary'!$B$9*Assumptions!$B$8*10</f>
-        <v>-168</v>
+        <v>-171</v>
       </c>
       <c r="F78" s="64" t="n">
         <f aca="false">-'Holdco Summary'!$B$9*Assumptions!$B$8*10</f>
-        <v>-168</v>
+        <v>-171</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -23464,23 +23474,23 @@
       </c>
       <c r="B79" s="66" t="n">
         <f aca="false">B73+B77+B78</f>
-        <v>3856.83871229652</v>
+        <v>3969.85555587508</v>
       </c>
       <c r="C79" s="66" t="n">
         <f aca="false">C73+C77+C78</f>
-        <v>10826.8009881922</v>
+        <v>11158.2813117735</v>
       </c>
       <c r="D79" s="66" t="n">
         <f aca="false">D73+D77+D78</f>
-        <v>523.38298108827</v>
+        <v>533.969833230827</v>
       </c>
       <c r="E79" s="66" t="n">
         <f aca="false">E73+E77+E78</f>
-        <v>8124.20052381665</v>
+        <v>8402.30046791515</v>
       </c>
       <c r="F79" s="66" t="n">
         <f aca="false">F73+F77+F78</f>
-        <v>5739.41519331722</v>
+        <v>5916.44587325905</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -23489,23 +23499,23 @@
       </c>
       <c r="B80" s="67" t="n">
         <f aca="false">B79/'Holdco Summary'!$B$9</f>
-        <v>4.59147465749586</v>
+        <v>4.64310591330418</v>
       </c>
       <c r="C80" s="67" t="n">
         <f aca="false">C79/'Holdco Summary'!$B$9</f>
-        <v>12.8890487954669</v>
+        <v>13.0506214172789</v>
       </c>
       <c r="D80" s="67" t="n">
         <f aca="false">D79/'Holdco Summary'!$B$9</f>
-        <v>0.623074977486035</v>
+        <v>0.62452612073781</v>
       </c>
       <c r="E80" s="67" t="n">
         <f aca="false">E79/'Holdco Summary'!$B$9</f>
-        <v>9.67166729025792</v>
+        <v>9.82725200925749</v>
       </c>
       <c r="F80" s="67" t="n">
         <f aca="false">F79/'Holdco Summary'!$B$9</f>
-        <v>6.83263713490145</v>
+        <v>6.9198197348059</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -23514,23 +23524,23 @@
       </c>
       <c r="B81" s="68" t="n">
         <f aca="false">B79/'Holdco Summary'!$B$9</f>
-        <v>4.59147465749586</v>
+        <v>4.64310591330418</v>
       </c>
       <c r="C81" s="68" t="n">
         <f aca="false">C79/'Holdco Summary'!$B$9</f>
-        <v>12.8890487954669</v>
+        <v>13.0506214172789</v>
       </c>
       <c r="D81" s="68" t="n">
         <f aca="false">D79/'Holdco Summary'!$B$9</f>
-        <v>0.623074977486035</v>
+        <v>0.62452612073781</v>
       </c>
       <c r="E81" s="69" t="n">
         <f aca="false">E79/'Holdco Summary'!$B$9</f>
-        <v>9.67166729025792</v>
+        <v>9.82725200925749</v>
       </c>
       <c r="F81" s="70" t="n">
         <f aca="false">F79/'Holdco Summary'!$B$9</f>
-        <v>6.83263713490145</v>
+        <v>6.9198197348059</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -23539,23 +23549,23 @@
       </c>
       <c r="B82" s="51" t="n">
         <f aca="false">(B79/'Holdco Summary'!$B$9)^(1/10)-1</f>
-        <v>0.164649431844847</v>
+        <v>0.165952502895083</v>
       </c>
       <c r="C82" s="51" t="n">
         <f aca="false">(C79/'Holdco Summary'!$B$9)^(1/10)-1</f>
-        <v>0.291284942436493</v>
+        <v>0.292894592849268</v>
       </c>
       <c r="D82" s="51" t="n">
         <f aca="false">(D79/'Holdco Summary'!$B$9)^(1/10)-1</f>
-        <v>-0.0462072190141125</v>
+        <v>-0.045985312895805</v>
       </c>
       <c r="E82" s="51" t="n">
         <f aca="false">(E79/'Holdco Summary'!$B$9)^(1/10)-1</f>
-        <v>0.25472957508494</v>
+        <v>0.256733550220737</v>
       </c>
       <c r="F82" s="51" t="n">
         <f aca="false">(F79/'Holdco Summary'!$B$9)^(1/10)-1</f>
-        <v>0.211877816332995</v>
+        <v>0.213415331908954</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -23564,23 +23574,23 @@
       </c>
       <c r="B83" s="68" t="n">
         <f aca="false">B80/(1+'Holdco Summary'!$B$21)^10</f>
-        <v>1.93948851491393</v>
+        <v>1.96129811534096</v>
       </c>
       <c r="C83" s="68" t="n">
         <f aca="false">C80/(1+'Holdco Summary'!$B$21)^10</f>
-        <v>5.44447350181108</v>
+        <v>5.51272352336294</v>
       </c>
       <c r="D83" s="68" t="n">
         <f aca="false">D80/(1+'Holdco Summary'!$B$21)^10</f>
-        <v>0.263193603996389</v>
+        <v>0.263806582588293</v>
       </c>
       <c r="E83" s="69" t="n">
         <f aca="false">E80/(1+'Holdco Summary'!$B$21)^10</f>
-        <v>4.08541678410449</v>
+        <v>4.15113745079773</v>
       </c>
       <c r="F83" s="70" t="n">
         <f aca="false">F80/(1+'Holdco Summary'!$B$21)^10</f>
-        <v>2.88617976537917</v>
+        <v>2.92300663775207</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -23589,23 +23599,23 @@
       </c>
       <c r="B84" s="68" t="n">
         <f aca="false">B80/(1+'Holdco Summary'!$B$22)^10</f>
-        <v>1.35259493481467</v>
+        <v>1.36780490117492</v>
       </c>
       <c r="C84" s="68" t="n">
         <f aca="false">C80/(1+'Holdco Summary'!$B$22)^10</f>
-        <v>3.79696359357363</v>
+        <v>3.84456100533563</v>
       </c>
       <c r="D84" s="68" t="n">
         <f aca="false">D80/(1+'Holdco Summary'!$B$22)^10</f>
-        <v>0.183550628376334</v>
+        <v>0.183978118269769</v>
       </c>
       <c r="E84" s="69" t="n">
         <f aca="false">E80/(1+'Holdco Summary'!$B$22)^10</f>
-        <v>2.84916049066256</v>
+        <v>2.89499393602631</v>
       </c>
       <c r="F84" s="70" t="n">
         <f aca="false">F80/(1+'Holdco Summary'!$B$22)^10</f>
-        <v>2.01281528691584</v>
+        <v>2.03849826500703</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -23614,23 +23624,23 @@
       </c>
       <c r="B85" s="67" t="n">
         <f aca="false">B80/(1+'Holdco Summary'!$B$23)^10</f>
-        <v>1.13494231387911</v>
+        <v>1.14770477067279</v>
       </c>
       <c r="C85" s="67" t="n">
         <f aca="false">C80/(1+'Holdco Summary'!$B$23)^10</f>
-        <v>3.18597573869788</v>
+        <v>3.22591401973781</v>
       </c>
       <c r="D85" s="67" t="n">
         <f aca="false">D80/(1+'Holdco Summary'!$B$23)^10</f>
-        <v>0.154014605201774</v>
+        <v>0.154373305620004</v>
       </c>
       <c r="E85" s="67" t="n">
         <f aca="false">E80/(1+'Holdco Summary'!$B$23)^10</f>
-        <v>2.39068823685087</v>
+        <v>2.42914639989383</v>
       </c>
       <c r="F85" s="67" t="n">
         <f aca="false">F80/(1+'Holdco Summary'!$B$23)^10</f>
-        <v>1.68892340222796</v>
+        <v>1.71047360756428</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -23639,23 +23649,23 @@
       </c>
       <c r="B86" s="46" t="n">
         <f aca="false">(B80/(1+'Holdco Summary'!$B$23)^10)^(1/10)-1</f>
-        <v>0.0127386363868236</v>
+        <v>0.0138717416478982</v>
       </c>
       <c r="C86" s="46" t="n">
         <f aca="false">(C80/(1+'Holdco Summary'!$B$23)^10)^(1/10)-1</f>
-        <v>0.122856471683907</v>
+        <v>0.124256167695016</v>
       </c>
       <c r="D86" s="46" t="n">
         <f aca="false">(D80/(1+'Holdco Summary'!$B$23)^10)^(1/10)-1</f>
-        <v>-0.17061497305575</v>
+        <v>-0.170422011213743</v>
       </c>
       <c r="E86" s="71" t="n">
         <f aca="false">(E80/(1+'Holdco Summary'!$B$23)^10)^(1/10)-1</f>
-        <v>0.0910691957260348</v>
+        <v>0.0928117828006405</v>
       </c>
       <c r="F86" s="72" t="n">
         <f aca="false">(F80/(1+'Holdco Summary'!$B$23)^10)^(1/10)-1</f>
-        <v>0.0538067968112996</v>
+        <v>0.0551437668773511</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -23743,6 +23753,7 @@
     <oddHeader/>
     <oddFooter>&amp;LLeviathan Core PE Holdco — Internal / Confidential&amp;R&amp;A  |  Page &amp;P of &amp;N</oddFooter>
   </headerFooter>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
 

--- a/models/Leviathan_PE_HOLDCO_Model_IC_VLetalis_Faxon.xlsx
+++ b/models/Leviathan_PE_HOLDCO_Model_IC_VLetalis_Faxon.xlsx
@@ -265,7 +265,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1420" uniqueCount="748">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1445" uniqueCount="758">
   <si>
     <t xml:space="preserve">LEVIATHAN FUND — CORE PE VEHICLE</t>
   </si>
@@ -2059,7 +2059,7 @@
     <t xml:space="preserve">L3HARRIS MISSILE SOLUTIONS (MSL) — PRE-IPO STAKE BUILD ($15M, IPO Q1 2027)</t>
   </si>
   <si>
-    <t xml:space="preserve">Weapons-sleeve holding #11. Pre-IPO entry at a discount to the Q1-2027 IPO valuation. Revenue is built by program (PAC-3, THAAD, Standard Missile, Tomahawk, GMLRS/PrSM/tactical, hypersonics/strategic, space) with each line tied to a production-ramp driver. Blue = input; green = link; black = formula. USD $M. 7-yr implied equity CAGR feeds Weapons Sleeve row 22.</t>
+    <t xml:space="preserve">Weapons-sleeve holding #11. Pre-IPO entry at a discount to the Q1-2027 IPO valuation. Revenue is built by program (PAC-3, THAAD, Standard Missile, Tomahawk, GMLRS/PrSM/tactical, hypersonics/strategic, space, Golden Dome NGI/GMD/SM-3/GPI) plus a Golden Dome space-based-interceptor propulsion step, with each line tied to a production-ramp driver. Blue = input; green = link; black = formula. USD $M. 7-yr implied equity CAGR feeds Weapons Sleeve row 22.</t>
   </si>
   <si>
     <t xml:space="preserve">DEAL TERMS, IPO &amp; PRE-IPO ENTRY</t>
@@ -2173,6 +2173,12 @@
     <t xml:space="preserve">RS-25 / RL10 and other space propulsion (non-munitions).</t>
   </si>
   <si>
+    <t xml:space="preserve">8  Golden Dome midcourse / terminal interceptors (NGI, GMD, SM-3, GPI)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Golden Dome FY27 request $17.5B (only $398M base budget; rest relies on reconciliation) — SpaceNews / GovConWire. MSL supplies NGI large SRMs + DACS/ACS (Lockheed team) and DACS on essentially all MDA interceptors (L3Harris).</t>
+  </si>
+  <si>
     <t xml:space="preserve">PROGRAM REVENUE — FY26E SPLIT (ESTIMATE) &amp; PROGRAM CAGR = DRIVER + SHARE GAIN</t>
   </si>
   <si>
@@ -2182,7 +2188,7 @@
     <t xml:space="preserve">PAC-3 MSE solid rocket motors</t>
   </si>
   <si>
-    <t xml:space="preserve">Program split of the ~$4.1B FY26 segment is an ESTIMATE (L3Harris does not disclose program revenue). Bear share-loss on SM and tactical reflects new SRM entrants (Anduril, Ursa Major, X-Bow, Prometheus).</t>
+    <t xml:space="preserve">Program split of the ~$4.1B FY26 segment is an ESTIMATE (L3Harris does not disclose program revenue); Golden Dome line carved out of the prior $900M hypersonics &amp; strategic estimate. Bear share-loss on SM and tactical reflects new SRM entrants (Anduril, Ursa Major, X-Bow, Prometheus).</t>
   </si>
   <si>
     <t xml:space="preserve">THAAD boost motors</t>
@@ -2197,15 +2203,33 @@
     <t xml:space="preserve">GMLRS / PrSM / tactical motors (Javelin, Stinger)</t>
   </si>
   <si>
-    <t xml:space="preserve">Hypersonics &amp; strategic</t>
+    <t xml:space="preserve">Hypersonics &amp; strategic (ex-Golden Dome)</t>
   </si>
   <si>
     <t xml:space="preserve">Space &amp; liquid propulsion / other</t>
   </si>
   <si>
+    <t xml:space="preserve">Golden Dome interceptor propulsion &amp; DACS (NGI, GMD, SM-3, GPI)</t>
+  </si>
+  <si>
     <t xml:space="preserve">TOTAL FY26E / revenue-weighted program CAGR</t>
   </si>
   <si>
+    <t xml:space="preserve">GOLDEN DOME SPACE-BASED INTERCEPTOR (SBI) PROPULSION STEP — ADDED ON TOP OF PROGRAM CAGR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">First SBI production year for MSL (t, years from FY26)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Space Force $3.2B SBI OTAs to 12 firms (Apr-26); Golden Dome czar says SBIs not guaranteed on cost (Breaking Defense). Base = FY30 production; Bear 99 = SBI cancelled or MSL not selected.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MSL full-rate SBI propulsion / DACS revenue ($M/yr)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kill-vehicle DACS + orbital propulsion content across a constellation of thousands of SBIs; CBO: up to $542B 20-yr life-cycle cost for a global SBI layer.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Exit EBIT margin</t>
   </si>
   <si>
@@ -2221,7 +2245,10 @@
     <t xml:space="preserve">PROJECTIONS — YEAR 0 (FY26E) TO YEAR 10, BY SCENARIO ($M)</t>
   </si>
   <si>
-    <t xml:space="preserve">Revenue ($M)</t>
+    <t xml:space="preserve">Program revenue ex-SBI ($M)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Golden Dome SBI propulsion revenue ($M)</t>
   </si>
   <si>
     <t xml:space="preserve">EBIT margin</t>
@@ -2239,6 +2266,9 @@
     <t xml:space="preserve">Day-1 IPO mark-up on pre-IPO entry (at IPO valuation)</t>
   </si>
   <si>
+    <t xml:space="preserve">Year-7 Golden Dome share of revenue (NGI/GMD/SM-3/GPI line + SBI)</t>
+  </si>
+  <si>
     <t xml:space="preserve">STAKE RETURNS — $15M CHECK (from Weapons Sleeve, incl. dilution retention 0.92 / 0.88 / 0.82)</t>
   </si>
   <si>
@@ -2248,7 +2278,7 @@
     <t xml:space="preserve">• Timing: model assumes pre-IPO funding in Q4-26 alongside the rest of the sleeve, so 5 / 7 / 10-yr holds align. If the IPO slips to the company-guided mid-2027, entry terms (not the hold clock) are the exposure.</t>
   </si>
   <si>
-    <t xml:space="preserve">• Swing factors: (1) IPO multiple (every 4x on the IPO multiple moves the entry mark ~18%); (2) PAC-3 / THAAD ramp delivery; (3) share loss to new SRM entrants in SM and tactical motors.</t>
+    <t xml:space="preserve">• Swing factors: (1) IPO multiple (every 4x moves the entry mark ~18%); (2) Golden Dome funding — FY27 $17.5B request is ~98% reconciliation-dependent, and SBI is not guaranteed; (3) PAC-3 / THAAD ramp delivery; (4) share loss to new SRM entrants.</t>
   </si>
   <si>
     <t xml:space="preserve">CONSUMER / VALUE SLEEVE — BOTTOM-UP ($200M)</t>
@@ -6313,7 +6343,7 @@
       </c>
       <c r="B22" s="78" t="n">
         <f aca="false">'MSL Build'!$B$13</f>
-        <v>10681.97856</v>
+        <v>10731.30168</v>
       </c>
       <c r="C22" s="78" t="n">
         <f aca="false">'MSL Build'!$B$14</f>
@@ -6321,26 +6351,26 @@
       </c>
       <c r="D22" s="46" t="n">
         <f aca="false">C22/B22</f>
-        <v>0.00140423423579686</v>
+        <v>0.00139778010601972</v>
       </c>
       <c r="E22" s="47" t="s">
         <v>456</v>
       </c>
       <c r="F22" s="123" t="n">
-        <f aca="false">'MSL Build'!C$80-$R22*$Q$5</f>
-        <v>0.101420922002584</v>
+        <f aca="false">'MSL Build'!C$96-$R22*$Q$5</f>
+        <v>0.112609979034539</v>
       </c>
       <c r="G22" s="123" t="n">
-        <f aca="false">'MSL Build'!D$80-$R22*$Q$6</f>
-        <v>0.211081228173655</v>
+        <f aca="false">'MSL Build'!D$96-$R22*$Q$6</f>
+        <v>0.231038742033648</v>
       </c>
       <c r="H22" s="123" t="n">
-        <f aca="false">'MSL Build'!E$80-$R22*$Q$7</f>
-        <v>-0.0794229924192035</v>
+        <f aca="false">'MSL Build'!E$96-$R22*$Q$7</f>
+        <v>-0.0793307932939748</v>
       </c>
       <c r="I22" s="123" t="n">
-        <f aca="false">'MSL Build'!F$80-$R22*$Q$8</f>
-        <v>0.242208498655892</v>
+        <f aca="false">'MSL Build'!F$96-$R22*$Q$8</f>
+        <v>0.265434710144012</v>
       </c>
       <c r="J22" s="75" t="s">
         <v>457</v>
@@ -6361,19 +6391,19 @@
       </c>
       <c r="S22" s="117" t="n">
         <f aca="false">F22+$R22*$Q$5</f>
-        <v>0.123920922002584</v>
+        <v>0.135109979034539</v>
       </c>
       <c r="T22" s="117" t="n">
         <f aca="false">G22+$R22*$Q$6</f>
-        <v>0.247081228173655</v>
+        <v>0.267038742033648</v>
       </c>
       <c r="U22" s="117" t="n">
         <f aca="false">H22+$R22*$Q$7</f>
-        <v>-0.0614229924192035</v>
+        <v>-0.0613307932939748</v>
       </c>
       <c r="V22" s="117" t="n">
         <f aca="false">I22+$R22*$Q$8</f>
-        <v>0.269208498655892</v>
+        <v>0.292434710144012</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7066,51 +7096,51 @@
       </c>
       <c r="C37" s="95" t="n">
         <f aca="false">B37*(1+S22)^5*'Weapons Sleeve'!$B$6</f>
-        <v>24.7490119423027</v>
+        <v>26.0057147643323</v>
       </c>
       <c r="D37" s="68" t="n">
         <f aca="false">C37/B37</f>
-        <v>1.64993412948685</v>
+        <v>1.73371431762216</v>
       </c>
       <c r="E37" s="46" t="n">
         <f aca="false">(C37/B37)^(1/5)-1</f>
-        <v>0.105333470962327</v>
+        <v>0.116337482902856</v>
       </c>
       <c r="F37" s="95" t="n">
         <f aca="false">B37*(1+T22)^5*'Weapons Sleeve'!$B$6</f>
-        <v>41.6248610187656</v>
+        <v>45.0638775961842</v>
       </c>
       <c r="G37" s="68" t="n">
         <f aca="false">F37/B37</f>
-        <v>2.77499073458437</v>
+        <v>3.00425850641228</v>
       </c>
       <c r="H37" s="46" t="n">
         <f aca="false">(F37/B37)^(1/5)-1</f>
-        <v>0.226456946858027</v>
+        <v>0.246084402522203</v>
       </c>
       <c r="I37" s="95" t="n">
         <f aca="false">B37*(1+U22)^5*'Weapons Sleeve'!$B$6</f>
-        <v>10.0514482643763</v>
+        <v>10.0563861481051</v>
       </c>
       <c r="J37" s="68" t="n">
         <f aca="false">I37/B37</f>
-        <v>0.670096550958419</v>
+        <v>0.670425743207006</v>
       </c>
       <c r="K37" s="46" t="n">
         <f aca="false">(I37/B37)^(1/5)-1</f>
-        <v>-0.0769452180797366</v>
+        <v>-0.0768545437474829</v>
       </c>
       <c r="L37" s="96" t="n">
         <f aca="false">B37*(1+V22)^5*'Weapons Sleeve'!$B$6</f>
-        <v>45.4510524263535</v>
+        <v>49.7647872606111</v>
       </c>
       <c r="M37" s="69" t="n">
         <f aca="false">L37/B37</f>
-        <v>3.0300701617569</v>
+        <v>3.31765248404074</v>
       </c>
       <c r="N37" s="71" t="n">
         <f aca="false">(L37/B37)^(1/5)-1</f>
-        <v>0.248218275619018</v>
+        <v>0.271060371053744</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7123,51 +7153,51 @@
       </c>
       <c r="C38" s="97" t="n">
         <f aca="false">SUM(C27:C37)</f>
-        <v>961.729175793093</v>
+        <v>962.985878615122</v>
       </c>
       <c r="D38" s="98" t="n">
         <f aca="false">C38/B38</f>
-        <v>2.37463994022986</v>
+        <v>2.3777429101608</v>
       </c>
       <c r="E38" s="99" t="n">
         <f aca="false">(C38/B38)^(1/5)-1</f>
-        <v>0.188829446220983</v>
+        <v>0.189139975437631</v>
       </c>
       <c r="F38" s="97" t="n">
         <f aca="false">SUM(F27:F37)</f>
-        <v>1597.68612242863</v>
+        <v>1601.12513900605</v>
       </c>
       <c r="G38" s="98" t="n">
         <f aca="false">F38/B38</f>
-        <v>3.94490400599662</v>
+        <v>3.95339540495321</v>
       </c>
       <c r="H38" s="99" t="n">
         <f aca="false">(F38/B38)^(1/5)-1</f>
-        <v>0.315852736366111</v>
+        <v>0.31641872340284</v>
       </c>
       <c r="I38" s="97" t="n">
         <f aca="false">SUM(I27:I37)</f>
-        <v>448.471104924246</v>
+        <v>448.476042807974</v>
       </c>
       <c r="J38" s="98" t="n">
         <f aca="false">I38/B38</f>
-        <v>1.10733606154135</v>
+        <v>1.10734825384685</v>
       </c>
       <c r="K38" s="99" t="n">
         <f aca="false">(I38/B38)^(1/5)-1</f>
-        <v>0.0206007630100915</v>
+        <v>0.0206030104617783</v>
       </c>
       <c r="L38" s="100" t="n">
         <f aca="false">SUM(L27:L37)</f>
-        <v>1604.43461063542</v>
+        <v>1608.74834546968</v>
       </c>
       <c r="M38" s="101" t="n">
         <f aca="false">L38/B38</f>
-        <v>3.96156693984054</v>
+        <v>3.97221813696216</v>
       </c>
       <c r="N38" s="102" t="n">
         <f aca="false">(L38/B38)^(1/5)-1</f>
-        <v>0.31696247263922</v>
+        <v>0.317669877854288</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7855,51 +7885,51 @@
       </c>
       <c r="C53" s="95" t="n">
         <f aca="false">B53*(1+S22)^7*'Weapons Sleeve'!$B$7</f>
-        <v>29.9036514177801</v>
+        <v>32.0508478841477</v>
       </c>
       <c r="D53" s="68" t="n">
         <f aca="false">C53/B53</f>
-        <v>1.99357676118534</v>
+        <v>2.13672319227651</v>
       </c>
       <c r="E53" s="46" t="n">
         <f aca="false">(C53/B53)^(1/7)-1</f>
-        <v>0.103582255722015</v>
+        <v>0.114568833653784</v>
       </c>
       <c r="F53" s="95" t="n">
         <f aca="false">B53*(1+T22)^7*'Weapons Sleeve'!$B$7</f>
-        <v>61.9208807843048</v>
+        <v>69.1995375693674</v>
       </c>
       <c r="G53" s="68" t="n">
         <f aca="false">F53/B53</f>
-        <v>4.12805871895365</v>
+        <v>4.61330250462449</v>
       </c>
       <c r="H53" s="46" t="n">
         <f aca="false">(F53/B53)^(1/7)-1</f>
-        <v>0.224513831813248</v>
+        <v>0.244110191070421</v>
       </c>
       <c r="I53" s="95" t="n">
         <f aca="false">B53*(1+U22)^7*'Weapons Sleeve'!$B$7</f>
-        <v>8.46960796617199</v>
+        <v>8.47543364081529</v>
       </c>
       <c r="J53" s="68" t="n">
         <f aca="false">I53/B53</f>
-        <v>0.564640531078133</v>
+        <v>0.565028909387686</v>
       </c>
       <c r="K53" s="46" t="n">
         <f aca="false">(I53/B53)^(1/7)-1</f>
-        <v>-0.0784076433515728</v>
+        <v>-0.0783171126775695</v>
       </c>
       <c r="L53" s="96" t="n">
         <f aca="false">B53*(1+V22)^7*'Weapons Sleeve'!$B$7</f>
-        <v>70.0333226779095</v>
+        <v>79.5122829066679</v>
       </c>
       <c r="M53" s="69" t="n">
         <f aca="false">L53/B53</f>
-        <v>4.6688881785273</v>
+        <v>5.30081886044452</v>
       </c>
       <c r="N53" s="71" t="n">
         <f aca="false">(L53/B53)^(1/7)-1</f>
-        <v>0.246240683403705</v>
+        <v>0.26904658937462</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7912,51 +7942,51 @@
       </c>
       <c r="C54" s="97" t="n">
         <f aca="false">SUM(C43:C53)</f>
-        <v>1367.85556437661</v>
+        <v>1370.00276084297</v>
       </c>
       <c r="D54" s="98" t="n">
         <f aca="false">C54/B54</f>
-        <v>3.3774211466089</v>
+        <v>3.38272286627895</v>
       </c>
       <c r="E54" s="99" t="n">
         <f aca="false">(C54/B54)^(1/7)-1</f>
-        <v>0.189904683804596</v>
+        <v>0.190171341234809</v>
       </c>
       <c r="F54" s="97" t="n">
         <f aca="false">SUM(F43:F53)</f>
-        <v>2817.66321252754</v>
+        <v>2824.9418693126</v>
       </c>
       <c r="G54" s="98" t="n">
         <f aca="false">F54/B54</f>
-        <v>6.95719311735195</v>
+        <v>6.97516510941384</v>
       </c>
       <c r="H54" s="99" t="n">
         <f aca="false">(F54/B54)^(1/7)-1</f>
-        <v>0.319312637995968</v>
+        <v>0.319798968530986</v>
       </c>
       <c r="I54" s="97" t="n">
         <f aca="false">SUM(I43:I53)</f>
-        <v>465.723649144541</v>
+        <v>465.729474819185</v>
       </c>
       <c r="J54" s="98" t="n">
         <f aca="false">I54/B54</f>
-        <v>1.14993493615936</v>
+        <v>1.1499493205412</v>
       </c>
       <c r="K54" s="99" t="n">
         <f aca="false">(I54/B54)^(1/7)-1</f>
-        <v>0.0201583997119177</v>
+        <v>0.0201602227056523</v>
       </c>
       <c r="L54" s="100" t="n">
         <f aca="false">SUM(L43:L53)</f>
-        <v>2828.63891069913</v>
+        <v>2838.11787092789</v>
       </c>
       <c r="M54" s="101" t="n">
         <f aca="false">L54/B54</f>
-        <v>6.98429360666453</v>
+        <v>7.00769844673553</v>
       </c>
       <c r="N54" s="102" t="n">
         <f aca="false">(L54/B54)^(1/7)-1</f>
-        <v>0.32004557875878</v>
+        <v>0.320676610492032</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8644,51 +8674,51 @@
       </c>
       <c r="C69" s="95" t="n">
         <f aca="false">B69*(1+S22)^10*'Weapons Sleeve'!$B$8</f>
-        <v>39.5605817216917</v>
+        <v>43.6801909523572</v>
       </c>
       <c r="D69" s="68" t="n">
         <f aca="false">C69/B69</f>
-        <v>2.63737211477945</v>
+        <v>2.91201273015715</v>
       </c>
       <c r="E69" s="46" t="n">
         <f aca="false">(C69/B69)^(1/10)-1</f>
-        <v>0.101836464649542</v>
+        <v>0.11280566257219</v>
       </c>
       <c r="F69" s="95" t="n">
         <f aca="false">B69*(1+T22)^10*'Weapons Sleeve'!$B$8</f>
-        <v>111.905783314577</v>
+        <v>131.160799659986</v>
       </c>
       <c r="G69" s="68" t="n">
         <f aca="false">F69/B69</f>
-        <v>7.46038555430515</v>
+        <v>8.74405331066571</v>
       </c>
       <c r="H69" s="46" t="n">
         <f aca="false">(F69/B69)^(1/10)-1</f>
-        <v>0.222576735321695</v>
+        <v>0.242142094489054</v>
       </c>
       <c r="I69" s="95" t="n">
         <f aca="false">B69*(1+U22)^10*'Weapons Sleeve'!$B$8</f>
-        <v>6.52535617622677</v>
+        <v>6.53176905600472</v>
       </c>
       <c r="J69" s="68" t="n">
         <f aca="false">I69/B69</f>
-        <v>0.435023745081785</v>
+        <v>0.435451270400315</v>
       </c>
       <c r="K69" s="46" t="n">
         <f aca="false">(I69/B69)^(1/10)-1</f>
-        <v>-0.0798655389459918</v>
+        <v>-0.0797751514852756</v>
       </c>
       <c r="L69" s="96" t="n">
         <f aca="false">B69*(1+V22)^10*'Weapons Sleeve'!$B$8</f>
-        <v>133.424267223044</v>
+        <v>159.952577339082</v>
       </c>
       <c r="M69" s="69" t="n">
         <f aca="false">L69/B69</f>
-        <v>8.89495114820293</v>
+        <v>10.6635051559388</v>
       </c>
       <c r="N69" s="71" t="n">
         <f aca="false">(L69/B69)^(1/10)-1</f>
-        <v>0.244269216530295</v>
+        <v>0.26703904512969</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8701,51 +8731,51 @@
       </c>
       <c r="C70" s="97" t="n">
         <f aca="false">SUM(C59:C69)</f>
-        <v>2353.82540279516</v>
+        <v>2357.94501202583</v>
       </c>
       <c r="D70" s="98" t="n">
         <f aca="false">C70/B70</f>
-        <v>5.81191457480287</v>
+        <v>5.82208644944649</v>
       </c>
       <c r="E70" s="99" t="n">
         <f aca="false">(C70/B70)^(1/10)-1</f>
-        <v>0.192427332423751</v>
+        <v>0.192635864036574</v>
       </c>
       <c r="F70" s="97" t="n">
         <f aca="false">SUM(F59:F69)</f>
-        <v>6772.83040582878</v>
+        <v>6792.08542217419</v>
       </c>
       <c r="G70" s="98" t="n">
         <f aca="false">F70/B70</f>
-        <v>16.7230380390834</v>
+        <v>16.770581289319</v>
       </c>
       <c r="H70" s="99" t="n">
         <f aca="false">(F70/B70)^(1/10)-1</f>
-        <v>0.325352854416582</v>
+        <v>0.325729168300645</v>
       </c>
       <c r="I70" s="97" t="n">
         <f aca="false">SUM(I59:I69)</f>
-        <v>494.569881367072</v>
+        <v>494.57629424685</v>
       </c>
       <c r="J70" s="98" t="n">
         <f aca="false">I70/B70</f>
-        <v>1.22116020090635</v>
+        <v>1.22117603517741</v>
       </c>
       <c r="K70" s="99" t="n">
         <f aca="false">(I70/B70)^(1/10)-1</f>
-        <v>0.0201810781311162</v>
+        <v>0.0201824009493221</v>
       </c>
       <c r="L70" s="100" t="n">
         <f aca="false">SUM(L59:L69)</f>
-        <v>6791.82840558708</v>
+        <v>6818.35671570312</v>
       </c>
       <c r="M70" s="101" t="n">
         <f aca="false">L70/B70</f>
-        <v>16.7699466804619</v>
+        <v>16.8354486807484</v>
       </c>
       <c r="N70" s="102" t="n">
         <f aca="false">(L70/B70)^(1/10)-1</f>
-        <v>0.325724151576512</v>
+        <v>0.326241060370445</v>
       </c>
     </row>
   </sheetData>
@@ -12265,7 +12295,7 @@
     <tabColor rgb="FF7A3B2E"/>
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:M103"/>
+  <dimension ref="A1:M120"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="50"/>
@@ -12338,7 +12368,7 @@
         <v>475</v>
       </c>
       <c r="B6" s="153" t="n">
-        <f aca="false">B38</f>
+        <f aca="false">B40</f>
         <v>4100</v>
       </c>
       <c r="C6" s="129" t="s">
@@ -12423,8 +12453,8 @@
         <v>607</v>
       </c>
       <c r="B10" s="153" t="n">
-        <f aca="false">C51</f>
-        <v>571.2288</v>
+        <f aca="false">C61</f>
+        <v>573.8664</v>
       </c>
       <c r="C10" s="129" t="s">
         <v>608</v>
@@ -12446,7 +12476,7 @@
       </c>
       <c r="B11" s="153" t="n">
         <f aca="false">B9*B10</f>
-        <v>12567.0336</v>
+        <v>12625.0608</v>
       </c>
       <c r="C11" s="129" t="s">
         <v>610</v>
@@ -12489,7 +12519,7 @@
       </c>
       <c r="B13" s="153" t="n">
         <f aca="false">B11*(1-B12)</f>
-        <v>10681.97856</v>
+        <v>10731.30168</v>
       </c>
       <c r="C13" s="129" t="s">
         <v>614</v>
@@ -12532,7 +12562,7 @@
       </c>
       <c r="B15" s="155" t="n">
         <f aca="false">B14/B13</f>
-        <v>0.00140423423579686</v>
+        <v>0.00139778010601972</v>
       </c>
       <c r="C15" s="129" t="s">
         <v>616</v>
@@ -12823,108 +12853,89 @@
       <c r="L27" s="129"/>
       <c r="M27" s="129"/>
     </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="60" t="s">
+    <row r="28" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="127" t="s">
         <v>635</v>
       </c>
-      <c r="B29" s="125"/>
-      <c r="C29" s="125"/>
-      <c r="D29" s="125"/>
-      <c r="E29" s="125"/>
-      <c r="F29" s="125"/>
-      <c r="G29" s="125"/>
-      <c r="H29" s="125"/>
-      <c r="I29" s="125"/>
-      <c r="J29" s="125"/>
-      <c r="K29" s="125"/>
-      <c r="L29" s="125"/>
-      <c r="M29" s="125"/>
-    </row>
-    <row r="30" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="126" t="s">
+      <c r="B28" s="133" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="C28" s="133" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="D28" s="133" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="E28" s="133" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F28" s="129" t="s">
         <v>636</v>
       </c>
-      <c r="B30" s="126" t="s">
+      <c r="G28" s="129"/>
+      <c r="H28" s="129"/>
+      <c r="I28" s="129"/>
+      <c r="J28" s="129"/>
+      <c r="K28" s="129"/>
+      <c r="L28" s="129"/>
+      <c r="M28" s="129"/>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="60" t="s">
+        <v>637</v>
+      </c>
+      <c r="B30" s="125"/>
+      <c r="C30" s="125"/>
+      <c r="D30" s="125"/>
+      <c r="E30" s="125"/>
+      <c r="F30" s="125"/>
+      <c r="G30" s="125"/>
+      <c r="H30" s="125"/>
+      <c r="I30" s="125"/>
+      <c r="J30" s="125"/>
+      <c r="K30" s="125"/>
+      <c r="L30" s="125"/>
+      <c r="M30" s="125"/>
+    </row>
+    <row r="31" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="126" t="s">
+        <v>638</v>
+      </c>
+      <c r="B31" s="126" t="s">
         <v>505</v>
       </c>
-      <c r="C30" s="126" t="s">
+      <c r="C31" s="126" t="s">
         <v>506</v>
       </c>
-      <c r="D30" s="126" t="s">
+      <c r="D31" s="126" t="s">
         <v>507</v>
       </c>
-      <c r="E30" s="126" t="s">
+      <c r="E31" s="126" t="s">
         <v>508</v>
       </c>
-      <c r="F30" s="126" t="s">
+      <c r="F31" s="126" t="s">
         <v>509</v>
       </c>
-      <c r="G30" s="126" t="s">
+      <c r="G31" s="126" t="s">
         <v>510</v>
       </c>
-      <c r="H30" s="126" t="s">
+      <c r="H31" s="126" t="s">
         <v>511</v>
       </c>
-      <c r="I30" s="126" t="s">
+      <c r="I31" s="126" t="s">
         <v>512</v>
       </c>
-      <c r="J30" s="126" t="s">
+      <c r="J31" s="126" t="s">
         <v>513</v>
       </c>
-      <c r="K30" s="126" t="s">
+      <c r="K31" s="126" t="s">
         <v>514</v>
       </c>
-      <c r="L30" s="126" t="s">
+      <c r="L31" s="126" t="s">
         <v>515</v>
       </c>
-      <c r="M30" s="126" t="s">
+      <c r="M31" s="126" t="s">
         <v>516</v>
-      </c>
-    </row>
-    <row r="31" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="127" t="s">
-        <v>637</v>
-      </c>
-      <c r="B31" s="156" t="n">
-        <v>600</v>
-      </c>
-      <c r="C31" s="135" t="n">
-        <v>1</v>
-      </c>
-      <c r="D31" s="133" t="n">
-        <v>0</v>
-      </c>
-      <c r="E31" s="133" t="n">
-        <v>0</v>
-      </c>
-      <c r="F31" s="133" t="n">
-        <v>0</v>
-      </c>
-      <c r="G31" s="133" t="n">
-        <v>0</v>
-      </c>
-      <c r="H31" s="130" t="n">
-        <f aca="false">INDEX(B$21:B$27,$C31)+D31</f>
-        <v>0.18</v>
-      </c>
-      <c r="I31" s="130" t="n">
-        <f aca="false">INDEX(C$21:C$27,$C31)+E31</f>
-        <v>0.25</v>
-      </c>
-      <c r="J31" s="130" t="n">
-        <f aca="false">INDEX(D$21:D$27,$C31)+F31</f>
-        <v>0.05</v>
-      </c>
-      <c r="K31" s="130" t="n">
-        <f aca="false">INDEX(E$21:E$27,$C31)+G31</f>
-        <v>0.28</v>
-      </c>
-      <c r="L31" s="130" t="n">
-        <f aca="false">B31/$B$38</f>
-        <v>0.146341463414634</v>
-      </c>
-      <c r="M31" s="129" t="s">
-        <v>638</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12932,10 +12943,10 @@
         <v>639</v>
       </c>
       <c r="B32" s="156" t="n">
-        <v>250</v>
+        <v>600</v>
       </c>
       <c r="C32" s="135" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D32" s="133" t="n">
         <v>0</v>
@@ -12950,36 +12961,38 @@
         <v>0</v>
       </c>
       <c r="H32" s="130" t="n">
-        <f aca="false">INDEX(B$21:B$27,$C32)+D32</f>
-        <v>0.2</v>
+        <f aca="false">INDEX(B$21:B$28,$C32)+D32</f>
+        <v>0.18</v>
       </c>
       <c r="I32" s="130" t="n">
-        <f aca="false">INDEX(C$21:C$27,$C32)+E32</f>
+        <f aca="false">INDEX(C$21:C$28,$C32)+E32</f>
+        <v>0.25</v>
+      </c>
+      <c r="J32" s="130" t="n">
+        <f aca="false">INDEX(D$21:D$28,$C32)+F32</f>
+        <v>0.05</v>
+      </c>
+      <c r="K32" s="130" t="n">
+        <f aca="false">INDEX(E$21:E$28,$C32)+G32</f>
         <v>0.28</v>
       </c>
-      <c r="J32" s="130" t="n">
-        <f aca="false">INDEX(D$21:D$27,$C32)+F32</f>
-        <v>0.05</v>
-      </c>
-      <c r="K32" s="130" t="n">
-        <f aca="false">INDEX(E$21:E$27,$C32)+G32</f>
-        <v>0.3</v>
-      </c>
       <c r="L32" s="130" t="n">
-        <f aca="false">B32/$B$38</f>
-        <v>0.0609756097560976</v>
-      </c>
-      <c r="M32" s="129"/>
+        <f aca="false">B32/$B$40</f>
+        <v>0.146341463414634</v>
+      </c>
+      <c r="M32" s="129" t="s">
+        <v>640</v>
+      </c>
     </row>
     <row r="33" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="127" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="B33" s="156" t="n">
-        <v>600</v>
+        <v>250</v>
       </c>
       <c r="C33" s="135" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D33" s="133" t="n">
         <v>0</v>
@@ -12988,42 +13001,42 @@
         <v>0</v>
       </c>
       <c r="F33" s="133" t="n">
-        <v>-0.03</v>
+        <v>0</v>
       </c>
       <c r="G33" s="133" t="n">
         <v>0</v>
       </c>
       <c r="H33" s="130" t="n">
-        <f aca="false">INDEX(B$21:B$27,$C33)+D33</f>
-        <v>0.12</v>
+        <f aca="false">INDEX(B$21:B$28,$C33)+D33</f>
+        <v>0.2</v>
       </c>
       <c r="I33" s="130" t="n">
-        <f aca="false">INDEX(C$21:C$27,$C33)+E33</f>
-        <v>0.18</v>
+        <f aca="false">INDEX(C$21:C$28,$C33)+E33</f>
+        <v>0.28</v>
       </c>
       <c r="J33" s="130" t="n">
-        <f aca="false">INDEX(D$21:D$27,$C33)+F33</f>
-        <v>0</v>
+        <f aca="false">INDEX(D$21:D$28,$C33)+F33</f>
+        <v>0.05</v>
       </c>
       <c r="K33" s="130" t="n">
-        <f aca="false">INDEX(E$21:E$27,$C33)+G33</f>
-        <v>0.22</v>
+        <f aca="false">INDEX(E$21:E$28,$C33)+G33</f>
+        <v>0.3</v>
       </c>
       <c r="L33" s="130" t="n">
-        <f aca="false">B33/$B$38</f>
-        <v>0.146341463414634</v>
+        <f aca="false">B33/$B$40</f>
+        <v>0.0609756097560976</v>
       </c>
       <c r="M33" s="129"/>
     </row>
     <row r="34" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="127" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="B34" s="156" t="n">
-        <v>200</v>
+        <v>600</v>
       </c>
       <c r="C34" s="135" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D34" s="133" t="n">
         <v>0</v>
@@ -13032,1925 +13045,2551 @@
         <v>0</v>
       </c>
       <c r="F34" s="133" t="n">
-        <v>0</v>
+        <v>-0.03</v>
       </c>
       <c r="G34" s="133" t="n">
         <v>0</v>
       </c>
       <c r="H34" s="130" t="n">
-        <f aca="false">INDEX(B$21:B$27,$C34)+D34</f>
-        <v>0.2</v>
+        <f aca="false">INDEX(B$21:B$28,$C34)+D34</f>
+        <v>0.12</v>
       </c>
       <c r="I34" s="130" t="n">
-        <f aca="false">INDEX(C$21:C$27,$C34)+E34</f>
-        <v>0.28</v>
+        <f aca="false">INDEX(C$21:C$28,$C34)+E34</f>
+        <v>0.18</v>
       </c>
       <c r="J34" s="130" t="n">
-        <f aca="false">INDEX(D$21:D$27,$C34)+F34</f>
-        <v>0.06</v>
+        <f aca="false">INDEX(D$21:D$28,$C34)+F34</f>
+        <v>0</v>
       </c>
       <c r="K34" s="130" t="n">
-        <f aca="false">INDEX(E$21:E$27,$C34)+G34</f>
-        <v>0.3</v>
+        <f aca="false">INDEX(E$21:E$28,$C34)+G34</f>
+        <v>0.22</v>
       </c>
       <c r="L34" s="130" t="n">
-        <f aca="false">B34/$B$38</f>
-        <v>0.0487804878048781</v>
+        <f aca="false">B34/$B$40</f>
+        <v>0.146341463414634</v>
       </c>
       <c r="M34" s="129"/>
     </row>
     <row r="35" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="127" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="B35" s="156" t="n">
-        <v>850</v>
+        <v>200</v>
       </c>
       <c r="C35" s="135" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D35" s="133" t="n">
         <v>0</v>
       </c>
       <c r="E35" s="133" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="F35" s="133" t="n">
-        <v>-0.02</v>
+        <v>0</v>
       </c>
       <c r="G35" s="133" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="H35" s="130" t="n">
-        <f aca="false">INDEX(B$21:B$27,$C35)+D35</f>
-        <v>0.1</v>
+        <f aca="false">INDEX(B$21:B$28,$C35)+D35</f>
+        <v>0.2</v>
       </c>
       <c r="I35" s="130" t="n">
-        <f aca="false">INDEX(C$21:C$27,$C35)+E35</f>
-        <v>0.17</v>
+        <f aca="false">INDEX(C$21:C$28,$C35)+E35</f>
+        <v>0.28</v>
       </c>
       <c r="J35" s="130" t="n">
-        <f aca="false">INDEX(D$21:D$27,$C35)+F35</f>
-        <v>0</v>
+        <f aca="false">INDEX(D$21:D$28,$C35)+F35</f>
+        <v>0.06</v>
       </c>
       <c r="K35" s="130" t="n">
-        <f aca="false">INDEX(E$21:E$27,$C35)+G35</f>
-        <v>0.19</v>
+        <f aca="false">INDEX(E$21:E$28,$C35)+G35</f>
+        <v>0.3</v>
       </c>
       <c r="L35" s="130" t="n">
-        <f aca="false">B35/$B$38</f>
-        <v>0.207317073170732</v>
+        <f aca="false">B35/$B$40</f>
+        <v>0.0487804878048781</v>
       </c>
       <c r="M35" s="129"/>
     </row>
     <row r="36" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="127" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="B36" s="156" t="n">
-        <v>900</v>
+        <v>850</v>
       </c>
       <c r="C36" s="135" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D36" s="133" t="n">
         <v>0</v>
       </c>
       <c r="E36" s="133" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="F36" s="133" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="G36" s="133" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="H36" s="130" t="n">
+        <f aca="false">INDEX(B$21:B$28,$C36)+D36</f>
+        <v>0.1</v>
+      </c>
+      <c r="I36" s="130" t="n">
+        <f aca="false">INDEX(C$21:C$28,$C36)+E36</f>
+        <v>0.17</v>
+      </c>
+      <c r="J36" s="130" t="n">
+        <f aca="false">INDEX(D$21:D$28,$C36)+F36</f>
         <v>0</v>
       </c>
-      <c r="G36" s="133" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="H36" s="130" t="n">
-        <f aca="false">INDEX(B$21:B$27,$C36)+D36</f>
-        <v>0.08</v>
-      </c>
-      <c r="I36" s="130" t="n">
-        <f aca="false">INDEX(C$21:C$27,$C36)+E36</f>
-        <v>0.16</v>
-      </c>
-      <c r="J36" s="130" t="n">
-        <f aca="false">INDEX(D$21:D$27,$C36)+F36</f>
-        <v>0.02</v>
-      </c>
       <c r="K36" s="130" t="n">
-        <f aca="false">INDEX(E$21:E$27,$C36)+G36</f>
-        <v>0.18</v>
+        <f aca="false">INDEX(E$21:E$28,$C36)+G36</f>
+        <v>0.19</v>
       </c>
       <c r="L36" s="130" t="n">
-        <f aca="false">B36/$B$38</f>
-        <v>0.219512195121951</v>
+        <f aca="false">B36/$B$40</f>
+        <v>0.207317073170732</v>
       </c>
       <c r="M36" s="129"/>
     </row>
     <row r="37" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="127" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="B37" s="156" t="n">
-        <v>700</v>
+        <v>600</v>
       </c>
       <c r="C37" s="135" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D37" s="133" t="n">
         <v>0</v>
       </c>
       <c r="E37" s="133" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="F37" s="133" t="n">
         <v>0</v>
       </c>
       <c r="G37" s="133" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="H37" s="130" t="n">
+        <f aca="false">INDEX(B$21:B$28,$C37)+D37</f>
+        <v>0.08</v>
+      </c>
+      <c r="I37" s="130" t="n">
+        <f aca="false">INDEX(C$21:C$28,$C37)+E37</f>
+        <v>0.16</v>
+      </c>
+      <c r="J37" s="130" t="n">
+        <f aca="false">INDEX(D$21:D$28,$C37)+F37</f>
+        <v>0.02</v>
+      </c>
+      <c r="K37" s="130" t="n">
+        <f aca="false">INDEX(E$21:E$28,$C37)+G37</f>
+        <v>0.18</v>
+      </c>
+      <c r="L37" s="130" t="n">
+        <f aca="false">B37/$B$40</f>
+        <v>0.146341463414634</v>
+      </c>
+      <c r="M37" s="129"/>
+    </row>
+    <row r="38" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A38" s="127" t="s">
+        <v>646</v>
+      </c>
+      <c r="B38" s="156" t="n">
+        <v>700</v>
+      </c>
+      <c r="C38" s="135" t="n">
+        <v>7</v>
+      </c>
+      <c r="D38" s="133" t="n">
         <v>0</v>
       </c>
-      <c r="H37" s="130" t="n">
-        <f aca="false">INDEX(B$21:B$27,$C37)+D37</f>
+      <c r="E38" s="133" t="n">
+        <v>0</v>
+      </c>
+      <c r="F38" s="133" t="n">
+        <v>0</v>
+      </c>
+      <c r="G38" s="133" t="n">
+        <v>0</v>
+      </c>
+      <c r="H38" s="130" t="n">
+        <f aca="false">INDEX(B$21:B$28,$C38)+D38</f>
         <v>0.03</v>
       </c>
-      <c r="I37" s="130" t="n">
-        <f aca="false">INDEX(C$21:C$27,$C37)+E37</f>
+      <c r="I38" s="130" t="n">
+        <f aca="false">INDEX(C$21:C$28,$C38)+E38</f>
         <v>0.06</v>
       </c>
-      <c r="J37" s="130" t="n">
-        <f aca="false">INDEX(D$21:D$27,$C37)+F37</f>
+      <c r="J38" s="130" t="n">
+        <f aca="false">INDEX(D$21:D$28,$C38)+F38</f>
         <v>-0.02</v>
       </c>
-      <c r="K37" s="130" t="n">
-        <f aca="false">INDEX(E$21:E$27,$C37)+G37</f>
+      <c r="K38" s="130" t="n">
+        <f aca="false">INDEX(E$21:E$28,$C38)+G38</f>
         <v>0.03</v>
       </c>
-      <c r="L37" s="130" t="n">
-        <f aca="false">B37/$B$38</f>
+      <c r="L38" s="130" t="n">
+        <f aca="false">B38/$B$40</f>
         <v>0.170731707317073</v>
       </c>
-      <c r="M37" s="129"/>
-    </row>
-    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="137" t="s">
-        <v>645</v>
-      </c>
-      <c r="B38" s="157" t="n">
-        <f aca="false">SUM(B31:B37)</f>
+      <c r="M38" s="129"/>
+    </row>
+    <row r="39" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A39" s="127" t="s">
+        <v>647</v>
+      </c>
+      <c r="B39" s="156" t="n">
+        <v>300</v>
+      </c>
+      <c r="C39" s="135" t="n">
+        <v>8</v>
+      </c>
+      <c r="D39" s="133" t="n">
+        <v>0</v>
+      </c>
+      <c r="E39" s="133" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="F39" s="133" t="n">
+        <v>0</v>
+      </c>
+      <c r="G39" s="133" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="H39" s="130" t="n">
+        <f aca="false">INDEX(B$21:B$28,$C39)+D39</f>
+        <v>0.15</v>
+      </c>
+      <c r="I39" s="130" t="n">
+        <f aca="false">INDEX(C$21:C$28,$C39)+E39</f>
+        <v>0.27</v>
+      </c>
+      <c r="J39" s="130" t="n">
+        <f aca="false">INDEX(D$21:D$28,$C39)+F39</f>
+        <v>0.03</v>
+      </c>
+      <c r="K39" s="130" t="n">
+        <f aca="false">INDEX(E$21:E$28,$C39)+G39</f>
+        <v>0.32</v>
+      </c>
+      <c r="L39" s="130" t="n">
+        <f aca="false">B39/$B$40</f>
+        <v>0.0731707317073171</v>
+      </c>
+      <c r="M39" s="129"/>
+    </row>
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="137" t="s">
+        <v>648</v>
+      </c>
+      <c r="B40" s="157" t="n">
+        <f aca="false">SUM(B32:B39)</f>
         <v>4100</v>
       </c>
-      <c r="H38" s="139" t="n">
-        <f aca="false">SUMPRODUCT($B$31:$B$37,H31:H37)/$B$38</f>
-        <v>0.109268292682927</v>
-      </c>
-      <c r="I38" s="139" t="n">
-        <f aca="false">SUMPRODUCT($B$31:$B$37,I31:I37)/$B$38</f>
-        <v>0.174268292682927</v>
-      </c>
-      <c r="J38" s="139" t="n">
-        <f aca="false">SUMPRODUCT($B$31:$B$37,J31:J37)/$B$38</f>
-        <v>0.0142682926829268</v>
-      </c>
-      <c r="K38" s="139" t="n">
-        <f aca="false">SUMPRODUCT($B$31:$B$37,K31:K37)/$B$38</f>
-        <v>0.190121951219512</v>
-      </c>
-      <c r="L38" s="139" t="n">
-        <f aca="false">SUM(L31:L37)</f>
+      <c r="H40" s="139" t="n">
+        <f aca="false">SUMPRODUCT($B$32:$B$39,H32:H39)/$B$40</f>
+        <v>0.114390243902439</v>
+      </c>
+      <c r="I40" s="139" t="n">
+        <f aca="false">SUMPRODUCT($B$32:$B$39,I32:I39)/$B$40</f>
+        <v>0.182317073170732</v>
+      </c>
+      <c r="J40" s="139" t="n">
+        <f aca="false">SUMPRODUCT($B$32:$B$39,J32:J39)/$B$40</f>
+        <v>0.015</v>
+      </c>
+      <c r="K40" s="139" t="n">
+        <f aca="false">SUMPRODUCT($B$32:$B$39,K32:K39)/$B$40</f>
+        <v>0.200365853658537</v>
+      </c>
+      <c r="L40" s="139" t="n">
+        <f aca="false">SUM(L32:L39)</f>
         <v>1</v>
       </c>
     </row>
-    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="60" t="s">
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A42" s="60" t="s">
+        <v>649</v>
+      </c>
+      <c r="B42" s="125"/>
+      <c r="C42" s="125"/>
+      <c r="D42" s="125"/>
+      <c r="E42" s="125"/>
+      <c r="F42" s="125"/>
+      <c r="G42" s="125"/>
+      <c r="H42" s="125"/>
+      <c r="I42" s="125"/>
+      <c r="J42" s="125"/>
+      <c r="K42" s="125"/>
+      <c r="L42" s="125"/>
+      <c r="M42" s="125"/>
+    </row>
+    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A43" s="126" t="s">
+        <v>465</v>
+      </c>
+      <c r="B43" s="126" t="s">
+        <v>36</v>
+      </c>
+      <c r="C43" s="126" t="s">
+        <v>37</v>
+      </c>
+      <c r="D43" s="126" t="s">
+        <v>38</v>
+      </c>
+      <c r="E43" s="126" t="s">
+        <v>39</v>
+      </c>
+      <c r="F43" s="126" t="s">
+        <v>516</v>
+      </c>
+      <c r="G43" s="126"/>
+      <c r="H43" s="126"/>
+      <c r="I43" s="126"/>
+      <c r="J43" s="126"/>
+      <c r="K43" s="126"/>
+      <c r="L43" s="126"/>
+      <c r="M43" s="126"/>
+    </row>
+    <row r="44" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A44" s="127" t="s">
+        <v>650</v>
+      </c>
+      <c r="B44" s="135" t="n">
+        <v>4</v>
+      </c>
+      <c r="C44" s="135" t="n">
+        <v>3</v>
+      </c>
+      <c r="D44" s="135" t="n">
+        <v>99</v>
+      </c>
+      <c r="E44" s="135" t="n">
+        <v>3</v>
+      </c>
+      <c r="F44" s="129" t="s">
+        <v>651</v>
+      </c>
+      <c r="G44" s="129"/>
+      <c r="H44" s="129"/>
+      <c r="I44" s="129"/>
+      <c r="J44" s="129"/>
+      <c r="K44" s="129"/>
+      <c r="L44" s="129"/>
+      <c r="M44" s="129"/>
+    </row>
+    <row r="45" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A45" s="127" t="s">
+        <v>652</v>
+      </c>
+      <c r="B45" s="156" t="n">
+        <v>400</v>
+      </c>
+      <c r="C45" s="156" t="n">
+        <v>900</v>
+      </c>
+      <c r="D45" s="156" t="n">
+        <v>0</v>
+      </c>
+      <c r="E45" s="156" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F45" s="129" t="s">
+        <v>653</v>
+      </c>
+      <c r="G45" s="129"/>
+      <c r="H45" s="129"/>
+      <c r="I45" s="129"/>
+      <c r="J45" s="129"/>
+      <c r="K45" s="129"/>
+      <c r="L45" s="129"/>
+      <c r="M45" s="129"/>
+    </row>
+    <row r="46" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A46" s="127" t="s">
+        <v>540</v>
+      </c>
+      <c r="B46" s="135" t="n">
+        <v>3</v>
+      </c>
+      <c r="C46" s="135" t="n">
+        <v>3</v>
+      </c>
+      <c r="D46" s="135" t="n">
+        <v>3</v>
+      </c>
+      <c r="E46" s="135" t="n">
+        <v>2</v>
+      </c>
+      <c r="F46" s="129" t="s">
+        <v>541</v>
+      </c>
+      <c r="G46" s="129"/>
+      <c r="H46" s="129"/>
+      <c r="I46" s="129"/>
+      <c r="J46" s="129"/>
+      <c r="K46" s="129"/>
+      <c r="L46" s="129"/>
+      <c r="M46" s="129"/>
+    </row>
+    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A48" s="60" t="s">
         <v>542</v>
       </c>
-      <c r="B40" s="125"/>
-      <c r="C40" s="125"/>
-      <c r="D40" s="125"/>
-      <c r="E40" s="125"/>
-      <c r="F40" s="125"/>
-      <c r="G40" s="125"/>
-      <c r="H40" s="125"/>
-      <c r="I40" s="125"/>
-      <c r="J40" s="125"/>
-      <c r="K40" s="125"/>
-      <c r="L40" s="125"/>
-      <c r="M40" s="125"/>
-    </row>
-    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A41" s="126" t="s">
+      <c r="B48" s="125"/>
+      <c r="C48" s="125"/>
+      <c r="D48" s="125"/>
+      <c r="E48" s="125"/>
+      <c r="F48" s="125"/>
+      <c r="G48" s="125"/>
+      <c r="H48" s="125"/>
+      <c r="I48" s="125"/>
+      <c r="J48" s="125"/>
+      <c r="K48" s="125"/>
+      <c r="L48" s="125"/>
+      <c r="M48" s="125"/>
+    </row>
+    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A49" s="126" t="s">
         <v>465</v>
       </c>
-      <c r="B41" s="126" t="s">
+      <c r="B49" s="126" t="s">
         <v>36</v>
       </c>
-      <c r="C41" s="126" t="s">
+      <c r="C49" s="126" t="s">
         <v>37</v>
       </c>
-      <c r="D41" s="126" t="s">
+      <c r="D49" s="126" t="s">
         <v>38</v>
       </c>
-      <c r="E41" s="126" t="s">
+      <c r="E49" s="126" t="s">
         <v>39</v>
       </c>
-      <c r="F41" s="126" t="s">
+      <c r="F49" s="126" t="s">
         <v>516</v>
       </c>
-      <c r="G41" s="126"/>
-      <c r="H41" s="126"/>
-      <c r="I41" s="126"/>
-      <c r="J41" s="126"/>
-      <c r="K41" s="126"/>
-      <c r="L41" s="126"/>
-      <c r="M41" s="126"/>
-    </row>
-    <row r="42" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A42" s="127" t="s">
-        <v>646</v>
-      </c>
-      <c r="B42" s="133" t="n">
+      <c r="G49" s="126"/>
+      <c r="H49" s="126"/>
+      <c r="I49" s="126"/>
+      <c r="J49" s="126"/>
+      <c r="K49" s="126"/>
+      <c r="L49" s="126"/>
+      <c r="M49" s="126"/>
+    </row>
+    <row r="50" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A50" s="127" t="s">
+        <v>654</v>
+      </c>
+      <c r="B50" s="133" t="n">
         <v>0.14</v>
       </c>
-      <c r="C42" s="133" t="n">
+      <c r="C50" s="133" t="n">
         <v>0.16</v>
       </c>
-      <c r="D42" s="133" t="n">
+      <c r="D50" s="133" t="n">
         <v>0.11</v>
       </c>
-      <c r="E42" s="133" t="n">
+      <c r="E50" s="133" t="n">
         <v>0.16</v>
       </c>
-      <c r="F42" s="129" t="s">
-        <v>647</v>
-      </c>
-      <c r="G42" s="129"/>
-      <c r="H42" s="129"/>
-      <c r="I42" s="129"/>
-      <c r="J42" s="129"/>
-      <c r="K42" s="129"/>
-      <c r="L42" s="129"/>
-      <c r="M42" s="129"/>
-    </row>
-    <row r="43" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A43" s="127" t="s">
-        <v>648</v>
-      </c>
-      <c r="B43" s="141" t="n">
+      <c r="F50" s="129" t="s">
+        <v>655</v>
+      </c>
+      <c r="G50" s="129"/>
+      <c r="H50" s="129"/>
+      <c r="I50" s="129"/>
+      <c r="J50" s="129"/>
+      <c r="K50" s="129"/>
+      <c r="L50" s="129"/>
+      <c r="M50" s="129"/>
+    </row>
+    <row r="51" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A51" s="127" t="s">
+        <v>656</v>
+      </c>
+      <c r="B51" s="141" t="n">
         <v>20</v>
       </c>
-      <c r="C43" s="141" t="n">
+      <c r="C51" s="141" t="n">
         <v>24</v>
       </c>
-      <c r="D43" s="141" t="n">
+      <c r="D51" s="141" t="n">
         <v>14</v>
       </c>
-      <c r="E43" s="141" t="n">
+      <c r="E51" s="141" t="n">
         <v>24</v>
       </c>
-      <c r="F43" s="129" t="s">
-        <v>649</v>
-      </c>
-      <c r="G43" s="129"/>
-      <c r="H43" s="129"/>
-      <c r="I43" s="129"/>
-      <c r="J43" s="129"/>
-      <c r="K43" s="129"/>
-      <c r="L43" s="129"/>
-      <c r="M43" s="129"/>
-    </row>
-    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="60" t="s">
-        <v>650</v>
-      </c>
-      <c r="B45" s="125"/>
-      <c r="C45" s="125"/>
-      <c r="D45" s="125"/>
-      <c r="E45" s="125"/>
-      <c r="F45" s="125"/>
-      <c r="G45" s="125"/>
-      <c r="H45" s="125"/>
-      <c r="I45" s="125"/>
-      <c r="J45" s="125"/>
-      <c r="K45" s="125"/>
-      <c r="L45" s="125"/>
-      <c r="M45" s="125"/>
-    </row>
-    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="126" t="s">
+      <c r="F51" s="129" t="s">
+        <v>657</v>
+      </c>
+      <c r="G51" s="129"/>
+      <c r="H51" s="129"/>
+      <c r="I51" s="129"/>
+      <c r="J51" s="129"/>
+      <c r="K51" s="129"/>
+      <c r="L51" s="129"/>
+      <c r="M51" s="129"/>
+    </row>
+    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A53" s="60" t="s">
+        <v>658</v>
+      </c>
+      <c r="B53" s="125"/>
+      <c r="C53" s="125"/>
+      <c r="D53" s="125"/>
+      <c r="E53" s="125"/>
+      <c r="F53" s="125"/>
+      <c r="G53" s="125"/>
+      <c r="H53" s="125"/>
+      <c r="I53" s="125"/>
+      <c r="J53" s="125"/>
+      <c r="K53" s="125"/>
+      <c r="L53" s="125"/>
+      <c r="M53" s="125"/>
+    </row>
+    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A54" s="126" t="s">
         <v>548</v>
       </c>
-      <c r="B46" s="126" t="s">
+      <c r="B54" s="126" t="s">
         <v>202</v>
       </c>
-      <c r="C46" s="126" t="s">
+      <c r="C54" s="126" t="s">
         <v>549</v>
       </c>
-      <c r="D46" s="126" t="s">
+      <c r="D54" s="126" t="s">
         <v>550</v>
       </c>
-      <c r="E46" s="126" t="s">
+      <c r="E54" s="126" t="s">
         <v>551</v>
       </c>
-      <c r="F46" s="126" t="s">
+      <c r="F54" s="126" t="s">
         <v>552</v>
       </c>
-      <c r="G46" s="126" t="s">
+      <c r="G54" s="126" t="s">
         <v>553</v>
       </c>
-      <c r="H46" s="126" t="s">
+      <c r="H54" s="126" t="s">
         <v>554</v>
       </c>
-      <c r="I46" s="126" t="s">
+      <c r="I54" s="126" t="s">
         <v>555</v>
       </c>
-      <c r="J46" s="126" t="s">
+      <c r="J54" s="126" t="s">
         <v>556</v>
       </c>
-      <c r="K46" s="126" t="s">
+      <c r="K54" s="126" t="s">
         <v>557</v>
       </c>
-      <c r="L46" s="126" t="s">
+      <c r="L54" s="126" t="s">
         <v>558</v>
       </c>
     </row>
-    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="142" t="s">
+    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A55" s="142" t="s">
         <v>559</v>
       </c>
-      <c r="B47" s="143" t="n">
+      <c r="B55" s="143" t="n">
         <v>0</v>
       </c>
-      <c r="C47" s="143" t="n">
+      <c r="C55" s="143" t="n">
         <v>1</v>
       </c>
-      <c r="D47" s="143" t="n">
+      <c r="D55" s="143" t="n">
         <v>2</v>
       </c>
-      <c r="E47" s="143" t="n">
+      <c r="E55" s="143" t="n">
         <v>3</v>
       </c>
-      <c r="F47" s="143" t="n">
+      <c r="F55" s="143" t="n">
         <v>4</v>
       </c>
-      <c r="G47" s="143" t="n">
+      <c r="G55" s="143" t="n">
         <v>5</v>
       </c>
-      <c r="H47" s="143" t="n">
+      <c r="H55" s="143" t="n">
         <v>6</v>
       </c>
-      <c r="I47" s="143" t="n">
+      <c r="I55" s="143" t="n">
         <v>7</v>
       </c>
-      <c r="J47" s="143" t="n">
+      <c r="J55" s="143" t="n">
         <v>8</v>
       </c>
-      <c r="K47" s="143" t="n">
+      <c r="K55" s="143" t="n">
         <v>9</v>
       </c>
-      <c r="L47" s="143" t="n">
+      <c r="L55" s="143" t="n">
         <v>10</v>
       </c>
     </row>
-    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="137" t="s">
+    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A56" s="137" t="s">
         <v>560</v>
       </c>
-      <c r="B48" s="144"/>
-      <c r="C48" s="144"/>
-      <c r="D48" s="144"/>
-      <c r="E48" s="144"/>
-      <c r="F48" s="144"/>
-      <c r="G48" s="144"/>
-      <c r="H48" s="144"/>
-      <c r="I48" s="144"/>
-      <c r="J48" s="144"/>
-      <c r="K48" s="144"/>
-      <c r="L48" s="144"/>
-    </row>
-    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="145" t="s">
-        <v>651</v>
-      </c>
-      <c r="B49" s="158" t="n">
-        <f aca="false">SUMPRODUCT($B$31:$B$37,(1+$H$31:$H$37)^B$47)</f>
-        <v>4100</v>
-      </c>
-      <c r="C49" s="158" t="n">
-        <f aca="false">SUMPRODUCT($B$31:$B$37,(1+$H$31:$H$37)^C$47)</f>
-        <v>4548</v>
-      </c>
-      <c r="D49" s="158" t="n">
-        <f aca="false">SUMPRODUCT($B$31:$B$37,(1+$H$31:$H$37)^D$47)</f>
-        <v>5056.97</v>
-      </c>
-      <c r="E49" s="158" t="n">
-        <f aca="false">SUMPRODUCT($B$31:$B$37,(1+$H$31:$H$37)^E$47)</f>
-        <v>5636.3757</v>
-      </c>
-      <c r="F49" s="158" t="n">
-        <f aca="false">SUMPRODUCT($B$31:$B$37,(1+$H$31:$H$37)^F$47)</f>
-        <v>6297.279503</v>
-      </c>
-      <c r="G49" s="158" t="n">
-        <f aca="false">SUMPRODUCT($B$31:$B$37,(1+$H$31:$H$37)^G$47)</f>
-        <v>7052.62428513</v>
-      </c>
-      <c r="H49" s="158" t="n">
-        <f aca="false">SUMPRODUCT($B$31:$B$37,(1+$H$31:$H$37)^H$47)</f>
-        <v>7917.5692511447</v>
-      </c>
-      <c r="I49" s="158" t="n">
-        <f aca="false">SUMPRODUCT($B$31:$B$37,(1+$H$31:$H$37)^I$47)</f>
-        <v>8909.88762748362</v>
-      </c>
-      <c r="J49" s="158" t="n">
-        <f aca="false">SUMPRODUCT($B$31:$B$37,(1+$H$31:$H$37)^J$47)</f>
-        <v>10050.4377941043</v>
-      </c>
-      <c r="K49" s="158" t="n">
-        <f aca="false">SUMPRODUCT($B$31:$B$37,(1+$H$31:$H$37)^K$47)</f>
-        <v>11363.7216587854</v>
-      </c>
-      <c r="L49" s="158" t="n">
-        <f aca="false">SUMPRODUCT($B$31:$B$37,(1+$H$31:$H$37)^L$47)</f>
-        <v>12878.5467015371</v>
-      </c>
-    </row>
-    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="127" t="s">
-        <v>652</v>
-      </c>
-      <c r="B50" s="130" t="n">
-        <f aca="false">$B$7+(B$42-$B$7)*MIN(B$47/$B$17,1)</f>
-        <v>0.122</v>
-      </c>
-      <c r="C50" s="130" t="n">
-        <f aca="false">$B$7+(B$42-$B$7)*MIN(C$47/$B$17,1)</f>
-        <v>0.1256</v>
-      </c>
-      <c r="D50" s="130" t="n">
-        <f aca="false">$B$7+(B$42-$B$7)*MIN(D$47/$B$17,1)</f>
-        <v>0.1292</v>
-      </c>
-      <c r="E50" s="130" t="n">
-        <f aca="false">$B$7+(B$42-$B$7)*MIN(E$47/$B$17,1)</f>
-        <v>0.1328</v>
-      </c>
-      <c r="F50" s="130" t="n">
-        <f aca="false">$B$7+(B$42-$B$7)*MIN(F$47/$B$17,1)</f>
-        <v>0.1364</v>
-      </c>
-      <c r="G50" s="130" t="n">
-        <f aca="false">$B$7+(B$42-$B$7)*MIN(G$47/$B$17,1)</f>
-        <v>0.14</v>
-      </c>
-      <c r="H50" s="130" t="n">
-        <f aca="false">$B$7+(B$42-$B$7)*MIN(H$47/$B$17,1)</f>
-        <v>0.14</v>
-      </c>
-      <c r="I50" s="130" t="n">
-        <f aca="false">$B$7+(B$42-$B$7)*MIN(I$47/$B$17,1)</f>
-        <v>0.14</v>
-      </c>
-      <c r="J50" s="130" t="n">
-        <f aca="false">$B$7+(B$42-$B$7)*MIN(J$47/$B$17,1)</f>
-        <v>0.14</v>
-      </c>
-      <c r="K50" s="130" t="n">
-        <f aca="false">$B$7+(B$42-$B$7)*MIN(K$47/$B$17,1)</f>
-        <v>0.14</v>
-      </c>
-      <c r="L50" s="130" t="n">
-        <f aca="false">$B$7+(B$42-$B$7)*MIN(L$47/$B$17,1)</f>
-        <v>0.14</v>
-      </c>
-    </row>
-    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="127" t="s">
-        <v>653</v>
-      </c>
-      <c r="B51" s="153" t="n">
-        <f aca="false">B49*B50</f>
-        <v>500.2</v>
-      </c>
-      <c r="C51" s="153" t="n">
-        <f aca="false">C49*C50</f>
-        <v>571.2288</v>
-      </c>
-      <c r="D51" s="153" t="n">
-        <f aca="false">D49*D50</f>
-        <v>653.360524</v>
-      </c>
-      <c r="E51" s="153" t="n">
-        <f aca="false">E49*E50</f>
-        <v>748.51069296</v>
-      </c>
-      <c r="F51" s="153" t="n">
-        <f aca="false">F49*F50</f>
-        <v>858.9489242092</v>
-      </c>
-      <c r="G51" s="153" t="n">
-        <f aca="false">G49*G50</f>
-        <v>987.3673999182</v>
-      </c>
-      <c r="H51" s="153" t="n">
-        <f aca="false">H49*H50</f>
-        <v>1108.45969516026</v>
-      </c>
-      <c r="I51" s="153" t="n">
-        <f aca="false">I49*I50</f>
-        <v>1247.38426784771</v>
-      </c>
-      <c r="J51" s="153" t="n">
-        <f aca="false">J49*J50</f>
-        <v>1407.0612911746</v>
-      </c>
-      <c r="K51" s="153" t="n">
-        <f aca="false">K49*K50</f>
-        <v>1590.92103222995</v>
-      </c>
-      <c r="L51" s="153" t="n">
-        <f aca="false">L49*L50</f>
-        <v>1802.99653821519</v>
-      </c>
-    </row>
-    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="127" t="s">
-        <v>567</v>
-      </c>
-      <c r="B52" s="153" t="n">
-        <f aca="false">$B$13</f>
-        <v>10681.97856</v>
-      </c>
-      <c r="C52" s="153" t="n">
-        <f aca="false">C51*B$43</f>
-        <v>11424.576</v>
-      </c>
-      <c r="D52" s="153" t="n">
-        <f aca="false">D51*B$43</f>
-        <v>13067.21048</v>
-      </c>
-      <c r="E52" s="153" t="n">
-        <f aca="false">E51*B$43</f>
-        <v>14970.2138592</v>
-      </c>
-      <c r="F52" s="153" t="n">
-        <f aca="false">F51*B$43</f>
-        <v>17178.978484184</v>
-      </c>
-      <c r="G52" s="153" t="n">
-        <f aca="false">G51*B$43</f>
-        <v>19747.347998364</v>
-      </c>
-      <c r="H52" s="153" t="n">
-        <f aca="false">H51*B$43</f>
-        <v>22169.1939032052</v>
-      </c>
-      <c r="I52" s="153" t="n">
-        <f aca="false">I51*B$43</f>
-        <v>24947.6853569541</v>
-      </c>
-      <c r="J52" s="153" t="n">
-        <f aca="false">J51*B$43</f>
-        <v>28141.225823492</v>
-      </c>
-      <c r="K52" s="153" t="n">
-        <f aca="false">K51*B$43</f>
-        <v>31818.420644599</v>
-      </c>
-      <c r="L52" s="153" t="n">
-        <f aca="false">L51*B$43</f>
-        <v>36059.9307643038</v>
-      </c>
-    </row>
-    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="145" t="s">
-        <v>654</v>
-      </c>
-      <c r="B53" s="158" t="n">
-        <f aca="false">$B$13</f>
-        <v>10681.97856</v>
-      </c>
-      <c r="C53" s="158" t="n">
-        <f aca="false">C52*(1-$B$16)</f>
-        <v>11081.83872</v>
-      </c>
-      <c r="D53" s="158" t="n">
-        <f aca="false">D52*(1-$B$16)</f>
-        <v>12675.1941656</v>
-      </c>
-      <c r="E53" s="158" t="n">
-        <f aca="false">E52*(1-$B$16)</f>
-        <v>14521.107443424</v>
-      </c>
-      <c r="F53" s="158" t="n">
-        <f aca="false">F52*(1-$B$16)</f>
-        <v>16663.6091296585</v>
-      </c>
-      <c r="G53" s="158" t="n">
-        <f aca="false">G52*(1-$B$16)</f>
-        <v>19154.9275584131</v>
-      </c>
-      <c r="H53" s="158" t="n">
-        <f aca="false">H52*(1-$B$16)</f>
-        <v>21504.118086109</v>
-      </c>
-      <c r="I53" s="158" t="n">
-        <f aca="false">I52*(1-$B$16)</f>
-        <v>24199.2547962455</v>
-      </c>
-      <c r="J53" s="158" t="n">
-        <f aca="false">J52*(1-$B$16)</f>
-        <v>27296.9890487872</v>
-      </c>
-      <c r="K53" s="158" t="n">
-        <f aca="false">K52*(1-$B$16)</f>
-        <v>30863.8680252611</v>
-      </c>
-      <c r="L53" s="158" t="n">
-        <f aca="false">L52*(1-$B$16)</f>
-        <v>34978.1328413747</v>
-      </c>
-    </row>
-    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="137" t="s">
-        <v>569</v>
-      </c>
-      <c r="B55" s="144"/>
-      <c r="C55" s="144"/>
-      <c r="D55" s="144"/>
-      <c r="E55" s="144"/>
-      <c r="F55" s="144"/>
-      <c r="G55" s="144"/>
-      <c r="H55" s="144"/>
-      <c r="I55" s="144"/>
-      <c r="J55" s="144"/>
-      <c r="K55" s="144"/>
-      <c r="L55" s="144"/>
-    </row>
-    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="145" t="s">
-        <v>651</v>
-      </c>
-      <c r="B56" s="158" t="n">
-        <f aca="false">SUMPRODUCT($B$31:$B$37,(1+$I$31:$I$37)^B$47)</f>
-        <v>4100</v>
-      </c>
-      <c r="C56" s="158" t="n">
-        <f aca="false">SUMPRODUCT($B$31:$B$37,(1+$I$31:$I$37)^C$47)</f>
-        <v>4814.5</v>
-      </c>
-      <c r="D56" s="158" t="n">
-        <f aca="false">SUMPRODUCT($B$31:$B$37,(1+$I$31:$I$37)^D$47)</f>
-        <v>5671.345</v>
-      </c>
-      <c r="E56" s="158" t="n">
-        <f aca="false">SUMPRODUCT($B$31:$B$37,(1+$I$31:$I$37)^E$47)</f>
-        <v>6701.30125</v>
-      </c>
-      <c r="F56" s="158" t="n">
-        <f aca="false">SUMPRODUCT($B$31:$B$37,(1+$I$31:$I$37)^F$47)</f>
-        <v>7942.1833825</v>
-      </c>
-      <c r="G56" s="158" t="n">
-        <f aca="false">SUMPRODUCT($B$31:$B$37,(1+$I$31:$I$37)^G$47)</f>
-        <v>9440.543794645</v>
-      </c>
-      <c r="H56" s="158" t="n">
-        <f aca="false">SUMPRODUCT($B$31:$B$37,(1+$I$31:$I$37)^H$47)</f>
-        <v>11253.7814218035</v>
-      </c>
-      <c r="I56" s="158" t="n">
-        <f aca="false">SUMPRODUCT($B$31:$B$37,(1+$I$31:$I$37)^I$47)</f>
-        <v>13452.7768209288</v>
-      </c>
-      <c r="J56" s="158" t="n">
-        <f aca="false">SUMPRODUCT($B$31:$B$37,(1+$I$31:$I$37)^J$47)</f>
-        <v>16125.1882792186</v>
-      </c>
-      <c r="K56" s="158" t="n">
-        <f aca="false">SUMPRODUCT($B$31:$B$37,(1+$I$31:$I$37)^K$47)</f>
-        <v>19379.5787915447</v>
-      </c>
-      <c r="L56" s="158" t="n">
-        <f aca="false">SUMPRODUCT($B$31:$B$37,(1+$I$31:$I$37)^L$47)</f>
-        <v>23350.5881624233</v>
-      </c>
+      <c r="B56" s="144"/>
+      <c r="C56" s="144"/>
+      <c r="D56" s="144"/>
+      <c r="E56" s="144"/>
+      <c r="F56" s="144"/>
+      <c r="G56" s="144"/>
+      <c r="H56" s="144"/>
+      <c r="I56" s="144"/>
+      <c r="J56" s="144"/>
+      <c r="K56" s="144"/>
+      <c r="L56" s="144"/>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="127" t="s">
-        <v>652</v>
-      </c>
-      <c r="B57" s="130" t="n">
-        <f aca="false">$B$7+(C$42-$B$7)*MIN(B$47/$B$17,1)</f>
-        <v>0.122</v>
-      </c>
-      <c r="C57" s="130" t="n">
-        <f aca="false">$B$7+(C$42-$B$7)*MIN(C$47/$B$17,1)</f>
-        <v>0.1296</v>
-      </c>
-      <c r="D57" s="130" t="n">
-        <f aca="false">$B$7+(C$42-$B$7)*MIN(D$47/$B$17,1)</f>
-        <v>0.1372</v>
-      </c>
-      <c r="E57" s="130" t="n">
-        <f aca="false">$B$7+(C$42-$B$7)*MIN(E$47/$B$17,1)</f>
-        <v>0.1448</v>
-      </c>
-      <c r="F57" s="130" t="n">
-        <f aca="false">$B$7+(C$42-$B$7)*MIN(F$47/$B$17,1)</f>
-        <v>0.1524</v>
-      </c>
-      <c r="G57" s="130" t="n">
-        <f aca="false">$B$7+(C$42-$B$7)*MIN(G$47/$B$17,1)</f>
-        <v>0.16</v>
-      </c>
-      <c r="H57" s="130" t="n">
-        <f aca="false">$B$7+(C$42-$B$7)*MIN(H$47/$B$17,1)</f>
-        <v>0.16</v>
-      </c>
-      <c r="I57" s="130" t="n">
-        <f aca="false">$B$7+(C$42-$B$7)*MIN(I$47/$B$17,1)</f>
-        <v>0.16</v>
-      </c>
-      <c r="J57" s="130" t="n">
-        <f aca="false">$B$7+(C$42-$B$7)*MIN(J$47/$B$17,1)</f>
-        <v>0.16</v>
-      </c>
-      <c r="K57" s="130" t="n">
-        <f aca="false">$B$7+(C$42-$B$7)*MIN(K$47/$B$17,1)</f>
-        <v>0.16</v>
-      </c>
-      <c r="L57" s="130" t="n">
-        <f aca="false">$B$7+(C$42-$B$7)*MIN(L$47/$B$17,1)</f>
-        <v>0.16</v>
+        <v>659</v>
+      </c>
+      <c r="B57" s="153" t="n">
+        <f aca="false">SUMPRODUCT($B$32:$B$39,(1+$H$32:$H$39)^B$55)</f>
+        <v>4100</v>
+      </c>
+      <c r="C57" s="153" t="n">
+        <f aca="false">SUMPRODUCT($B$32:$B$39,(1+$H$32:$H$39)^C$55)</f>
+        <v>4569</v>
+      </c>
+      <c r="D57" s="153" t="n">
+        <f aca="false">SUMPRODUCT($B$32:$B$39,(1+$H$32:$H$39)^D$55)</f>
+        <v>5103.8</v>
+      </c>
+      <c r="E57" s="153" t="n">
+        <f aca="false">SUMPRODUCT($B$32:$B$39,(1+$H$32:$H$39)^E$55)</f>
+        <v>5714.7246</v>
+      </c>
+      <c r="F57" s="153" t="n">
+        <f aca="false">SUMPRODUCT($B$32:$B$39,(1+$H$32:$H$39)^F$55)</f>
+        <v>6413.83469</v>
+      </c>
+      <c r="G57" s="153" t="n">
+        <f aca="false">SUMPRODUCT($B$32:$B$39,(1+$H$32:$H$39)^G$55)</f>
+        <v>7215.23301834</v>
+      </c>
+      <c r="H57" s="153" t="n">
+        <f aca="false">SUMPRODUCT($B$32:$B$39,(1+$H$32:$H$39)^H$55)</f>
+        <v>8135.425183949</v>
+      </c>
+      <c r="I57" s="153" t="n">
+        <f aca="false">SUMPRODUCT($B$32:$B$39,(1+$H$32:$H$39)^I$55)</f>
+        <v>9193.74631099039</v>
+      </c>
+      <c r="J57" s="153" t="n">
+        <f aca="false">SUMPRODUCT($B$32:$B$39,(1+$H$32:$H$39)^J$55)</f>
+        <v>10412.8655897814</v>
+      </c>
+      <c r="K57" s="153" t="n">
+        <f aca="false">SUMPRODUCT($B$32:$B$39,(1+$H$32:$H$39)^K$55)</f>
+        <v>11819.38315823</v>
+      </c>
+      <c r="L57" s="153" t="n">
+        <f aca="false">SUMPRODUCT($B$32:$B$39,(1+$H$32:$H$39)^L$55)</f>
+        <v>13444.5365230676</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="127" t="s">
-        <v>653</v>
+        <v>660</v>
       </c>
       <c r="B58" s="153" t="n">
-        <f aca="false">B56*B57</f>
+        <f aca="false">B$45*MIN(MAX(B$55-B$44+1,0)/B$46,1)</f>
+        <v>0</v>
+      </c>
+      <c r="C58" s="153" t="n">
+        <f aca="false">B$45*MIN(MAX(C$55-B$44+1,0)/B$46,1)</f>
+        <v>0</v>
+      </c>
+      <c r="D58" s="153" t="n">
+        <f aca="false">B$45*MIN(MAX(D$55-B$44+1,0)/B$46,1)</f>
+        <v>0</v>
+      </c>
+      <c r="E58" s="153" t="n">
+        <f aca="false">B$45*MIN(MAX(E$55-B$44+1,0)/B$46,1)</f>
+        <v>0</v>
+      </c>
+      <c r="F58" s="153" t="n">
+        <f aca="false">B$45*MIN(MAX(F$55-B$44+1,0)/B$46,1)</f>
+        <v>133.333333333333</v>
+      </c>
+      <c r="G58" s="153" t="n">
+        <f aca="false">B$45*MIN(MAX(G$55-B$44+1,0)/B$46,1)</f>
+        <v>266.666666666667</v>
+      </c>
+      <c r="H58" s="153" t="n">
+        <f aca="false">B$45*MIN(MAX(H$55-B$44+1,0)/B$46,1)</f>
+        <v>400</v>
+      </c>
+      <c r="I58" s="153" t="n">
+        <f aca="false">B$45*MIN(MAX(I$55-B$44+1,0)/B$46,1)</f>
+        <v>400</v>
+      </c>
+      <c r="J58" s="153" t="n">
+        <f aca="false">B$45*MIN(MAX(J$55-B$44+1,0)/B$46,1)</f>
+        <v>400</v>
+      </c>
+      <c r="K58" s="153" t="n">
+        <f aca="false">B$45*MIN(MAX(K$55-B$44+1,0)/B$46,1)</f>
+        <v>400</v>
+      </c>
+      <c r="L58" s="153" t="n">
+        <f aca="false">B$45*MIN(MAX(L$55-B$44+1,0)/B$46,1)</f>
+        <v>400</v>
+      </c>
+    </row>
+    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A59" s="145" t="s">
+        <v>563</v>
+      </c>
+      <c r="B59" s="158" t="n">
+        <f aca="false">B57+B58</f>
+        <v>4100</v>
+      </c>
+      <c r="C59" s="158" t="n">
+        <f aca="false">C57+C58</f>
+        <v>4569</v>
+      </c>
+      <c r="D59" s="158" t="n">
+        <f aca="false">D57+D58</f>
+        <v>5103.8</v>
+      </c>
+      <c r="E59" s="158" t="n">
+        <f aca="false">E57+E58</f>
+        <v>5714.7246</v>
+      </c>
+      <c r="F59" s="158" t="n">
+        <f aca="false">F57+F58</f>
+        <v>6547.16802333333</v>
+      </c>
+      <c r="G59" s="158" t="n">
+        <f aca="false">G57+G58</f>
+        <v>7481.89968500667</v>
+      </c>
+      <c r="H59" s="158" t="n">
+        <f aca="false">H57+H58</f>
+        <v>8535.425183949</v>
+      </c>
+      <c r="I59" s="158" t="n">
+        <f aca="false">I57+I58</f>
+        <v>9593.74631099039</v>
+      </c>
+      <c r="J59" s="158" t="n">
+        <f aca="false">J57+J58</f>
+        <v>10812.8655897814</v>
+      </c>
+      <c r="K59" s="158" t="n">
+        <f aca="false">K57+K58</f>
+        <v>12219.38315823</v>
+      </c>
+      <c r="L59" s="158" t="n">
+        <f aca="false">L57+L58</f>
+        <v>13844.5365230676</v>
+      </c>
+    </row>
+    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A60" s="127" t="s">
+        <v>661</v>
+      </c>
+      <c r="B60" s="130" t="n">
+        <f aca="false">$B$7+(B$50-$B$7)*MIN(B$55/$B$17,1)</f>
+        <v>0.122</v>
+      </c>
+      <c r="C60" s="130" t="n">
+        <f aca="false">$B$7+(B$50-$B$7)*MIN(C$55/$B$17,1)</f>
+        <v>0.1256</v>
+      </c>
+      <c r="D60" s="130" t="n">
+        <f aca="false">$B$7+(B$50-$B$7)*MIN(D$55/$B$17,1)</f>
+        <v>0.1292</v>
+      </c>
+      <c r="E60" s="130" t="n">
+        <f aca="false">$B$7+(B$50-$B$7)*MIN(E$55/$B$17,1)</f>
+        <v>0.1328</v>
+      </c>
+      <c r="F60" s="130" t="n">
+        <f aca="false">$B$7+(B$50-$B$7)*MIN(F$55/$B$17,1)</f>
+        <v>0.1364</v>
+      </c>
+      <c r="G60" s="130" t="n">
+        <f aca="false">$B$7+(B$50-$B$7)*MIN(G$55/$B$17,1)</f>
+        <v>0.14</v>
+      </c>
+      <c r="H60" s="130" t="n">
+        <f aca="false">$B$7+(B$50-$B$7)*MIN(H$55/$B$17,1)</f>
+        <v>0.14</v>
+      </c>
+      <c r="I60" s="130" t="n">
+        <f aca="false">$B$7+(B$50-$B$7)*MIN(I$55/$B$17,1)</f>
+        <v>0.14</v>
+      </c>
+      <c r="J60" s="130" t="n">
+        <f aca="false">$B$7+(B$50-$B$7)*MIN(J$55/$B$17,1)</f>
+        <v>0.14</v>
+      </c>
+      <c r="K60" s="130" t="n">
+        <f aca="false">$B$7+(B$50-$B$7)*MIN(K$55/$B$17,1)</f>
+        <v>0.14</v>
+      </c>
+      <c r="L60" s="130" t="n">
+        <f aca="false">$B$7+(B$50-$B$7)*MIN(L$55/$B$17,1)</f>
+        <v>0.14</v>
+      </c>
+    </row>
+    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A61" s="127" t="s">
+        <v>662</v>
+      </c>
+      <c r="B61" s="153" t="n">
+        <f aca="false">B59*B60</f>
         <v>500.2</v>
       </c>
-      <c r="C58" s="153" t="n">
-        <f aca="false">C56*C57</f>
-        <v>623.9592</v>
-      </c>
-      <c r="D58" s="153" t="n">
-        <f aca="false">D56*D57</f>
-        <v>778.108534</v>
-      </c>
-      <c r="E58" s="153" t="n">
-        <f aca="false">E56*E57</f>
-        <v>970.348421</v>
-      </c>
-      <c r="F58" s="153" t="n">
-        <f aca="false">F56*F57</f>
-        <v>1210.388747493</v>
-      </c>
-      <c r="G58" s="153" t="n">
-        <f aca="false">G56*G57</f>
-        <v>1510.4870071432</v>
-      </c>
-      <c r="H58" s="153" t="n">
-        <f aca="false">H56*H57</f>
-        <v>1800.60502748855</v>
-      </c>
-      <c r="I58" s="153" t="n">
-        <f aca="false">I56*I57</f>
-        <v>2152.4442913486</v>
-      </c>
-      <c r="J58" s="153" t="n">
-        <f aca="false">J56*J57</f>
-        <v>2580.03012467497</v>
-      </c>
-      <c r="K58" s="153" t="n">
-        <f aca="false">K56*K57</f>
-        <v>3100.73260664715</v>
-      </c>
-      <c r="L58" s="153" t="n">
-        <f aca="false">L56*L57</f>
-        <v>3736.09410598774</v>
-      </c>
-    </row>
-    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A59" s="127" t="s">
+      <c r="C61" s="153" t="n">
+        <f aca="false">C59*C60</f>
+        <v>573.8664</v>
+      </c>
+      <c r="D61" s="153" t="n">
+        <f aca="false">D59*D60</f>
+        <v>659.41096</v>
+      </c>
+      <c r="E61" s="153" t="n">
+        <f aca="false">E59*E60</f>
+        <v>758.91542688</v>
+      </c>
+      <c r="F61" s="153" t="n">
+        <f aca="false">F59*F60</f>
+        <v>893.033718382667</v>
+      </c>
+      <c r="G61" s="153" t="n">
+        <f aca="false">G59*G60</f>
+        <v>1047.46595590093</v>
+      </c>
+      <c r="H61" s="153" t="n">
+        <f aca="false">H59*H60</f>
+        <v>1194.95952575286</v>
+      </c>
+      <c r="I61" s="153" t="n">
+        <f aca="false">I59*I60</f>
+        <v>1343.12448353865</v>
+      </c>
+      <c r="J61" s="153" t="n">
+        <f aca="false">J59*J60</f>
+        <v>1513.8011825694</v>
+      </c>
+      <c r="K61" s="153" t="n">
+        <f aca="false">K59*K60</f>
+        <v>1710.7136421522</v>
+      </c>
+      <c r="L61" s="153" t="n">
+        <f aca="false">L59*L60</f>
+        <v>1938.23511322946</v>
+      </c>
+    </row>
+    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A62" s="127" t="s">
         <v>567</v>
       </c>
-      <c r="B59" s="153" t="n">
+      <c r="B62" s="153" t="n">
         <f aca="false">$B$13</f>
-        <v>10681.97856</v>
-      </c>
-      <c r="C59" s="153" t="n">
-        <f aca="false">C58*C$43</f>
-        <v>14975.0208</v>
-      </c>
-      <c r="D59" s="153" t="n">
-        <f aca="false">D58*C$43</f>
-        <v>18674.604816</v>
-      </c>
-      <c r="E59" s="153" t="n">
-        <f aca="false">E58*C$43</f>
-        <v>23288.362104</v>
-      </c>
-      <c r="F59" s="153" t="n">
-        <f aca="false">F58*C$43</f>
-        <v>29049.329939832</v>
-      </c>
-      <c r="G59" s="153" t="n">
-        <f aca="false">G58*C$43</f>
-        <v>36251.6881714368</v>
-      </c>
-      <c r="H59" s="153" t="n">
-        <f aca="false">H58*C$43</f>
-        <v>43214.5206597253</v>
-      </c>
-      <c r="I59" s="153" t="n">
-        <f aca="false">I58*C$43</f>
-        <v>51658.6629923665</v>
-      </c>
-      <c r="J59" s="153" t="n">
-        <f aca="false">J58*C$43</f>
-        <v>61920.7229921994</v>
-      </c>
-      <c r="K59" s="153" t="n">
-        <f aca="false">K58*C$43</f>
-        <v>74417.5825595316</v>
-      </c>
-      <c r="L59" s="153" t="n">
-        <f aca="false">L58*C$43</f>
-        <v>89666.2585437057</v>
-      </c>
-    </row>
-    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A60" s="145" t="s">
-        <v>654</v>
-      </c>
-      <c r="B60" s="158" t="n">
-        <f aca="false">$B$13</f>
-        <v>10681.97856</v>
-      </c>
-      <c r="C60" s="158" t="n">
-        <f aca="false">C59*(1-$B$16)</f>
-        <v>14525.770176</v>
-      </c>
-      <c r="D60" s="158" t="n">
-        <f aca="false">D59*(1-$B$16)</f>
-        <v>18114.36667152</v>
-      </c>
-      <c r="E60" s="158" t="n">
-        <f aca="false">E59*(1-$B$16)</f>
-        <v>22589.71124088</v>
-      </c>
-      <c r="F60" s="158" t="n">
-        <f aca="false">F59*(1-$B$16)</f>
-        <v>28177.850041637</v>
-      </c>
-      <c r="G60" s="158" t="n">
-        <f aca="false">G59*(1-$B$16)</f>
-        <v>35164.1375262937</v>
-      </c>
-      <c r="H60" s="158" t="n">
-        <f aca="false">H59*(1-$B$16)</f>
-        <v>41918.0850399335</v>
-      </c>
-      <c r="I60" s="158" t="n">
-        <f aca="false">I59*(1-$B$16)</f>
-        <v>50108.9031025955</v>
-      </c>
-      <c r="J60" s="158" t="n">
-        <f aca="false">J59*(1-$B$16)</f>
-        <v>60063.1013024334</v>
-      </c>
-      <c r="K60" s="158" t="n">
-        <f aca="false">K59*(1-$B$16)</f>
-        <v>72185.0550827456</v>
-      </c>
-      <c r="L60" s="158" t="n">
-        <f aca="false">L59*(1-$B$16)</f>
-        <v>86976.2707873945</v>
-      </c>
-    </row>
-    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A62" s="137" t="s">
-        <v>570</v>
-      </c>
-      <c r="B62" s="144"/>
-      <c r="C62" s="144"/>
-      <c r="D62" s="144"/>
-      <c r="E62" s="144"/>
-      <c r="F62" s="144"/>
-      <c r="G62" s="144"/>
-      <c r="H62" s="144"/>
-      <c r="I62" s="144"/>
-      <c r="J62" s="144"/>
-      <c r="K62" s="144"/>
-      <c r="L62" s="144"/>
+        <v>10731.30168</v>
+      </c>
+      <c r="C62" s="153" t="n">
+        <f aca="false">C61*B$51</f>
+        <v>11477.328</v>
+      </c>
+      <c r="D62" s="153" t="n">
+        <f aca="false">D61*B$51</f>
+        <v>13188.2192</v>
+      </c>
+      <c r="E62" s="153" t="n">
+        <f aca="false">E61*B$51</f>
+        <v>15178.3085376</v>
+      </c>
+      <c r="F62" s="153" t="n">
+        <f aca="false">F61*B$51</f>
+        <v>17860.6743676533</v>
+      </c>
+      <c r="G62" s="153" t="n">
+        <f aca="false">G61*B$51</f>
+        <v>20949.3191180187</v>
+      </c>
+      <c r="H62" s="153" t="n">
+        <f aca="false">H61*B$51</f>
+        <v>23899.1905150572</v>
+      </c>
+      <c r="I62" s="153" t="n">
+        <f aca="false">I61*B$51</f>
+        <v>26862.4896707731</v>
+      </c>
+      <c r="J62" s="153" t="n">
+        <f aca="false">J61*B$51</f>
+        <v>30276.023651388</v>
+      </c>
+      <c r="K62" s="153" t="n">
+        <f aca="false">K61*B$51</f>
+        <v>34214.2728430441</v>
+      </c>
+      <c r="L62" s="153" t="n">
+        <f aca="false">L61*B$51</f>
+        <v>38764.7022645893</v>
+      </c>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="145" t="s">
-        <v>651</v>
+        <v>663</v>
       </c>
       <c r="B63" s="158" t="n">
-        <f aca="false">SUMPRODUCT($B$31:$B$37,(1+$J$31:$J$37)^B$47)</f>
-        <v>4100</v>
+        <f aca="false">$B$13</f>
+        <v>10731.30168</v>
       </c>
       <c r="C63" s="158" t="n">
-        <f aca="false">SUMPRODUCT($B$31:$B$37,(1+$J$31:$J$37)^C$47)</f>
-        <v>4158.5</v>
+        <f aca="false">C62*(1-$B$16)</f>
+        <v>11133.00816</v>
       </c>
       <c r="D63" s="158" t="n">
-        <f aca="false">SUMPRODUCT($B$31:$B$37,(1+$J$31:$J$37)^D$47)</f>
-        <v>4220.485</v>
+        <f aca="false">D62*(1-$B$16)</f>
+        <v>12792.572624</v>
       </c>
       <c r="E63" s="158" t="n">
-        <f aca="false">SUMPRODUCT($B$31:$B$37,(1+$J$31:$J$37)^E$47)</f>
-        <v>4286.10605</v>
+        <f aca="false">E62*(1-$B$16)</f>
+        <v>14722.959281472</v>
       </c>
       <c r="F63" s="158" t="n">
-        <f aca="false">SUMPRODUCT($B$31:$B$37,(1+$J$31:$J$37)^F$47)</f>
-        <v>4355.5223605</v>
+        <f aca="false">F62*(1-$B$16)</f>
+        <v>17324.8541366237</v>
       </c>
       <c r="G63" s="158" t="n">
-        <f aca="false">SUMPRODUCT($B$31:$B$37,(1+$J$31:$J$37)^G$47)</f>
-        <v>4428.901724285</v>
+        <f aca="false">G62*(1-$B$16)</f>
+        <v>20320.8395444781</v>
       </c>
       <c r="H63" s="158" t="n">
-        <f aca="false">SUMPRODUCT($B$31:$B$37,(1+$J$31:$J$37)^H$47)</f>
-        <v>4506.42096092485</v>
+        <f aca="false">H62*(1-$B$16)</f>
+        <v>23182.2147996055</v>
       </c>
       <c r="I63" s="158" t="n">
-        <f aca="false">SUMPRODUCT($B$31:$B$37,(1+$J$31:$J$37)^I$47)</f>
-        <v>4588.26638521314</v>
+        <f aca="false">I62*(1-$B$16)</f>
+        <v>26056.6149806499</v>
       </c>
       <c r="J63" s="158" t="n">
-        <f aca="false">SUMPRODUCT($B$31:$B$37,(1+$J$31:$J$37)^J$47)</f>
-        <v>4674.63430083616</v>
+        <f aca="false">J62*(1-$B$16)</f>
+        <v>29367.7429418464</v>
       </c>
       <c r="K63" s="158" t="n">
-        <f aca="false">SUMPRODUCT($B$31:$B$37,(1+$J$31:$J$37)^K$47)</f>
-        <v>4765.73152063346</v>
+        <f aca="false">K62*(1-$B$16)</f>
+        <v>33187.8446577527</v>
       </c>
       <c r="L63" s="158" t="n">
-        <f aca="false">SUMPRODUCT($B$31:$B$37,(1+$J$31:$J$37)^L$47)</f>
-        <v>4861.77591488596</v>
-      </c>
-    </row>
-    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A64" s="127" t="s">
-        <v>652</v>
-      </c>
-      <c r="B64" s="130" t="n">
-        <f aca="false">$B$7+(D$42-$B$7)*MIN(B$47/$B$17,1)</f>
-        <v>0.122</v>
-      </c>
-      <c r="C64" s="130" t="n">
-        <f aca="false">$B$7+(D$42-$B$7)*MIN(C$47/$B$17,1)</f>
-        <v>0.1196</v>
-      </c>
-      <c r="D64" s="130" t="n">
-        <f aca="false">$B$7+(D$42-$B$7)*MIN(D$47/$B$17,1)</f>
-        <v>0.1172</v>
-      </c>
-      <c r="E64" s="130" t="n">
-        <f aca="false">$B$7+(D$42-$B$7)*MIN(E$47/$B$17,1)</f>
-        <v>0.1148</v>
-      </c>
-      <c r="F64" s="130" t="n">
-        <f aca="false">$B$7+(D$42-$B$7)*MIN(F$47/$B$17,1)</f>
-        <v>0.1124</v>
-      </c>
-      <c r="G64" s="130" t="n">
-        <f aca="false">$B$7+(D$42-$B$7)*MIN(G$47/$B$17,1)</f>
-        <v>0.11</v>
-      </c>
-      <c r="H64" s="130" t="n">
-        <f aca="false">$B$7+(D$42-$B$7)*MIN(H$47/$B$17,1)</f>
-        <v>0.11</v>
-      </c>
-      <c r="I64" s="130" t="n">
-        <f aca="false">$B$7+(D$42-$B$7)*MIN(I$47/$B$17,1)</f>
-        <v>0.11</v>
-      </c>
-      <c r="J64" s="130" t="n">
-        <f aca="false">$B$7+(D$42-$B$7)*MIN(J$47/$B$17,1)</f>
-        <v>0.11</v>
-      </c>
-      <c r="K64" s="130" t="n">
-        <f aca="false">$B$7+(D$42-$B$7)*MIN(K$47/$B$17,1)</f>
-        <v>0.11</v>
-      </c>
-      <c r="L64" s="130" t="n">
-        <f aca="false">$B$7+(D$42-$B$7)*MIN(L$47/$B$17,1)</f>
-        <v>0.11</v>
+        <f aca="false">L62*(1-$B$16)</f>
+        <v>37601.7611966516</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A65" s="127" t="s">
-        <v>653</v>
-      </c>
-      <c r="B65" s="153" t="n">
-        <f aca="false">B63*B64</f>
-        <v>500.2</v>
-      </c>
-      <c r="C65" s="153" t="n">
-        <f aca="false">C63*C64</f>
-        <v>497.3566</v>
-      </c>
-      <c r="D65" s="153" t="n">
-        <f aca="false">D63*D64</f>
-        <v>494.640842</v>
-      </c>
-      <c r="E65" s="153" t="n">
-        <f aca="false">E63*E64</f>
-        <v>492.04497454</v>
-      </c>
-      <c r="F65" s="153" t="n">
-        <f aca="false">F63*F64</f>
-        <v>489.5607133202</v>
-      </c>
-      <c r="G65" s="153" t="n">
-        <f aca="false">G63*G64</f>
-        <v>487.17918967135</v>
-      </c>
-      <c r="H65" s="153" t="n">
-        <f aca="false">H63*H64</f>
-        <v>495.706305701734</v>
-      </c>
-      <c r="I65" s="153" t="n">
-        <f aca="false">I63*I64</f>
-        <v>504.709302373446</v>
-      </c>
-      <c r="J65" s="153" t="n">
-        <f aca="false">J63*J64</f>
-        <v>514.209773091978</v>
-      </c>
-      <c r="K65" s="153" t="n">
-        <f aca="false">K63*K64</f>
-        <v>524.230467269681</v>
-      </c>
-      <c r="L65" s="153" t="n">
-        <f aca="false">L63*L64</f>
-        <v>534.795350637456</v>
-      </c>
+      <c r="A65" s="137" t="s">
+        <v>569</v>
+      </c>
+      <c r="B65" s="144"/>
+      <c r="C65" s="144"/>
+      <c r="D65" s="144"/>
+      <c r="E65" s="144"/>
+      <c r="F65" s="144"/>
+      <c r="G65" s="144"/>
+      <c r="H65" s="144"/>
+      <c r="I65" s="144"/>
+      <c r="J65" s="144"/>
+      <c r="K65" s="144"/>
+      <c r="L65" s="144"/>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="127" t="s">
-        <v>567</v>
+        <v>659</v>
       </c>
       <c r="B66" s="153" t="n">
-        <f aca="false">$B$13</f>
-        <v>10681.97856</v>
+        <f aca="false">SUMPRODUCT($B$32:$B$39,(1+$I$32:$I$39)^B$55)</f>
+        <v>4100</v>
       </c>
       <c r="C66" s="153" t="n">
-        <f aca="false">C65*D$43</f>
-        <v>6962.9924</v>
+        <f aca="false">SUMPRODUCT($B$32:$B$39,(1+$I$32:$I$39)^C$55)</f>
+        <v>4847.5</v>
       </c>
       <c r="D66" s="153" t="n">
-        <f aca="false">D65*D$43</f>
-        <v>6924.971788</v>
+        <f aca="false">SUMPRODUCT($B$32:$B$39,(1+$I$32:$I$39)^D$55)</f>
+        <v>5751.535</v>
       </c>
       <c r="E66" s="153" t="n">
-        <f aca="false">E65*D$43</f>
-        <v>6888.62964356</v>
+        <f aca="false">SUMPRODUCT($B$32:$B$39,(1+$I$32:$I$39)^E$55)</f>
+        <v>6847.54735</v>
       </c>
       <c r="F66" s="153" t="n">
-        <f aca="false">F65*D$43</f>
-        <v>6853.8499864828</v>
+        <f aca="false">SUMPRODUCT($B$32:$B$39,(1+$I$32:$I$39)^F$55)</f>
+        <v>8179.4254975</v>
       </c>
       <c r="G66" s="153" t="n">
-        <f aca="false">G65*D$43</f>
-        <v>6820.5086553989</v>
+        <f aca="false">SUMPRODUCT($B$32:$B$39,(1+$I$32:$I$39)^G$55)</f>
+        <v>9801.592379575</v>
       </c>
       <c r="H66" s="153" t="n">
-        <f aca="false">H65*D$43</f>
-        <v>6939.88827982427</v>
+        <f aca="false">SUMPRODUCT($B$32:$B$39,(1+$I$32:$I$39)^H$55)</f>
+        <v>11781.6243993654</v>
       </c>
       <c r="I66" s="153" t="n">
-        <f aca="false">I65*D$43</f>
-        <v>7065.93023322824</v>
+        <f aca="false">SUMPRODUCT($B$32:$B$39,(1+$I$32:$I$39)^I$55)</f>
+        <v>14203.5384810853</v>
       </c>
       <c r="J66" s="153" t="n">
-        <f aca="false">J65*D$43</f>
-        <v>7198.93682328769</v>
+        <f aca="false">SUMPRODUCT($B$32:$B$39,(1+$I$32:$I$39)^J$55)</f>
+        <v>17171.9208388548</v>
       </c>
       <c r="K66" s="153" t="n">
-        <f aca="false">K65*D$43</f>
-        <v>7339.22654177553</v>
+        <f aca="false">SUMPRODUCT($B$32:$B$39,(1+$I$32:$I$39)^K$55)</f>
+        <v>20817.116833718</v>
       </c>
       <c r="L66" s="153" t="n">
-        <f aca="false">L65*D$43</f>
-        <v>7487.13490892438</v>
+        <f aca="false">SUMPRODUCT($B$32:$B$39,(1+$I$32:$I$39)^L$55)</f>
+        <v>25301.7591980486</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A67" s="145" t="s">
-        <v>654</v>
-      </c>
-      <c r="B67" s="158" t="n">
-        <f aca="false">$B$13</f>
-        <v>10681.97856</v>
-      </c>
-      <c r="C67" s="158" t="n">
-        <f aca="false">C66*(1-$B$16)</f>
-        <v>6754.102628</v>
-      </c>
-      <c r="D67" s="158" t="n">
-        <f aca="false">D66*(1-$B$16)</f>
-        <v>6717.22263436</v>
-      </c>
-      <c r="E67" s="158" t="n">
-        <f aca="false">E66*(1-$B$16)</f>
-        <v>6681.9707542532</v>
-      </c>
-      <c r="F67" s="158" t="n">
-        <f aca="false">F66*(1-$B$16)</f>
-        <v>6648.23448688832</v>
-      </c>
-      <c r="G67" s="158" t="n">
-        <f aca="false">G66*(1-$B$16)</f>
-        <v>6615.89339573693</v>
-      </c>
-      <c r="H67" s="158" t="n">
-        <f aca="false">H66*(1-$B$16)</f>
-        <v>6731.69163142954</v>
-      </c>
-      <c r="I67" s="158" t="n">
-        <f aca="false">I66*(1-$B$16)</f>
-        <v>6853.95232623139</v>
-      </c>
-      <c r="J67" s="158" t="n">
-        <f aca="false">J66*(1-$B$16)</f>
-        <v>6982.96871858906</v>
-      </c>
-      <c r="K67" s="158" t="n">
-        <f aca="false">K66*(1-$B$16)</f>
-        <v>7119.04974552227</v>
-      </c>
-      <c r="L67" s="158" t="n">
-        <f aca="false">L66*(1-$B$16)</f>
-        <v>7262.52086165665</v>
+      <c r="A67" s="127" t="s">
+        <v>660</v>
+      </c>
+      <c r="B67" s="153" t="n">
+        <f aca="false">C$45*MIN(MAX(B$55-C$44+1,0)/C$46,1)</f>
+        <v>0</v>
+      </c>
+      <c r="C67" s="153" t="n">
+        <f aca="false">C$45*MIN(MAX(C$55-C$44+1,0)/C$46,1)</f>
+        <v>0</v>
+      </c>
+      <c r="D67" s="153" t="n">
+        <f aca="false">C$45*MIN(MAX(D$55-C$44+1,0)/C$46,1)</f>
+        <v>0</v>
+      </c>
+      <c r="E67" s="153" t="n">
+        <f aca="false">C$45*MIN(MAX(E$55-C$44+1,0)/C$46,1)</f>
+        <v>300</v>
+      </c>
+      <c r="F67" s="153" t="n">
+        <f aca="false">C$45*MIN(MAX(F$55-C$44+1,0)/C$46,1)</f>
+        <v>600</v>
+      </c>
+      <c r="G67" s="153" t="n">
+        <f aca="false">C$45*MIN(MAX(G$55-C$44+1,0)/C$46,1)</f>
+        <v>900</v>
+      </c>
+      <c r="H67" s="153" t="n">
+        <f aca="false">C$45*MIN(MAX(H$55-C$44+1,0)/C$46,1)</f>
+        <v>900</v>
+      </c>
+      <c r="I67" s="153" t="n">
+        <f aca="false">C$45*MIN(MAX(I$55-C$44+1,0)/C$46,1)</f>
+        <v>900</v>
+      </c>
+      <c r="J67" s="153" t="n">
+        <f aca="false">C$45*MIN(MAX(J$55-C$44+1,0)/C$46,1)</f>
+        <v>900</v>
+      </c>
+      <c r="K67" s="153" t="n">
+        <f aca="false">C$45*MIN(MAX(K$55-C$44+1,0)/C$46,1)</f>
+        <v>900</v>
+      </c>
+      <c r="L67" s="153" t="n">
+        <f aca="false">C$45*MIN(MAX(L$55-C$44+1,0)/C$46,1)</f>
+        <v>900</v>
+      </c>
+    </row>
+    <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A68" s="145" t="s">
+        <v>563</v>
+      </c>
+      <c r="B68" s="158" t="n">
+        <f aca="false">B66+B67</f>
+        <v>4100</v>
+      </c>
+      <c r="C68" s="158" t="n">
+        <f aca="false">C66+C67</f>
+        <v>4847.5</v>
+      </c>
+      <c r="D68" s="158" t="n">
+        <f aca="false">D66+D67</f>
+        <v>5751.535</v>
+      </c>
+      <c r="E68" s="158" t="n">
+        <f aca="false">E66+E67</f>
+        <v>7147.54735</v>
+      </c>
+      <c r="F68" s="158" t="n">
+        <f aca="false">F66+F67</f>
+        <v>8779.4254975</v>
+      </c>
+      <c r="G68" s="158" t="n">
+        <f aca="false">G66+G67</f>
+        <v>10701.592379575</v>
+      </c>
+      <c r="H68" s="158" t="n">
+        <f aca="false">H66+H67</f>
+        <v>12681.6243993654</v>
+      </c>
+      <c r="I68" s="158" t="n">
+        <f aca="false">I66+I67</f>
+        <v>15103.5384810853</v>
+      </c>
+      <c r="J68" s="158" t="n">
+        <f aca="false">J66+J67</f>
+        <v>18071.9208388548</v>
+      </c>
+      <c r="K68" s="158" t="n">
+        <f aca="false">K66+K67</f>
+        <v>21717.116833718</v>
+      </c>
+      <c r="L68" s="158" t="n">
+        <f aca="false">L66+L67</f>
+        <v>26201.7591980486</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A69" s="137" t="s">
-        <v>571</v>
-      </c>
-      <c r="B69" s="144"/>
-      <c r="C69" s="144"/>
-      <c r="D69" s="144"/>
-      <c r="E69" s="144"/>
-      <c r="F69" s="144"/>
-      <c r="G69" s="144"/>
-      <c r="H69" s="144"/>
-      <c r="I69" s="144"/>
-      <c r="J69" s="144"/>
-      <c r="K69" s="144"/>
-      <c r="L69" s="144"/>
+      <c r="A69" s="127" t="s">
+        <v>661</v>
+      </c>
+      <c r="B69" s="130" t="n">
+        <f aca="false">$B$7+(C$50-$B$7)*MIN(B$55/$B$17,1)</f>
+        <v>0.122</v>
+      </c>
+      <c r="C69" s="130" t="n">
+        <f aca="false">$B$7+(C$50-$B$7)*MIN(C$55/$B$17,1)</f>
+        <v>0.1296</v>
+      </c>
+      <c r="D69" s="130" t="n">
+        <f aca="false">$B$7+(C$50-$B$7)*MIN(D$55/$B$17,1)</f>
+        <v>0.1372</v>
+      </c>
+      <c r="E69" s="130" t="n">
+        <f aca="false">$B$7+(C$50-$B$7)*MIN(E$55/$B$17,1)</f>
+        <v>0.1448</v>
+      </c>
+      <c r="F69" s="130" t="n">
+        <f aca="false">$B$7+(C$50-$B$7)*MIN(F$55/$B$17,1)</f>
+        <v>0.1524</v>
+      </c>
+      <c r="G69" s="130" t="n">
+        <f aca="false">$B$7+(C$50-$B$7)*MIN(G$55/$B$17,1)</f>
+        <v>0.16</v>
+      </c>
+      <c r="H69" s="130" t="n">
+        <f aca="false">$B$7+(C$50-$B$7)*MIN(H$55/$B$17,1)</f>
+        <v>0.16</v>
+      </c>
+      <c r="I69" s="130" t="n">
+        <f aca="false">$B$7+(C$50-$B$7)*MIN(I$55/$B$17,1)</f>
+        <v>0.16</v>
+      </c>
+      <c r="J69" s="130" t="n">
+        <f aca="false">$B$7+(C$50-$B$7)*MIN(J$55/$B$17,1)</f>
+        <v>0.16</v>
+      </c>
+      <c r="K69" s="130" t="n">
+        <f aca="false">$B$7+(C$50-$B$7)*MIN(K$55/$B$17,1)</f>
+        <v>0.16</v>
+      </c>
+      <c r="L69" s="130" t="n">
+        <f aca="false">$B$7+(C$50-$B$7)*MIN(L$55/$B$17,1)</f>
+        <v>0.16</v>
+      </c>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A70" s="145" t="s">
-        <v>651</v>
-      </c>
-      <c r="B70" s="158" t="n">
-        <f aca="false">SUMPRODUCT($B$31:$B$37,(1+$K$31:$K$37)^B$47)</f>
-        <v>4100</v>
-      </c>
-      <c r="C70" s="158" t="n">
-        <f aca="false">SUMPRODUCT($B$31:$B$37,(1+$K$31:$K$37)^C$47)</f>
-        <v>4879.5</v>
-      </c>
-      <c r="D70" s="158" t="n">
-        <f aca="false">SUMPRODUCT($B$31:$B$37,(1+$K$31:$K$37)^D$47)</f>
-        <v>5836.055</v>
-      </c>
-      <c r="E70" s="158" t="n">
-        <f aca="false">SUMPRODUCT($B$31:$B$37,(1+$K$31:$K$37)^E$47)</f>
-        <v>7012.47285</v>
-      </c>
-      <c r="F70" s="158" t="n">
-        <f aca="false">SUMPRODUCT($B$31:$B$37,(1+$K$31:$K$37)^F$47)</f>
-        <v>8462.3529515</v>
-      </c>
-      <c r="G70" s="158" t="n">
-        <f aca="false">SUMPRODUCT($B$31:$B$37,(1+$K$31:$K$37)^G$47)</f>
-        <v>10252.902144045</v>
-      </c>
-      <c r="H70" s="158" t="n">
-        <f aca="false">SUMPRODUCT($B$31:$B$37,(1+$K$31:$K$37)^H$47)</f>
-        <v>12468.5064044055</v>
-      </c>
-      <c r="I70" s="158" t="n">
-        <f aca="false">SUMPRODUCT($B$31:$B$37,(1+$K$31:$K$37)^I$47)</f>
-        <v>15215.2658050176</v>
-      </c>
-      <c r="J70" s="158" t="n">
-        <f aca="false">SUMPRODUCT($B$31:$B$37,(1+$K$31:$K$37)^J$47)</f>
-        <v>18626.7580988777</v>
-      </c>
-      <c r="K70" s="158" t="n">
-        <f aca="false">SUMPRODUCT($B$31:$B$37,(1+$K$31:$K$37)^K$47)</f>
-        <v>22871.370600254</v>
-      </c>
-      <c r="L70" s="158" t="n">
-        <f aca="false">SUMPRODUCT($B$31:$B$37,(1+$K$31:$K$37)^L$47)</f>
-        <v>28161.6353923262</v>
+      <c r="A70" s="127" t="s">
+        <v>662</v>
+      </c>
+      <c r="B70" s="153" t="n">
+        <f aca="false">B68*B69</f>
+        <v>500.2</v>
+      </c>
+      <c r="C70" s="153" t="n">
+        <f aca="false">C68*C69</f>
+        <v>628.236</v>
+      </c>
+      <c r="D70" s="153" t="n">
+        <f aca="false">D68*D69</f>
+        <v>789.110602</v>
+      </c>
+      <c r="E70" s="153" t="n">
+        <f aca="false">E68*E69</f>
+        <v>1034.96485628</v>
+      </c>
+      <c r="F70" s="153" t="n">
+        <f aca="false">F68*F69</f>
+        <v>1337.984445819</v>
+      </c>
+      <c r="G70" s="153" t="n">
+        <f aca="false">G68*G69</f>
+        <v>1712.254780732</v>
+      </c>
+      <c r="H70" s="153" t="n">
+        <f aca="false">H68*H69</f>
+        <v>2029.05990389846</v>
+      </c>
+      <c r="I70" s="153" t="n">
+        <f aca="false">I68*I69</f>
+        <v>2416.56615697365</v>
+      </c>
+      <c r="J70" s="153" t="n">
+        <f aca="false">J68*J69</f>
+        <v>2891.50733421677</v>
+      </c>
+      <c r="K70" s="153" t="n">
+        <f aca="false">K68*K69</f>
+        <v>3474.73869339489</v>
+      </c>
+      <c r="L70" s="153" t="n">
+        <f aca="false">L68*L69</f>
+        <v>4192.28147168777</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="127" t="s">
-        <v>652</v>
-      </c>
-      <c r="B71" s="130" t="n">
-        <f aca="false">$B$7+(E$42-$B$7)*MIN(B$47/$B$17,1)</f>
+        <v>567</v>
+      </c>
+      <c r="B71" s="153" t="n">
+        <f aca="false">$B$13</f>
+        <v>10731.30168</v>
+      </c>
+      <c r="C71" s="153" t="n">
+        <f aca="false">C70*C$51</f>
+        <v>15077.664</v>
+      </c>
+      <c r="D71" s="153" t="n">
+        <f aca="false">D70*C$51</f>
+        <v>18938.654448</v>
+      </c>
+      <c r="E71" s="153" t="n">
+        <f aca="false">E70*C$51</f>
+        <v>24839.15655072</v>
+      </c>
+      <c r="F71" s="153" t="n">
+        <f aca="false">F70*C$51</f>
+        <v>32111.626699656</v>
+      </c>
+      <c r="G71" s="153" t="n">
+        <f aca="false">G70*C$51</f>
+        <v>41094.114737568</v>
+      </c>
+      <c r="H71" s="153" t="n">
+        <f aca="false">H70*C$51</f>
+        <v>48697.4376935629</v>
+      </c>
+      <c r="I71" s="153" t="n">
+        <f aca="false">I70*C$51</f>
+        <v>57997.5877673676</v>
+      </c>
+      <c r="J71" s="153" t="n">
+        <f aca="false">J70*C$51</f>
+        <v>69396.1760212024</v>
+      </c>
+      <c r="K71" s="153" t="n">
+        <f aca="false">K70*C$51</f>
+        <v>83393.7286414773</v>
+      </c>
+      <c r="L71" s="153" t="n">
+        <f aca="false">L70*C$51</f>
+        <v>100614.755320506</v>
+      </c>
+    </row>
+    <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A72" s="145" t="s">
+        <v>663</v>
+      </c>
+      <c r="B72" s="158" t="n">
+        <f aca="false">$B$13</f>
+        <v>10731.30168</v>
+      </c>
+      <c r="C72" s="158" t="n">
+        <f aca="false">C71*(1-$B$16)</f>
+        <v>14625.33408</v>
+      </c>
+      <c r="D72" s="158" t="n">
+        <f aca="false">D71*(1-$B$16)</f>
+        <v>18370.49481456</v>
+      </c>
+      <c r="E72" s="158" t="n">
+        <f aca="false">E71*(1-$B$16)</f>
+        <v>24093.9818541984</v>
+      </c>
+      <c r="F72" s="158" t="n">
+        <f aca="false">F71*(1-$B$16)</f>
+        <v>31148.2778986663</v>
+      </c>
+      <c r="G72" s="158" t="n">
+        <f aca="false">G71*(1-$B$16)</f>
+        <v>39861.291295441</v>
+      </c>
+      <c r="H72" s="158" t="n">
+        <f aca="false">H71*(1-$B$16)</f>
+        <v>47236.5145627561</v>
+      </c>
+      <c r="I72" s="158" t="n">
+        <f aca="false">I71*(1-$B$16)</f>
+        <v>56257.6601343466</v>
+      </c>
+      <c r="J72" s="158" t="n">
+        <f aca="false">J71*(1-$B$16)</f>
+        <v>67314.2907405663</v>
+      </c>
+      <c r="K72" s="158" t="n">
+        <f aca="false">K71*(1-$B$16)</f>
+        <v>80891.916782233</v>
+      </c>
+      <c r="L72" s="158" t="n">
+        <f aca="false">L71*(1-$B$16)</f>
+        <v>97596.3126608913</v>
+      </c>
+    </row>
+    <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A74" s="137" t="s">
+        <v>570</v>
+      </c>
+      <c r="B74" s="144"/>
+      <c r="C74" s="144"/>
+      <c r="D74" s="144"/>
+      <c r="E74" s="144"/>
+      <c r="F74" s="144"/>
+      <c r="G74" s="144"/>
+      <c r="H74" s="144"/>
+      <c r="I74" s="144"/>
+      <c r="J74" s="144"/>
+      <c r="K74" s="144"/>
+      <c r="L74" s="144"/>
+    </row>
+    <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A75" s="127" t="s">
+        <v>659</v>
+      </c>
+      <c r="B75" s="153" t="n">
+        <f aca="false">SUMPRODUCT($B$32:$B$39,(1+$J$32:$J$39)^B$55)</f>
+        <v>4100</v>
+      </c>
+      <c r="C75" s="153" t="n">
+        <f aca="false">SUMPRODUCT($B$32:$B$39,(1+$J$32:$J$39)^C$55)</f>
+        <v>4161.5</v>
+      </c>
+      <c r="D75" s="153" t="n">
+        <f aca="false">SUMPRODUCT($B$32:$B$39,(1+$J$32:$J$39)^D$55)</f>
+        <v>4226.635</v>
+      </c>
+      <c r="E75" s="153" t="n">
+        <f aca="false">SUMPRODUCT($B$32:$B$39,(1+$J$32:$J$39)^E$55)</f>
+        <v>4295.56175</v>
+      </c>
+      <c r="F75" s="153" t="n">
+        <f aca="false">SUMPRODUCT($B$32:$B$39,(1+$J$32:$J$39)^F$55)</f>
+        <v>4368.4453555</v>
+      </c>
+      <c r="G75" s="153" t="n">
+        <f aca="false">SUMPRODUCT($B$32:$B$39,(1+$J$32:$J$39)^G$55)</f>
+        <v>4445.459705615</v>
+      </c>
+      <c r="H75" s="153" t="n">
+        <f aca="false">SUMPRODUCT($B$32:$B$39,(1+$J$32:$J$39)^H$55)</f>
+        <v>4526.78792410435</v>
+      </c>
+      <c r="I75" s="153" t="n">
+        <f aca="false">SUMPRODUCT($B$32:$B$39,(1+$J$32:$J$39)^I$55)</f>
+        <v>4612.62284454582</v>
+      </c>
+      <c r="J75" s="153" t="n">
+        <f aca="false">SUMPRODUCT($B$32:$B$39,(1+$J$32:$J$39)^J$55)</f>
+        <v>4703.16751095177</v>
+      </c>
+      <c r="K75" s="153" t="n">
+        <f aca="false">SUMPRODUCT($B$32:$B$39,(1+$J$32:$J$39)^K$55)</f>
+        <v>4798.63570519554</v>
+      </c>
+      <c r="L75" s="153" t="n">
+        <f aca="false">SUMPRODUCT($B$32:$B$39,(1+$J$32:$J$39)^L$55)</f>
+        <v>4899.25250269077</v>
+      </c>
+    </row>
+    <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A76" s="127" t="s">
+        <v>660</v>
+      </c>
+      <c r="B76" s="153" t="n">
+        <f aca="false">D$45*MIN(MAX(B$55-D$44+1,0)/D$46,1)</f>
+        <v>0</v>
+      </c>
+      <c r="C76" s="153" t="n">
+        <f aca="false">D$45*MIN(MAX(C$55-D$44+1,0)/D$46,1)</f>
+        <v>0</v>
+      </c>
+      <c r="D76" s="153" t="n">
+        <f aca="false">D$45*MIN(MAX(D$55-D$44+1,0)/D$46,1)</f>
+        <v>0</v>
+      </c>
+      <c r="E76" s="153" t="n">
+        <f aca="false">D$45*MIN(MAX(E$55-D$44+1,0)/D$46,1)</f>
+        <v>0</v>
+      </c>
+      <c r="F76" s="153" t="n">
+        <f aca="false">D$45*MIN(MAX(F$55-D$44+1,0)/D$46,1)</f>
+        <v>0</v>
+      </c>
+      <c r="G76" s="153" t="n">
+        <f aca="false">D$45*MIN(MAX(G$55-D$44+1,0)/D$46,1)</f>
+        <v>0</v>
+      </c>
+      <c r="H76" s="153" t="n">
+        <f aca="false">D$45*MIN(MAX(H$55-D$44+1,0)/D$46,1)</f>
+        <v>0</v>
+      </c>
+      <c r="I76" s="153" t="n">
+        <f aca="false">D$45*MIN(MAX(I$55-D$44+1,0)/D$46,1)</f>
+        <v>0</v>
+      </c>
+      <c r="J76" s="153" t="n">
+        <f aca="false">D$45*MIN(MAX(J$55-D$44+1,0)/D$46,1)</f>
+        <v>0</v>
+      </c>
+      <c r="K76" s="153" t="n">
+        <f aca="false">D$45*MIN(MAX(K$55-D$44+1,0)/D$46,1)</f>
+        <v>0</v>
+      </c>
+      <c r="L76" s="153" t="n">
+        <f aca="false">D$45*MIN(MAX(L$55-D$44+1,0)/D$46,1)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A77" s="145" t="s">
+        <v>563</v>
+      </c>
+      <c r="B77" s="158" t="n">
+        <f aca="false">B75+B76</f>
+        <v>4100</v>
+      </c>
+      <c r="C77" s="158" t="n">
+        <f aca="false">C75+C76</f>
+        <v>4161.5</v>
+      </c>
+      <c r="D77" s="158" t="n">
+        <f aca="false">D75+D76</f>
+        <v>4226.635</v>
+      </c>
+      <c r="E77" s="158" t="n">
+        <f aca="false">E75+E76</f>
+        <v>4295.56175</v>
+      </c>
+      <c r="F77" s="158" t="n">
+        <f aca="false">F75+F76</f>
+        <v>4368.4453555</v>
+      </c>
+      <c r="G77" s="158" t="n">
+        <f aca="false">G75+G76</f>
+        <v>4445.459705615</v>
+      </c>
+      <c r="H77" s="158" t="n">
+        <f aca="false">H75+H76</f>
+        <v>4526.78792410435</v>
+      </c>
+      <c r="I77" s="158" t="n">
+        <f aca="false">I75+I76</f>
+        <v>4612.62284454582</v>
+      </c>
+      <c r="J77" s="158" t="n">
+        <f aca="false">J75+J76</f>
+        <v>4703.16751095177</v>
+      </c>
+      <c r="K77" s="158" t="n">
+        <f aca="false">K75+K76</f>
+        <v>4798.63570519554</v>
+      </c>
+      <c r="L77" s="158" t="n">
+        <f aca="false">L75+L76</f>
+        <v>4899.25250269077</v>
+      </c>
+    </row>
+    <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A78" s="127" t="s">
+        <v>661</v>
+      </c>
+      <c r="B78" s="130" t="n">
+        <f aca="false">$B$7+(D$50-$B$7)*MIN(B$55/$B$17,1)</f>
         <v>0.122</v>
       </c>
-      <c r="C71" s="130" t="n">
-        <f aca="false">$B$7+(E$42-$B$7)*MIN(C$47/$B$17,1)</f>
-        <v>0.1296</v>
-      </c>
-      <c r="D71" s="130" t="n">
-        <f aca="false">$B$7+(E$42-$B$7)*MIN(D$47/$B$17,1)</f>
-        <v>0.1372</v>
-      </c>
-      <c r="E71" s="130" t="n">
-        <f aca="false">$B$7+(E$42-$B$7)*MIN(E$47/$B$17,1)</f>
-        <v>0.1448</v>
-      </c>
-      <c r="F71" s="130" t="n">
-        <f aca="false">$B$7+(E$42-$B$7)*MIN(F$47/$B$17,1)</f>
-        <v>0.1524</v>
-      </c>
-      <c r="G71" s="130" t="n">
-        <f aca="false">$B$7+(E$42-$B$7)*MIN(G$47/$B$17,1)</f>
-        <v>0.16</v>
-      </c>
-      <c r="H71" s="130" t="n">
-        <f aca="false">$B$7+(E$42-$B$7)*MIN(H$47/$B$17,1)</f>
-        <v>0.16</v>
-      </c>
-      <c r="I71" s="130" t="n">
-        <f aca="false">$B$7+(E$42-$B$7)*MIN(I$47/$B$17,1)</f>
-        <v>0.16</v>
-      </c>
-      <c r="J71" s="130" t="n">
-        <f aca="false">$B$7+(E$42-$B$7)*MIN(J$47/$B$17,1)</f>
-        <v>0.16</v>
-      </c>
-      <c r="K71" s="130" t="n">
-        <f aca="false">$B$7+(E$42-$B$7)*MIN(K$47/$B$17,1)</f>
-        <v>0.16</v>
-      </c>
-      <c r="L71" s="130" t="n">
-        <f aca="false">$B$7+(E$42-$B$7)*MIN(L$47/$B$17,1)</f>
-        <v>0.16</v>
-      </c>
-    </row>
-    <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A72" s="127" t="s">
-        <v>653</v>
-      </c>
-      <c r="B72" s="153" t="n">
-        <f aca="false">B70*B71</f>
-        <v>500.2</v>
-      </c>
-      <c r="C72" s="153" t="n">
-        <f aca="false">C70*C71</f>
-        <v>632.3832</v>
-      </c>
-      <c r="D72" s="153" t="n">
-        <f aca="false">D70*D71</f>
-        <v>800.706746</v>
-      </c>
-      <c r="E72" s="153" t="n">
-        <f aca="false">E70*E71</f>
-        <v>1015.40606868</v>
-      </c>
-      <c r="F72" s="153" t="n">
-        <f aca="false">F70*F71</f>
-        <v>1289.6625898086</v>
-      </c>
-      <c r="G72" s="153" t="n">
-        <f aca="false">G70*G71</f>
-        <v>1640.4643430472</v>
-      </c>
-      <c r="H72" s="153" t="n">
-        <f aca="false">H70*H71</f>
-        <v>1994.96102470489</v>
-      </c>
-      <c r="I72" s="153" t="n">
-        <f aca="false">I70*I71</f>
-        <v>2434.44252880282</v>
-      </c>
-      <c r="J72" s="153" t="n">
-        <f aca="false">J70*J71</f>
-        <v>2980.28129582043</v>
-      </c>
-      <c r="K72" s="153" t="n">
-        <f aca="false">K70*K71</f>
-        <v>3659.41929604064</v>
-      </c>
-      <c r="L72" s="153" t="n">
-        <f aca="false">L70*L71</f>
-        <v>4505.8616627722</v>
-      </c>
-    </row>
-    <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A73" s="127" t="s">
-        <v>567</v>
-      </c>
-      <c r="B73" s="153" t="n">
-        <f aca="false">$B$13</f>
-        <v>10681.97856</v>
-      </c>
-      <c r="C73" s="153" t="n">
-        <f aca="false">C72*E$43</f>
-        <v>15177.1968</v>
-      </c>
-      <c r="D73" s="153" t="n">
-        <f aca="false">D72*E$43</f>
-        <v>19216.961904</v>
-      </c>
-      <c r="E73" s="153" t="n">
-        <f aca="false">E72*E$43</f>
-        <v>24369.74564832</v>
-      </c>
-      <c r="F73" s="153" t="n">
-        <f aca="false">F72*E$43</f>
-        <v>30951.9021554064</v>
-      </c>
-      <c r="G73" s="153" t="n">
-        <f aca="false">G72*E$43</f>
-        <v>39371.1442331328</v>
-      </c>
-      <c r="H73" s="153" t="n">
-        <f aca="false">H72*E$43</f>
-        <v>47879.0645929173</v>
-      </c>
-      <c r="I73" s="153" t="n">
-        <f aca="false">I72*E$43</f>
-        <v>58426.6206912677</v>
-      </c>
-      <c r="J73" s="153" t="n">
-        <f aca="false">J72*E$43</f>
-        <v>71526.7510996904</v>
-      </c>
-      <c r="K73" s="153" t="n">
-        <f aca="false">K72*E$43</f>
-        <v>87826.0631049753</v>
-      </c>
-      <c r="L73" s="153" t="n">
-        <f aca="false">L72*E$43</f>
-        <v>108140.679906533</v>
-      </c>
-    </row>
-    <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A74" s="145" t="s">
-        <v>654</v>
-      </c>
-      <c r="B74" s="158" t="n">
-        <f aca="false">$B$13</f>
-        <v>10681.97856</v>
-      </c>
-      <c r="C74" s="158" t="n">
-        <f aca="false">C73*(1-$B$16)</f>
-        <v>14721.880896</v>
-      </c>
-      <c r="D74" s="158" t="n">
-        <f aca="false">D73*(1-$B$16)</f>
-        <v>18640.45304688</v>
-      </c>
-      <c r="E74" s="158" t="n">
-        <f aca="false">E73*(1-$B$16)</f>
-        <v>23638.6532788704</v>
-      </c>
-      <c r="F74" s="158" t="n">
-        <f aca="false">F73*(1-$B$16)</f>
-        <v>30023.3450907442</v>
-      </c>
-      <c r="G74" s="158" t="n">
-        <f aca="false">G73*(1-$B$16)</f>
-        <v>38190.0099061388</v>
-      </c>
-      <c r="H74" s="158" t="n">
-        <f aca="false">H73*(1-$B$16)</f>
-        <v>46442.6926551298</v>
-      </c>
-      <c r="I74" s="158" t="n">
-        <f aca="false">I73*(1-$B$16)</f>
-        <v>56673.8220705297</v>
-      </c>
-      <c r="J74" s="158" t="n">
-        <f aca="false">J73*(1-$B$16)</f>
-        <v>69380.9485666997</v>
-      </c>
-      <c r="K74" s="158" t="n">
-        <f aca="false">K73*(1-$B$16)</f>
-        <v>85191.281211826</v>
-      </c>
-      <c r="L74" s="158" t="n">
-        <f aca="false">L73*(1-$B$16)</f>
-        <v>104896.459509337</v>
-      </c>
-    </row>
-    <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A77" s="60" t="s">
-        <v>655</v>
-      </c>
-      <c r="B77" s="125"/>
-      <c r="C77" s="125"/>
-      <c r="D77" s="125"/>
-      <c r="E77" s="125"/>
-      <c r="F77" s="125"/>
-      <c r="G77" s="125"/>
-      <c r="H77" s="125"/>
-      <c r="I77" s="125"/>
-      <c r="J77" s="125"/>
-      <c r="K77" s="125"/>
-      <c r="L77" s="125"/>
-      <c r="M77" s="125"/>
-    </row>
-    <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A78" s="126" t="s">
-        <v>27</v>
-      </c>
-      <c r="B78" s="126" t="s">
-        <v>573</v>
-      </c>
-      <c r="C78" s="126" t="s">
-        <v>36</v>
-      </c>
-      <c r="D78" s="126" t="s">
-        <v>37</v>
-      </c>
-      <c r="E78" s="126" t="s">
-        <v>38</v>
-      </c>
-      <c r="F78" s="126" t="s">
-        <v>39</v>
-      </c>
-      <c r="G78" s="126" t="s">
-        <v>40</v>
+      <c r="C78" s="130" t="n">
+        <f aca="false">$B$7+(D$50-$B$7)*MIN(C$55/$B$17,1)</f>
+        <v>0.1196</v>
+      </c>
+      <c r="D78" s="130" t="n">
+        <f aca="false">$B$7+(D$50-$B$7)*MIN(D$55/$B$17,1)</f>
+        <v>0.1172</v>
+      </c>
+      <c r="E78" s="130" t="n">
+        <f aca="false">$B$7+(D$50-$B$7)*MIN(E$55/$B$17,1)</f>
+        <v>0.1148</v>
+      </c>
+      <c r="F78" s="130" t="n">
+        <f aca="false">$B$7+(D$50-$B$7)*MIN(F$55/$B$17,1)</f>
+        <v>0.1124</v>
+      </c>
+      <c r="G78" s="130" t="n">
+        <f aca="false">$B$7+(D$50-$B$7)*MIN(G$55/$B$17,1)</f>
+        <v>0.11</v>
+      </c>
+      <c r="H78" s="130" t="n">
+        <f aca="false">$B$7+(D$50-$B$7)*MIN(H$55/$B$17,1)</f>
+        <v>0.11</v>
+      </c>
+      <c r="I78" s="130" t="n">
+        <f aca="false">$B$7+(D$50-$B$7)*MIN(I$55/$B$17,1)</f>
+        <v>0.11</v>
+      </c>
+      <c r="J78" s="130" t="n">
+        <f aca="false">$B$7+(D$50-$B$7)*MIN(J$55/$B$17,1)</f>
+        <v>0.11</v>
+      </c>
+      <c r="K78" s="130" t="n">
+        <f aca="false">$B$7+(D$50-$B$7)*MIN(K$55/$B$17,1)</f>
+        <v>0.11</v>
+      </c>
+      <c r="L78" s="130" t="n">
+        <f aca="false">$B$7+(D$50-$B$7)*MIN(L$55/$B$17,1)</f>
+        <v>0.11</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="127" t="s">
+        <v>662</v>
+      </c>
+      <c r="B79" s="153" t="n">
+        <f aca="false">B77*B78</f>
+        <v>500.2</v>
+      </c>
+      <c r="C79" s="153" t="n">
+        <f aca="false">C77*C78</f>
+        <v>497.7154</v>
+      </c>
+      <c r="D79" s="153" t="n">
+        <f aca="false">D77*D78</f>
+        <v>495.361622</v>
+      </c>
+      <c r="E79" s="153" t="n">
+        <f aca="false">E77*E78</f>
+        <v>493.1304889</v>
+      </c>
+      <c r="F79" s="153" t="n">
+        <f aca="false">F77*F78</f>
+        <v>491.0132579582</v>
+      </c>
+      <c r="G79" s="153" t="n">
+        <f aca="false">G77*G78</f>
+        <v>489.00056761765</v>
+      </c>
+      <c r="H79" s="153" t="n">
+        <f aca="false">H77*H78</f>
+        <v>497.946671651479</v>
+      </c>
+      <c r="I79" s="153" t="n">
+        <f aca="false">I77*I78</f>
+        <v>507.38851290004</v>
+      </c>
+      <c r="J79" s="153" t="n">
+        <f aca="false">J77*J78</f>
+        <v>517.348426204694</v>
+      </c>
+      <c r="K79" s="153" t="n">
+        <f aca="false">K77*K78</f>
+        <v>527.84992757151</v>
+      </c>
+      <c r="L79" s="153" t="n">
+        <f aca="false">L77*L78</f>
+        <v>538.917775295985</v>
+      </c>
+    </row>
+    <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A80" s="127" t="s">
+        <v>567</v>
+      </c>
+      <c r="B80" s="153" t="n">
+        <f aca="false">$B$13</f>
+        <v>10731.30168</v>
+      </c>
+      <c r="C80" s="153" t="n">
+        <f aca="false">C79*D$51</f>
+        <v>6968.0156</v>
+      </c>
+      <c r="D80" s="153" t="n">
+        <f aca="false">D79*D$51</f>
+        <v>6935.062708</v>
+      </c>
+      <c r="E80" s="153" t="n">
+        <f aca="false">E79*D$51</f>
+        <v>6903.8268446</v>
+      </c>
+      <c r="F80" s="153" t="n">
+        <f aca="false">F79*D$51</f>
+        <v>6874.1856114148</v>
+      </c>
+      <c r="G80" s="153" t="n">
+        <f aca="false">G79*D$51</f>
+        <v>6846.0079466471</v>
+      </c>
+      <c r="H80" s="153" t="n">
+        <f aca="false">H79*D$51</f>
+        <v>6971.2534031207</v>
+      </c>
+      <c r="I80" s="153" t="n">
+        <f aca="false">I79*D$51</f>
+        <v>7103.43918060056</v>
+      </c>
+      <c r="J80" s="153" t="n">
+        <f aca="false">J79*D$51</f>
+        <v>7242.87796686572</v>
+      </c>
+      <c r="K80" s="153" t="n">
+        <f aca="false">K79*D$51</f>
+        <v>7389.89898600114</v>
+      </c>
+      <c r="L80" s="153" t="n">
+        <f aca="false">L79*D$51</f>
+        <v>7544.84885414379</v>
+      </c>
+    </row>
+    <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A81" s="145" t="s">
+        <v>663</v>
+      </c>
+      <c r="B81" s="158" t="n">
+        <f aca="false">$B$13</f>
+        <v>10731.30168</v>
+      </c>
+      <c r="C81" s="158" t="n">
+        <f aca="false">C80*(1-$B$16)</f>
+        <v>6758.975132</v>
+      </c>
+      <c r="D81" s="158" t="n">
+        <f aca="false">D80*(1-$B$16)</f>
+        <v>6727.01082676</v>
+      </c>
+      <c r="E81" s="158" t="n">
+        <f aca="false">E80*(1-$B$16)</f>
+        <v>6696.712039262</v>
+      </c>
+      <c r="F81" s="158" t="n">
+        <f aca="false">F80*(1-$B$16)</f>
+        <v>6667.96004307236</v>
+      </c>
+      <c r="G81" s="158" t="n">
+        <f aca="false">G80*(1-$B$16)</f>
+        <v>6640.62770824769</v>
+      </c>
+      <c r="H81" s="158" t="n">
+        <f aca="false">H80*(1-$B$16)</f>
+        <v>6762.11580102708</v>
+      </c>
+      <c r="I81" s="158" t="n">
+        <f aca="false">I80*(1-$B$16)</f>
+        <v>6890.33600518254</v>
+      </c>
+      <c r="J81" s="158" t="n">
+        <f aca="false">J80*(1-$B$16)</f>
+        <v>7025.59162785975</v>
+      </c>
+      <c r="K81" s="158" t="n">
+        <f aca="false">K80*(1-$B$16)</f>
+        <v>7168.2020164211</v>
+      </c>
+      <c r="L81" s="158" t="n">
+        <f aca="false">L80*(1-$B$16)</f>
+        <v>7318.50338851947</v>
+      </c>
+    </row>
+    <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A83" s="137" t="s">
+        <v>571</v>
+      </c>
+      <c r="B83" s="144"/>
+      <c r="C83" s="144"/>
+      <c r="D83" s="144"/>
+      <c r="E83" s="144"/>
+      <c r="F83" s="144"/>
+      <c r="G83" s="144"/>
+      <c r="H83" s="144"/>
+      <c r="I83" s="144"/>
+      <c r="J83" s="144"/>
+      <c r="K83" s="144"/>
+      <c r="L83" s="144"/>
+    </row>
+    <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A84" s="127" t="s">
+        <v>659</v>
+      </c>
+      <c r="B84" s="153" t="n">
+        <f aca="false">SUMPRODUCT($B$32:$B$39,(1+$K$32:$K$39)^B$55)</f>
+        <v>4100</v>
+      </c>
+      <c r="C84" s="153" t="n">
+        <f aca="false">SUMPRODUCT($B$32:$B$39,(1+$K$32:$K$39)^C$55)</f>
+        <v>4921.5</v>
+      </c>
+      <c r="D84" s="153" t="n">
+        <f aca="false">SUMPRODUCT($B$32:$B$39,(1+$K$32:$K$39)^D$55)</f>
+        <v>5941.055</v>
+      </c>
+      <c r="E84" s="153" t="n">
+        <f aca="false">SUMPRODUCT($B$32:$B$39,(1+$K$32:$K$39)^E$55)</f>
+        <v>7209.55365</v>
+      </c>
+      <c r="F84" s="153" t="n">
+        <f aca="false">SUMPRODUCT($B$32:$B$39,(1+$K$32:$K$39)^F$55)</f>
+        <v>8791.5069515</v>
+      </c>
+      <c r="G84" s="153" t="n">
+        <f aca="false">SUMPRODUCT($B$32:$B$39,(1+$K$32:$K$39)^G$55)</f>
+        <v>10768.814089965</v>
+      </c>
+      <c r="H84" s="153" t="n">
+        <f aca="false">SUMPRODUCT($B$32:$B$39,(1+$K$32:$K$39)^H$55)</f>
+        <v>13245.5959988056</v>
+      </c>
+      <c r="I84" s="153" t="n">
+        <f aca="false">SUMPRODUCT($B$32:$B$39,(1+$K$32:$K$39)^I$55)</f>
+        <v>16354.4053440526</v>
+      </c>
+      <c r="J84" s="153" t="n">
+        <f aca="false">SUMPRODUCT($B$32:$B$39,(1+$K$32:$K$39)^J$55)</f>
+        <v>20264.2121942278</v>
+      </c>
+      <c r="K84" s="153" t="n">
+        <f aca="false">SUMPRODUCT($B$32:$B$39,(1+$K$32:$K$39)^K$55)</f>
+        <v>25190.6820926283</v>
+      </c>
+      <c r="L84" s="153" t="n">
+        <f aca="false">SUMPRODUCT($B$32:$B$39,(1+$K$32:$K$39)^L$55)</f>
+        <v>31409.4156243446</v>
+      </c>
+    </row>
+    <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A85" s="127" t="s">
+        <v>660</v>
+      </c>
+      <c r="B85" s="153" t="n">
+        <f aca="false">E$45*MIN(MAX(B$55-E$44+1,0)/E$46,1)</f>
+        <v>0</v>
+      </c>
+      <c r="C85" s="153" t="n">
+        <f aca="false">E$45*MIN(MAX(C$55-E$44+1,0)/E$46,1)</f>
+        <v>0</v>
+      </c>
+      <c r="D85" s="153" t="n">
+        <f aca="false">E$45*MIN(MAX(D$55-E$44+1,0)/E$46,1)</f>
+        <v>0</v>
+      </c>
+      <c r="E85" s="153" t="n">
+        <f aca="false">E$45*MIN(MAX(E$55-E$44+1,0)/E$46,1)</f>
+        <v>500</v>
+      </c>
+      <c r="F85" s="153" t="n">
+        <f aca="false">E$45*MIN(MAX(F$55-E$44+1,0)/E$46,1)</f>
+        <v>1000</v>
+      </c>
+      <c r="G85" s="153" t="n">
+        <f aca="false">E$45*MIN(MAX(G$55-E$44+1,0)/E$46,1)</f>
+        <v>1000</v>
+      </c>
+      <c r="H85" s="153" t="n">
+        <f aca="false">E$45*MIN(MAX(H$55-E$44+1,0)/E$46,1)</f>
+        <v>1000</v>
+      </c>
+      <c r="I85" s="153" t="n">
+        <f aca="false">E$45*MIN(MAX(I$55-E$44+1,0)/E$46,1)</f>
+        <v>1000</v>
+      </c>
+      <c r="J85" s="153" t="n">
+        <f aca="false">E$45*MIN(MAX(J$55-E$44+1,0)/E$46,1)</f>
+        <v>1000</v>
+      </c>
+      <c r="K85" s="153" t="n">
+        <f aca="false">E$45*MIN(MAX(K$55-E$44+1,0)/E$46,1)</f>
+        <v>1000</v>
+      </c>
+      <c r="L85" s="153" t="n">
+        <f aca="false">E$45*MIN(MAX(L$55-E$44+1,0)/E$46,1)</f>
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A86" s="145" t="s">
+        <v>563</v>
+      </c>
+      <c r="B86" s="158" t="n">
+        <f aca="false">B84+B85</f>
+        <v>4100</v>
+      </c>
+      <c r="C86" s="158" t="n">
+        <f aca="false">C84+C85</f>
+        <v>4921.5</v>
+      </c>
+      <c r="D86" s="158" t="n">
+        <f aca="false">D84+D85</f>
+        <v>5941.055</v>
+      </c>
+      <c r="E86" s="158" t="n">
+        <f aca="false">E84+E85</f>
+        <v>7709.55365</v>
+      </c>
+      <c r="F86" s="158" t="n">
+        <f aca="false">F84+F85</f>
+        <v>9791.5069515</v>
+      </c>
+      <c r="G86" s="158" t="n">
+        <f aca="false">G84+G85</f>
+        <v>11768.814089965</v>
+      </c>
+      <c r="H86" s="158" t="n">
+        <f aca="false">H84+H85</f>
+        <v>14245.5959988056</v>
+      </c>
+      <c r="I86" s="158" t="n">
+        <f aca="false">I84+I85</f>
+        <v>17354.4053440526</v>
+      </c>
+      <c r="J86" s="158" t="n">
+        <f aca="false">J84+J85</f>
+        <v>21264.2121942278</v>
+      </c>
+      <c r="K86" s="158" t="n">
+        <f aca="false">K84+K85</f>
+        <v>26190.6820926283</v>
+      </c>
+      <c r="L86" s="158" t="n">
+        <f aca="false">L84+L85</f>
+        <v>32409.4156243446</v>
+      </c>
+    </row>
+    <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A87" s="127" t="s">
+        <v>661</v>
+      </c>
+      <c r="B87" s="130" t="n">
+        <f aca="false">$B$7+(E$50-$B$7)*MIN(B$55/$B$17,1)</f>
+        <v>0.122</v>
+      </c>
+      <c r="C87" s="130" t="n">
+        <f aca="false">$B$7+(E$50-$B$7)*MIN(C$55/$B$17,1)</f>
+        <v>0.1296</v>
+      </c>
+      <c r="D87" s="130" t="n">
+        <f aca="false">$B$7+(E$50-$B$7)*MIN(D$55/$B$17,1)</f>
+        <v>0.1372</v>
+      </c>
+      <c r="E87" s="130" t="n">
+        <f aca="false">$B$7+(E$50-$B$7)*MIN(E$55/$B$17,1)</f>
+        <v>0.1448</v>
+      </c>
+      <c r="F87" s="130" t="n">
+        <f aca="false">$B$7+(E$50-$B$7)*MIN(F$55/$B$17,1)</f>
+        <v>0.1524</v>
+      </c>
+      <c r="G87" s="130" t="n">
+        <f aca="false">$B$7+(E$50-$B$7)*MIN(G$55/$B$17,1)</f>
+        <v>0.16</v>
+      </c>
+      <c r="H87" s="130" t="n">
+        <f aca="false">$B$7+(E$50-$B$7)*MIN(H$55/$B$17,1)</f>
+        <v>0.16</v>
+      </c>
+      <c r="I87" s="130" t="n">
+        <f aca="false">$B$7+(E$50-$B$7)*MIN(I$55/$B$17,1)</f>
+        <v>0.16</v>
+      </c>
+      <c r="J87" s="130" t="n">
+        <f aca="false">$B$7+(E$50-$B$7)*MIN(J$55/$B$17,1)</f>
+        <v>0.16</v>
+      </c>
+      <c r="K87" s="130" t="n">
+        <f aca="false">$B$7+(E$50-$B$7)*MIN(K$55/$B$17,1)</f>
+        <v>0.16</v>
+      </c>
+      <c r="L87" s="130" t="n">
+        <f aca="false">$B$7+(E$50-$B$7)*MIN(L$55/$B$17,1)</f>
+        <v>0.16</v>
+      </c>
+    </row>
+    <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A88" s="127" t="s">
+        <v>662</v>
+      </c>
+      <c r="B88" s="153" t="n">
+        <f aca="false">B86*B87</f>
+        <v>500.2</v>
+      </c>
+      <c r="C88" s="153" t="n">
+        <f aca="false">C86*C87</f>
+        <v>637.8264</v>
+      </c>
+      <c r="D88" s="153" t="n">
+        <f aca="false">D86*D87</f>
+        <v>815.112746</v>
+      </c>
+      <c r="E88" s="153" t="n">
+        <f aca="false">E86*E87</f>
+        <v>1116.34336852</v>
+      </c>
+      <c r="F88" s="153" t="n">
+        <f aca="false">F86*F87</f>
+        <v>1492.2256594086</v>
+      </c>
+      <c r="G88" s="153" t="n">
+        <f aca="false">G86*G87</f>
+        <v>1883.0102543944</v>
+      </c>
+      <c r="H88" s="153" t="n">
+        <f aca="false">H86*H87</f>
+        <v>2279.29535980889</v>
+      </c>
+      <c r="I88" s="153" t="n">
+        <f aca="false">I86*I87</f>
+        <v>2776.70485504842</v>
+      </c>
+      <c r="J88" s="153" t="n">
+        <f aca="false">J86*J87</f>
+        <v>3402.27395107645</v>
+      </c>
+      <c r="K88" s="153" t="n">
+        <f aca="false">K86*K87</f>
+        <v>4190.50913482052</v>
+      </c>
+      <c r="L88" s="153" t="n">
+        <f aca="false">L86*L87</f>
+        <v>5185.50649989514</v>
+      </c>
+    </row>
+    <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A89" s="127" t="s">
+        <v>567</v>
+      </c>
+      <c r="B89" s="153" t="n">
+        <f aca="false">$B$13</f>
+        <v>10731.30168</v>
+      </c>
+      <c r="C89" s="153" t="n">
+        <f aca="false">C88*E$51</f>
+        <v>15307.8336</v>
+      </c>
+      <c r="D89" s="153" t="n">
+        <f aca="false">D88*E$51</f>
+        <v>19562.705904</v>
+      </c>
+      <c r="E89" s="153" t="n">
+        <f aca="false">E88*E$51</f>
+        <v>26792.24084448</v>
+      </c>
+      <c r="F89" s="153" t="n">
+        <f aca="false">F88*E$51</f>
+        <v>35813.4158258064</v>
+      </c>
+      <c r="G89" s="153" t="n">
+        <f aca="false">G88*E$51</f>
+        <v>45192.2461054656</v>
+      </c>
+      <c r="H89" s="153" t="n">
+        <f aca="false">H88*E$51</f>
+        <v>54703.0886354133</v>
+      </c>
+      <c r="I89" s="153" t="n">
+        <f aca="false">I88*E$51</f>
+        <v>66640.9165211621</v>
+      </c>
+      <c r="J89" s="153" t="n">
+        <f aca="false">J88*E$51</f>
+        <v>81654.5748258347</v>
+      </c>
+      <c r="K89" s="153" t="n">
+        <f aca="false">K88*E$51</f>
+        <v>100572.219235693</v>
+      </c>
+      <c r="L89" s="153" t="n">
+        <f aca="false">L88*E$51</f>
+        <v>124452.155997483</v>
+      </c>
+    </row>
+    <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A90" s="145" t="s">
+        <v>663</v>
+      </c>
+      <c r="B90" s="158" t="n">
+        <f aca="false">$B$13</f>
+        <v>10731.30168</v>
+      </c>
+      <c r="C90" s="158" t="n">
+        <f aca="false">C89*(1-$B$16)</f>
+        <v>14848.598592</v>
+      </c>
+      <c r="D90" s="158" t="n">
+        <f aca="false">D89*(1-$B$16)</f>
+        <v>18975.82472688</v>
+      </c>
+      <c r="E90" s="158" t="n">
+        <f aca="false">E89*(1-$B$16)</f>
+        <v>25988.4736191456</v>
+      </c>
+      <c r="F90" s="158" t="n">
+        <f aca="false">F89*(1-$B$16)</f>
+        <v>34739.0133510322</v>
+      </c>
+      <c r="G90" s="158" t="n">
+        <f aca="false">G89*(1-$B$16)</f>
+        <v>43836.4787223016</v>
+      </c>
+      <c r="H90" s="158" t="n">
+        <f aca="false">H89*(1-$B$16)</f>
+        <v>53061.9959763509</v>
+      </c>
+      <c r="I90" s="158" t="n">
+        <f aca="false">I89*(1-$B$16)</f>
+        <v>64641.6890255273</v>
+      </c>
+      <c r="J90" s="158" t="n">
+        <f aca="false">J89*(1-$B$16)</f>
+        <v>79204.9375810597</v>
+      </c>
+      <c r="K90" s="158" t="n">
+        <f aca="false">K89*(1-$B$16)</f>
+        <v>97555.0526586218</v>
+      </c>
+      <c r="L90" s="158" t="n">
+        <f aca="false">L89*(1-$B$16)</f>
+        <v>120718.591317559</v>
+      </c>
+    </row>
+    <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A93" s="60" t="s">
+        <v>664</v>
+      </c>
+      <c r="B93" s="125"/>
+      <c r="C93" s="125"/>
+      <c r="D93" s="125"/>
+      <c r="E93" s="125"/>
+      <c r="F93" s="125"/>
+      <c r="G93" s="125"/>
+      <c r="H93" s="125"/>
+      <c r="I93" s="125"/>
+      <c r="J93" s="125"/>
+      <c r="K93" s="125"/>
+      <c r="L93" s="125"/>
+      <c r="M93" s="125"/>
+    </row>
+    <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A94" s="126" t="s">
+        <v>27</v>
+      </c>
+      <c r="B94" s="126" t="s">
+        <v>573</v>
+      </c>
+      <c r="C94" s="126" t="s">
+        <v>36</v>
+      </c>
+      <c r="D94" s="126" t="s">
+        <v>37</v>
+      </c>
+      <c r="E94" s="126" t="s">
+        <v>38</v>
+      </c>
+      <c r="F94" s="126" t="s">
+        <v>39</v>
+      </c>
+      <c r="G94" s="126" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A95" s="127" t="s">
         <v>574</v>
       </c>
-      <c r="B79" s="147" t="n">
+      <c r="B95" s="147" t="n">
         <v>5</v>
       </c>
-      <c r="C79" s="130" t="n">
-        <f aca="false">(G53/$B$13)^(1/$B79)-1</f>
-        <v>0.123895060194143</v>
-      </c>
-      <c r="D79" s="130" t="n">
-        <f aca="false">(G60/$B$13)^(1/$B79)-1</f>
-        <v>0.269081910125599</v>
-      </c>
-      <c r="E79" s="130" t="n">
-        <f aca="false">(G67/$B$13)^(1/$B79)-1</f>
-        <v>-0.0913693982044872</v>
-      </c>
-      <c r="F79" s="130" t="n">
-        <f aca="false">(G74/$B$13)^(1/$B79)-1</f>
-        <v>0.290207653552962</v>
-      </c>
-      <c r="G79" s="130" t="n">
-        <f aca="false">C79*'Defense Supercycle'!$B$17+D79*'Defense Supercycle'!$B$18+E79*'Defense Supercycle'!$B$19+F79*'Defense Supercycle'!$B$20</f>
-        <v>0.152848992921035</v>
-      </c>
-    </row>
-    <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A80" s="145" t="s">
+      <c r="C95" s="130" t="n">
+        <f aca="false">(G63/$B$13)^(1/$B95)-1</f>
+        <v>0.136208014970308</v>
+      </c>
+      <c r="D95" s="130" t="n">
+        <f aca="false">(G72/$B$13)^(1/$B95)-1</f>
+        <v>0.300109081388199</v>
+      </c>
+      <c r="E95" s="130" t="n">
+        <f aca="false">(G81/$B$13)^(1/$B95)-1</f>
+        <v>-0.0915284196829586</v>
+      </c>
+      <c r="F95" s="130" t="n">
+        <f aca="false">(G90/$B$13)^(1/$B95)-1</f>
+        <v>0.325063378813437</v>
+      </c>
+      <c r="G95" s="130" t="n">
+        <f aca="false">C95*'Defense Supercycle'!$B$17+D95*'Defense Supercycle'!$B$18+E95*'Defense Supercycle'!$B$19+F95*'Defense Supercycle'!$B$20</f>
+        <v>0.17135112095326</v>
+      </c>
+    </row>
+    <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A96" s="145" t="s">
         <v>575</v>
       </c>
-      <c r="B80" s="147" t="n">
+      <c r="B96" s="147" t="n">
         <v>7</v>
       </c>
-      <c r="C80" s="148" t="n">
-        <f aca="false">(I53/$B$13)^(1/$B80)-1</f>
-        <v>0.123920922002584</v>
-      </c>
-      <c r="D80" s="148" t="n">
-        <f aca="false">(I60/$B$13)^(1/$B80)-1</f>
-        <v>0.247081228173655</v>
-      </c>
-      <c r="E80" s="148" t="n">
-        <f aca="false">(I67/$B$13)^(1/$B80)-1</f>
-        <v>-0.0614229924192035</v>
-      </c>
-      <c r="F80" s="148" t="n">
-        <f aca="false">(I74/$B$13)^(1/$B80)-1</f>
-        <v>0.269208498655892</v>
-      </c>
-      <c r="G80" s="130" t="n">
-        <f aca="false">C80*'Defense Supercycle'!$B$17+D80*'Defense Supercycle'!$B$18+E80*'Defense Supercycle'!$B$19+F80*'Defense Supercycle'!$B$20</f>
-        <v>0.14870254788008</v>
-      </c>
-    </row>
-    <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A81" s="127" t="s">
+      <c r="C96" s="148" t="n">
+        <f aca="false">(I63/$B$13)^(1/$B96)-1</f>
+        <v>0.135109979034539</v>
+      </c>
+      <c r="D96" s="148" t="n">
+        <f aca="false">(I72/$B$13)^(1/$B96)-1</f>
+        <v>0.267038742033648</v>
+      </c>
+      <c r="E96" s="148" t="n">
+        <f aca="false">(I81/$B$13)^(1/$B96)-1</f>
+        <v>-0.0613307932939748</v>
+      </c>
+      <c r="F96" s="148" t="n">
+        <f aca="false">(I90/$B$13)^(1/$B96)-1</f>
+        <v>0.292434710144012</v>
+      </c>
+      <c r="G96" s="130" t="n">
+        <f aca="false">C96*'Defense Supercycle'!$B$17+D96*'Defense Supercycle'!$B$18+E96*'Defense Supercycle'!$B$19+F96*'Defense Supercycle'!$B$20</f>
+        <v>0.16222476360146</v>
+      </c>
+    </row>
+    <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A97" s="127" t="s">
         <v>576</v>
       </c>
-      <c r="B81" s="147" t="n">
+      <c r="B97" s="147" t="n">
         <v>10</v>
       </c>
-      <c r="C81" s="130" t="n">
-        <f aca="false">(L53/$B$13)^(1/$B81)-1</f>
-        <v>0.125938039985265</v>
-      </c>
-      <c r="D81" s="130" t="n">
-        <f aca="false">(L60/$B$13)^(1/$B81)-1</f>
-        <v>0.233317540263184</v>
-      </c>
-      <c r="E81" s="130" t="n">
-        <f aca="false">(L67/$B$13)^(1/$B81)-1</f>
-        <v>-0.0378482611003012</v>
-      </c>
-      <c r="F81" s="130" t="n">
-        <f aca="false">(L74/$B$13)^(1/$B81)-1</f>
-        <v>0.256640096114641</v>
-      </c>
-      <c r="G81" s="130" t="n">
-        <f aca="false">C81*'Defense Supercycle'!$B$17+D81*'Defense Supercycle'!$B$18+E81*'Defense Supercycle'!$B$19+F81*'Defense Supercycle'!$B$20</f>
-        <v>0.147820278311316</v>
-      </c>
-    </row>
-    <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A82" s="127" t="s">
+      <c r="C97" s="130" t="n">
+        <f aca="false">(L63/$B$13)^(1/$B97)-1</f>
+        <v>0.133588883315237</v>
+      </c>
+      <c r="D97" s="130" t="n">
+        <f aca="false">(L72/$B$13)^(1/$B97)-1</f>
+        <v>0.24703344300807</v>
+      </c>
+      <c r="E97" s="130" t="n">
+        <f aca="false">(L81/$B$13)^(1/$B97)-1</f>
+        <v>-0.0375526358899257</v>
+      </c>
+      <c r="F97" s="130" t="n">
+        <f aca="false">(L90/$B$13)^(1/$B97)-1</f>
+        <v>0.273832061228545</v>
+      </c>
+      <c r="G97" s="130" t="n">
+        <f aca="false">C97*'Defense Supercycle'!$B$17+D97*'Defense Supercycle'!$B$18+E97*'Defense Supercycle'!$B$19+F97*'Defense Supercycle'!$B$20</f>
+        <v>0.157315272044667</v>
+      </c>
+    </row>
+    <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A98" s="127" t="s">
         <v>577</v>
       </c>
-      <c r="C82" s="153" t="n">
-        <f aca="false">I49</f>
-        <v>8909.88762748362</v>
-      </c>
-      <c r="D82" s="153" t="n">
-        <f aca="false">I56</f>
-        <v>13452.7768209288</v>
-      </c>
-      <c r="E82" s="153" t="n">
-        <f aca="false">I63</f>
-        <v>4588.26638521314</v>
-      </c>
-      <c r="F82" s="153" t="n">
-        <f aca="false">I70</f>
-        <v>15215.2658050176</v>
-      </c>
-      <c r="G82" s="153" t="n">
-        <f aca="false">C82*'Defense Supercycle'!$B$17+D82*'Defense Supercycle'!$B$18+E82*'Defense Supercycle'!$B$19+F82*'Defense Supercycle'!$B$20</f>
-        <v>10343.1734661344</v>
-      </c>
-    </row>
-    <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A83" s="127" t="s">
-        <v>656</v>
-      </c>
-      <c r="C83" s="134" t="n">
+      <c r="C98" s="153" t="n">
+        <f aca="false">I59</f>
+        <v>9593.74631099039</v>
+      </c>
+      <c r="D98" s="153" t="n">
+        <f aca="false">I68</f>
+        <v>15103.5384810853</v>
+      </c>
+      <c r="E98" s="153" t="n">
+        <f aca="false">I77</f>
+        <v>4612.62284454582</v>
+      </c>
+      <c r="F98" s="153" t="n">
+        <f aca="false">I86</f>
+        <v>17354.4053440526</v>
+      </c>
+      <c r="G98" s="153" t="n">
+        <f aca="false">C98*'Defense Supercycle'!$B$17+D98*'Defense Supercycle'!$B$18+E98*'Defense Supercycle'!$B$19+F98*'Defense Supercycle'!$B$20</f>
+        <v>11388.1246885068</v>
+      </c>
+    </row>
+    <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A99" s="127" t="s">
+        <v>665</v>
+      </c>
+      <c r="C99" s="134" t="n">
         <f aca="false">B11/B13</f>
         <v>1.17647058823529</v>
       </c>
     </row>
-    <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A85" s="60" t="s">
-        <v>657</v>
-      </c>
-      <c r="B85" s="125"/>
-      <c r="C85" s="125"/>
-      <c r="D85" s="125"/>
-      <c r="E85" s="125"/>
-      <c r="F85" s="125"/>
-      <c r="G85" s="125"/>
-      <c r="H85" s="125"/>
-      <c r="I85" s="125"/>
-      <c r="J85" s="125"/>
-      <c r="K85" s="125"/>
-      <c r="L85" s="125"/>
-      <c r="M85" s="125"/>
-    </row>
-    <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A86" s="126" t="s">
+    <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A100" s="127" t="s">
+        <v>666</v>
+      </c>
+      <c r="C100" s="130" t="n">
+        <f aca="false">(I58+$B$39*(1+H$39)^7)/I59</f>
+        <v>0.124873633855443</v>
+      </c>
+      <c r="D100" s="130" t="n">
+        <f aca="false">(I67+$B$39*(1+I$39)^7)/I68</f>
+        <v>0.165433258148455</v>
+      </c>
+      <c r="E100" s="130" t="n">
+        <f aca="false">(I76+$B$39*(1+J$39)^7)/I77</f>
+        <v>0.0799896657633171</v>
+      </c>
+      <c r="F100" s="130" t="n">
+        <f aca="false">(I85+$B$39*(1+K$39)^7)/I86</f>
+        <v>0.1783283061477</v>
+      </c>
+    </row>
+    <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A102" s="60" t="s">
+        <v>667</v>
+      </c>
+      <c r="B102" s="125"/>
+      <c r="C102" s="125"/>
+      <c r="D102" s="125"/>
+      <c r="E102" s="125"/>
+      <c r="F102" s="125"/>
+      <c r="G102" s="125"/>
+      <c r="H102" s="125"/>
+      <c r="I102" s="125"/>
+      <c r="J102" s="125"/>
+      <c r="K102" s="125"/>
+      <c r="L102" s="125"/>
+      <c r="M102" s="125"/>
+    </row>
+    <row r="103" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A103" s="126" t="s">
         <v>580</v>
       </c>
-      <c r="B86" s="126" t="s">
+      <c r="B103" s="126" t="s">
         <v>248</v>
       </c>
-      <c r="C86" s="126" t="s">
+      <c r="C103" s="126" t="s">
         <v>356</v>
       </c>
-      <c r="D86" s="126" t="s">
+      <c r="D103" s="126" t="s">
         <v>359</v>
       </c>
-      <c r="E86" s="126" t="s">
+      <c r="E103" s="126" t="s">
         <v>362</v>
       </c>
-      <c r="F86" s="126" t="s">
+      <c r="F103" s="126" t="s">
         <v>581</v>
       </c>
-      <c r="G86" s="126" t="s">
+      <c r="G103" s="126" t="s">
         <v>582</v>
       </c>
-      <c r="H86" s="126" t="s">
+      <c r="H103" s="126" t="s">
         <v>583</v>
       </c>
-      <c r="I86" s="126" t="s">
+      <c r="I103" s="126" t="s">
         <v>584</v>
       </c>
     </row>
-    <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A87" s="127" t="s">
+    <row r="104" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A104" s="127" t="s">
         <v>585</v>
       </c>
-      <c r="B87" s="149" t="n">
+      <c r="B104" s="149" t="n">
         <f aca="false">'Weapons Sleeve'!B37</f>
         <v>15</v>
       </c>
-      <c r="C87" s="149" t="n">
+      <c r="C104" s="149" t="n">
         <f aca="false">'Weapons Sleeve'!C37</f>
-        <v>24.7490119423027</v>
-      </c>
-      <c r="D87" s="149" t="n">
+        <v>26.0057147643323</v>
+      </c>
+      <c r="D104" s="149" t="n">
         <f aca="false">'Weapons Sleeve'!F37</f>
-        <v>41.6248610187656</v>
-      </c>
-      <c r="E87" s="149" t="n">
+        <v>45.0638775961842</v>
+      </c>
+      <c r="E104" s="149" t="n">
         <f aca="false">'Weapons Sleeve'!I37</f>
-        <v>10.0514482643763</v>
-      </c>
-      <c r="F87" s="149" t="n">
+        <v>10.0563861481051</v>
+      </c>
+      <c r="F104" s="149" t="n">
         <f aca="false">'Weapons Sleeve'!L37</f>
-        <v>45.4510524263535</v>
-      </c>
-      <c r="G87" s="146" t="n">
-        <f aca="false">C87*'Defense Supercycle'!$B$17+D87*'Defense Supercycle'!$B$18+E87*'Defense Supercycle'!$B$19+F87*'Defense Supercycle'!$B$20</f>
-        <v>29.8686457323371</v>
-      </c>
-      <c r="H87" s="150" t="n">
-        <f aca="false">G87/B87</f>
-        <v>1.99124304882247</v>
-      </c>
-      <c r="I87" s="140" t="n">
-        <f aca="false">H87^(1/5)-1</f>
-        <v>0.147690679073171</v>
-      </c>
-    </row>
-    <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A88" s="127" t="s">
+        <v>49.7647872606111</v>
+      </c>
+      <c r="G104" s="146" t="n">
+        <f aca="false">C104*'Defense Supercycle'!$B$17+D104*'Defense Supercycle'!$B$18+E104*'Defense Supercycle'!$B$19+F104*'Defense Supercycle'!$B$20</f>
+        <v>31.941717054303</v>
+      </c>
+      <c r="H104" s="150" t="n">
+        <f aca="false">G104/B104</f>
+        <v>2.1294478036202</v>
+      </c>
+      <c r="I104" s="140" t="n">
+        <f aca="false">H104^(1/5)-1</f>
+        <v>0.16319733860115</v>
+      </c>
+    </row>
+    <row r="105" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A105" s="127" t="s">
         <v>586</v>
       </c>
-      <c r="B88" s="149" t="n">
+      <c r="B105" s="149" t="n">
         <f aca="false">'Weapons Sleeve'!B53</f>
         <v>15</v>
       </c>
-      <c r="C88" s="149" t="n">
+      <c r="C105" s="149" t="n">
         <f aca="false">'Weapons Sleeve'!C53</f>
-        <v>29.9036514177801</v>
-      </c>
-      <c r="D88" s="149" t="n">
+        <v>32.0508478841477</v>
+      </c>
+      <c r="D105" s="149" t="n">
         <f aca="false">'Weapons Sleeve'!F53</f>
-        <v>61.9208807843048</v>
-      </c>
-      <c r="E88" s="149" t="n">
+        <v>69.1995375693674</v>
+      </c>
+      <c r="E105" s="149" t="n">
         <f aca="false">'Weapons Sleeve'!I53</f>
-        <v>8.46960796617199</v>
-      </c>
-      <c r="F88" s="149" t="n">
+        <v>8.47543364081529</v>
+      </c>
+      <c r="F105" s="149" t="n">
         <f aca="false">'Weapons Sleeve'!L53</f>
-        <v>70.0333226779095</v>
-      </c>
-      <c r="G88" s="146" t="n">
-        <f aca="false">C88*'Defense Supercycle'!$B$17+D88*'Defense Supercycle'!$B$18+E88*'Defense Supercycle'!$B$19+F88*'Defense Supercycle'!$B$20</f>
-        <v>40.7123029306895</v>
-      </c>
-      <c r="H88" s="150" t="n">
-        <f aca="false">G88/B88</f>
-        <v>2.71415352871263</v>
-      </c>
-      <c r="I88" s="140" t="n">
-        <f aca="false">H88^(1/7)-1</f>
-        <v>0.153314554940325</v>
-      </c>
-    </row>
-    <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A89" s="127" t="s">
+        <v>79.5122829066679</v>
+      </c>
+      <c r="G105" s="146" t="n">
+        <f aca="false">C105*'Defense Supercycle'!$B$17+D105*'Defense Supercycle'!$B$18+E105*'Defense Supercycle'!$B$19+F105*'Defense Supercycle'!$B$20</f>
+        <v>44.9209234223308</v>
+      </c>
+      <c r="H105" s="150" t="n">
+        <f aca="false">G105/B105</f>
+        <v>2.99472822815538</v>
+      </c>
+      <c r="I105" s="140" t="n">
+        <f aca="false">H105^(1/7)-1</f>
+        <v>0.169636895698346</v>
+      </c>
+    </row>
+    <row r="106" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A106" s="127" t="s">
         <v>587</v>
       </c>
-      <c r="B89" s="149" t="n">
+      <c r="B106" s="149" t="n">
         <f aca="false">'Weapons Sleeve'!B69</f>
         <v>15</v>
       </c>
-      <c r="C89" s="149" t="n">
+      <c r="C106" s="149" t="n">
         <f aca="false">'Weapons Sleeve'!C69</f>
-        <v>39.5605817216917</v>
-      </c>
-      <c r="D89" s="149" t="n">
+        <v>43.6801909523572</v>
+      </c>
+      <c r="D106" s="149" t="n">
         <f aca="false">'Weapons Sleeve'!F69</f>
-        <v>111.905783314577</v>
-      </c>
-      <c r="E89" s="149" t="n">
+        <v>131.160799659986</v>
+      </c>
+      <c r="E106" s="149" t="n">
         <f aca="false">'Weapons Sleeve'!I69</f>
-        <v>6.52535617622677</v>
-      </c>
-      <c r="F89" s="149" t="n">
+        <v>6.53176905600472</v>
+      </c>
+      <c r="F106" s="149" t="n">
         <f aca="false">'Weapons Sleeve'!L69</f>
-        <v>133.424267223044</v>
-      </c>
-      <c r="G89" s="146" t="n">
-        <f aca="false">C89*'Defense Supercycle'!$B$17+D89*'Defense Supercycle'!$B$18+E89*'Defense Supercycle'!$B$19+F89*'Defense Supercycle'!$B$20</f>
-        <v>66.7711511132962</v>
-      </c>
-      <c r="H89" s="150" t="n">
-        <f aca="false">G89/B89</f>
-        <v>4.45141007421975</v>
-      </c>
-      <c r="I89" s="140" t="n">
-        <f aca="false">H89^(1/10)-1</f>
-        <v>0.161046892510819</v>
-      </c>
-    </row>
-    <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A90" s="127" t="s">
+        <v>159.952577339082</v>
+      </c>
+      <c r="G106" s="146" t="n">
+        <f aca="false">C106*'Defense Supercycle'!$B$17+D106*'Defense Supercycle'!$B$18+E106*'Defense Supercycle'!$B$19+F106*'Defense Supercycle'!$B$20</f>
+        <v>77.4189378028201</v>
+      </c>
+      <c r="H106" s="150" t="n">
+        <f aca="false">G106/B106</f>
+        <v>5.16126252018801</v>
+      </c>
+      <c r="I106" s="140" t="n">
+        <f aca="false">H106^(1/10)-1</f>
+        <v>0.17835349681784</v>
+      </c>
+    </row>
+    <row r="107" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A107" s="127" t="s">
         <v>588</v>
       </c>
-      <c r="C90" s="151" t="n">
+      <c r="C107" s="151" t="n">
         <f aca="false">'Weapons Sleeve'!D53</f>
-        <v>1.99357676118534</v>
-      </c>
-      <c r="D90" s="151" t="n">
+        <v>2.13672319227651</v>
+      </c>
+      <c r="D107" s="151" t="n">
         <f aca="false">'Weapons Sleeve'!G53</f>
-        <v>4.12805871895365</v>
-      </c>
-      <c r="E90" s="151" t="n">
+        <v>4.61330250462449</v>
+      </c>
+      <c r="E107" s="151" t="n">
         <f aca="false">'Weapons Sleeve'!J53</f>
-        <v>0.564640531078133</v>
-      </c>
-      <c r="F90" s="151" t="n">
+        <v>0.565028909387686</v>
+      </c>
+      <c r="F107" s="151" t="n">
         <f aca="false">'Weapons Sleeve'!M53</f>
-        <v>4.6688881785273</v>
-      </c>
-    </row>
-    <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A92" s="60" t="s">
+        <v>5.30081886044452</v>
+      </c>
+    </row>
+    <row r="109" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A109" s="60" t="s">
         <v>589</v>
       </c>
-      <c r="B92" s="125"/>
-      <c r="C92" s="125"/>
-      <c r="D92" s="125"/>
-      <c r="E92" s="125"/>
-      <c r="F92" s="125"/>
-      <c r="G92" s="125"/>
-      <c r="H92" s="125"/>
-      <c r="I92" s="125"/>
-      <c r="J92" s="125"/>
-      <c r="K92" s="125"/>
-      <c r="L92" s="125"/>
-      <c r="M92" s="125"/>
-    </row>
-    <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A93" s="127" t="s">
+      <c r="B109" s="125"/>
+      <c r="C109" s="125"/>
+      <c r="D109" s="125"/>
+      <c r="E109" s="125"/>
+      <c r="F109" s="125"/>
+      <c r="G109" s="125"/>
+      <c r="H109" s="125"/>
+      <c r="I109" s="125"/>
+      <c r="J109" s="125"/>
+      <c r="K109" s="125"/>
+      <c r="L109" s="125"/>
+      <c r="M109" s="125"/>
+    </row>
+    <row r="110" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A110" s="127" t="s">
         <v>590</v>
       </c>
-      <c r="B93" s="145" t="str">
-        <f aca="false">IF(ABS('Weapons Sleeve'!S22-C80)&lt;0.00001,"OK","CHECK")</f>
+      <c r="B110" s="145" t="str">
+        <f aca="false">IF(ABS('Weapons Sleeve'!S22-C96)&lt;0.00001,"OK","CHECK")</f>
         <v>OK</v>
       </c>
     </row>
-    <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A94" s="127" t="s">
+    <row r="111" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A111" s="127" t="s">
         <v>591</v>
       </c>
-      <c r="B94" s="145" t="str">
+      <c r="B111" s="145" t="str">
         <f aca="false">IF(ABS('Weapons Sleeve'!C23-'Weapons Sleeve'!B5)&lt;0.001,"OK","CHECK")</f>
         <v>OK</v>
       </c>
     </row>
-    <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A95" s="127" t="s">
+    <row r="112" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A112" s="127" t="s">
         <v>593</v>
       </c>
-      <c r="B95" s="145" t="str">
-        <f aca="false">IF(ABS(L38-1)&lt;0.0001,"OK","CHECK")</f>
+      <c r="B112" s="145" t="str">
+        <f aca="false">IF(ABS(L40-1)&lt;0.0001,"OK","CHECK")</f>
         <v>OK</v>
       </c>
     </row>
-    <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A96" s="127" t="s">
-        <v>658</v>
-      </c>
-      <c r="B96" s="145" t="str">
+    <row r="113" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A113" s="127" t="s">
+        <v>668</v>
+      </c>
+      <c r="B113" s="145" t="str">
         <f aca="false">IF(AND(B6&gt;=3900,B6&lt;=4300),"OK","CHECK")</f>
         <v>OK</v>
       </c>
     </row>
-    <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A98" s="60" t="s">
+    <row r="115" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A115" s="60" t="s">
         <v>78</v>
       </c>
-      <c r="B98" s="125"/>
-      <c r="C98" s="125"/>
-      <c r="D98" s="125"/>
-      <c r="E98" s="125"/>
-      <c r="F98" s="125"/>
-      <c r="G98" s="125"/>
-      <c r="H98" s="125"/>
-      <c r="I98" s="125"/>
-      <c r="J98" s="125"/>
-      <c r="K98" s="125"/>
-      <c r="L98" s="125"/>
-      <c r="M98" s="125"/>
-    </row>
-    <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A99" s="152" t="str">
+      <c r="B115" s="125"/>
+      <c r="C115" s="125"/>
+      <c r="D115" s="125"/>
+      <c r="E115" s="125"/>
+      <c r="F115" s="125"/>
+      <c r="G115" s="125"/>
+      <c r="H115" s="125"/>
+      <c r="I115" s="125"/>
+      <c r="J115" s="125"/>
+      <c r="K115" s="125"/>
+      <c r="L115" s="125"/>
+      <c r="M115" s="125"/>
+    </row>
+    <row r="116" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A116" s="152" t="str">
         <f aca="false">"• IPO "&amp;B8&amp;" at "&amp;TEXT(B9,"0")&amp;"x 2027E EBIT of $"&amp;TEXT(B10,"#,##0")&amp;"M = $"&amp;TEXT(B11/1000,"0.0")&amp;"B; pre-IPO entry at "&amp;TEXT(B12,"0%")&amp;" discount = $"&amp;TEXT(B13/1000,"0.0")&amp;"B. $"&amp;TEXT(B14,"0")&amp;"M buys "&amp;TEXT(B15,"0.00%")&amp;"."</f>
-        <v>• IPO Q1 2027 at 22x 2027E EBIT of $571M = $12.6B; pre-IPO entry at 15% discount = $10.7B. $15M buys 0.14%.</v>
-      </c>
-      <c r="B99" s="152"/>
-      <c r="C99" s="152"/>
-      <c r="D99" s="152"/>
-      <c r="E99" s="152"/>
-      <c r="F99" s="152"/>
-      <c r="G99" s="152"/>
-      <c r="H99" s="152"/>
-      <c r="I99" s="152"/>
-      <c r="J99" s="152"/>
-      <c r="K99" s="152"/>
-      <c r="L99" s="152"/>
-      <c r="M99" s="152"/>
-    </row>
-    <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A100" s="152" t="str">
-        <f aca="false">"• 7-yr implied equity CAGR: Base "&amp;TEXT(C80,"0.0%")&amp;" / Bull "&amp;TEXT(D80,"0.0%")&amp;" / Bear "&amp;TEXT(E80,"0.0%")&amp;" / Shock "&amp;TEXT(F80,"0.0%")&amp;"; probability-weighted "&amp;TEXT(G80,"0.0%")&amp;"."</f>
-        <v>• 7-yr implied equity CAGR: Base 12.4% / Bull 24.7% / Bear -6.1% / Shock 26.9%; probability-weighted 14.9%.</v>
-      </c>
-      <c r="B100" s="152"/>
-      <c r="C100" s="152"/>
-      <c r="D100" s="152"/>
-      <c r="E100" s="152"/>
-      <c r="F100" s="152"/>
-      <c r="G100" s="152"/>
-      <c r="H100" s="152"/>
-      <c r="I100" s="152"/>
-      <c r="J100" s="152"/>
-      <c r="K100" s="152"/>
-      <c r="L100" s="152"/>
-      <c r="M100" s="152"/>
-    </row>
-    <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A101" s="152" t="str">
-        <f aca="false">"• 7-yr stake Expected proceeds $"&amp;TEXT(G88,"0.0")&amp;"M on $"&amp;TEXT(B88,"0.0")&amp;"M = "&amp;TEXT(H88,"0.00")&amp;"x / "&amp;TEXT(I88,"0.0%")&amp;" gross IRR (after 0.88 retention)."</f>
-        <v>• 7-yr stake Expected proceeds $40.7M on $15.0M = 2.71x / 15.3% gross IRR (after 0.88 retention).</v>
-      </c>
-      <c r="B101" s="152"/>
-      <c r="C101" s="152"/>
-      <c r="D101" s="152"/>
-      <c r="E101" s="152"/>
-      <c r="F101" s="152"/>
-      <c r="G101" s="152"/>
-      <c r="H101" s="152"/>
-      <c r="I101" s="152"/>
-      <c r="J101" s="152"/>
-      <c r="K101" s="152"/>
-      <c r="L101" s="152"/>
-      <c r="M101" s="152"/>
-    </row>
-    <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A102" s="152" t="s">
-        <v>659</v>
-      </c>
-      <c r="B102" s="152"/>
-      <c r="C102" s="152"/>
-      <c r="D102" s="152"/>
-      <c r="E102" s="152"/>
-      <c r="F102" s="152"/>
-      <c r="G102" s="152"/>
-      <c r="H102" s="152"/>
-      <c r="I102" s="152"/>
-      <c r="J102" s="152"/>
-      <c r="K102" s="152"/>
-      <c r="L102" s="152"/>
-      <c r="M102" s="152"/>
-    </row>
-    <row r="103" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A103" s="152" t="s">
-        <v>660</v>
-      </c>
-      <c r="B103" s="152"/>
-      <c r="C103" s="152"/>
-      <c r="D103" s="152"/>
-      <c r="E103" s="152"/>
-      <c r="F103" s="152"/>
-      <c r="G103" s="152"/>
-      <c r="H103" s="152"/>
-      <c r="I103" s="152"/>
-      <c r="J103" s="152"/>
-      <c r="K103" s="152"/>
-      <c r="L103" s="152"/>
-      <c r="M103" s="152"/>
+        <v>• IPO Q1 2027 at 22x 2027E EBIT of $574M = $12.6B; pre-IPO entry at 15% discount = $10.7B. $15M buys 0.14%.</v>
+      </c>
+      <c r="B116" s="152"/>
+      <c r="C116" s="152"/>
+      <c r="D116" s="152"/>
+      <c r="E116" s="152"/>
+      <c r="F116" s="152"/>
+      <c r="G116" s="152"/>
+      <c r="H116" s="152"/>
+      <c r="I116" s="152"/>
+      <c r="J116" s="152"/>
+      <c r="K116" s="152"/>
+      <c r="L116" s="152"/>
+      <c r="M116" s="152"/>
+    </row>
+    <row r="117" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A117" s="152" t="str">
+        <f aca="false">"• 7-yr implied equity CAGR: Base "&amp;TEXT(C96,"0.0%")&amp;" / Bull "&amp;TEXT(D96,"0.0%")&amp;" / Bear "&amp;TEXT(E96,"0.0%")&amp;" / Shock "&amp;TEXT(F96,"0.0%")&amp;"; probability-weighted "&amp;TEXT(G96,"0.0%")&amp;"."</f>
+        <v>• 7-yr implied equity CAGR: Base 13.5% / Bull 26.7% / Bear -6.1% / Shock 29.2%; probability-weighted 16.2%.</v>
+      </c>
+      <c r="B117" s="152"/>
+      <c r="C117" s="152"/>
+      <c r="D117" s="152"/>
+      <c r="E117" s="152"/>
+      <c r="F117" s="152"/>
+      <c r="G117" s="152"/>
+      <c r="H117" s="152"/>
+      <c r="I117" s="152"/>
+      <c r="J117" s="152"/>
+      <c r="K117" s="152"/>
+      <c r="L117" s="152"/>
+      <c r="M117" s="152"/>
+    </row>
+    <row r="118" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A118" s="152" t="str">
+        <f aca="false">"• 7-yr stake Expected proceeds $"&amp;TEXT(G105,"0.0")&amp;"M on $"&amp;TEXT(B105,"0.0")&amp;"M = "&amp;TEXT(H105,"0.00")&amp;"x / "&amp;TEXT(I105,"0.0%")&amp;" gross IRR (after 0.88 retention)."</f>
+        <v>• 7-yr stake Expected proceeds $44.9M on $15.0M = 2.99x / 17.0% gross IRR (after 0.88 retention).</v>
+      </c>
+      <c r="B118" s="152"/>
+      <c r="C118" s="152"/>
+      <c r="D118" s="152"/>
+      <c r="E118" s="152"/>
+      <c r="F118" s="152"/>
+      <c r="G118" s="152"/>
+      <c r="H118" s="152"/>
+      <c r="I118" s="152"/>
+      <c r="J118" s="152"/>
+      <c r="K118" s="152"/>
+      <c r="L118" s="152"/>
+      <c r="M118" s="152"/>
+    </row>
+    <row r="119" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A119" s="152" t="s">
+        <v>669</v>
+      </c>
+      <c r="B119" s="152"/>
+      <c r="C119" s="152"/>
+      <c r="D119" s="152"/>
+      <c r="E119" s="152"/>
+      <c r="F119" s="152"/>
+      <c r="G119" s="152"/>
+      <c r="H119" s="152"/>
+      <c r="I119" s="152"/>
+      <c r="J119" s="152"/>
+      <c r="K119" s="152"/>
+      <c r="L119" s="152"/>
+      <c r="M119" s="152"/>
+    </row>
+    <row r="120" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A120" s="152" t="s">
+        <v>670</v>
+      </c>
+      <c r="B120" s="152"/>
+      <c r="C120" s="152"/>
+      <c r="D120" s="152"/>
+      <c r="E120" s="152"/>
+      <c r="F120" s="152"/>
+      <c r="G120" s="152"/>
+      <c r="H120" s="152"/>
+      <c r="I120" s="152"/>
+      <c r="J120" s="152"/>
+      <c r="K120" s="152"/>
+      <c r="L120" s="152"/>
+      <c r="M120" s="152"/>
     </row>
   </sheetData>
-  <mergeCells count="31">
+  <mergeCells count="36">
     <mergeCell ref="A2:M2"/>
     <mergeCell ref="C5:M5"/>
     <mergeCell ref="C6:M6"/>
@@ -14973,15 +15612,20 @@
     <mergeCell ref="F25:M25"/>
     <mergeCell ref="F26:M26"/>
     <mergeCell ref="F27:M27"/>
-    <mergeCell ref="M31:M37"/>
-    <mergeCell ref="F41:M41"/>
-    <mergeCell ref="F42:M42"/>
+    <mergeCell ref="F28:M28"/>
+    <mergeCell ref="M32:M39"/>
     <mergeCell ref="F43:M43"/>
-    <mergeCell ref="A99:M99"/>
-    <mergeCell ref="A100:M100"/>
-    <mergeCell ref="A101:M101"/>
-    <mergeCell ref="A102:M102"/>
-    <mergeCell ref="A103:M103"/>
+    <mergeCell ref="F44:M44"/>
+    <mergeCell ref="F45:M45"/>
+    <mergeCell ref="F46:M46"/>
+    <mergeCell ref="F49:M49"/>
+    <mergeCell ref="F50:M50"/>
+    <mergeCell ref="F51:M51"/>
+    <mergeCell ref="A116:M116"/>
+    <mergeCell ref="A117:M117"/>
+    <mergeCell ref="A118:M118"/>
+    <mergeCell ref="A119:M119"/>
+    <mergeCell ref="A120:M120"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -15015,7 +15659,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="10" t="s">
-        <v>661</v>
+        <v>671</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -15033,7 +15677,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="41" t="s">
-        <v>662</v>
+        <v>672</v>
       </c>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -15212,7 +15856,7 @@
         <v>249</v>
       </c>
       <c r="E11" s="43" t="s">
-        <v>663</v>
+        <v>673</v>
       </c>
       <c r="F11" s="43" t="s">
         <v>36</v>
@@ -15236,7 +15880,7 @@
     </row>
     <row r="12" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="44" t="s">
-        <v>664</v>
+        <v>674</v>
       </c>
       <c r="B12" s="79" t="n">
         <v>10100</v>
@@ -15249,7 +15893,7 @@
         <v>0.00346534653465347</v>
       </c>
       <c r="E12" s="47" t="s">
-        <v>665</v>
+        <v>675</v>
       </c>
       <c r="F12" s="80" t="n">
         <v>0.28</v>
@@ -15264,7 +15908,7 @@
         <v>-0.18</v>
       </c>
       <c r="J12" s="75" t="s">
-        <v>666</v>
+        <v>676</v>
       </c>
       <c r="K12" s="1"/>
       <c r="L12" s="1"/>
@@ -15273,7 +15917,7 @@
     </row>
     <row r="13" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="44" t="s">
-        <v>667</v>
+        <v>677</v>
       </c>
       <c r="B13" s="79" t="n">
         <v>10100</v>
@@ -15286,7 +15930,7 @@
         <v>0.00311881188118812</v>
       </c>
       <c r="E13" s="47" t="s">
-        <v>668</v>
+        <v>678</v>
       </c>
       <c r="F13" s="80" t="n">
         <v>0.27</v>
@@ -15301,7 +15945,7 @@
         <v>-0.16</v>
       </c>
       <c r="J13" s="75" t="s">
-        <v>669</v>
+        <v>679</v>
       </c>
       <c r="K13" s="1"/>
       <c r="L13" s="1"/>
@@ -15310,7 +15954,7 @@
     </row>
     <row r="14" customFormat="false" ht="71.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="44" t="s">
-        <v>670</v>
+        <v>680</v>
       </c>
       <c r="B14" s="79" t="n">
         <v>3760</v>
@@ -15323,7 +15967,7 @@
         <v>0.00651595744680851</v>
       </c>
       <c r="E14" s="47" t="s">
-        <v>671</v>
+        <v>681</v>
       </c>
       <c r="F14" s="80" t="n">
         <v>0.22</v>
@@ -15338,7 +15982,7 @@
         <v>-0.05</v>
       </c>
       <c r="J14" s="75" t="s">
-        <v>672</v>
+        <v>682</v>
       </c>
       <c r="K14" s="1"/>
       <c r="L14" s="1"/>
@@ -15347,7 +15991,7 @@
     </row>
     <row r="15" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="44" t="s">
-        <v>673</v>
+        <v>683</v>
       </c>
       <c r="B15" s="79" t="n">
         <v>280</v>
@@ -15360,7 +16004,7 @@
         <v>0.0625</v>
       </c>
       <c r="E15" s="47" t="s">
-        <v>674</v>
+        <v>684</v>
       </c>
       <c r="F15" s="80" t="n">
         <v>0.14</v>
@@ -15375,7 +16019,7 @@
         <v>-0.14</v>
       </c>
       <c r="J15" s="75" t="s">
-        <v>675</v>
+        <v>685</v>
       </c>
       <c r="K15" s="1"/>
       <c r="L15" s="1"/>
@@ -15384,7 +16028,7 @@
     </row>
     <row r="16" customFormat="false" ht="82.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="44" t="s">
-        <v>676</v>
+        <v>686</v>
       </c>
       <c r="B16" s="79" t="n">
         <v>945</v>
@@ -15397,7 +16041,7 @@
         <v>0.0148148148148148</v>
       </c>
       <c r="E16" s="47" t="s">
-        <v>677</v>
+        <v>687</v>
       </c>
       <c r="F16" s="80" t="n">
         <v>0.07</v>
@@ -15412,7 +16056,7 @@
         <v>-0.08</v>
       </c>
       <c r="J16" s="75" t="s">
-        <v>678</v>
+        <v>688</v>
       </c>
       <c r="K16" s="1"/>
       <c r="L16" s="1"/>
@@ -15421,7 +16065,7 @@
     </row>
     <row r="17" customFormat="false" ht="93.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="44" t="s">
-        <v>679</v>
+        <v>689</v>
       </c>
       <c r="B17" s="79" t="n">
         <v>110</v>
@@ -15434,7 +16078,7 @@
         <v>0.0636363636363636</v>
       </c>
       <c r="E17" s="47" t="s">
-        <v>680</v>
+        <v>690</v>
       </c>
       <c r="F17" s="80" t="n">
         <v>0.2</v>
@@ -15449,7 +16093,7 @@
         <v>-0.28</v>
       </c>
       <c r="J17" s="75" t="s">
-        <v>681</v>
+        <v>691</v>
       </c>
       <c r="K17" s="1"/>
       <c r="L17" s="1"/>
@@ -15458,7 +16102,7 @@
     </row>
     <row r="18" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="44" t="s">
-        <v>682</v>
+        <v>692</v>
       </c>
       <c r="B18" s="79" t="n">
         <v>18000</v>
@@ -15471,7 +16115,7 @@
         <v>0.000583333333333333</v>
       </c>
       <c r="E18" s="47" t="s">
-        <v>683</v>
+        <v>693</v>
       </c>
       <c r="F18" s="80" t="n">
         <v>0.25</v>
@@ -15486,7 +16130,7 @@
         <v>-0.12</v>
       </c>
       <c r="J18" s="75" t="s">
-        <v>684</v>
+        <v>694</v>
       </c>
       <c r="K18" s="1"/>
       <c r="L18" s="1"/>
@@ -15495,7 +16139,7 @@
     </row>
     <row r="19" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="44" t="s">
-        <v>685</v>
+        <v>695</v>
       </c>
       <c r="B19" s="79" t="n">
         <v>3730</v>
@@ -15508,7 +16152,7 @@
         <v>0.00402144772117963</v>
       </c>
       <c r="E19" s="47" t="s">
-        <v>686</v>
+        <v>696</v>
       </c>
       <c r="F19" s="80" t="n">
         <v>0.15</v>
@@ -15523,7 +16167,7 @@
         <v>-0.16</v>
       </c>
       <c r="J19" s="75" t="s">
-        <v>687</v>
+        <v>697</v>
       </c>
       <c r="K19" s="1"/>
       <c r="L19" s="1"/>
@@ -15532,7 +16176,7 @@
     </row>
     <row r="20" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="44" t="s">
-        <v>688</v>
+        <v>698</v>
       </c>
       <c r="B20" s="79" t="n">
         <v>159000</v>
@@ -15545,7 +16189,7 @@
         <v>0.000283018867924528</v>
       </c>
       <c r="E20" s="47" t="s">
-        <v>689</v>
+        <v>699</v>
       </c>
       <c r="F20" s="80" t="n">
         <v>0.18</v>
@@ -15560,7 +16204,7 @@
         <v>-0.08</v>
       </c>
       <c r="J20" s="75" t="s">
-        <v>690</v>
+        <v>700</v>
       </c>
       <c r="K20" s="1"/>
       <c r="L20" s="1"/>
@@ -15569,7 +16213,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="16" t="s">
-        <v>691</v>
+        <v>701</v>
       </c>
       <c r="B21" s="1"/>
       <c r="C21" s="50" t="n">
@@ -17625,7 +18269,7 @@
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="42" t="s">
-        <v>692</v>
+        <v>702</v>
       </c>
       <c r="B65" s="1"/>
       <c r="C65" s="1"/>
@@ -17643,7 +18287,7 @@
     </row>
     <row r="66" customFormat="false" ht="159.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A66" s="11" t="s">
-        <v>693</v>
+        <v>703</v>
       </c>
       <c r="B66" s="11"/>
       <c r="C66" s="11"/>
@@ -17691,7 +18335,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="167" t="s">
-        <v>694</v>
+        <v>704</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -17701,7 +18345,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="41" t="s">
-        <v>695</v>
+        <v>705</v>
       </c>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -17719,7 +18363,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="42" t="s">
-        <v>696</v>
+        <v>706</v>
       </c>
       <c r="B4" s="1"/>
       <c r="C4" s="1"/>
@@ -17753,7 +18397,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="41" t="s">
-        <v>697</v>
+        <v>707</v>
       </c>
       <c r="B7" s="1"/>
       <c r="C7" s="1"/>
@@ -17771,7 +18415,7 @@
     </row>
     <row r="9" customFormat="false" ht="36.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="11" t="s">
-        <v>698</v>
+        <v>708</v>
       </c>
       <c r="B9" s="11"/>
       <c r="C9" s="11"/>
@@ -17789,7 +18433,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="60" t="s">
-        <v>699</v>
+        <v>709</v>
       </c>
       <c r="B11" s="1"/>
       <c r="C11" s="1"/>
@@ -17844,7 +18488,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="44" t="s">
-        <v>700</v>
+        <v>710</v>
       </c>
       <c r="B14" s="68" t="n">
         <f aca="false">'Fund Economics'!B12/Assumptions!$B$5</f>
@@ -17869,7 +18513,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="44" t="s">
-        <v>701</v>
+        <v>711</v>
       </c>
       <c r="B15" s="68" t="n">
         <f aca="false">'Fund Economics'!B6/Assumptions!$B$5</f>
@@ -17919,7 +18563,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="44" t="s">
-        <v>702</v>
+        <v>712</v>
       </c>
       <c r="B17" s="68" t="n">
         <f aca="false">(1+'PME, DPI &amp; Sensitivity'!$B$5)^5</f>
@@ -17944,7 +18588,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="65" t="s">
-        <v>703</v>
+        <v>713</v>
       </c>
       <c r="B18" s="67" t="n">
         <f aca="false">'Fund Economics'!B14/(1+'PME, DPI &amp; Sensitivity'!$B$5)^5</f>
@@ -17969,7 +18613,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="44" t="s">
-        <v>704</v>
+        <v>714</v>
       </c>
       <c r="B19" s="46" t="n">
         <f aca="false">('Fund Economics'!B14/(1+'PME, DPI &amp; Sensitivity'!$B$5)^5)^(1/5)-1</f>
@@ -17994,7 +18638,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="44" t="s">
-        <v>705</v>
+        <v>715</v>
       </c>
       <c r="B20" s="68" t="n">
         <f aca="false">(1+'PME, DPI &amp; Sensitivity'!$B$6)^5</f>
@@ -18019,7 +18663,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="65" t="s">
-        <v>706</v>
+        <v>716</v>
       </c>
       <c r="B21" s="67" t="n">
         <f aca="false">'Fund Economics'!B14/(1+'PME, DPI &amp; Sensitivity'!$B$6)^5</f>
@@ -18044,7 +18688,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="44" t="s">
-        <v>707</v>
+        <v>717</v>
       </c>
       <c r="B22" s="46" t="n">
         <f aca="false">('Fund Economics'!B14/(1+'PME, DPI &amp; Sensitivity'!$B$6)^5)^(1/5)-1</f>
@@ -18069,7 +18713,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="55" t="s">
-        <v>708</v>
+        <v>718</v>
       </c>
       <c r="B23" s="68" t="n">
         <f aca="false">('Fund Economics'!B6/Assumptions!$B$5)/(1+'PME, DPI &amp; Sensitivity'!$B$5)^5</f>
@@ -18094,7 +18738,7 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="55" t="s">
-        <v>709</v>
+        <v>719</v>
       </c>
       <c r="B24" s="68" t="n">
         <f aca="false">('Fund Economics'!B6/Assumptions!$B$5)/(1+'PME, DPI &amp; Sensitivity'!$B$6)^5</f>
@@ -18135,7 +18779,7 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="60" t="s">
-        <v>710</v>
+        <v>720</v>
       </c>
       <c r="B27" s="1"/>
       <c r="C27" s="1"/>
@@ -18190,7 +18834,7 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="44" t="s">
-        <v>700</v>
+        <v>710</v>
       </c>
       <c r="B30" s="68" t="n">
         <f aca="false">'Fund Economics'!B28/Assumptions!$B$5</f>
@@ -18215,7 +18859,7 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="44" t="s">
-        <v>701</v>
+        <v>711</v>
       </c>
       <c r="B31" s="68" t="n">
         <f aca="false">'Fund Economics'!B22/Assumptions!$B$5</f>
@@ -18265,7 +18909,7 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="44" t="s">
-        <v>702</v>
+        <v>712</v>
       </c>
       <c r="B33" s="68" t="n">
         <f aca="false">(1+'PME, DPI &amp; Sensitivity'!$B$5)^7</f>
@@ -18290,7 +18934,7 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="65" t="s">
-        <v>703</v>
+        <v>713</v>
       </c>
       <c r="B34" s="67" t="n">
         <f aca="false">'Fund Economics'!B30/(1+'PME, DPI &amp; Sensitivity'!$B$5)^7</f>
@@ -18315,7 +18959,7 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="44" t="s">
-        <v>704</v>
+        <v>714</v>
       </c>
       <c r="B35" s="46" t="n">
         <f aca="false">('Fund Economics'!B30/(1+'PME, DPI &amp; Sensitivity'!$B$5)^7)^(1/7)-1</f>
@@ -18340,7 +18984,7 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="44" t="s">
-        <v>705</v>
+        <v>715</v>
       </c>
       <c r="B36" s="68" t="n">
         <f aca="false">(1+'PME, DPI &amp; Sensitivity'!$B$6)^7</f>
@@ -18365,7 +19009,7 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="65" t="s">
-        <v>706</v>
+        <v>716</v>
       </c>
       <c r="B37" s="67" t="n">
         <f aca="false">'Fund Economics'!B30/(1+'PME, DPI &amp; Sensitivity'!$B$6)^7</f>
@@ -18390,7 +19034,7 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="44" t="s">
-        <v>707</v>
+        <v>717</v>
       </c>
       <c r="B38" s="46" t="n">
         <f aca="false">('Fund Economics'!B30/(1+'PME, DPI &amp; Sensitivity'!$B$6)^7)^(1/7)-1</f>
@@ -18415,7 +19059,7 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="55" t="s">
-        <v>708</v>
+        <v>718</v>
       </c>
       <c r="B39" s="68" t="n">
         <f aca="false">('Fund Economics'!B22/Assumptions!$B$5)/(1+'PME, DPI &amp; Sensitivity'!$B$5)^7</f>
@@ -18440,7 +19084,7 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="55" t="s">
-        <v>709</v>
+        <v>719</v>
       </c>
       <c r="B40" s="68" t="n">
         <f aca="false">('Fund Economics'!B22/Assumptions!$B$5)/(1+'PME, DPI &amp; Sensitivity'!$B$6)^7</f>
@@ -18481,7 +19125,7 @@
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="60" t="s">
-        <v>711</v>
+        <v>721</v>
       </c>
       <c r="B43" s="1"/>
       <c r="C43" s="1"/>
@@ -18536,7 +19180,7 @@
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="44" t="s">
-        <v>700</v>
+        <v>710</v>
       </c>
       <c r="B46" s="68" t="n">
         <f aca="false">'Fund Economics'!B44/Assumptions!$B$5</f>
@@ -18561,7 +19205,7 @@
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="44" t="s">
-        <v>701</v>
+        <v>711</v>
       </c>
       <c r="B47" s="68" t="n">
         <f aca="false">'Fund Economics'!B38/Assumptions!$B$5</f>
@@ -18611,7 +19255,7 @@
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A49" s="44" t="s">
-        <v>702</v>
+        <v>712</v>
       </c>
       <c r="B49" s="68" t="n">
         <f aca="false">(1+'PME, DPI &amp; Sensitivity'!$B$5)^10</f>
@@ -18636,7 +19280,7 @@
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A50" s="65" t="s">
-        <v>703</v>
+        <v>713</v>
       </c>
       <c r="B50" s="67" t="n">
         <f aca="false">'Fund Economics'!B46/(1+'PME, DPI &amp; Sensitivity'!$B$5)^10</f>
@@ -18661,7 +19305,7 @@
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A51" s="44" t="s">
-        <v>704</v>
+        <v>714</v>
       </c>
       <c r="B51" s="46" t="n">
         <f aca="false">('Fund Economics'!B46/(1+'PME, DPI &amp; Sensitivity'!$B$5)^10)^(1/10)-1</f>
@@ -18686,7 +19330,7 @@
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A52" s="44" t="s">
-        <v>705</v>
+        <v>715</v>
       </c>
       <c r="B52" s="68" t="n">
         <f aca="false">(1+'PME, DPI &amp; Sensitivity'!$B$6)^10</f>
@@ -18711,7 +19355,7 @@
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A53" s="65" t="s">
-        <v>706</v>
+        <v>716</v>
       </c>
       <c r="B53" s="67" t="n">
         <f aca="false">'Fund Economics'!B46/(1+'PME, DPI &amp; Sensitivity'!$B$6)^10</f>
@@ -18736,7 +19380,7 @@
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A54" s="44" t="s">
-        <v>707</v>
+        <v>717</v>
       </c>
       <c r="B54" s="46" t="n">
         <f aca="false">('Fund Economics'!B46/(1+'PME, DPI &amp; Sensitivity'!$B$6)^10)^(1/10)-1</f>
@@ -18761,7 +19405,7 @@
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A55" s="55" t="s">
-        <v>708</v>
+        <v>718</v>
       </c>
       <c r="B55" s="68" t="n">
         <f aca="false">('Fund Economics'!B38/Assumptions!$B$5)/(1+'PME, DPI &amp; Sensitivity'!$B$5)^10</f>
@@ -18786,7 +19430,7 @@
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A56" s="55" t="s">
-        <v>709</v>
+        <v>719</v>
       </c>
       <c r="B56" s="68" t="n">
         <f aca="false">('Fund Economics'!B38/Assumptions!$B$5)/(1+'PME, DPI &amp; Sensitivity'!$B$6)^10</f>
@@ -18827,7 +19471,7 @@
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A59" s="168" t="s">
-        <v>712</v>
+        <v>722</v>
       </c>
       <c r="B59" s="1"/>
       <c r="C59" s="1"/>
@@ -18837,7 +19481,7 @@
     </row>
     <row r="60" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A60" s="11" t="s">
-        <v>713</v>
+        <v>723</v>
       </c>
       <c r="B60" s="11"/>
       <c r="C60" s="11"/>
@@ -18847,19 +19491,19 @@
     </row>
     <row r="61" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A61" s="53" t="s">
-        <v>714</v>
+        <v>724</v>
       </c>
       <c r="B61" s="43" t="s">
-        <v>715</v>
+        <v>725</v>
       </c>
       <c r="C61" s="43" t="s">
-        <v>716</v>
+        <v>726</v>
       </c>
       <c r="D61" s="43" t="s">
-        <v>717</v>
+        <v>727</v>
       </c>
       <c r="E61" s="43" t="s">
-        <v>718</v>
+        <v>728</v>
       </c>
       <c r="F61" s="54"/>
     </row>
@@ -18880,7 +19524,7 @@
         <v>0.182691512588688</v>
       </c>
       <c r="E62" s="75" t="s">
-        <v>719</v>
+        <v>729</v>
       </c>
       <c r="F62" s="169"/>
     </row>
@@ -19040,7 +19684,7 @@
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="172" t="s">
-        <v>720</v>
+        <v>730</v>
       </c>
       <c r="B72" s="172"/>
       <c r="C72" s="172"/>
@@ -19053,13 +19697,13 @@
         <v>27</v>
       </c>
       <c r="B73" s="173" t="s">
-        <v>721</v>
+        <v>731</v>
       </c>
       <c r="C73" s="173" t="s">
-        <v>722</v>
+        <v>732</v>
       </c>
       <c r="D73" s="173" t="s">
-        <v>723</v>
+        <v>733</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19068,15 +19712,15 @@
       </c>
       <c r="B74" s="175" t="n">
         <f aca="false">'Holdco Summary'!F38</f>
-        <v>2.27595084398942</v>
+        <v>2.27789073310531</v>
       </c>
       <c r="C74" s="175" t="n">
         <f aca="false">'Holdco Summary'!F59</f>
-        <v>3.45301348617188</v>
+        <v>3.45695158110001</v>
       </c>
       <c r="D74" s="175" t="n">
         <f aca="false">'Holdco Summary'!F80</f>
-        <v>6.9198197348059</v>
+        <v>6.92978280116615</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19085,15 +19729,15 @@
       </c>
       <c r="B75" s="175" t="n">
         <f aca="false">'Holdco Summary'!F39</f>
-        <v>2.27595084398942</v>
+        <v>2.27789073310531</v>
       </c>
       <c r="C75" s="175" t="n">
         <f aca="false">'Holdco Summary'!F60</f>
-        <v>3.45301348617188</v>
+        <v>3.45695158110001</v>
       </c>
       <c r="D75" s="175" t="n">
         <f aca="false">'Holdco Summary'!F81</f>
-        <v>6.9198197348059</v>
+        <v>6.92978280116615</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19102,66 +19746,66 @@
       </c>
       <c r="B76" s="176" t="n">
         <f aca="false">'Holdco Summary'!F40</f>
-        <v>0.178779502986822</v>
+        <v>0.178980379232583</v>
       </c>
       <c r="C76" s="176" t="n">
         <f aca="false">'Holdco Summary'!F61</f>
-        <v>0.193673267252674</v>
+        <v>0.193867652435981</v>
       </c>
       <c r="D76" s="176" t="n">
         <f aca="false">'Holdco Summary'!F82</f>
-        <v>0.213415331908954</v>
+        <v>0.213589924779007</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="177" t="s">
-        <v>703</v>
+        <v>713</v>
       </c>
       <c r="B77" s="178" t="n">
         <f aca="false">'Holdco Summary'!F41</f>
-        <v>1.47921188718093</v>
+        <v>1.48047268200329</v>
       </c>
       <c r="C77" s="178" t="n">
         <f aca="false">'Holdco Summary'!F62</f>
-        <v>1.88891662484182</v>
+        <v>1.89107089762696</v>
       </c>
       <c r="D77" s="178" t="n">
         <f aca="false">'Holdco Summary'!F83</f>
-        <v>2.92300663775207</v>
+        <v>2.92721514465246</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="177" t="s">
-        <v>706</v>
+        <v>716</v>
       </c>
       <c r="B78" s="178" t="n">
         <f aca="false">'Holdco Summary'!F42</f>
-        <v>1.23529493442159</v>
+        <v>1.23634782851398</v>
       </c>
       <c r="C78" s="178" t="n">
         <f aca="false">'Holdco Summary'!F63</f>
-        <v>1.46774013529633</v>
+        <v>1.46941406446161</v>
       </c>
       <c r="D78" s="178" t="n">
         <f aca="false">'Holdco Summary'!F84</f>
-        <v>2.03849826500703</v>
+        <v>2.04143326826837</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="177" t="s">
-        <v>724</v>
+        <v>734</v>
       </c>
       <c r="B79" s="178" t="n">
         <f aca="false">'Holdco Summary'!F43</f>
-        <v>1.13154981031405</v>
+        <v>1.13251427805153</v>
       </c>
       <c r="C79" s="178" t="n">
         <f aca="false">'Holdco Summary'!F64</f>
-        <v>1.29811566880597</v>
+        <v>1.29959614455619</v>
       </c>
       <c r="D79" s="178" t="n">
         <f aca="false">'Holdco Summary'!F85</f>
-        <v>1.71047360756428</v>
+        <v>1.71293632519461</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19170,42 +19814,42 @@
       </c>
       <c r="B80" s="179" t="n">
         <f aca="false">'Holdco Summary'!F44</f>
-        <v>0.0250256547711496</v>
+        <v>0.0252003297674637</v>
       </c>
       <c r="C80" s="179" t="n">
         <f aca="false">'Holdco Summary'!F65</f>
-        <v>0.0379767541327605</v>
+        <v>0.0381457847269406</v>
       </c>
       <c r="D80" s="179" t="n">
         <f aca="false">'Holdco Summary'!F86</f>
-        <v>0.0551437668773511</v>
+        <v>0.0552955867643536</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="180" t="s">
-        <v>704</v>
+        <v>714</v>
       </c>
       <c r="B81" s="181" t="n">
         <f aca="false">B77^(1/5)-1</f>
-        <v>0.0814490853090109</v>
+        <v>0.0816333754427367</v>
       </c>
       <c r="C81" s="181" t="n">
         <f aca="false">C77^(1/7)-1</f>
-        <v>0.0951130892226371</v>
+        <v>0.0952914242531939</v>
       </c>
       <c r="D81" s="181" t="n">
         <f aca="false">D77^(1/10)-1</f>
-        <v>0.113225075145829</v>
+        <v>0.113385252090832</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="182" t="s">
-        <v>725</v>
+        <v>735</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="183" t="s">
-        <v>726</v>
+        <v>736</v>
       </c>
       <c r="B84" s="183"/>
       <c r="C84" s="183"/>
@@ -19215,24 +19859,24 @@
     </row>
     <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="182" t="s">
-        <v>727</v>
+        <v>737</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="173" t="s">
-        <v>714</v>
+        <v>724</v>
       </c>
       <c r="B86" s="173" t="s">
-        <v>715</v>
+        <v>725</v>
       </c>
       <c r="C86" s="173" t="s">
-        <v>716</v>
+        <v>726</v>
       </c>
       <c r="D86" s="173" t="s">
-        <v>717</v>
+        <v>727</v>
       </c>
       <c r="E86" s="173" t="s">
-        <v>718</v>
+        <v>728</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19241,18 +19885,18 @@
       </c>
       <c r="B87" s="185" t="n">
         <f aca="false">(((1-$A87)*('Defense Supercycle'!$B$17*'Holdco Summary'!B37+'Defense Supercycle'!$B$18*'Holdco Summary'!C37+'Defense Supercycle'!$B$19*'Holdco Summary'!D37)/('Defense Supercycle'!$B$17+'Defense Supercycle'!$B$18+'Defense Supercycle'!$B$19)+$A87*'Holdco Summary'!E37)/'Holdco Summary'!$B$9)^(1/5)-1</f>
-        <v>0.172041492331849</v>
+        <v>0.172207840878696</v>
       </c>
       <c r="C87" s="185" t="n">
         <f aca="false">(((1-$A87)*('Defense Supercycle'!$B$17*'Holdco Summary'!B58+'Defense Supercycle'!$B$18*'Holdco Summary'!C58+'Defense Supercycle'!$B$19*'Holdco Summary'!D58)/('Defense Supercycle'!$B$17+'Defense Supercycle'!$B$18+'Defense Supercycle'!$B$19)+$A87*'Holdco Summary'!E58)/'Holdco Summary'!$B$9)^(1/7)-1</f>
-        <v>0.185622386660826</v>
+        <v>0.18578010834768</v>
       </c>
       <c r="D87" s="185" t="n">
         <f aca="false">(((1-$A87)*('Defense Supercycle'!$B$17*'Holdco Summary'!B79+'Defense Supercycle'!$B$18*'Holdco Summary'!C79+'Defense Supercycle'!$B$19*'Holdco Summary'!D79)/('Defense Supercycle'!$B$17+'Defense Supercycle'!$B$18+'Defense Supercycle'!$B$19)+$A87*'Holdco Summary'!E79)/'Holdco Summary'!$B$9)^(1/10)-1</f>
-        <v>0.204103263202339</v>
+        <v>0.204241159928257</v>
       </c>
       <c r="E87" s="186" t="s">
-        <v>719</v>
+        <v>729</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19261,15 +19905,15 @@
       </c>
       <c r="B88" s="185" t="n">
         <f aca="false">(((1-$A88)*('Defense Supercycle'!$B$17*'Holdco Summary'!B37+'Defense Supercycle'!$B$18*'Holdco Summary'!C37+'Defense Supercycle'!$B$19*'Holdco Summary'!D37)/('Defense Supercycle'!$B$17+'Defense Supercycle'!$B$18+'Defense Supercycle'!$B$19)+$A88*'Holdco Summary'!E37)/'Holdco Summary'!$B$9)^(1/5)-1</f>
-        <v>0.174304711633184</v>
+        <v>0.174482743829994</v>
       </c>
       <c r="C88" s="185" t="n">
         <f aca="false">(((1-$A88)*('Defense Supercycle'!$B$17*'Holdco Summary'!B58+'Defense Supercycle'!$B$18*'Holdco Summary'!C58+'Defense Supercycle'!$B$19*'Holdco Summary'!D58)/('Defense Supercycle'!$B$17+'Defense Supercycle'!$B$18+'Defense Supercycle'!$B$19)+$A88*'Holdco Summary'!E58)/'Holdco Summary'!$B$9)^(1/7)-1</f>
-        <v>0.188342511590328</v>
+        <v>0.188512782942706</v>
       </c>
       <c r="D88" s="185" t="n">
         <f aca="false">(((1-$A88)*('Defense Supercycle'!$B$17*'Holdco Summary'!B79+'Defense Supercycle'!$B$18*'Holdco Summary'!C79+'Defense Supercycle'!$B$19*'Holdco Summary'!D79)/('Defense Supercycle'!$B$17+'Defense Supercycle'!$B$18+'Defense Supercycle'!$B$19)+$A88*'Holdco Summary'!E79)/'Holdco Summary'!$B$9)^(1/10)-1</f>
-        <v>0.207279596577157</v>
+        <v>0.207430289114929</v>
       </c>
       <c r="E88" s="186" t="str">
         <f aca="false">IF(ABS($A88-'Defense Supercycle'!$B$20)&lt;0.0001,"current base case","")</f>
@@ -19282,15 +19926,15 @@
       </c>
       <c r="B89" s="185" t="n">
         <f aca="false">(((1-$A89)*('Defense Supercycle'!$B$17*'Holdco Summary'!B37+'Defense Supercycle'!$B$18*'Holdco Summary'!C37+'Defense Supercycle'!$B$19*'Holdco Summary'!D37)/('Defense Supercycle'!$B$17+'Defense Supercycle'!$B$18+'Defense Supercycle'!$B$19)+$A89*'Holdco Summary'!E37)/'Holdco Summary'!$B$9)^(1/5)-1</f>
-        <v>0.176550616781995</v>
+        <v>0.176740156722539</v>
       </c>
       <c r="C89" s="185" t="n">
         <f aca="false">(((1-$A89)*('Defense Supercycle'!$B$17*'Holdco Summary'!B58+'Defense Supercycle'!$B$18*'Holdco Summary'!C58+'Defense Supercycle'!$B$19*'Holdco Summary'!D58)/('Defense Supercycle'!$B$17+'Defense Supercycle'!$B$18+'Defense Supercycle'!$B$19)+$A89*'Holdco Summary'!E58)/'Holdco Summary'!$B$9)^(1/7)-1</f>
-        <v>0.191025783454299</v>
+        <v>0.191208271207095</v>
       </c>
       <c r="D89" s="185" t="n">
         <f aca="false">(((1-$A89)*('Defense Supercycle'!$B$17*'Holdco Summary'!B79+'Defense Supercycle'!$B$18*'Holdco Summary'!C79+'Defense Supercycle'!$B$19*'Holdco Summary'!D79)/('Defense Supercycle'!$B$17+'Defense Supercycle'!$B$18+'Defense Supercycle'!$B$19)+$A89*'Holdco Summary'!E79)/'Holdco Summary'!$B$9)^(1/10)-1</f>
-        <v>0.210382453298415</v>
+        <v>0.210545364352326</v>
       </c>
       <c r="E89" s="186" t="str">
         <f aca="false">IF(ABS($A89-'Defense Supercycle'!$B$20)&lt;0.0001,"current base case","")</f>
@@ -19303,15 +19947,15 @@
       </c>
       <c r="B90" s="185" t="n">
         <f aca="false">(((1-$A90)*('Defense Supercycle'!$B$17*'Holdco Summary'!B37+'Defense Supercycle'!$B$18*'Holdco Summary'!C37+'Defense Supercycle'!$B$19*'Holdco Summary'!D37)/('Defense Supercycle'!$B$17+'Defense Supercycle'!$B$18+'Defense Supercycle'!$B$19)+$A90*'Holdco Summary'!E37)/'Holdco Summary'!$B$9)^(1/5)-1</f>
-        <v>0.178779502986822</v>
+        <v>0.178980379232583</v>
       </c>
       <c r="C90" s="185" t="n">
         <f aca="false">(((1-$A90)*('Defense Supercycle'!$B$17*'Holdco Summary'!B58+'Defense Supercycle'!$B$18*'Holdco Summary'!C58+'Defense Supercycle'!$B$19*'Holdco Summary'!D58)/('Defense Supercycle'!$B$17+'Defense Supercycle'!$B$18+'Defense Supercycle'!$B$19)+$A90*'Holdco Summary'!E58)/'Holdco Summary'!$B$9)^(1/7)-1</f>
-        <v>0.193673267252674</v>
+        <v>0.193867652435981</v>
       </c>
       <c r="D90" s="185" t="n">
         <f aca="false">(((1-$A90)*('Defense Supercycle'!$B$17*'Holdco Summary'!B79+'Defense Supercycle'!$B$18*'Holdco Summary'!C79+'Defense Supercycle'!$B$19*'Holdco Summary'!D79)/('Defense Supercycle'!$B$17+'Defense Supercycle'!$B$18+'Defense Supercycle'!$B$19)+$A90*'Holdco Summary'!E79)/'Holdco Summary'!$B$9)^(1/10)-1</f>
-        <v>0.213415331908954</v>
+        <v>0.213589924779007</v>
       </c>
       <c r="E90" s="186" t="str">
         <f aca="false">IF(ABS($A90-'Defense Supercycle'!$B$20)&lt;0.0001,"current base case","")</f>
@@ -19324,15 +19968,15 @@
       </c>
       <c r="B91" s="185" t="n">
         <f aca="false">(((1-$A91)*('Defense Supercycle'!$B$17*'Holdco Summary'!B37+'Defense Supercycle'!$B$18*'Holdco Summary'!C37+'Defense Supercycle'!$B$19*'Holdco Summary'!D37)/('Defense Supercycle'!$B$17+'Defense Supercycle'!$B$18+'Defense Supercycle'!$B$19)+$A91*'Holdco Summary'!E37)/'Holdco Summary'!$B$9)^(1/5)-1</f>
-        <v>0.180991657699962</v>
+        <v>0.181203703124343</v>
       </c>
       <c r="C91" s="185" t="n">
         <f aca="false">(((1-$A91)*('Defense Supercycle'!$B$17*'Holdco Summary'!B58+'Defense Supercycle'!$B$18*'Holdco Summary'!C58+'Defense Supercycle'!$B$19*'Holdco Summary'!D58)/('Defense Supercycle'!$B$17+'Defense Supercycle'!$B$18+'Defense Supercycle'!$B$19)+$A91*'Holdco Summary'!E58)/'Holdco Summary'!$B$9)^(1/7)-1</f>
-        <v>0.196285981360697</v>
+        <v>0.196491958472039</v>
       </c>
       <c r="D91" s="185" t="n">
         <f aca="false">(((1-$A91)*('Defense Supercycle'!$B$17*'Holdco Summary'!B79+'Defense Supercycle'!$B$18*'Holdco Summary'!C79+'Defense Supercycle'!$B$19*'Holdco Summary'!D79)/('Defense Supercycle'!$B$17+'Defense Supercycle'!$B$18+'Defense Supercycle'!$B$19)+$A91*'Holdco Summary'!E79)/'Holdco Summary'!$B$9)^(1/10)-1</f>
-        <v>0.216381482898982</v>
+        <v>0.216567257692529</v>
       </c>
       <c r="E91" s="186" t="str">
         <f aca="false">IF(ABS($A91-'Defense Supercycle'!$B$20)&lt;0.0001,"current base case","")</f>
@@ -19345,15 +19989,15 @@
       </c>
       <c r="B92" s="185" t="n">
         <f aca="false">(((1-$A92)*('Defense Supercycle'!$B$17*'Holdco Summary'!B37+'Defense Supercycle'!$B$18*'Holdco Summary'!C37+'Defense Supercycle'!$B$19*'Holdco Summary'!D37)/('Defense Supercycle'!$B$17+'Defense Supercycle'!$B$18+'Defense Supercycle'!$B$19)+$A92*'Holdco Summary'!E37)/'Holdco Summary'!$B$9)^(1/5)-1</f>
-        <v>0.183187360891462</v>
+        <v>0.18341041253085</v>
       </c>
       <c r="C92" s="185" t="n">
         <f aca="false">(((1-$A92)*('Defense Supercycle'!$B$17*'Holdco Summary'!B58+'Defense Supercycle'!$B$18*'Holdco Summary'!C58+'Defense Supercycle'!$B$19*'Holdco Summary'!D58)/('Defense Supercycle'!$B$17+'Defense Supercycle'!$B$18+'Defense Supercycle'!$B$19)+$A92*'Holdco Summary'!E58)/'Holdco Summary'!$B$9)^(1/7)-1</f>
-        <v>0.198864900242989</v>
+        <v>0.19908217647936</v>
       </c>
       <c r="D92" s="185" t="n">
         <f aca="false">(((1-$A92)*('Defense Supercycle'!$B$17*'Holdco Summary'!B79+'Defense Supercycle'!$B$18*'Holdco Summary'!C79+'Defense Supercycle'!$B$19*'Holdco Summary'!D79)/('Defense Supercycle'!$B$17+'Defense Supercycle'!$B$18+'Defense Supercycle'!$B$19)+$A92*'Holdco Summary'!E79)/'Holdco Summary'!$B$9)^(1/10)-1</f>
-        <v>0.219283931794773</v>
+        <v>0.219480422073763</v>
       </c>
       <c r="E92" s="186" t="str">
         <f aca="false">IF(ABS($A92-'Defense Supercycle'!$B$20)&lt;0.0001,"current base case","")</f>
@@ -19366,15 +20010,15 @@
       </c>
       <c r="B93" s="185" t="n">
         <f aca="false">(((1-$A93)*('Defense Supercycle'!$B$17*'Holdco Summary'!B37+'Defense Supercycle'!$B$18*'Holdco Summary'!C37+'Defense Supercycle'!$B$19*'Holdco Summary'!D37)/('Defense Supercycle'!$B$17+'Defense Supercycle'!$B$18+'Defense Supercycle'!$B$19)+$A93*'Holdco Summary'!E37)/'Holdco Summary'!$B$9)^(1/5)-1</f>
-        <v>0.18536688531101</v>
+        <v>0.185600784222324</v>
       </c>
       <c r="C93" s="185" t="n">
         <f aca="false">(((1-$A93)*('Defense Supercycle'!$B$17*'Holdco Summary'!B58+'Defense Supercycle'!$B$18*'Holdco Summary'!C58+'Defense Supercycle'!$B$19*'Holdco Summary'!D58)/('Defense Supercycle'!$B$17+'Defense Supercycle'!$B$18+'Defense Supercycle'!$B$19)+$A93*'Holdco Summary'!E58)/'Holdco Summary'!$B$9)^(1/7)-1</f>
-        <v>0.20141095697163</v>
+        <v>0.201639251516203</v>
       </c>
       <c r="D93" s="185" t="n">
         <f aca="false">(((1-$A93)*('Defense Supercycle'!$B$17*'Holdco Summary'!B79+'Defense Supercycle'!$B$18*'Holdco Summary'!C79+'Defense Supercycle'!$B$19*'Holdco Summary'!D79)/('Defense Supercycle'!$B$17+'Defense Supercycle'!$B$18+'Defense Supercycle'!$B$19)+$A93*'Holdco Summary'!E79)/'Holdco Summary'!$B$9)^(1/10)-1</f>
-        <v>0.222125499610033</v>
+        <v>0.222332269414816</v>
       </c>
       <c r="E93" s="186" t="str">
         <f aca="false">IF(ABS($A93-'Defense Supercycle'!$B$20)&lt;0.0001,"current base case","")</f>
@@ -19387,15 +20031,15 @@
       </c>
       <c r="B94" s="188" t="n">
         <f aca="false">(((1-$A94)*('Defense Supercycle'!$B$17*'Holdco Summary'!B37+'Defense Supercycle'!$B$18*'Holdco Summary'!C37+'Defense Supercycle'!$B$19*'Holdco Summary'!D37)/('Defense Supercycle'!$B$17+'Defense Supercycle'!$B$18+'Defense Supercycle'!$B$19)+$A94*'Holdco Summary'!E37)/'Holdco Summary'!$B$9)^(1/5)-1</f>
-        <v>0.189678454222763</v>
+        <v>0.189933586255205</v>
       </c>
       <c r="C94" s="188" t="n">
         <f aca="false">(((1-$A94)*('Defense Supercycle'!$B$17*'Holdco Summary'!B58+'Defense Supercycle'!$B$18*'Holdco Summary'!C58+'Defense Supercycle'!$B$19*'Holdco Summary'!D58)/('Defense Supercycle'!$B$17+'Defense Supercycle'!$B$18+'Defense Supercycle'!$B$19)+$A94*'Holdco Summary'!E58)/'Holdco Summary'!$B$9)^(1/7)-1</f>
-        <v>0.206408023162932</v>
+        <v>0.206657556547628</v>
       </c>
       <c r="D94" s="188" t="n">
         <f aca="false">(((1-$A94)*('Defense Supercycle'!$B$17*'Holdco Summary'!B79+'Defense Supercycle'!$B$18*'Holdco Summary'!C79+'Defense Supercycle'!$B$19*'Holdco Summary'!D79)/('Defense Supercycle'!$B$17+'Defense Supercycle'!$B$18+'Defense Supercycle'!$B$19)+$A94*'Holdco Summary'!E79)/'Holdco Summary'!$B$9)^(1/10)-1</f>
-        <v>0.227636360519233</v>
+        <v>0.227862490446989</v>
       </c>
       <c r="E94" s="189" t="str">
         <f aca="false">IF(ABS($A94-'Defense Supercycle'!$B$20)&lt;0.0001,"current base case","")</f>
@@ -19404,7 +20048,7 @@
     </row>
     <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A97" s="190" t="s">
-        <v>728</v>
+        <v>738</v>
       </c>
       <c r="B97" s="190"/>
       <c r="C97" s="190"/>
@@ -19414,7 +20058,7 @@
     </row>
     <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A98" s="191" t="s">
-        <v>729</v>
+        <v>739</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19422,18 +20066,18 @@
         <v>27</v>
       </c>
       <c r="B99" s="192" t="s">
-        <v>721</v>
+        <v>731</v>
       </c>
       <c r="C99" s="192" t="s">
-        <v>722</v>
+        <v>732</v>
       </c>
       <c r="D99" s="192" t="s">
-        <v>723</v>
+        <v>733</v>
       </c>
     </row>
     <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A100" s="0" t="s">
-        <v>730</v>
+        <v>740</v>
       </c>
       <c r="B100" s="193" t="n">
         <v>5</v>
@@ -19447,7 +20091,7 @@
     </row>
     <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A101" s="0" t="s">
-        <v>731</v>
+        <v>741</v>
       </c>
       <c r="B101" s="194" t="n">
         <f aca="false">'Holdco Summary'!$B$7</f>
@@ -19464,19 +20108,19 @@
     </row>
     <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A102" s="0" t="s">
-        <v>732</v>
+        <v>742</v>
       </c>
       <c r="B102" s="194" t="n">
         <f aca="false">'Holdco Summary'!F29</f>
-        <v>1140.135517048</v>
+        <v>1142.20858836997</v>
       </c>
       <c r="C102" s="194" t="n">
         <f aca="false">'Holdco Summary'!F50</f>
-        <v>1814.10519107791</v>
+        <v>1818.31381156955</v>
       </c>
       <c r="D102" s="194" t="n">
         <f aca="false">'Holdco Summary'!F71</f>
-        <v>3845.38877575814</v>
+        <v>3856.03656244766</v>
       </c>
     </row>
     <row r="103" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19485,15 +20129,15 @@
       </c>
       <c r="B103" s="195" t="n">
         <f aca="false">B102/B101</f>
-        <v>2.81514942480987</v>
+        <v>2.82026811943201</v>
       </c>
       <c r="C103" s="195" t="n">
         <f aca="false">C102/C101</f>
-        <v>4.47927207673558</v>
+        <v>4.4896637322705</v>
       </c>
       <c r="D103" s="195" t="n">
         <f aca="false">D102/D101</f>
-        <v>9.49478710063738</v>
+        <v>9.52107793196954</v>
       </c>
     </row>
     <row r="104" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19502,66 +20146,66 @@
       </c>
       <c r="B104" s="196" t="n">
         <f aca="false">B103^(1/B$100)-1</f>
-        <v>0.229986345820906</v>
+        <v>0.230433309691283</v>
       </c>
       <c r="C104" s="196" t="n">
         <f aca="false">C103^(1/C$100)-1</f>
-        <v>0.23888112043644</v>
+        <v>0.239291303285014</v>
       </c>
       <c r="D104" s="196" t="n">
         <f aca="false">D103^(1/D$100)-1</f>
-        <v>0.252415757426635</v>
+        <v>0.252762116902707</v>
       </c>
     </row>
     <row r="105" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A105" s="0" t="s">
-        <v>733</v>
+        <v>743</v>
       </c>
       <c r="B105" s="197" t="n">
         <f aca="false">'Holdco Summary'!F37/'Holdco Summary'!F31</f>
-        <v>0.866888959910737</v>
+        <v>0.866827309203302</v>
       </c>
       <c r="C105" s="197" t="n">
         <f aca="false">'Holdco Summary'!F58/'Holdco Summary'!F52</f>
-        <v>0.843078546393105</v>
+        <v>0.843026885255229</v>
       </c>
       <c r="D105" s="197" t="n">
         <f aca="false">'Holdco Summary'!F79/'Holdco Summary'!F73</f>
-        <v>0.822800372429311</v>
+        <v>0.822766686545173</v>
       </c>
     </row>
     <row r="106" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A106" s="0" t="s">
-        <v>734</v>
+        <v>744</v>
       </c>
       <c r="B106" s="198" t="n">
         <f aca="false">B102*B105</f>
-        <v>988.370892531031</v>
+        <v>990.097597205639</v>
       </c>
       <c r="C106" s="198" t="n">
         <f aca="false">C102*C105</f>
-        <v>1529.43316749815</v>
+        <v>1532.88742898404</v>
       </c>
       <c r="D106" s="198" t="n">
         <f aca="false">D102*D105</f>
-        <v>3163.98731682929</v>
+        <v>3172.6184256821</v>
       </c>
     </row>
     <row r="107" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A107" s="0" t="s">
-        <v>735</v>
+        <v>745</v>
       </c>
       <c r="B107" s="195" t="n">
         <f aca="false">B106/B101</f>
-        <v>2.44042195686674</v>
+        <v>2.44468542519911</v>
       </c>
       <c r="C107" s="195" t="n">
         <f aca="false">C106/C101</f>
-        <v>3.77637819135345</v>
+        <v>3.78490723205936</v>
       </c>
       <c r="D107" s="195" t="n">
         <f aca="false">D106/D101</f>
-        <v>7.81231436254146</v>
+        <v>7.83362574242495</v>
       </c>
     </row>
     <row r="108" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19570,66 +20214,66 @@
       </c>
       <c r="B108" s="196" t="n">
         <f aca="false">B107^(1/B$100)-1</f>
-        <v>0.195344216874197</v>
+        <v>0.195761583599108</v>
       </c>
       <c r="C108" s="196" t="n">
         <f aca="false">C107^(1/C$100)-1</f>
-        <v>0.209036339363743</v>
+        <v>0.209426053387375</v>
       </c>
       <c r="D108" s="196" t="n">
         <f aca="false">D107^(1/D$100)-1</f>
-        <v>0.228225107618929</v>
+        <v>0.228559747193399</v>
       </c>
     </row>
     <row r="109" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A109" s="199" t="s">
-        <v>703</v>
+        <v>713</v>
       </c>
       <c r="B109" s="200" t="n">
         <f aca="false">B107/(1+'Holdco Summary'!$B$21)^B$100</f>
-        <v>1.58610682557932</v>
+        <v>1.58887778746302</v>
       </c>
       <c r="C109" s="200" t="n">
         <f aca="false">C107/(1+'Holdco Summary'!$B$21)^C$100</f>
-        <v>2.06580819214981</v>
+        <v>2.0704738694916</v>
       </c>
       <c r="D109" s="200" t="n">
         <f aca="false">D107/(1+'Holdco Summary'!$B$21)^D$100</f>
-        <v>3.30000601360392</v>
+        <v>3.30900817077656</v>
       </c>
     </row>
     <row r="110" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A110" s="199" t="s">
-        <v>706</v>
+        <v>716</v>
       </c>
       <c r="B110" s="200" t="n">
         <f aca="false">B107/(1+'Holdco Summary'!$B$22)^B$100</f>
-        <v>1.32456326512064</v>
+        <v>1.32687730491985</v>
       </c>
       <c r="C110" s="200" t="n">
         <f aca="false">C107/(1+'Holdco Summary'!$B$22)^C$100</f>
-        <v>1.60518974504559</v>
+        <v>1.60881510457858</v>
       </c>
       <c r="D110" s="200" t="n">
         <f aca="false">D107/(1+'Holdco Summary'!$B$22)^D$100</f>
-        <v>2.30141678310309</v>
+        <v>2.30769486729926</v>
       </c>
     </row>
     <row r="111" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A111" s="199" t="s">
-        <v>724</v>
+        <v>734</v>
       </c>
       <c r="B111" s="200" t="n">
         <f aca="false">B107/(1+'Holdco Summary'!$B$23)^B$100</f>
-        <v>1.21332102126527</v>
+        <v>1.2154407185318</v>
       </c>
       <c r="C111" s="200" t="n">
         <f aca="false">C107/(1+'Holdco Summary'!$B$23)^C$100</f>
-        <v>1.41968043888754</v>
+        <v>1.4228868212039</v>
       </c>
       <c r="D111" s="200" t="n">
         <f aca="false">D107/(1+'Holdco Summary'!$B$23)^D$100</f>
-        <v>1.93108462983644</v>
+        <v>1.93635247700999</v>
       </c>
     </row>
     <row r="112" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19638,37 +20282,37 @@
       </c>
       <c r="B112" s="201" t="n">
         <f aca="false">B111^(1/B$100)-1</f>
-        <v>0.0394297538036497</v>
+        <v>0.0397926813905285</v>
       </c>
       <c r="C112" s="201" t="n">
         <f aca="false">C111^(1/C$100)-1</f>
-        <v>0.0513359472728199</v>
+        <v>0.0516748290325</v>
       </c>
       <c r="D112" s="201" t="n">
         <f aca="false">D111^(1/D$100)-1</f>
-        <v>0.0680218327121123</v>
+        <v>0.0683128236464343</v>
       </c>
     </row>
     <row r="113" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A113" s="0" t="s">
-        <v>704</v>
+        <v>714</v>
       </c>
       <c r="B113" s="201" t="n">
         <f aca="false">B109^(1/B$100)-1</f>
-        <v>0.0966460705267862</v>
+        <v>0.0970289757789977</v>
       </c>
       <c r="C113" s="201" t="n">
         <f aca="false">C109^(1/C$100)-1</f>
-        <v>0.109207650792424</v>
+        <v>0.109565186593922</v>
       </c>
       <c r="D113" s="201" t="n">
         <f aca="false">D109^(1/D$100)-1</f>
-        <v>0.126812025338467</v>
+        <v>0.127119034122385</v>
       </c>
     </row>
     <row r="115" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A115" s="190" t="s">
-        <v>736</v>
+        <v>746</v>
       </c>
       <c r="B115" s="190"/>
       <c r="C115" s="190"/>
@@ -19698,7 +20342,7 @@
     </row>
     <row r="117" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A117" s="0" t="s">
-        <v>737</v>
+        <v>747</v>
       </c>
       <c r="B117" s="203" t="n">
         <f aca="false">'Defense Supercycle'!B17</f>
@@ -19723,27 +20367,27 @@
     </row>
     <row r="118" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A118" s="0" t="s">
-        <v>738</v>
+        <v>748</v>
       </c>
       <c r="B118" s="194" t="n">
         <f aca="false">'Weapons Sleeve'!C54</f>
-        <v>1367.85556437661</v>
+        <v>1370.00276084297</v>
       </c>
       <c r="C118" s="194" t="n">
         <f aca="false">'Weapons Sleeve'!F54</f>
-        <v>2817.66321252754</v>
+        <v>2824.9418693126</v>
       </c>
       <c r="D118" s="194" t="n">
         <f aca="false">'Weapons Sleeve'!I54</f>
-        <v>465.723649144541</v>
+        <v>465.729474819185</v>
       </c>
       <c r="E118" s="206" t="n">
         <f aca="false">'Weapons Sleeve'!L54</f>
-        <v>2828.63891069913</v>
+        <v>2838.11787092789</v>
       </c>
       <c r="F118" s="207" t="n">
         <f aca="false">SUMPRODUCT(B117:E117,B118:E118)</f>
-        <v>1814.10519107791</v>
+        <v>1818.31381156955</v>
       </c>
     </row>
     <row r="119" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19752,23 +20396,23 @@
       </c>
       <c r="B119" s="208" t="n">
         <f aca="false">'Weapons Sleeve'!D54</f>
-        <v>3.3774211466089</v>
+        <v>3.38272286627895</v>
       </c>
       <c r="C119" s="208" t="n">
         <f aca="false">'Weapons Sleeve'!G54</f>
-        <v>6.95719311735195</v>
+        <v>6.97516510941384</v>
       </c>
       <c r="D119" s="208" t="n">
         <f aca="false">'Weapons Sleeve'!J54</f>
-        <v>1.14993493615936</v>
+        <v>1.1499493205412</v>
       </c>
       <c r="E119" s="209" t="n">
         <f aca="false">'Weapons Sleeve'!M54</f>
-        <v>6.98429360666453</v>
+        <v>7.00769844673553</v>
       </c>
       <c r="F119" s="210" t="n">
         <f aca="false">F118/'Weapons Sleeve'!B54</f>
-        <v>4.47927207673558</v>
+        <v>4.48966373227049</v>
       </c>
     </row>
     <row r="120" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19777,48 +20421,48 @@
       </c>
       <c r="B120" s="203" t="n">
         <f aca="false">'Weapons Sleeve'!E54</f>
-        <v>0.189904683804596</v>
+        <v>0.190171341234809</v>
       </c>
       <c r="C120" s="203" t="n">
         <f aca="false">'Weapons Sleeve'!H54</f>
-        <v>0.319312637995968</v>
+        <v>0.319798968530986</v>
       </c>
       <c r="D120" s="203" t="n">
         <f aca="false">'Weapons Sleeve'!K54</f>
-        <v>0.0201583997119177</v>
+        <v>0.0201602227056523</v>
       </c>
       <c r="E120" s="204" t="n">
         <f aca="false">'Weapons Sleeve'!N54</f>
-        <v>0.32004557875878</v>
+        <v>0.320676610492032</v>
       </c>
       <c r="F120" s="205" t="n">
         <f aca="false">F119^(1/$C$100)-1</f>
-        <v>0.23888112043644</v>
+        <v>0.239291303285014</v>
       </c>
     </row>
     <row r="121" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A121" s="199" t="s">
-        <v>739</v>
+        <v>749</v>
       </c>
       <c r="B121" s="200" t="n">
         <f aca="false">B119/(1+'Holdco Summary'!$B$23)^$C$100</f>
-        <v>1.26969770842981</v>
+        <v>1.27169082122907</v>
       </c>
       <c r="C121" s="200" t="n">
         <f aca="false">C119/(1+'Holdco Summary'!$B$23)^$C$100</f>
-        <v>2.61546658671061</v>
+        <v>2.62222292420787</v>
       </c>
       <c r="D121" s="200" t="n">
         <f aca="false">D119/(1+'Holdco Summary'!$B$23)^$C$100</f>
-        <v>0.432303136003901</v>
+        <v>0.432308543625829</v>
       </c>
       <c r="E121" s="200" t="n">
         <f aca="false">E119/(1+'Holdco Summary'!$B$23)^$C$100</f>
-        <v>2.62565466444324</v>
+        <v>2.63445341073941</v>
       </c>
       <c r="F121" s="200" t="n">
         <f aca="false">F119/(1+'Holdco Summary'!$B$23)^$C$100</f>
-        <v>1.68392428553814</v>
+        <v>1.68783089375983</v>
       </c>
     </row>
   </sheetData>
@@ -19853,7 +20497,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="10" t="s">
-        <v>740</v>
+        <v>750</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -19863,7 +20507,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="41" t="s">
-        <v>741</v>
+        <v>751</v>
       </c>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -19881,7 +20525,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="60" t="s">
-        <v>742</v>
+        <v>752</v>
       </c>
       <c r="B4" s="1"/>
       <c r="C4" s="1"/>
@@ -20002,7 +20646,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="60" t="s">
-        <v>743</v>
+        <v>753</v>
       </c>
       <c r="B11" s="1"/>
       <c r="C11" s="1"/>
@@ -20123,7 +20767,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="60" t="s">
-        <v>744</v>
+        <v>754</v>
       </c>
       <c r="B18" s="1"/>
       <c r="C18" s="1"/>
@@ -20254,7 +20898,7 @@
     </row>
     <row r="26" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="73" t="s">
-        <v>745</v>
+        <v>755</v>
       </c>
       <c r="B26" s="73"/>
       <c r="C26" s="73"/>
@@ -20264,7 +20908,7 @@
     </row>
     <row r="27" customFormat="false" ht="40.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="73" t="s">
-        <v>746</v>
+        <v>756</v>
       </c>
       <c r="B27" s="73"/>
       <c r="C27" s="73"/>
@@ -20274,7 +20918,7 @@
     </row>
     <row r="28" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="73" t="s">
-        <v>747</v>
+        <v>757</v>
       </c>
       <c r="B28" s="73"/>
       <c r="C28" s="73"/>
@@ -20392,23 +21036,23 @@
       </c>
       <c r="B6" s="17" t="n">
         <f aca="false">'Holdco Summary'!F61</f>
-        <v>0.193673267252674</v>
+        <v>0.193867652435981</v>
       </c>
       <c r="C6" s="18" t="n">
         <f aca="false">'Holdco Summary'!F59</f>
-        <v>3.45301348617188</v>
+        <v>3.45695158110001</v>
       </c>
       <c r="D6" s="19" t="n">
         <f aca="false">'Holdco Summary'!F58</f>
-        <v>2952.32653067696</v>
+        <v>2955.69360184051</v>
       </c>
       <c r="E6" s="18" t="n">
         <f aca="false">'Holdco Summary'!F64</f>
-        <v>1.29811566880597</v>
+        <v>1.29959614455619</v>
       </c>
       <c r="F6" s="18" t="n">
         <f aca="false">'Holdco Summary'!F62</f>
-        <v>1.88891662484182</v>
+        <v>1.89107089762696</v>
       </c>
       <c r="G6" s="1"/>
     </row>
@@ -20459,23 +21103,23 @@
       </c>
       <c r="B10" s="21" t="n">
         <f aca="false">'Holdco Summary'!B40</f>
-        <v>0.156236964998106</v>
+        <v>0.156368517839949</v>
       </c>
       <c r="C10" s="21" t="n">
         <f aca="false">'Holdco Summary'!C40</f>
-        <v>0.273025081505314</v>
+        <v>0.273270029093361</v>
       </c>
       <c r="D10" s="21" t="n">
         <f aca="false">'Holdco Summary'!D40</f>
-        <v>-0.053191710305405</v>
+        <v>-0.0531902729796255</v>
       </c>
       <c r="E10" s="21" t="n">
         <f aca="false">'Holdco Summary'!E40</f>
-        <v>0.214318971802798</v>
+        <v>0.214690003316135</v>
       </c>
       <c r="F10" s="17" t="n">
         <f aca="false">'Holdco Summary'!F40</f>
-        <v>0.178779502986822</v>
+        <v>0.178980379232583</v>
       </c>
       <c r="G10" s="1"/>
     </row>
@@ -20485,23 +21129,23 @@
       </c>
       <c r="B11" s="21" t="n">
         <f aca="false">'Holdco Summary'!B61</f>
-        <v>0.160229366235885</v>
+        <v>0.16034699198549</v>
       </c>
       <c r="C11" s="21" t="n">
         <f aca="false">'Holdco Summary'!C61</f>
-        <v>0.281797106824369</v>
+        <v>0.282016356262477</v>
       </c>
       <c r="D11" s="21" t="n">
         <f aca="false">'Holdco Summary'!D61</f>
-        <v>-0.0504059739765521</v>
+        <v>-0.050404646421905</v>
       </c>
       <c r="E11" s="21" t="n">
         <f aca="false">'Holdco Summary'!E61</f>
-        <v>0.234046609741583</v>
+        <v>0.234405051582679</v>
       </c>
       <c r="F11" s="17" t="n">
         <f aca="false">'Holdco Summary'!F61</f>
-        <v>0.193673267252674</v>
+        <v>0.193867652435981</v>
       </c>
       <c r="G11" s="1"/>
     </row>
@@ -20511,23 +21155,23 @@
       </c>
       <c r="B12" s="21" t="n">
         <f aca="false">'Holdco Summary'!B82</f>
-        <v>0.165952502895083</v>
+        <v>0.166049261583913</v>
       </c>
       <c r="C12" s="21" t="n">
         <f aca="false">'Holdco Summary'!C82</f>
-        <v>0.292894592849268</v>
+        <v>0.293072966232131</v>
       </c>
       <c r="D12" s="21" t="n">
         <f aca="false">'Holdco Summary'!D82</f>
-        <v>-0.045985312895805</v>
+        <v>-0.0459841671478525</v>
       </c>
       <c r="E12" s="21" t="n">
         <f aca="false">'Holdco Summary'!E82</f>
-        <v>0.256733550220737</v>
+        <v>0.257050617522171</v>
       </c>
       <c r="F12" s="17" t="n">
         <f aca="false">'Holdco Summary'!F82</f>
-        <v>0.213415331908954</v>
+        <v>0.213589924779007</v>
       </c>
       <c r="G12" s="1"/>
     </row>
@@ -20578,23 +21222,23 @@
       </c>
       <c r="B16" s="22" t="n">
         <f aca="false">'Holdco Summary'!B38</f>
-        <v>2.06649447492898</v>
+        <v>2.0676703372186</v>
       </c>
       <c r="C16" s="22" t="n">
         <f aca="false">'Holdco Summary'!C38</f>
-        <v>3.3433727747867</v>
+        <v>3.34659056807551</v>
       </c>
       <c r="D16" s="22" t="n">
         <f aca="false">'Holdco Summary'!D38</f>
-        <v>0.760869645511103</v>
+        <v>0.76087542081371</v>
       </c>
       <c r="E16" s="22" t="n">
         <f aca="false">'Holdco Summary'!E38</f>
-        <v>2.64036459832027</v>
+        <v>2.64440084144004</v>
       </c>
       <c r="F16" s="18" t="n">
         <f aca="false">'Holdco Summary'!F38</f>
-        <v>2.27595084398942</v>
+        <v>2.27789073310531</v>
       </c>
       <c r="G16" s="1"/>
     </row>
@@ -20604,23 +21248,23 @@
       </c>
       <c r="B17" s="22" t="n">
         <f aca="false">'Holdco Summary'!B59</f>
-        <v>2.83013384503586</v>
+        <v>2.83214291775293</v>
       </c>
       <c r="C17" s="22" t="n">
         <f aca="false">'Holdco Summary'!C59</f>
-        <v>5.68505942879856</v>
+        <v>5.6918698678957</v>
       </c>
       <c r="D17" s="22" t="n">
         <f aca="false">'Holdco Summary'!D59</f>
-        <v>0.696250975084011</v>
+        <v>0.696257788738565</v>
       </c>
       <c r="E17" s="22" t="n">
         <f aca="false">'Holdco Summary'!E59</f>
-        <v>4.35833834962331</v>
+        <v>4.36720755217653</v>
       </c>
       <c r="F17" s="18" t="n">
         <f aca="false">'Holdco Summary'!F59</f>
-        <v>3.45301348617188</v>
+        <v>3.45695158110001</v>
       </c>
       <c r="G17" s="1"/>
     </row>
@@ -20630,23 +21274,23 @@
       </c>
       <c r="B18" s="22" t="n">
         <f aca="false">'Holdco Summary'!B80</f>
-        <v>4.64310591330418</v>
+        <v>4.64696051843229</v>
       </c>
       <c r="C18" s="22" t="n">
         <f aca="false">'Holdco Summary'!C80</f>
-        <v>13.0506214172789</v>
+        <v>13.0686378068419</v>
       </c>
       <c r="D18" s="22" t="n">
         <f aca="false">'Holdco Summary'!D80</f>
-        <v>0.62452612073781</v>
+        <v>0.624533621181994</v>
       </c>
       <c r="E18" s="22" t="n">
         <f aca="false">'Holdco Summary'!E80</f>
-        <v>9.82725200925749</v>
+        <v>9.85207381989238</v>
       </c>
       <c r="F18" s="18" t="n">
         <f aca="false">'Holdco Summary'!F80</f>
-        <v>6.9198197348059</v>
+        <v>6.92978280116615</v>
       </c>
       <c r="G18" s="1"/>
     </row>
@@ -20697,23 +21341,23 @@
       </c>
       <c r="B22" s="23" t="n">
         <f aca="false">'Holdco Summary'!B37</f>
-        <v>1766.85277606428</v>
+        <v>1767.8581383219</v>
       </c>
       <c r="C22" s="23" t="n">
         <f aca="false">'Holdco Summary'!C37</f>
-        <v>2858.58372244263</v>
+        <v>2861.33493570456</v>
       </c>
       <c r="D22" s="23" t="n">
         <f aca="false">'Holdco Summary'!D37</f>
-        <v>650.543546911993</v>
+        <v>650.548484795722</v>
       </c>
       <c r="E22" s="23" t="n">
         <f aca="false">'Holdco Summary'!E37</f>
-        <v>2257.51173156383</v>
+        <v>2260.96271943124</v>
       </c>
       <c r="F22" s="19" t="n">
         <f aca="false">'Holdco Summary'!F37</f>
-        <v>1945.93797161096</v>
+        <v>1947.59657680504</v>
       </c>
       <c r="G22" s="1"/>
     </row>
@@ -20723,23 +21367,23 @@
       </c>
       <c r="B23" s="23" t="n">
         <f aca="false">'Holdco Summary'!B58</f>
-        <v>2419.76443750566</v>
+        <v>2421.48219467876</v>
       </c>
       <c r="C23" s="23" t="n">
         <f aca="false">'Holdco Summary'!C58</f>
-        <v>4860.72581162277</v>
+        <v>4866.54873705082</v>
       </c>
       <c r="D23" s="23" t="n">
         <f aca="false">'Holdco Summary'!D58</f>
-        <v>595.29458369683</v>
+        <v>595.300409371473</v>
       </c>
       <c r="E23" s="23" t="n">
         <f aca="false">'Holdco Summary'!E58</f>
-        <v>3726.37928892793</v>
+        <v>3733.96245711093</v>
       </c>
       <c r="F23" s="19" t="n">
         <f aca="false">'Holdco Summary'!F58</f>
-        <v>2952.32653067696</v>
+        <v>2955.69360184051</v>
       </c>
       <c r="G23" s="1"/>
     </row>
@@ -20749,23 +21393,23 @@
       </c>
       <c r="B24" s="23" t="n">
         <f aca="false">'Holdco Summary'!B79</f>
-        <v>3969.85555587508</v>
+        <v>3973.15124325961</v>
       </c>
       <c r="C24" s="23" t="n">
         <f aca="false">'Holdco Summary'!C79</f>
-        <v>11158.2813117735</v>
+        <v>11173.6853248498</v>
       </c>
       <c r="D24" s="23" t="n">
         <f aca="false">'Holdco Summary'!D79</f>
-        <v>533.969833230827</v>
+        <v>533.976246110605</v>
       </c>
       <c r="E24" s="23" t="n">
         <f aca="false">'Holdco Summary'!E79</f>
-        <v>8402.30046791515</v>
+        <v>8423.52311600798</v>
       </c>
       <c r="F24" s="19" t="n">
         <f aca="false">'Holdco Summary'!F79</f>
-        <v>5916.44587325905</v>
+        <v>5924.96429499706</v>
       </c>
       <c r="G24" s="1"/>
     </row>
@@ -20816,23 +21460,23 @@
       </c>
       <c r="B28" s="22" t="n">
         <f aca="false">'Holdco Summary'!B43</f>
-        <v>1.02741297655714</v>
+        <v>1.02799758793146</v>
       </c>
       <c r="C28" s="22" t="n">
         <f aca="false">'Holdco Summary'!C43</f>
-        <v>1.66224716105364</v>
+        <v>1.66384697301583</v>
       </c>
       <c r="D28" s="22" t="n">
         <f aca="false">'Holdco Summary'!D43</f>
-        <v>0.378286686342777</v>
+        <v>0.378289557688873</v>
       </c>
       <c r="E28" s="22" t="n">
         <f aca="false">'Holdco Summary'!E43</f>
-        <v>1.31272785099005</v>
+        <v>1.31473457716721</v>
       </c>
       <c r="F28" s="18" t="n">
         <f aca="false">'Holdco Summary'!F43</f>
-        <v>1.13154981031405</v>
+        <v>1.13251427805153</v>
       </c>
       <c r="G28" s="1"/>
     </row>
@@ -20842,23 +21486,23 @@
       </c>
       <c r="B29" s="22" t="n">
         <f aca="false">'Holdco Summary'!B64</f>
-        <v>1.06395214028894</v>
+        <v>1.06470742513919</v>
       </c>
       <c r="C29" s="22" t="n">
         <f aca="false">'Holdco Summary'!C64</f>
-        <v>2.1372244134494</v>
+        <v>2.13978470976415</v>
       </c>
       <c r="D29" s="22" t="n">
         <f aca="false">'Holdco Summary'!D64</f>
-        <v>0.26174653061665</v>
+        <v>0.261749092121774</v>
       </c>
       <c r="E29" s="22" t="n">
         <f aca="false">'Holdco Summary'!E64</f>
-        <v>1.63846081814068</v>
+        <v>1.64179507989502</v>
       </c>
       <c r="F29" s="18" t="n">
         <f aca="false">'Holdco Summary'!F64</f>
-        <v>1.29811566880597</v>
+        <v>1.29959614455619</v>
       </c>
       <c r="G29" s="1"/>
     </row>
@@ -20868,23 +21512,23 @@
       </c>
       <c r="B30" s="22" t="n">
         <f aca="false">'Holdco Summary'!B85</f>
-        <v>1.14770477067279</v>
+        <v>1.1486575701086</v>
       </c>
       <c r="C30" s="22" t="n">
         <f aca="false">'Holdco Summary'!C85</f>
-        <v>3.22591401973781</v>
+        <v>3.23036739569731</v>
       </c>
       <c r="D30" s="22" t="n">
         <f aca="false">'Holdco Summary'!D85</f>
-        <v>0.154373305620004</v>
+        <v>0.154375159615096</v>
       </c>
       <c r="E30" s="22" t="n">
         <f aca="false">'Holdco Summary'!E85</f>
-        <v>2.42914639989383</v>
+        <v>2.43528197186103</v>
       </c>
       <c r="F30" s="18" t="n">
         <f aca="false">'Holdco Summary'!F85</f>
-        <v>1.71047360756428</v>
+        <v>1.71293632519461</v>
       </c>
       <c r="G30" s="1"/>
     </row>
@@ -20935,23 +21579,23 @@
       </c>
       <c r="B34" s="22" t="n">
         <f aca="false">'Holdco Summary'!B41</f>
-        <v>1.34307961886846</v>
+        <v>1.34384384867645</v>
       </c>
       <c r="C34" s="22" t="n">
         <f aca="false">'Holdco Summary'!C41</f>
-        <v>2.17296290242927</v>
+        <v>2.17505424728228</v>
       </c>
       <c r="D34" s="22" t="n">
         <f aca="false">'Holdco Summary'!D41</f>
-        <v>0.494513063499362</v>
+        <v>0.494516817049791</v>
       </c>
       <c r="E34" s="22" t="n">
         <f aca="false">'Holdco Summary'!E41</f>
-        <v>1.71605582371937</v>
+        <v>1.71867910480564</v>
       </c>
       <c r="F34" s="18" t="n">
         <f aca="false">'Holdco Summary'!F41</f>
-        <v>1.47921188718093</v>
+        <v>1.48047268200329</v>
       </c>
       <c r="G34" s="1"/>
     </row>
@@ -20961,23 +21605,23 @@
       </c>
       <c r="B35" s="22" t="n">
         <f aca="false">'Holdco Summary'!B62</f>
-        <v>1.54818013072471</v>
+        <v>1.54927916230132</v>
       </c>
       <c r="C35" s="22" t="n">
         <f aca="false">'Holdco Summary'!C62</f>
-        <v>3.1099221915222</v>
+        <v>3.11364773493075</v>
       </c>
       <c r="D35" s="22" t="n">
         <f aca="false">'Holdco Summary'!D62</f>
-        <v>0.380873126376505</v>
+        <v>0.380876853678879</v>
       </c>
       <c r="E35" s="22" t="n">
         <f aca="false">'Holdco Summary'!E62</f>
-        <v>2.38416032785786</v>
+        <v>2.38901208537892</v>
       </c>
       <c r="F35" s="18" t="n">
         <f aca="false">'Holdco Summary'!F62</f>
-        <v>1.88891662484182</v>
+        <v>1.89107089762696</v>
       </c>
       <c r="G35" s="1"/>
     </row>
@@ -20987,23 +21631,23 @@
       </c>
       <c r="B36" s="22" t="n">
         <f aca="false">'Holdco Summary'!B83</f>
-        <v>1.96129811534096</v>
+        <v>1.96292634220339</v>
       </c>
       <c r="C36" s="22" t="n">
         <f aca="false">'Holdco Summary'!C83</f>
-        <v>5.51272352336294</v>
+        <v>5.52033384101557</v>
       </c>
       <c r="D36" s="22" t="n">
         <f aca="false">'Holdco Summary'!D83</f>
-        <v>0.263806582588293</v>
+        <v>0.263809750856973</v>
       </c>
       <c r="E36" s="22" t="n">
         <f aca="false">'Holdco Summary'!E83</f>
-        <v>4.15113745079773</v>
+        <v>4.16162245185663</v>
       </c>
       <c r="F36" s="18" t="n">
         <f aca="false">'Holdco Summary'!F83</f>
-        <v>2.92300663775207</v>
+        <v>2.92721514465246</v>
       </c>
       <c r="G36" s="1"/>
     </row>
@@ -21200,23 +21844,23 @@
       </c>
       <c r="B48" s="31" t="n">
         <f aca="false">'Holdco Summary'!B29/'Holdco Summary'!$B$7</f>
-        <v>2.37463994022986</v>
+        <v>2.3777429101608</v>
       </c>
       <c r="C48" s="31" t="n">
         <f aca="false">'Holdco Summary'!C29/'Holdco Summary'!$B$7</f>
-        <v>3.94490400599662</v>
+        <v>3.95339540495321</v>
       </c>
       <c r="D48" s="31" t="n">
         <f aca="false">'Holdco Summary'!D29/'Holdco Summary'!$B$7</f>
-        <v>1.10733606154135</v>
+        <v>1.10734825384685</v>
       </c>
       <c r="E48" s="31" t="n">
         <f aca="false">'Holdco Summary'!E29/'Holdco Summary'!$B$7</f>
-        <v>3.96156693984054</v>
+        <v>3.97221813696216</v>
       </c>
       <c r="F48" s="31" t="n">
         <f aca="false">'Holdco Summary'!F29/'Holdco Summary'!$B$7</f>
-        <v>2.81514942480987</v>
+        <v>2.82026811943201</v>
       </c>
       <c r="G48" s="1"/>
     </row>
@@ -21252,23 +21896,23 @@
       </c>
       <c r="B50" s="32" t="n">
         <f aca="false">'Holdco Summary'!B31/'Holdco Summary'!$B$9</f>
-        <v>2.34078607446123</v>
+        <v>2.34225590232325</v>
       </c>
       <c r="C50" s="32" t="n">
         <f aca="false">'Holdco Summary'!C31/'Holdco Summary'!$B$9</f>
-        <v>3.93688394928338</v>
+        <v>3.94090619089439</v>
       </c>
       <c r="D50" s="32" t="n">
         <f aca="false">'Holdco Summary'!D31/'Holdco Summary'!$B$9</f>
-        <v>0.860869645511103</v>
+        <v>0.86087542081371</v>
       </c>
       <c r="E50" s="32" t="n">
         <f aca="false">'Holdco Summary'!E31/'Holdco Summary'!$B$9</f>
-        <v>3.05812372870034</v>
+        <v>3.06316903260005</v>
       </c>
       <c r="F50" s="32" t="n">
         <f aca="false">'Holdco Summary'!F31/'Holdco Summary'!$B$9</f>
-        <v>2.62542372696011</v>
+        <v>2.62784837178112</v>
       </c>
       <c r="G50" s="1"/>
     </row>
@@ -21345,23 +21989,23 @@
       </c>
       <c r="B55" s="31" t="n">
         <f aca="false">'Holdco Summary'!B50/'Holdco Summary'!$B$7</f>
-        <v>3.3774211466089</v>
+        <v>3.38272286627895</v>
       </c>
       <c r="C55" s="31" t="n">
         <f aca="false">'Holdco Summary'!C50/'Holdco Summary'!$B$7</f>
-        <v>6.95719311735195</v>
+        <v>6.97516510941384</v>
       </c>
       <c r="D55" s="31" t="n">
         <f aca="false">'Holdco Summary'!D50/'Holdco Summary'!$B$7</f>
-        <v>1.14993493615936</v>
+        <v>1.1499493205412</v>
       </c>
       <c r="E55" s="31" t="n">
         <f aca="false">'Holdco Summary'!E50/'Holdco Summary'!$B$7</f>
-        <v>6.98429360666453</v>
+        <v>7.00769844673553</v>
       </c>
       <c r="F55" s="31" t="n">
         <f aca="false">'Holdco Summary'!F50/'Holdco Summary'!$B$7</f>
-        <v>4.47927207673558</v>
+        <v>4.4896637322705</v>
       </c>
       <c r="G55" s="1"/>
     </row>
@@ -21397,23 +22041,23 @@
       </c>
       <c r="B57" s="32" t="n">
         <f aca="false">'Holdco Summary'!B52/'Holdco Summary'!$B$9</f>
-        <v>3.28421123909995</v>
+        <v>3.28672257999628</v>
       </c>
       <c r="C57" s="32" t="n">
         <f aca="false">'Holdco Summary'!C52/'Holdco Summary'!$B$9</f>
-        <v>6.85286821880332</v>
+        <v>6.86138126767474</v>
       </c>
       <c r="D57" s="32" t="n">
         <f aca="false">'Holdco Summary'!D52/'Holdco Summary'!$B$9</f>
-        <v>0.836250975084011</v>
+        <v>0.836257788738565</v>
       </c>
       <c r="E57" s="32" t="n">
         <f aca="false">'Holdco Summary'!E52/'Holdco Summary'!$B$9</f>
-        <v>5.19446686983425</v>
+        <v>5.20555337302578</v>
       </c>
       <c r="F57" s="32" t="n">
         <f aca="false">'Holdco Summary'!F52/'Holdco Summary'!$B$9</f>
-        <v>4.09571978903355</v>
+        <v>4.10064215218167</v>
       </c>
       <c r="G57" s="1"/>
     </row>
@@ -21490,23 +22134,23 @@
       </c>
       <c r="B62" s="31" t="n">
         <f aca="false">'Holdco Summary'!B71/'Holdco Summary'!$B$7</f>
-        <v>5.81191457480287</v>
+        <v>5.82208644944649</v>
       </c>
       <c r="C62" s="31" t="n">
         <f aca="false">'Holdco Summary'!C71/'Holdco Summary'!$B$7</f>
-        <v>16.7230380390834</v>
+        <v>16.770581289319</v>
       </c>
       <c r="D62" s="31" t="n">
         <f aca="false">'Holdco Summary'!D71/'Holdco Summary'!$B$7</f>
-        <v>1.22116020090635</v>
+        <v>1.22117603517741</v>
       </c>
       <c r="E62" s="31" t="n">
         <f aca="false">'Holdco Summary'!E71/'Holdco Summary'!$B$7</f>
-        <v>16.7699466804619</v>
+        <v>16.8354486807484</v>
       </c>
       <c r="F62" s="31" t="n">
         <f aca="false">'Holdco Summary'!F71/'Holdco Summary'!$B$7</f>
-        <v>9.49478710063738</v>
+        <v>9.52107793196954</v>
       </c>
       <c r="G62" s="1"/>
     </row>
@@ -21542,23 +22186,23 @@
       </c>
       <c r="B64" s="32" t="n">
         <f aca="false">'Holdco Summary'!B73/'Holdco Summary'!$B$9</f>
-        <v>5.51415114231203</v>
+        <v>5.51896939872217</v>
       </c>
       <c r="C64" s="32" t="n">
         <f aca="false">'Holdco Summary'!C73/'Holdco Summary'!$B$9</f>
-        <v>16.0235455222804</v>
+        <v>16.0460660092341</v>
       </c>
       <c r="D64" s="32" t="n">
         <f aca="false">'Holdco Summary'!D73/'Holdco Summary'!$B$9</f>
-        <v>0.82452612073781</v>
+        <v>0.824533621181994</v>
       </c>
       <c r="E64" s="32" t="n">
         <f aca="false">'Holdco Summary'!E73/'Holdco Summary'!$B$9</f>
-        <v>11.9943337622537</v>
+        <v>12.0253610255473</v>
       </c>
       <c r="F64" s="32" t="n">
         <f aca="false">'Holdco Summary'!F73/'Holdco Summary'!$B$9</f>
-        <v>8.41008337705924</v>
+        <v>8.42253692874289</v>
       </c>
       <c r="G64" s="1"/>
     </row>
@@ -21806,11 +22450,11 @@
       </c>
       <c r="B79" s="34" t="n">
         <f aca="false">'Holdco Summary'!F52</f>
-        <v>3501.84041962368</v>
+        <v>3506.04904011532</v>
       </c>
       <c r="C79" s="34" t="n">
         <f aca="false">'Fund Economics'!F22+'Holdco Summary'!F50+'Holdco Summary'!F51</f>
-        <v>3501.84041962368</v>
+        <v>3506.04904011532</v>
       </c>
       <c r="D79" s="36" t="str">
         <f aca="false">IF(ABS(B79-C79)&lt;0.001,"OK","CHECK")</f>
@@ -21857,7 +22501,7 @@
     <row r="83" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A83" s="40" t="str">
         <f aca="false">"• Underwrite to Expected: 7-yr holdco net IRR "&amp;TEXT('Holdco Summary'!F61,"0.0%")&amp;" / "&amp;TEXT('Holdco Summary'!F59,"0.00")&amp;"x net MOIC; Base "&amp;TEXT('Holdco Summary'!B61,"0.0%")&amp;", Bear "&amp;TEXT('Holdco Summary'!D61,"0.0%")&amp;"."</f>
-        <v>• Underwrite to Expected: 7-yr holdco net IRR 19.4% / 3.45x net MOIC; Base 16.0%, Bear -5.0%.</v>
+        <v>• Underwrite to Expected: 7-yr holdco net IRR 19.4% / 3.46x net MOIC; Base 16.0%, Bear -5.0%.</v>
       </c>
       <c r="B83" s="40"/>
       <c r="C83" s="40"/>
@@ -22332,23 +22976,23 @@
       </c>
       <c r="B29" s="62" t="n">
         <f aca="false">'Weapons Sleeve'!C38</f>
-        <v>961.729175793093</v>
+        <v>962.985878615122</v>
       </c>
       <c r="C29" s="62" t="n">
         <f aca="false">'Weapons Sleeve'!F38</f>
-        <v>1597.68612242863</v>
+        <v>1601.12513900605</v>
       </c>
       <c r="D29" s="62" t="n">
         <f aca="false">'Weapons Sleeve'!I38</f>
-        <v>448.471104924246</v>
+        <v>448.476042807974</v>
       </c>
       <c r="E29" s="63" t="n">
         <f aca="false">'Weapons Sleeve'!L38</f>
-        <v>1604.43461063542</v>
+        <v>1608.74834546968</v>
       </c>
       <c r="F29" s="64" t="n">
         <f aca="false">B29*'Defense Supercycle'!$B$17+C29*'Defense Supercycle'!$B$18+D29*'Defense Supercycle'!$B$19+E29*'Defense Supercycle'!$B$20</f>
-        <v>1140.135517048</v>
+        <v>1142.20858836997</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -22382,23 +23026,23 @@
       </c>
       <c r="B31" s="66" t="n">
         <f aca="false">B28+B29+B30</f>
-        <v>2001.37209366435</v>
+        <v>2002.62879648638</v>
       </c>
       <c r="C31" s="66" t="n">
         <f aca="false">C28+C29+C30</f>
-        <v>3366.03577663729</v>
+        <v>3369.4747932147</v>
       </c>
       <c r="D31" s="66" t="n">
         <f aca="false">D28+D29+D30</f>
-        <v>736.043546911993</v>
+        <v>736.048484795722</v>
       </c>
       <c r="E31" s="66" t="n">
         <f aca="false">E28+E29+E30</f>
-        <v>2614.69578803879</v>
+        <v>2619.00952287305</v>
       </c>
       <c r="F31" s="66" t="n">
         <f aca="false">F28+F29+F30</f>
-        <v>2244.7372865509</v>
+        <v>2246.81035787286</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -22457,11 +23101,11 @@
       </c>
       <c r="B34" s="62" t="n">
         <f aca="false">MAX(0,B31+B32+B33)</f>
-        <v>745.096588000347</v>
+        <v>746.353290822377</v>
       </c>
       <c r="C34" s="62" t="n">
         <f aca="false">MAX(0,C31+C32+C33)</f>
-        <v>2109.76027097329</v>
+        <v>2113.1992875507</v>
       </c>
       <c r="D34" s="62" t="n">
         <f aca="false">MAX(0,D31+D32+D33)</f>
@@ -22469,11 +23113,11 @@
       </c>
       <c r="E34" s="63" t="n">
         <f aca="false">MAX(0,E31+E32+E33)</f>
-        <v>1358.42028237479</v>
+        <v>1362.73401720905</v>
       </c>
       <c r="F34" s="64" t="n">
         <f aca="false">B34*'Defense Supercycle'!$B$17+C34*'Defense Supercycle'!$B$18+D34*'Defense Supercycle'!$B$19+E34*'Defense Supercycle'!$B$20</f>
-        <v>1066.4965746997</v>
+        <v>1068.5689053391</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -22482,11 +23126,11 @@
       </c>
       <c r="B35" s="62" t="n">
         <f aca="false">-Assumptions!$B$9*B34</f>
-        <v>-149.019317600069</v>
+        <v>-149.270658164475</v>
       </c>
       <c r="C35" s="62" t="n">
         <f aca="false">-Assumptions!$B$9*C34</f>
-        <v>-421.952054194657</v>
+        <v>-422.639857510141</v>
       </c>
       <c r="D35" s="62" t="n">
         <f aca="false">-Assumptions!$B$9*D34</f>
@@ -22494,11 +23138,11 @@
       </c>
       <c r="E35" s="63" t="n">
         <f aca="false">-Assumptions!$B$9*E34</f>
-        <v>-271.684056474957</v>
+        <v>-272.546803441809</v>
       </c>
       <c r="F35" s="64" t="n">
         <f aca="false">B35*'Defense Supercycle'!$B$17+C35*'Defense Supercycle'!$B$18+D35*'Defense Supercycle'!$B$19+E35*'Defense Supercycle'!$B$20</f>
-        <v>-213.299314939939</v>
+        <v>-213.71378106782</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -22532,23 +23176,23 @@
       </c>
       <c r="B37" s="66" t="n">
         <f aca="false">B31+B35+B36</f>
-        <v>1766.85277606428</v>
+        <v>1767.8581383219</v>
       </c>
       <c r="C37" s="66" t="n">
         <f aca="false">C31+C35+C36</f>
-        <v>2858.58372244263</v>
+        <v>2861.33493570456</v>
       </c>
       <c r="D37" s="66" t="n">
         <f aca="false">D31+D35+D36</f>
-        <v>650.543546911993</v>
+        <v>650.548484795722</v>
       </c>
       <c r="E37" s="66" t="n">
         <f aca="false">E31+E35+E36</f>
-        <v>2257.51173156383</v>
+        <v>2260.96271943124</v>
       </c>
       <c r="F37" s="66" t="n">
         <f aca="false">F31+F35+F36</f>
-        <v>1945.93797161096</v>
+        <v>1947.59657680504</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -22557,23 +23201,23 @@
       </c>
       <c r="B38" s="67" t="n">
         <f aca="false">B37/'Holdco Summary'!$B$9</f>
-        <v>2.06649447492898</v>
+        <v>2.0676703372186</v>
       </c>
       <c r="C38" s="67" t="n">
         <f aca="false">C37/'Holdco Summary'!$B$9</f>
-        <v>3.3433727747867</v>
+        <v>3.34659056807551</v>
       </c>
       <c r="D38" s="67" t="n">
         <f aca="false">D37/'Holdco Summary'!$B$9</f>
-        <v>0.760869645511103</v>
+        <v>0.76087542081371</v>
       </c>
       <c r="E38" s="67" t="n">
         <f aca="false">E37/'Holdco Summary'!$B$9</f>
-        <v>2.64036459832027</v>
+        <v>2.64440084144004</v>
       </c>
       <c r="F38" s="67" t="n">
         <f aca="false">F37/'Holdco Summary'!$B$9</f>
-        <v>2.27595084398942</v>
+        <v>2.27789073310531</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -22582,23 +23226,23 @@
       </c>
       <c r="B39" s="68" t="n">
         <f aca="false">B37/'Holdco Summary'!$B$9</f>
-        <v>2.06649447492898</v>
+        <v>2.0676703372186</v>
       </c>
       <c r="C39" s="68" t="n">
         <f aca="false">C37/'Holdco Summary'!$B$9</f>
-        <v>3.3433727747867</v>
+        <v>3.34659056807551</v>
       </c>
       <c r="D39" s="68" t="n">
         <f aca="false">D37/'Holdco Summary'!$B$9</f>
-        <v>0.760869645511103</v>
+        <v>0.76087542081371</v>
       </c>
       <c r="E39" s="69" t="n">
         <f aca="false">E37/'Holdco Summary'!$B$9</f>
-        <v>2.64036459832027</v>
+        <v>2.64440084144004</v>
       </c>
       <c r="F39" s="70" t="n">
         <f aca="false">F37/'Holdco Summary'!$B$9</f>
-        <v>2.27595084398942</v>
+        <v>2.27789073310531</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -22607,23 +23251,23 @@
       </c>
       <c r="B40" s="51" t="n">
         <f aca="false">(B37/'Holdco Summary'!$B$9)^(1/5)-1</f>
-        <v>0.156236964998106</v>
+        <v>0.156368517839949</v>
       </c>
       <c r="C40" s="51" t="n">
         <f aca="false">(C37/'Holdco Summary'!$B$9)^(1/5)-1</f>
-        <v>0.273025081505314</v>
+        <v>0.273270029093361</v>
       </c>
       <c r="D40" s="51" t="n">
         <f aca="false">(D37/'Holdco Summary'!$B$9)^(1/5)-1</f>
-        <v>-0.053191710305405</v>
+        <v>-0.0531902729796255</v>
       </c>
       <c r="E40" s="51" t="n">
         <f aca="false">(E37/'Holdco Summary'!$B$9)^(1/5)-1</f>
-        <v>0.214318971802798</v>
+        <v>0.214690003316135</v>
       </c>
       <c r="F40" s="51" t="n">
         <f aca="false">(F37/'Holdco Summary'!$B$9)^(1/5)-1</f>
-        <v>0.178779502986822</v>
+        <v>0.178980379232583</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -22632,23 +23276,23 @@
       </c>
       <c r="B41" s="68" t="n">
         <f aca="false">B38/(1+'Holdco Summary'!$B$21)^5</f>
-        <v>1.34307961886846</v>
+        <v>1.34384384867645</v>
       </c>
       <c r="C41" s="68" t="n">
         <f aca="false">C38/(1+'Holdco Summary'!$B$21)^5</f>
-        <v>2.17296290242927</v>
+        <v>2.17505424728228</v>
       </c>
       <c r="D41" s="68" t="n">
         <f aca="false">D38/(1+'Holdco Summary'!$B$21)^5</f>
-        <v>0.494513063499362</v>
+        <v>0.494516817049791</v>
       </c>
       <c r="E41" s="69" t="n">
         <f aca="false">E38/(1+'Holdco Summary'!$B$21)^5</f>
-        <v>1.71605582371937</v>
+        <v>1.71867910480564</v>
       </c>
       <c r="F41" s="70" t="n">
         <f aca="false">F38/(1+'Holdco Summary'!$B$21)^5</f>
-        <v>1.47921188718093</v>
+        <v>1.48047268200329</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -22657,23 +23301,23 @@
       </c>
       <c r="B42" s="68" t="n">
         <f aca="false">B38/(1+'Holdco Summary'!$B$22)^5</f>
-        <v>1.12161040895567</v>
+        <v>1.12224861989672</v>
       </c>
       <c r="C42" s="68" t="n">
         <f aca="false">C38/(1+'Holdco Summary'!$B$22)^5</f>
-        <v>1.81464879326553</v>
+        <v>1.81639528254502</v>
       </c>
       <c r="D42" s="68" t="n">
         <f aca="false">D38/(1+'Holdco Summary'!$B$22)^5</f>
-        <v>0.412969560101529</v>
+        <v>0.412972694704403</v>
       </c>
       <c r="E42" s="69" t="n">
         <f aca="false">E38/(1+'Holdco Summary'!$B$22)^5</f>
-        <v>1.43308412039952</v>
+        <v>1.43527483145689</v>
       </c>
       <c r="F42" s="70" t="n">
         <f aca="false">F38/(1+'Holdco Summary'!$B$22)^5</f>
-        <v>1.23529493442159</v>
+        <v>1.23634782851398</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -22682,23 +23326,23 @@
       </c>
       <c r="B43" s="67" t="n">
         <f aca="false">B38/(1+'Holdco Summary'!$B$23)^5</f>
-        <v>1.02741297655714</v>
+        <v>1.02799758793146</v>
       </c>
       <c r="C43" s="67" t="n">
         <f aca="false">C38/(1+'Holdco Summary'!$B$23)^5</f>
-        <v>1.66224716105364</v>
+        <v>1.66384697301583</v>
       </c>
       <c r="D43" s="67" t="n">
         <f aca="false">D38/(1+'Holdco Summary'!$B$23)^5</f>
-        <v>0.378286686342777</v>
+        <v>0.378289557688873</v>
       </c>
       <c r="E43" s="67" t="n">
         <f aca="false">E38/(1+'Holdco Summary'!$B$23)^5</f>
-        <v>1.31272785099005</v>
+        <v>1.31473457716721</v>
       </c>
       <c r="F43" s="67" t="n">
         <f aca="false">F38/(1+'Holdco Summary'!$B$23)^5</f>
-        <v>1.13154981031405</v>
+        <v>1.13251427805153</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -22707,23 +23351,23 @@
       </c>
       <c r="B44" s="46" t="n">
         <f aca="false">(B38/(1+'Holdco Summary'!$B$23)^5)^(1/5)-1</f>
-        <v>0.00542344782444015</v>
+        <v>0.00553784159995585</v>
       </c>
       <c r="C44" s="46" t="n">
         <f aca="false">(C38/(1+'Holdco Summary'!$B$23)^5)^(1/5)-1</f>
-        <v>0.106978331743751</v>
+        <v>0.107191329646401</v>
       </c>
       <c r="D44" s="46" t="n">
         <f aca="false">(D38/(1+'Holdco Summary'!$B$23)^5)^(1/5)-1</f>
-        <v>-0.17668844374383</v>
+        <v>-0.176687193895327</v>
       </c>
       <c r="E44" s="71" t="n">
         <f aca="false">(E38/(1+'Holdco Summary'!$B$23)^5)^(1/5)-1</f>
-        <v>0.0559295406980851</v>
+        <v>0.0562521767966391</v>
       </c>
       <c r="F44" s="72" t="n">
         <f aca="false">(F38/(1+'Holdco Summary'!$B$23)^5)^(1/5)-1</f>
-        <v>0.0250256547711496</v>
+        <v>0.0252003297674637</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -22803,23 +23447,23 @@
       </c>
       <c r="B50" s="62" t="n">
         <f aca="false">'Weapons Sleeve'!C54</f>
-        <v>1367.85556437661</v>
+        <v>1370.00276084297</v>
       </c>
       <c r="C50" s="62" t="n">
         <f aca="false">'Weapons Sleeve'!F54</f>
-        <v>2817.66321252754</v>
+        <v>2824.9418693126</v>
       </c>
       <c r="D50" s="62" t="n">
         <f aca="false">'Weapons Sleeve'!I54</f>
-        <v>465.723649144541</v>
+        <v>465.729474819185</v>
       </c>
       <c r="E50" s="63" t="n">
         <f aca="false">'Weapons Sleeve'!L54</f>
-        <v>2828.63891069913</v>
+        <v>2838.11787092789</v>
       </c>
       <c r="F50" s="64" t="n">
         <f aca="false">B50*'Defense Supercycle'!$B$17+C50*'Defense Supercycle'!$B$18+D50*'Defense Supercycle'!$B$19+E50*'Defense Supercycle'!$B$20</f>
-        <v>1814.10519107791</v>
+        <v>1818.31381156955</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -22853,23 +23497,23 @@
       </c>
       <c r="B52" s="66" t="n">
         <f aca="false">B49+B50+B51</f>
-        <v>2808.00060943046</v>
+        <v>2810.14780589682</v>
       </c>
       <c r="C52" s="66" t="n">
         <f aca="false">C49+C50+C51</f>
-        <v>5859.20232707684</v>
+        <v>5866.48098386191</v>
       </c>
       <c r="D52" s="66" t="n">
         <f aca="false">D49+D50+D51</f>
-        <v>714.99458369683</v>
+        <v>715.000409371473</v>
       </c>
       <c r="E52" s="66" t="n">
         <f aca="false">E49+E50+E51</f>
-        <v>4441.26917370829</v>
+        <v>4450.74813393705</v>
       </c>
       <c r="F52" s="66" t="n">
         <f aca="false">F49+F50+F51</f>
-        <v>3501.84041962368</v>
+        <v>3506.04904011532</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -22928,11 +23572,11 @@
       </c>
       <c r="B55" s="62" t="n">
         <f aca="false">MAX(0,B52+B53+B54)</f>
-        <v>1342.68085962396</v>
+        <v>1344.82805609033</v>
       </c>
       <c r="C55" s="62" t="n">
         <f aca="false">MAX(0,C52+C53+C54)</f>
-        <v>4393.88257727035</v>
+        <v>4401.16123405542</v>
       </c>
       <c r="D55" s="62" t="n">
         <f aca="false">MAX(0,D52+D53+D54)</f>
@@ -22940,11 +23584,11 @@
       </c>
       <c r="E55" s="63" t="n">
         <f aca="false">MAX(0,E52+E53+E54)</f>
-        <v>2975.9494239018</v>
+        <v>2985.42838413056</v>
       </c>
       <c r="F55" s="64" t="n">
         <f aca="false">B55*'Defense Supercycle'!$B$17+C55*'Defense Supercycle'!$B$18+D55*'Defense Supercycle'!$B$19+E55*'Defense Supercycle'!$B$20</f>
-        <v>2149.06944473364</v>
+        <v>2153.27719137409</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -22953,11 +23597,11 @@
       </c>
       <c r="B56" s="62" t="n">
         <f aca="false">-Assumptions!$B$9*B55</f>
-        <v>-268.536171924793</v>
+        <v>-268.965611218067</v>
       </c>
       <c r="C56" s="62" t="n">
         <f aca="false">-Assumptions!$B$9*C55</f>
-        <v>-878.776515454071</v>
+        <v>-880.232246811083</v>
       </c>
       <c r="D56" s="62" t="n">
         <f aca="false">-Assumptions!$B$9*D55</f>
@@ -22965,11 +23609,11 @@
       </c>
       <c r="E56" s="63" t="n">
         <f aca="false">-Assumptions!$B$9*E55</f>
-        <v>-595.189884780359</v>
+        <v>-597.085676826111</v>
       </c>
       <c r="F56" s="64" t="n">
         <f aca="false">B56*'Defense Supercycle'!$B$17+C56*'Defense Supercycle'!$B$18+D56*'Defense Supercycle'!$B$19+E56*'Defense Supercycle'!$B$20</f>
-        <v>-429.813888946728</v>
+        <v>-430.655438274817</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -23003,23 +23647,23 @@
       </c>
       <c r="B58" s="66" t="n">
         <f aca="false">B52+B56+B57</f>
-        <v>2419.76443750566</v>
+        <v>2421.48219467876</v>
       </c>
       <c r="C58" s="66" t="n">
         <f aca="false">C52+C56+C57</f>
-        <v>4860.72581162277</v>
+        <v>4866.54873705082</v>
       </c>
       <c r="D58" s="66" t="n">
         <f aca="false">D52+D56+D57</f>
-        <v>595.29458369683</v>
+        <v>595.300409371473</v>
       </c>
       <c r="E58" s="66" t="n">
         <f aca="false">E52+E56+E57</f>
-        <v>3726.37928892793</v>
+        <v>3733.96245711093</v>
       </c>
       <c r="F58" s="66" t="n">
         <f aca="false">F52+F56+F57</f>
-        <v>2952.32653067696</v>
+        <v>2955.69360184051</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -23028,23 +23672,23 @@
       </c>
       <c r="B59" s="67" t="n">
         <f aca="false">B58/'Holdco Summary'!$B$9</f>
-        <v>2.83013384503586</v>
+        <v>2.83214291775293</v>
       </c>
       <c r="C59" s="67" t="n">
         <f aca="false">C58/'Holdco Summary'!$B$9</f>
-        <v>5.68505942879856</v>
+        <v>5.6918698678957</v>
       </c>
       <c r="D59" s="67" t="n">
         <f aca="false">D58/'Holdco Summary'!$B$9</f>
-        <v>0.696250975084011</v>
+        <v>0.696257788738565</v>
       </c>
       <c r="E59" s="67" t="n">
         <f aca="false">E58/'Holdco Summary'!$B$9</f>
-        <v>4.35833834962331</v>
+        <v>4.36720755217653</v>
       </c>
       <c r="F59" s="67" t="n">
         <f aca="false">F58/'Holdco Summary'!$B$9</f>
-        <v>3.45301348617188</v>
+        <v>3.45695158110001</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -23053,23 +23697,23 @@
       </c>
       <c r="B60" s="68" t="n">
         <f aca="false">B58/'Holdco Summary'!$B$9</f>
-        <v>2.83013384503586</v>
+        <v>2.83214291775293</v>
       </c>
       <c r="C60" s="68" t="n">
         <f aca="false">C58/'Holdco Summary'!$B$9</f>
-        <v>5.68505942879856</v>
+        <v>5.6918698678957</v>
       </c>
       <c r="D60" s="68" t="n">
         <f aca="false">D58/'Holdco Summary'!$B$9</f>
-        <v>0.696250975084011</v>
+        <v>0.696257788738565</v>
       </c>
       <c r="E60" s="69" t="n">
         <f aca="false">E58/'Holdco Summary'!$B$9</f>
-        <v>4.35833834962331</v>
+        <v>4.36720755217653</v>
       </c>
       <c r="F60" s="70" t="n">
         <f aca="false">F58/'Holdco Summary'!$B$9</f>
-        <v>3.45301348617188</v>
+        <v>3.45695158110001</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -23078,23 +23722,23 @@
       </c>
       <c r="B61" s="51" t="n">
         <f aca="false">(B58/'Holdco Summary'!$B$9)^(1/7)-1</f>
-        <v>0.160229366235885</v>
+        <v>0.16034699198549</v>
       </c>
       <c r="C61" s="51" t="n">
         <f aca="false">(C58/'Holdco Summary'!$B$9)^(1/7)-1</f>
-        <v>0.281797106824369</v>
+        <v>0.282016356262477</v>
       </c>
       <c r="D61" s="51" t="n">
         <f aca="false">(D58/'Holdco Summary'!$B$9)^(1/7)-1</f>
-        <v>-0.0504059739765521</v>
+        <v>-0.050404646421905</v>
       </c>
       <c r="E61" s="51" t="n">
         <f aca="false">(E58/'Holdco Summary'!$B$9)^(1/7)-1</f>
-        <v>0.234046609741583</v>
+        <v>0.234405051582679</v>
       </c>
       <c r="F61" s="51" t="n">
         <f aca="false">(F58/'Holdco Summary'!$B$9)^(1/7)-1</f>
-        <v>0.193673267252674</v>
+        <v>0.193867652435981</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -23103,23 +23747,23 @@
       </c>
       <c r="B62" s="68" t="n">
         <f aca="false">B59/(1+'Holdco Summary'!$B$21)^7</f>
-        <v>1.54818013072471</v>
+        <v>1.54927916230132</v>
       </c>
       <c r="C62" s="68" t="n">
         <f aca="false">C59/(1+'Holdco Summary'!$B$21)^7</f>
-        <v>3.1099221915222</v>
+        <v>3.11364773493075</v>
       </c>
       <c r="D62" s="68" t="n">
         <f aca="false">D59/(1+'Holdco Summary'!$B$21)^7</f>
-        <v>0.380873126376505</v>
+        <v>0.380876853678879</v>
       </c>
       <c r="E62" s="69" t="n">
         <f aca="false">E59/(1+'Holdco Summary'!$B$21)^7</f>
-        <v>2.38416032785786</v>
+        <v>2.38901208537892</v>
       </c>
       <c r="F62" s="70" t="n">
         <f aca="false">F59/(1+'Holdco Summary'!$B$21)^7</f>
-        <v>1.88891662484182</v>
+        <v>1.89107089762696</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -23128,23 +23772,23 @@
       </c>
       <c r="B63" s="68" t="n">
         <f aca="false">B59/(1+'Holdco Summary'!$B$22)^7</f>
-        <v>1.20297851405869</v>
+        <v>1.20383249180114</v>
       </c>
       <c r="C63" s="68" t="n">
         <f aca="false">C59/(1+'Holdco Summary'!$B$22)^7</f>
-        <v>2.41649502054019</v>
+        <v>2.41938987016701</v>
       </c>
       <c r="D63" s="68" t="n">
         <f aca="false">D59/(1+'Holdco Summary'!$B$22)^7</f>
-        <v>0.295948887678089</v>
+        <v>0.29595178389448</v>
       </c>
       <c r="E63" s="69" t="n">
         <f aca="false">E59/(1+'Holdco Summary'!$B$22)^7</f>
-        <v>1.85255810455438</v>
+        <v>1.85632805350117</v>
       </c>
       <c r="F63" s="70" t="n">
         <f aca="false">F59/(1+'Holdco Summary'!$B$22)^7</f>
-        <v>1.46774013529633</v>
+        <v>1.46941406446161</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -23153,23 +23797,23 @@
       </c>
       <c r="B64" s="67" t="n">
         <f aca="false">B59/(1+'Holdco Summary'!$B$23)^7</f>
-        <v>1.06395214028894</v>
+        <v>1.06470742513919</v>
       </c>
       <c r="C64" s="67" t="n">
         <f aca="false">C59/(1+'Holdco Summary'!$B$23)^7</f>
-        <v>2.1372244134494</v>
+        <v>2.13978470976415</v>
       </c>
       <c r="D64" s="67" t="n">
         <f aca="false">D59/(1+'Holdco Summary'!$B$23)^7</f>
-        <v>0.26174653061665</v>
+        <v>0.261749092121774</v>
       </c>
       <c r="E64" s="67" t="n">
         <f aca="false">E59/(1+'Holdco Summary'!$B$23)^7</f>
-        <v>1.63846081814068</v>
+        <v>1.64179507989502</v>
       </c>
       <c r="F64" s="67" t="n">
         <f aca="false">F59/(1+'Holdco Summary'!$B$23)^7</f>
-        <v>1.29811566880597</v>
+        <v>1.29959614455619</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -23178,23 +23822,23 @@
       </c>
       <c r="B65" s="46" t="n">
         <f aca="false">(B59/(1+'Holdco Summary'!$B$23)^7)^(1/7)-1</f>
-        <v>0.00889510107468294</v>
+        <v>0.00899738433520847</v>
       </c>
       <c r="C65" s="46" t="n">
         <f aca="false">(C59/(1+'Holdco Summary'!$B$23)^7)^(1/7)-1</f>
-        <v>0.114606179847278</v>
+        <v>0.114796831532589</v>
       </c>
       <c r="D65" s="46" t="n">
         <f aca="false">(D59/(1+'Holdco Summary'!$B$23)^7)^(1/7)-1</f>
-        <v>-0.174266064327437</v>
+        <v>-0.174264909932091</v>
       </c>
       <c r="E65" s="71" t="n">
         <f aca="false">(E59/(1+'Holdco Summary'!$B$23)^7)^(1/7)-1</f>
-        <v>0.0730840084709419</v>
+        <v>0.0733956970284166</v>
       </c>
       <c r="F65" s="72" t="n">
         <f aca="false">(F59/(1+'Holdco Summary'!$B$23)^7)^(1/7)-1</f>
-        <v>0.0379767541327605</v>
+        <v>0.0381457847269406</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -23274,23 +23918,23 @@
       </c>
       <c r="B71" s="62" t="n">
         <f aca="false">'Weapons Sleeve'!C70</f>
-        <v>2353.82540279516</v>
+        <v>2357.94501202583</v>
       </c>
       <c r="C71" s="62" t="n">
         <f aca="false">'Weapons Sleeve'!F70</f>
-        <v>6772.83040582878</v>
+        <v>6792.08542217419</v>
       </c>
       <c r="D71" s="62" t="n">
         <f aca="false">'Weapons Sleeve'!I70</f>
-        <v>494.569881367072</v>
+        <v>494.57629424685</v>
       </c>
       <c r="E71" s="63" t="n">
         <f aca="false">'Weapons Sleeve'!L70</f>
-        <v>6791.82840558708</v>
+        <v>6818.35671570312</v>
       </c>
       <c r="F71" s="64" t="n">
         <f aca="false">B71*'Defense Supercycle'!$B$17+C71*'Defense Supercycle'!$B$18+D71*'Defense Supercycle'!$B$19+E71*'Defense Supercycle'!$B$20</f>
-        <v>3845.38877575814</v>
+        <v>3856.03656244766</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -23324,23 +23968,23 @@
       </c>
       <c r="B73" s="66" t="n">
         <f aca="false">B70+B71+B72</f>
-        <v>4714.59922667679</v>
+        <v>4718.71883590745</v>
       </c>
       <c r="C73" s="66" t="n">
         <f aca="false">C70+C71+C72</f>
-        <v>13700.1314215498</v>
+        <v>13719.3864378952</v>
       </c>
       <c r="D73" s="66" t="n">
         <f aca="false">D70+D71+D72</f>
-        <v>704.969833230827</v>
+        <v>704.976246110605</v>
       </c>
       <c r="E73" s="66" t="n">
         <f aca="false">E70+E71+E72</f>
-        <v>10255.1553667269</v>
+        <v>10281.6836768429</v>
       </c>
       <c r="F73" s="66" t="n">
         <f aca="false">F70+F71+F72</f>
-        <v>7190.62128738565</v>
+        <v>7201.26907407517</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -23399,11 +24043,11 @@
       </c>
       <c r="B76" s="62" t="n">
         <f aca="false">MAX(0,B73+B74+B75)</f>
-        <v>2868.71835400855</v>
+        <v>2872.83796323922</v>
       </c>
       <c r="C76" s="62" t="n">
         <f aca="false">MAX(0,C73+C74+C75)</f>
-        <v>11854.2505488815</v>
+        <v>11873.5055652269</v>
       </c>
       <c r="D76" s="62" t="n">
         <f aca="false">MAX(0,D73+D74+D75)</f>
@@ -23411,11 +24055,11 @@
       </c>
       <c r="E76" s="63" t="n">
         <f aca="false">MAX(0,E73+E74+E75)</f>
-        <v>8409.27449405865</v>
+        <v>8435.80280417468</v>
       </c>
       <c r="F76" s="64" t="n">
         <f aca="false">B76*'Defense Supercycle'!$B$17+C76*'Defense Supercycle'!$B$18+D76*'Defense Supercycle'!$B$19+E76*'Defense Supercycle'!$B$20</f>
-        <v>5515.87707063303</v>
+        <v>5526.52389539059</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -23424,11 +24068,11 @@
       </c>
       <c r="B77" s="62" t="n">
         <f aca="false">-Assumptions!$B$9*B76</f>
-        <v>-573.743670801711</v>
+        <v>-574.567592647844</v>
       </c>
       <c r="C77" s="62" t="n">
         <f aca="false">-Assumptions!$B$9*C76</f>
-        <v>-2370.85010977631</v>
+        <v>-2374.70111304539</v>
       </c>
       <c r="D77" s="62" t="n">
         <f aca="false">-Assumptions!$B$9*D76</f>
@@ -23436,11 +24080,11 @@
       </c>
       <c r="E77" s="63" t="n">
         <f aca="false">-Assumptions!$B$9*E76</f>
-        <v>-1681.85489881173</v>
+        <v>-1687.16056083494</v>
       </c>
       <c r="F77" s="64" t="n">
         <f aca="false">B77*'Defense Supercycle'!$B$17+C77*'Defense Supercycle'!$B$18+D77*'Defense Supercycle'!$B$19+E77*'Defense Supercycle'!$B$20</f>
-        <v>-1103.17541412661</v>
+        <v>-1105.30477907812</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -23474,23 +24118,23 @@
       </c>
       <c r="B79" s="66" t="n">
         <f aca="false">B73+B77+B78</f>
-        <v>3969.85555587508</v>
+        <v>3973.15124325961</v>
       </c>
       <c r="C79" s="66" t="n">
         <f aca="false">C73+C77+C78</f>
-        <v>11158.2813117735</v>
+        <v>11173.6853248498</v>
       </c>
       <c r="D79" s="66" t="n">
         <f aca="false">D73+D77+D78</f>
-        <v>533.969833230827</v>
+        <v>533.976246110605</v>
       </c>
       <c r="E79" s="66" t="n">
         <f aca="false">E73+E77+E78</f>
-        <v>8402.30046791515</v>
+        <v>8423.52311600798</v>
       </c>
       <c r="F79" s="66" t="n">
         <f aca="false">F73+F77+F78</f>
-        <v>5916.44587325905</v>
+        <v>5924.96429499706</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -23499,23 +24143,23 @@
       </c>
       <c r="B80" s="67" t="n">
         <f aca="false">B79/'Holdco Summary'!$B$9</f>
-        <v>4.64310591330418</v>
+        <v>4.64696051843229</v>
       </c>
       <c r="C80" s="67" t="n">
         <f aca="false">C79/'Holdco Summary'!$B$9</f>
-        <v>13.0506214172789</v>
+        <v>13.0686378068419</v>
       </c>
       <c r="D80" s="67" t="n">
         <f aca="false">D79/'Holdco Summary'!$B$9</f>
-        <v>0.62452612073781</v>
+        <v>0.624533621181994</v>
       </c>
       <c r="E80" s="67" t="n">
         <f aca="false">E79/'Holdco Summary'!$B$9</f>
-        <v>9.82725200925749</v>
+        <v>9.85207381989238</v>
       </c>
       <c r="F80" s="67" t="n">
         <f aca="false">F79/'Holdco Summary'!$B$9</f>
-        <v>6.9198197348059</v>
+        <v>6.92978280116615</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -23524,23 +24168,23 @@
       </c>
       <c r="B81" s="68" t="n">
         <f aca="false">B79/'Holdco Summary'!$B$9</f>
-        <v>4.64310591330418</v>
+        <v>4.64696051843229</v>
       </c>
       <c r="C81" s="68" t="n">
         <f aca="false">C79/'Holdco Summary'!$B$9</f>
-        <v>13.0506214172789</v>
+        <v>13.0686378068419</v>
       </c>
       <c r="D81" s="68" t="n">
         <f aca="false">D79/'Holdco Summary'!$B$9</f>
-        <v>0.62452612073781</v>
+        <v>0.624533621181994</v>
       </c>
       <c r="E81" s="69" t="n">
         <f aca="false">E79/'Holdco Summary'!$B$9</f>
-        <v>9.82725200925749</v>
+        <v>9.85207381989238</v>
       </c>
       <c r="F81" s="70" t="n">
         <f aca="false">F79/'Holdco Summary'!$B$9</f>
-        <v>6.9198197348059</v>
+        <v>6.92978280116615</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -23549,23 +24193,23 @@
       </c>
       <c r="B82" s="51" t="n">
         <f aca="false">(B79/'Holdco Summary'!$B$9)^(1/10)-1</f>
-        <v>0.165952502895083</v>
+        <v>0.166049261583913</v>
       </c>
       <c r="C82" s="51" t="n">
         <f aca="false">(C79/'Holdco Summary'!$B$9)^(1/10)-1</f>
-        <v>0.292894592849268</v>
+        <v>0.293072966232131</v>
       </c>
       <c r="D82" s="51" t="n">
         <f aca="false">(D79/'Holdco Summary'!$B$9)^(1/10)-1</f>
-        <v>-0.045985312895805</v>
+        <v>-0.0459841671478525</v>
       </c>
       <c r="E82" s="51" t="n">
         <f aca="false">(E79/'Holdco Summary'!$B$9)^(1/10)-1</f>
-        <v>0.256733550220737</v>
+        <v>0.257050617522171</v>
       </c>
       <c r="F82" s="51" t="n">
         <f aca="false">(F79/'Holdco Summary'!$B$9)^(1/10)-1</f>
-        <v>0.213415331908954</v>
+        <v>0.213589924779007</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -23574,23 +24218,23 @@
       </c>
       <c r="B83" s="68" t="n">
         <f aca="false">B80/(1+'Holdco Summary'!$B$21)^10</f>
-        <v>1.96129811534096</v>
+        <v>1.96292634220339</v>
       </c>
       <c r="C83" s="68" t="n">
         <f aca="false">C80/(1+'Holdco Summary'!$B$21)^10</f>
-        <v>5.51272352336294</v>
+        <v>5.52033384101557</v>
       </c>
       <c r="D83" s="68" t="n">
         <f aca="false">D80/(1+'Holdco Summary'!$B$21)^10</f>
-        <v>0.263806582588293</v>
+        <v>0.263809750856973</v>
       </c>
       <c r="E83" s="69" t="n">
         <f aca="false">E80/(1+'Holdco Summary'!$B$21)^10</f>
-        <v>4.15113745079773</v>
+        <v>4.16162245185663</v>
       </c>
       <c r="F83" s="70" t="n">
         <f aca="false">F80/(1+'Holdco Summary'!$B$21)^10</f>
-        <v>2.92300663775207</v>
+        <v>2.92721514465246</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -23599,23 +24243,23 @@
       </c>
       <c r="B84" s="68" t="n">
         <f aca="false">B80/(1+'Holdco Summary'!$B$22)^10</f>
-        <v>1.36780490117492</v>
+        <v>1.36894042293229</v>
       </c>
       <c r="C84" s="68" t="n">
         <f aca="false">C80/(1+'Holdco Summary'!$B$22)^10</f>
-        <v>3.84456100533563</v>
+        <v>3.84986842377617</v>
       </c>
       <c r="D84" s="68" t="n">
         <f aca="false">D80/(1+'Holdco Summary'!$B$22)^10</f>
-        <v>0.183978118269769</v>
+        <v>0.183980327813231</v>
       </c>
       <c r="E84" s="69" t="n">
         <f aca="false">E80/(1+'Holdco Summary'!$B$22)^10</f>
-        <v>2.89499393602631</v>
+        <v>2.90230615221874</v>
       </c>
       <c r="F84" s="70" t="n">
         <f aca="false">F80/(1+'Holdco Summary'!$B$22)^10</f>
-        <v>2.03849826500703</v>
+        <v>2.04143326826837</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -23624,23 +24268,23 @@
       </c>
       <c r="B85" s="67" t="n">
         <f aca="false">B80/(1+'Holdco Summary'!$B$23)^10</f>
-        <v>1.14770477067279</v>
+        <v>1.1486575701086</v>
       </c>
       <c r="C85" s="67" t="n">
         <f aca="false">C80/(1+'Holdco Summary'!$B$23)^10</f>
-        <v>3.22591401973781</v>
+        <v>3.23036739569731</v>
       </c>
       <c r="D85" s="67" t="n">
         <f aca="false">D80/(1+'Holdco Summary'!$B$23)^10</f>
-        <v>0.154373305620004</v>
+        <v>0.154375159615096</v>
       </c>
       <c r="E85" s="67" t="n">
         <f aca="false">E80/(1+'Holdco Summary'!$B$23)^10</f>
-        <v>2.42914639989383</v>
+        <v>2.43528197186103</v>
       </c>
       <c r="F85" s="67" t="n">
         <f aca="false">F80/(1+'Holdco Summary'!$B$23)^10</f>
-        <v>1.71047360756428</v>
+        <v>1.71293632519461</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -23649,23 +24293,23 @@
       </c>
       <c r="B86" s="46" t="n">
         <f aca="false">(B80/(1+'Holdco Summary'!$B$23)^10)^(1/10)-1</f>
-        <v>0.0138717416478982</v>
+        <v>0.0139558796381851</v>
       </c>
       <c r="C86" s="46" t="n">
         <f aca="false">(C80/(1+'Holdco Summary'!$B$23)^10)^(1/10)-1</f>
-        <v>0.124256167695016</v>
+        <v>0.124411274984461</v>
       </c>
       <c r="D86" s="46" t="n">
         <f aca="false">(D80/(1+'Holdco Summary'!$B$23)^10)^(1/10)-1</f>
-        <v>-0.170422011213743</v>
+        <v>-0.170421014911176</v>
       </c>
       <c r="E86" s="71" t="n">
         <f aca="false">(E80/(1+'Holdco Summary'!$B$23)^10)^(1/10)-1</f>
-        <v>0.0928117828006405</v>
+        <v>0.0930874934975405</v>
       </c>
       <c r="F86" s="72" t="n">
         <f aca="false">(F80/(1+'Holdco Summary'!$B$23)^10)^(1/10)-1</f>
-        <v>0.0551437668773511</v>
+        <v>0.0552955867643536</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
